--- a/data/shuttle-data.xlsx
+++ b/data/shuttle-data.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Routes" sheetId="1" r:id="R6cd6358903744048"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stops" sheetId="2" r:id="Rc43d3ac20b454909"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RouteStops" sheetId="3" r:id="R1ae612aa35884b03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Routes" sheetId="1" r:id="R2c741b4b6bc14b99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stops" sheetId="2" r:id="R40bd125e84d94d89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RouteStops" sheetId="3" r:id="R0b23edd062034d2c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15,6 +15,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="0.000000"/>
+  </x:numFmts>
   <x:fonts count="2">
     <x:font>
       <x:sz val="11"/>
@@ -47,7 +50,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="26">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -152,6 +155,17 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -162,7 +176,7 @@
         <x:color rgb="FF7F7F7F"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE7E6E6"/>
         </x:patternFill>
       </x:fill>
@@ -172,7 +186,7 @@
         <x:color rgb="FF7F7F7F"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE7E6E6"/>
         </x:patternFill>
       </x:fill>
@@ -182,7 +196,7 @@
         <x:color rgb="FF7F7F7F"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE7E6E6"/>
         </x:patternFill>
       </x:fill>
@@ -192,7 +206,7 @@
         <x:color rgb="FF9C6500"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -202,7 +216,7 @@
         <x:color rgb="FF385723"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -1032,7 +1046,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R649d3fee917e4396"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2bdcfef0748548a7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1050,6 +1064,8 @@
     <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -1080,6 +1096,12 @@
       <x:c r="I1" s="8" t="str">
         <x:v>備註</x:v>
       </x:c>
+      <x:c r="J1" t="str">
+        <x:v>定位狀態</x:v>
+      </x:c>
+      <x:c r="K1" t="str">
+        <x:v>最後定位時間</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="22" t="b">
@@ -1100,9 +1122,13 @@
       <x:c r="F2" s="19" t="str">
         <x:v>新竹市中華路三段9號</x:v>
       </x:c>
-      <x:c r="G2" s="23"/>
-      <x:c r="H2" s="23"/>
+      <x:c r="G2" s="28"/>
+      <x:c r="H2" s="28"/>
       <x:c r="I2" s="19" t="str"/>
+      <x:c r="J2" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K2" t="str"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="22" t="b">
@@ -1123,9 +1149,13 @@
       <x:c r="F3" s="19" t="str">
         <x:v>新竹市民族路34號</x:v>
       </x:c>
-      <x:c r="G3" s="23"/>
-      <x:c r="H3" s="23"/>
+      <x:c r="G3" s="28"/>
+      <x:c r="H3" s="28"/>
       <x:c r="I3" s="19" t="str"/>
+      <x:c r="J3" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K3" t="str"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="22" t="b">
@@ -1146,9 +1176,13 @@
       <x:c r="F4" s="19" t="str">
         <x:v>新竹市南大路81號</x:v>
       </x:c>
-      <x:c r="G4" s="23"/>
-      <x:c r="H4" s="23"/>
+      <x:c r="G4" s="28"/>
+      <x:c r="H4" s="28"/>
       <x:c r="I4" s="19" t="str"/>
+      <x:c r="J4" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K4" t="str"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="22" t="b">
@@ -1169,9 +1203,13 @@
       <x:c r="F5" s="19" t="str">
         <x:v>新竹市光復路二段321號</x:v>
       </x:c>
-      <x:c r="G5" s="23"/>
-      <x:c r="H5" s="23"/>
+      <x:c r="G5" s="28"/>
+      <x:c r="H5" s="28"/>
       <x:c r="I5" s="19" t="str"/>
+      <x:c r="J5" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K5" t="str"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="22" t="b">
@@ -1192,9 +1230,13 @@
       <x:c r="F6" s="19" t="str">
         <x:v>新竹市光復路二段101號</x:v>
       </x:c>
-      <x:c r="G6" s="23"/>
-      <x:c r="H6" s="23"/>
+      <x:c r="G6" s="28"/>
+      <x:c r="H6" s="28"/>
       <x:c r="I6" s="19" t="str"/>
+      <x:c r="J6" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K6" t="str"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="22" t="b">
@@ -1215,9 +1257,13 @@
       <x:c r="F7" s="19" t="str">
         <x:v>新竹市光復路二段3號</x:v>
       </x:c>
-      <x:c r="G7" s="23"/>
-      <x:c r="H7" s="23"/>
+      <x:c r="G7" s="28"/>
+      <x:c r="H7" s="28"/>
       <x:c r="I7" s="19" t="str"/>
+      <x:c r="J7" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K7" t="str"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="22" t="b">
@@ -1238,9 +1284,13 @@
       <x:c r="F8" s="19" t="str">
         <x:v>桃園市龍潭區南興路一段468號</x:v>
       </x:c>
-      <x:c r="G8" s="23"/>
-      <x:c r="H8" s="23"/>
+      <x:c r="G8" s="28"/>
+      <x:c r="H8" s="28"/>
       <x:c r="I8" s="19" t="str"/>
+      <x:c r="J8" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K8" t="str"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="22" t="b">
@@ -1261,9 +1311,13 @@
       <x:c r="F9" s="19" t="str">
         <x:v>桃園市龍潭區大昌路二段100號</x:v>
       </x:c>
-      <x:c r="G9" s="23"/>
-      <x:c r="H9" s="23"/>
+      <x:c r="G9" s="28"/>
+      <x:c r="H9" s="28"/>
       <x:c r="I9" s="19" t="str"/>
+      <x:c r="J9" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K9" t="str"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="22" t="b">
@@ -1284,9 +1338,13 @@
       <x:c r="F10" s="19" t="str">
         <x:v>桃園市蘆竹區新南路一段328號</x:v>
       </x:c>
-      <x:c r="G10" s="23"/>
-      <x:c r="H10" s="23"/>
+      <x:c r="G10" s="28"/>
+      <x:c r="H10" s="28"/>
       <x:c r="I10" s="19" t="str"/>
+      <x:c r="J10" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K10" t="str"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="22" t="b">
@@ -1307,9 +1365,13 @@
       <x:c r="F11" s="19" t="str">
         <x:v>桃園市平鎮區中豐路南勢二段291號</x:v>
       </x:c>
-      <x:c r="G11" s="23"/>
-      <x:c r="H11" s="23"/>
+      <x:c r="G11" s="28"/>
+      <x:c r="H11" s="28"/>
       <x:c r="I11" s="19" t="str"/>
+      <x:c r="J11" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K11" t="str"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="22" t="b">
@@ -1330,9 +1392,13 @@
       <x:c r="F12" s="19" t="str">
         <x:v>桃園市平鎮區環南路三段88號</x:v>
       </x:c>
-      <x:c r="G12" s="23"/>
-      <x:c r="H12" s="23"/>
+      <x:c r="G12" s="28"/>
+      <x:c r="H12" s="28"/>
       <x:c r="I12" s="19" t="str"/>
+      <x:c r="J12" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K12" t="str"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="22" t="b">
@@ -1353,9 +1419,13 @@
       <x:c r="F13" s="19" t="str">
         <x:v>桃園市中壢區新興路86號</x:v>
       </x:c>
-      <x:c r="G13" s="23"/>
-      <x:c r="H13" s="23"/>
+      <x:c r="G13" s="28"/>
+      <x:c r="H13" s="28"/>
       <x:c r="I13" s="19" t="str"/>
+      <x:c r="J13" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K13" t="str"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="22" t="b">
@@ -1376,9 +1446,13 @@
       <x:c r="F14" s="19" t="str">
         <x:v>桃園市平鎮區延平路二段231號</x:v>
       </x:c>
-      <x:c r="G14" s="23"/>
-      <x:c r="H14" s="23"/>
+      <x:c r="G14" s="28"/>
+      <x:c r="H14" s="28"/>
       <x:c r="I14" s="19" t="str"/>
+      <x:c r="J14" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K14" t="str"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="22" t="b">
@@ -1399,9 +1473,13 @@
       <x:c r="F15" s="19" t="str">
         <x:v>桃園市平鎮區延平路二段87號</x:v>
       </x:c>
-      <x:c r="G15" s="23"/>
-      <x:c r="H15" s="23"/>
+      <x:c r="G15" s="28"/>
+      <x:c r="H15" s="28"/>
       <x:c r="I15" s="19" t="str"/>
+      <x:c r="J15" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K15" t="str"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="22" t="b">
@@ -1422,9 +1500,13 @@
       <x:c r="F16" s="19" t="str">
         <x:v>桃園市中壢區延平路551號</x:v>
       </x:c>
-      <x:c r="G16" s="23"/>
-      <x:c r="H16" s="23"/>
+      <x:c r="G16" s="28"/>
+      <x:c r="H16" s="28"/>
       <x:c r="I16" s="19" t="str"/>
+      <x:c r="J16" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K16" t="str"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="22" t="b">
@@ -1445,9 +1527,13 @@
       <x:c r="F17" s="19" t="str">
         <x:v>桃園市中壢區中園路162號</x:v>
       </x:c>
-      <x:c r="G17" s="23"/>
-      <x:c r="H17" s="23"/>
+      <x:c r="G17" s="28"/>
+      <x:c r="H17" s="28"/>
       <x:c r="I17" s="19" t="str"/>
+      <x:c r="J17" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K17" t="str"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="22" t="b">
@@ -1466,9 +1552,13 @@
       <x:c r="F18" s="19" t="str">
         <x:v>桃園市中壢區東園路38-2號</x:v>
       </x:c>
-      <x:c r="G18" s="23"/>
-      <x:c r="H18" s="23"/>
+      <x:c r="G18" s="28"/>
+      <x:c r="H18" s="28"/>
       <x:c r="I18" s="19" t="str"/>
+      <x:c r="J18" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K18" t="str"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="22" t="b">
@@ -1489,9 +1579,13 @@
       <x:c r="F19" s="19" t="str">
         <x:v>新竹縣竹北市自強一路 福興路口</x:v>
       </x:c>
-      <x:c r="G19" s="23"/>
-      <x:c r="H19" s="23"/>
+      <x:c r="G19" s="28"/>
+      <x:c r="H19" s="28"/>
       <x:c r="I19" s="19" t="str"/>
+      <x:c r="J19" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K19" t="str"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="22" t="b">
@@ -1512,9 +1606,13 @@
       <x:c r="F20" s="19" t="str">
         <x:v>桃園市桃園區中山路694號</x:v>
       </x:c>
-      <x:c r="G20" s="23"/>
-      <x:c r="H20" s="23"/>
+      <x:c r="G20" s="28"/>
+      <x:c r="H20" s="28"/>
       <x:c r="I20" s="19" t="str"/>
+      <x:c r="J20" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K20" t="str"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="22" t="b">
@@ -1535,9 +1633,13 @@
       <x:c r="F21" s="19" t="str">
         <x:v>桃園市桃園區中山路1076號</x:v>
       </x:c>
-      <x:c r="G21" s="23"/>
-      <x:c r="H21" s="23"/>
+      <x:c r="G21" s="28"/>
+      <x:c r="H21" s="28"/>
       <x:c r="I21" s="19" t="str"/>
+      <x:c r="J21" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K21" t="str"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="22" t="b">
@@ -1558,9 +1660,13 @@
       <x:c r="F22" s="19" t="str">
         <x:v>桃園市桃園區龍安街56號</x:v>
       </x:c>
-      <x:c r="G22" s="23"/>
-      <x:c r="H22" s="23"/>
+      <x:c r="G22" s="28"/>
+      <x:c r="H22" s="28"/>
       <x:c r="I22" s="19" t="str"/>
+      <x:c r="J22" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K22" t="str"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="22" t="b">
@@ -1581,9 +1687,13 @@
       <x:c r="F23" s="19" t="str">
         <x:v>桃園市桃園區復興路345號</x:v>
       </x:c>
-      <x:c r="G23" s="23"/>
-      <x:c r="H23" s="23"/>
+      <x:c r="G23" s="28"/>
+      <x:c r="H23" s="28"/>
       <x:c r="I23" s="19" t="str"/>
+      <x:c r="J23" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K23" t="str"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="22" t="b">
@@ -1604,9 +1714,13 @@
       <x:c r="F24" s="19" t="str">
         <x:v>桃園市桃園區民權路6號</x:v>
       </x:c>
-      <x:c r="G24" s="23"/>
-      <x:c r="H24" s="23"/>
+      <x:c r="G24" s="28"/>
+      <x:c r="H24" s="28"/>
       <x:c r="I24" s="19" t="str"/>
+      <x:c r="J24" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K24" t="str"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="22" t="b">
@@ -1627,9 +1741,13 @@
       <x:c r="F25" s="19" t="str">
         <x:v>新北市林口區文化二路一段356號</x:v>
       </x:c>
-      <x:c r="G25" s="23"/>
-      <x:c r="H25" s="23"/>
+      <x:c r="G25" s="28"/>
+      <x:c r="H25" s="28"/>
       <x:c r="I25" s="19" t="str"/>
+      <x:c r="J25" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K25" t="str"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="22" t="b">
@@ -1650,9 +1768,13 @@
       <x:c r="F26" s="19" t="str">
         <x:v>新北市林口區文化二路一段269號</x:v>
       </x:c>
-      <x:c r="G26" s="23"/>
-      <x:c r="H26" s="23"/>
+      <x:c r="G26" s="28"/>
+      <x:c r="H26" s="28"/>
       <x:c r="I26" s="19" t="str"/>
+      <x:c r="J26" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K26" t="str"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="22" t="b">
@@ -1673,9 +1795,13 @@
       <x:c r="F27" s="19" t="str">
         <x:v>桃園市龜山區復興一路230號</x:v>
       </x:c>
-      <x:c r="G27" s="23"/>
-      <x:c r="H27" s="23"/>
+      <x:c r="G27" s="28"/>
+      <x:c r="H27" s="28"/>
       <x:c r="I27" s="19" t="str"/>
+      <x:c r="J27" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K27" t="str"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="22" t="b">
@@ -1696,9 +1822,13 @@
       <x:c r="F28" s="19" t="str">
         <x:v>基隆市仁愛區港西街4號</x:v>
       </x:c>
-      <x:c r="G28" s="23"/>
-      <x:c r="H28" s="23"/>
+      <x:c r="G28" s="28"/>
+      <x:c r="H28" s="28"/>
       <x:c r="I28" s="19" t="str"/>
+      <x:c r="J28" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K28" t="str"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="22" t="b">
@@ -1719,9 +1849,13 @@
       <x:c r="F29" s="19" t="str">
         <x:v>基隆市安樂區安樂路一段2號</x:v>
       </x:c>
-      <x:c r="G29" s="23"/>
-      <x:c r="H29" s="23"/>
+      <x:c r="G29" s="28"/>
+      <x:c r="H29" s="28"/>
       <x:c r="I29" s="19" t="str"/>
+      <x:c r="J29" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K29" t="str"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="22" t="b">
@@ -1742,9 +1876,13 @@
       <x:c r="F30" s="19" t="str">
         <x:v>基隆市安樂區安樂路二段132號</x:v>
       </x:c>
-      <x:c r="G30" s="23"/>
-      <x:c r="H30" s="23"/>
+      <x:c r="G30" s="28"/>
+      <x:c r="H30" s="28"/>
       <x:c r="I30" s="19" t="str"/>
+      <x:c r="J30" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K30" t="str"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="22" t="b">
@@ -1765,9 +1903,13 @@
       <x:c r="F31" s="19" t="str">
         <x:v>基隆市八堵火車站</x:v>
       </x:c>
-      <x:c r="G31" s="23"/>
-      <x:c r="H31" s="23"/>
+      <x:c r="G31" s="28"/>
+      <x:c r="H31" s="28"/>
       <x:c r="I31" s="19" t="str"/>
+      <x:c r="J31" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K31" t="str"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="22" t="b">
@@ -1788,9 +1930,13 @@
       <x:c r="F32" s="19" t="str">
         <x:v>基隆市七堵區崇智街2之10號</x:v>
       </x:c>
-      <x:c r="G32" s="23"/>
-      <x:c r="H32" s="23"/>
+      <x:c r="G32" s="28"/>
+      <x:c r="H32" s="28"/>
       <x:c r="I32" s="19" t="str"/>
+      <x:c r="J32" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K32" t="str"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="22" t="b">
@@ -1811,9 +1957,13 @@
       <x:c r="F33" s="19" t="str">
         <x:v>基隆市七堵區百一街151號</x:v>
       </x:c>
-      <x:c r="G33" s="23"/>
-      <x:c r="H33" s="23"/>
+      <x:c r="G33" s="28"/>
+      <x:c r="H33" s="28"/>
       <x:c r="I33" s="19" t="str"/>
+      <x:c r="J33" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K33" t="str"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="22" t="b">
@@ -1834,9 +1984,13 @@
       <x:c r="F34" s="19" t="str">
         <x:v>新北市新莊區富國路102號</x:v>
       </x:c>
-      <x:c r="G34" s="23"/>
-      <x:c r="H34" s="23"/>
+      <x:c r="G34" s="28"/>
+      <x:c r="H34" s="28"/>
       <x:c r="I34" s="19" t="str"/>
+      <x:c r="J34" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K34" t="str"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="22" t="b">
@@ -1857,9 +2011,13 @@
       <x:c r="F35" s="19" t="str">
         <x:v>新北市新莊區後港一路132號</x:v>
       </x:c>
-      <x:c r="G35" s="23"/>
-      <x:c r="H35" s="23"/>
+      <x:c r="G35" s="28"/>
+      <x:c r="H35" s="28"/>
       <x:c r="I35" s="19" t="str"/>
+      <x:c r="J35" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K35" t="str"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="22" t="b">
@@ -1880,9 +2038,13 @@
       <x:c r="F36" s="19" t="str">
         <x:v>新北市新莊區中正路555號</x:v>
       </x:c>
-      <x:c r="G36" s="23"/>
-      <x:c r="H36" s="23"/>
+      <x:c r="G36" s="28"/>
+      <x:c r="H36" s="28"/>
       <x:c r="I36" s="19" t="str"/>
+      <x:c r="J36" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K36" t="str"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="22" t="b">
@@ -1903,9 +2065,13 @@
       <x:c r="F37" s="19" t="str">
         <x:v>新北市新莊區中平路133號</x:v>
       </x:c>
-      <x:c r="G37" s="23"/>
-      <x:c r="H37" s="23"/>
+      <x:c r="G37" s="28"/>
+      <x:c r="H37" s="28"/>
       <x:c r="I37" s="19" t="str"/>
+      <x:c r="J37" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K37" t="str"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="22" t="b">
@@ -1926,9 +2092,13 @@
       <x:c r="F38" s="19" t="str">
         <x:v>新北市新莊區思源路339號</x:v>
       </x:c>
-      <x:c r="G38" s="23"/>
-      <x:c r="H38" s="23"/>
+      <x:c r="G38" s="28"/>
+      <x:c r="H38" s="28"/>
       <x:c r="I38" s="19" t="str"/>
+      <x:c r="J38" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K38" t="str"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="22" t="b">
@@ -1949,9 +2119,13 @@
       <x:c r="F39" s="19" t="str">
         <x:v>新北市新莊區新泰路370號</x:v>
       </x:c>
-      <x:c r="G39" s="23"/>
-      <x:c r="H39" s="23"/>
+      <x:c r="G39" s="28"/>
+      <x:c r="H39" s="28"/>
       <x:c r="I39" s="19" t="str"/>
+      <x:c r="J39" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K39" t="str"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="22" t="b">
@@ -1972,9 +2146,13 @@
       <x:c r="F40" s="19" t="str">
         <x:v>新北市新莊區公園一路16號</x:v>
       </x:c>
-      <x:c r="G40" s="23"/>
-      <x:c r="H40" s="23"/>
+      <x:c r="G40" s="28"/>
+      <x:c r="H40" s="28"/>
       <x:c r="I40" s="19" t="str"/>
+      <x:c r="J40" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K40" t="str"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="22" t="b">
@@ -1995,9 +2173,13 @@
       <x:c r="F41" s="19" t="str">
         <x:v>新北市新莊區公園一路146號</x:v>
       </x:c>
-      <x:c r="G41" s="23"/>
-      <x:c r="H41" s="23"/>
+      <x:c r="G41" s="28"/>
+      <x:c r="H41" s="28"/>
       <x:c r="I41" s="19" t="str"/>
+      <x:c r="J41" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K41" t="str"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="22" t="b">
@@ -2018,9 +2200,13 @@
       <x:c r="F42" s="19" t="str">
         <x:v>台北市北投區北投路二段 大業路452巷口</x:v>
       </x:c>
-      <x:c r="G42" s="23"/>
-      <x:c r="H42" s="23"/>
+      <x:c r="G42" s="28"/>
+      <x:c r="H42" s="28"/>
       <x:c r="I42" s="19" t="str"/>
+      <x:c r="J42" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K42" t="str"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="22" t="b">
@@ -2041,9 +2227,13 @@
       <x:c r="F43" s="19" t="str">
         <x:v>台北市中山區北安路537之2號</x:v>
       </x:c>
-      <x:c r="G43" s="23"/>
-      <x:c r="H43" s="23"/>
+      <x:c r="G43" s="28"/>
+      <x:c r="H43" s="28"/>
       <x:c r="I43" s="19" t="str"/>
+      <x:c r="J43" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K43" t="str"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="22" t="b">
@@ -2064,9 +2254,13 @@
       <x:c r="F44" s="19" t="str">
         <x:v>台北市捷運劍潭站</x:v>
       </x:c>
-      <x:c r="G44" s="23"/>
-      <x:c r="H44" s="23"/>
+      <x:c r="G44" s="28"/>
+      <x:c r="H44" s="28"/>
       <x:c r="I44" s="19" t="str"/>
+      <x:c r="J44" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K44" t="str"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="22" t="b">
@@ -2087,9 +2281,13 @@
       <x:c r="F45" s="19" t="str">
         <x:v>台北市捷運芝山站1號出口</x:v>
       </x:c>
-      <x:c r="G45" s="23"/>
-      <x:c r="H45" s="23"/>
+      <x:c r="G45" s="28"/>
+      <x:c r="H45" s="28"/>
       <x:c r="I45" s="19" t="str"/>
+      <x:c r="J45" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K45" t="str"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="22" t="b">
@@ -2110,9 +2308,13 @@
       <x:c r="F46" s="19" t="str">
         <x:v>台北市士林區中正路362號</x:v>
       </x:c>
-      <x:c r="G46" s="23"/>
-      <x:c r="H46" s="23"/>
+      <x:c r="G46" s="28"/>
+      <x:c r="H46" s="28"/>
       <x:c r="I46" s="19" t="str"/>
+      <x:c r="J46" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K46" t="str"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="22" t="b">
@@ -2133,9 +2335,13 @@
       <x:c r="F47" s="19" t="str">
         <x:v>台北市北投區石牌路二段126號</x:v>
       </x:c>
-      <x:c r="G47" s="23"/>
-      <x:c r="H47" s="23"/>
+      <x:c r="G47" s="28"/>
+      <x:c r="H47" s="28"/>
       <x:c r="I47" s="19" t="str"/>
+      <x:c r="J47" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K47" t="str"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="22" t="b">
@@ -2154,9 +2360,13 @@
       <x:c r="F48" s="19" t="str">
         <x:v>台北市士林區天母東路8號</x:v>
       </x:c>
-      <x:c r="G48" s="23"/>
-      <x:c r="H48" s="23"/>
+      <x:c r="G48" s="28"/>
+      <x:c r="H48" s="28"/>
       <x:c r="I48" s="19" t="str"/>
+      <x:c r="J48" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K48" t="str"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="22" t="b">
@@ -2177,9 +2387,13 @@
       <x:c r="F49" s="19" t="str">
         <x:v>台北市士林區忠誠路二段76巷口</x:v>
       </x:c>
-      <x:c r="G49" s="23"/>
-      <x:c r="H49" s="23"/>
+      <x:c r="G49" s="28"/>
+      <x:c r="H49" s="28"/>
       <x:c r="I49" s="19" t="str"/>
+      <x:c r="J49" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K49" t="str"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="22" t="b">
@@ -2200,9 +2414,13 @@
       <x:c r="F50" s="19" t="str">
         <x:v>台北市士林區忠誠路一段138號</x:v>
       </x:c>
-      <x:c r="G50" s="23"/>
-      <x:c r="H50" s="23"/>
+      <x:c r="G50" s="28"/>
+      <x:c r="H50" s="28"/>
       <x:c r="I50" s="19" t="str"/>
+      <x:c r="J50" t="str">
+        <x:v>未定位</x:v>
+      </x:c>
+      <x:c r="K50" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="A2:I50">
@@ -2227,7 +2445,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc27cb5b192be4e71"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda9ac5d0c5af46ac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3231,7 +3449,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4fafb6ac75a4f51"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbfd55fefdd3c4629"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/data/shuttle-data.xlsx
+++ b/data/shuttle-data.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Routes" sheetId="1" r:id="R8d49ae601fb540b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stops" sheetId="2" r:id="R66b77bb9364e44f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RouteStops" sheetId="3" r:id="R50736148c9f84c90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Routes" sheetId="1" r:id="R5503625625f34ed2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stops" sheetId="2" r:id="R373f2f3abdde4fa9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RouteStops" sheetId="3" r:id="Rc1e2318123b34da5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -36,7 +36,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF176B52"/>
+        <x:fgColor rgb="FF1F4E78"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -47,23 +47,9 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="22">
+  <x:cellXfs count="20">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <x:extLst>
-        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
-        </x:ext>
-      </x:extLst>
-    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <x:extLst>
-        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
-        </x:ext>
-      </x:extLst>
-    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -80,82 +66,84 @@
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-      <x:extLst>
-        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
-        </x:ext>
-      </x:extLst>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-      <x:extLst>
-        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
-        </x:ext>
-      </x:extLst>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-      <x:extLst>
-        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
-        </x:ext>
-      </x:extLst>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
-      <x:extLst>
-        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
-        </x:ext>
-      </x:extLst>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
+  <x:dxfs count="4">
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF7F7F7F"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE7E6E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF7F7F7F"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE7E6E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF7F7F7F"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE7E6E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+  </x:dxfs>
 </x:styleSheet>
 </file>
 
-<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
-<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
-  <xfpb:bag type="Checkbox"/>
-  <xfpb:bag type="XFControls">
-    <xfpb:bagId k="CellControl">0</xfpb:bagId>
-  </xfpb:bag>
-  <xfpb:bag type="XFComplement">
-    <xfpb:bagId k="XFControls">1</xfpb:bagId>
-  </xfpb:bag>
-  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
-    <xfpb:a k="MappedFeaturePropertyBags">
-      <xfpb:bagId>2</xfpb:bagId>
-    </xfpb:a>
-  </xfpb:bag>
-</xfpb:FeaturePropertyBags>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RoutesTable" displayName="RoutesTable" ref="A1:I21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RoutesTable" displayName="RoutesTable" ref="A1:I61" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="啟用"/>
     <x:tableColumn id="2" name="RouteID"/>
@@ -172,7 +160,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="StopsTable" displayName="StopsTable" ref="A1:G50" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="StopsTable" displayName="StopsTable" ref="A1:G145" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="啟用"/>
     <x:tableColumn id="2" name="StopID"/>
@@ -187,7 +175,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RouteStopsTable" displayName="RouteStopsTable" ref="A1:F54" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RouteStopsTable" displayName="RouteStopsTable" ref="A1:F164" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="6">
     <x:tableColumn id="1" name="啟用"/>
     <x:tableColumn id="2" name="RouteID"/>
@@ -395,560 +383,1580 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="9" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="11" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="10" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="10" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="10" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="48" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="28" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="38" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="16" t="str">
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="10" t="str">
         <x:v>啟用</x:v>
       </x:c>
-      <x:c r="B1" s="16" t="str">
+      <x:c r="B1" s="10" t="str">
         <x:v>RouteID</x:v>
       </x:c>
-      <x:c r="C1" s="16" t="str">
+      <x:c r="C1" s="10" t="str">
         <x:v>類型</x:v>
       </x:c>
-      <x:c r="D1" s="16" t="str">
+      <x:c r="D1" s="10" t="str">
         <x:v>路線編號</x:v>
       </x:c>
-      <x:c r="E1" s="16" t="str">
+      <x:c r="E1" s="10" t="str">
         <x:v>路線名稱</x:v>
       </x:c>
-      <x:c r="F1" s="16" t="str">
+      <x:c r="F1" s="10" t="str">
         <x:v>車型</x:v>
       </x:c>
-      <x:c r="G1" s="16" t="str">
+      <x:c r="G1" s="10" t="str">
         <x:v>生效日</x:v>
       </x:c>
-      <x:c r="H1" s="16" t="str">
+      <x:c r="H1" s="10" t="str">
         <x:v>行駛路線</x:v>
       </x:c>
-      <x:c r="I1" s="16" t="str">
+      <x:c r="I1" s="10" t="str">
         <x:v>備註</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="18" t="str">
-        <x:v>TRUE</x:v>
-      </x:c>
-      <x:c r="B2" s="18" t="str">
+    <x:row r="2" ht="24" customHeight="1">
+      <x:c r="A2" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B2" s="16" t="str">
         <x:v>M001</x:v>
       </x:c>
-      <x:c r="C2" s="18" t="str">
+      <x:c r="C2" s="16" t="str">
         <x:v>上班</x:v>
       </x:c>
-      <x:c r="D2" s="18" t="n">
+      <x:c r="D2" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E2" s="18" t="str">
+      <x:c r="E2" s="14" t="str">
         <x:v>新竹線</x:v>
       </x:c>
-      <x:c r="F2" s="18" t="str"/>
-      <x:c r="G2" s="18" t="str">
+      <x:c r="F2" s="16"/>
+      <x:c r="G2" s="16" t="str">
         <x:v>2026-06-23</x:v>
       </x:c>
-      <x:c r="H2" s="18" t="str">
+      <x:c r="H2" s="11" t="str">
         <x:v>中華路 → 民族路 → 東大路 → 光復路 → 中山高(竹北交流道) → 北二高 → 汐止 → 內湖辦公區 (汐止大門口轉乘【中壢線】或【中壢/南崁線】)</x:v>
       </x:c>
-      <x:c r="I2" s="18" t="str"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="18" t="str">
-        <x:v>TRUE</x:v>
-      </x:c>
-      <x:c r="B3" s="18" t="str">
+      <x:c r="I2" s="11"/>
+    </x:row>
+    <x:row r="3" ht="24" customHeight="1">
+      <x:c r="A3" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B3" s="16" t="str">
         <x:v>M002</x:v>
       </x:c>
-      <x:c r="C3" s="18" t="str">
+      <x:c r="C3" s="16" t="str">
         <x:v>上班</x:v>
       </x:c>
-      <x:c r="D3" s="18" t="n">
+      <x:c r="D3" s="16" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E3" s="18" t="str">
+      <x:c r="E3" s="14" t="str">
         <x:v>龍潭/大溪線</x:v>
       </x:c>
-      <x:c r="F3" s="18" t="str"/>
-      <x:c r="G3" s="18" t="str">
+      <x:c r="F3" s="16"/>
+      <x:c r="G3" s="16" t="str">
         <x:v>2026-06-23</x:v>
       </x:c>
-      <x:c r="H3" s="18" t="str">
+      <x:c r="H3" s="11" t="str">
         <x:v>北二高 → 汐止 → 內湖辦公區 (汐止大門口轉乘【中壢線】或【中壢/南崁線】)</x:v>
       </x:c>
-      <x:c r="I3" s="18" t="str"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="18" t="str">
-        <x:v>TRUE</x:v>
-      </x:c>
-      <x:c r="B4" s="18" t="str">
+      <x:c r="I3" s="11"/>
+    </x:row>
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B4" s="16" t="str">
         <x:v>M003</x:v>
       </x:c>
-      <x:c r="C4" s="18" t="str">
+      <x:c r="C4" s="16" t="str">
         <x:v>上班</x:v>
       </x:c>
-      <x:c r="D4" s="18" t="n">
+      <x:c r="D4" s="16" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E4" s="18" t="str">
+      <x:c r="E4" s="14" t="str">
         <x:v>南崁線</x:v>
       </x:c>
-      <x:c r="F4" s="18" t="str"/>
-      <x:c r="G4" s="18" t="str">
+      <x:c r="F4" s="16"/>
+      <x:c r="G4" s="16" t="str">
         <x:v>2026-06-23</x:v>
       </x:c>
-      <x:c r="H4" s="18" t="str">
+      <x:c r="H4" s="11" t="str">
         <x:v>新興路 → 健行路 → 新中北路 → 龍岡路 → 中正路 → 民族路 → 新屋交流道 → 中山高 → 台一省道 → 中山高/(桃園交流道) → 南崁 → 中山高 → 汐止 → 內湖辦公區 (汐止大門口轉乘此線)</x:v>
       </x:c>
-      <x:c r="I4" s="18" t="str"/>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="18" t="str">
-        <x:v>TRUE</x:v>
-      </x:c>
-      <x:c r="B5" s="18" t="str">
+      <x:c r="I4" s="11"/>
+    </x:row>
+    <x:row r="5" ht="24" customHeight="1">
+      <x:c r="A5" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B5" s="16" t="str">
         <x:v>M004</x:v>
       </x:c>
-      <x:c r="C5" s="18" t="str">
+      <x:c r="C5" s="16" t="str">
         <x:v>上班</x:v>
       </x:c>
-      <x:c r="D5" s="18" t="n">
+      <x:c r="D5" s="16" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E5" s="18" t="str">
+      <x:c r="E5" s="14" t="str">
         <x:v>中壢線</x:v>
       </x:c>
-      <x:c r="F5" s="18" t="str"/>
-      <x:c r="G5" s="18" t="str">
+      <x:c r="F5" s="16"/>
+      <x:c r="G5" s="16" t="str">
         <x:v>2026-06-23</x:v>
       </x:c>
-      <x:c r="H5" s="18" t="str">
+      <x:c r="H5" s="11" t="str">
         <x:v>中豐路 → 環南路 → 延平路 → 龍岡路 → 新中北路 → 新興路 → 健行路 → 新中北路 → 龍岡路 → 中正路 → 民族路 → 新屋交流道 → 中山高 → 汐止 → 內湖辦公區 (汐止大門口轉乘此線)</x:v>
       </x:c>
-      <x:c r="I5" s="18" t="str"/>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="18" t="str">
-        <x:v>TRUE</x:v>
-      </x:c>
-      <x:c r="B6" s="18" t="str">
+      <x:c r="I5" s="11"/>
+    </x:row>
+    <x:row r="6" ht="24" customHeight="1">
+      <x:c r="A6" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B6" s="16" t="str">
         <x:v>M005</x:v>
       </x:c>
-      <x:c r="C6" s="18" t="str">
+      <x:c r="C6" s="16" t="str">
         <x:v>上班</x:v>
       </x:c>
-      <x:c r="D6" s="18" t="n">
+      <x:c r="D6" s="16" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E6" s="18" t="str">
+      <x:c r="E6" s="14" t="str">
         <x:v>中壢/東園線</x:v>
       </x:c>
-      <x:c r="F6" s="18" t="str"/>
-      <x:c r="G6" s="18" t="str">
+      <x:c r="F6" s="16"/>
+      <x:c r="G6" s="16" t="str">
         <x:v>2026-06-23</x:v>
       </x:c>
-      <x:c r="H6" s="18" t="str">
+      <x:c r="H6" s="11" t="str">
         <x:v>延平路 → 中園路 → 東園路 → 中山高(中壢交流道) → 南崁 → 中山高(南崁交流道) → 汐止 → 內湖辦公區 (汐止大門口轉乘【中壢線】或【中壢/南崁線】)</x:v>
       </x:c>
-      <x:c r="I6" s="18" t="str"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="18" t="str">
-        <x:v>TRUE</x:v>
-      </x:c>
-      <x:c r="B7" s="18" t="str">
+      <x:c r="I6" s="11"/>
+    </x:row>
+    <x:row r="7" ht="24" customHeight="1">
+      <x:c r="A7" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B7" s="16" t="str">
         <x:v>M006</x:v>
       </x:c>
-      <x:c r="C7" s="18" t="str">
+      <x:c r="C7" s="16" t="str">
         <x:v>上班</x:v>
       </x:c>
-      <x:c r="D7" s="18" t="n">
+      <x:c r="D7" s="16" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="E7" s="18" t="str">
+      <x:c r="E7" s="14" t="str">
         <x:v>竹北/中壢線</x:v>
       </x:c>
-      <x:c r="F7" s="18" t="str"/>
-      <x:c r="G7" s="18" t="str">
+      <x:c r="F7" s="16"/>
+      <x:c r="G7" s="16" t="str">
         <x:v>2026-06-23</x:v>
       </x:c>
-      <x:c r="H7" s="18" t="str">
+      <x:c r="H7" s="11" t="str">
         <x:v>竹北 → 中山高 → 內壢 → 省道 → 東園路 → 中壢交流道 → 中山高 → 汐止 → 內湖辦公區 (汐止大門口轉乘【中壢線】或【中壢/南崁線】)</x:v>
       </x:c>
-      <x:c r="I7" s="18" t="str"/>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="18" t="str">
-        <x:v>TRUE</x:v>
-      </x:c>
-      <x:c r="B8" s="18" t="str">
+      <x:c r="I7" s="11"/>
+    </x:row>
+    <x:row r="8" ht="24" customHeight="1">
+      <x:c r="A8" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B8" s="16" t="str">
         <x:v>M007</x:v>
       </x:c>
-      <x:c r="C8" s="18" t="str">
+      <x:c r="C8" s="16" t="str">
         <x:v>上班</x:v>
       </x:c>
-      <x:c r="D8" s="18" t="n">
+      <x:c r="D8" s="16" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E8" s="18" t="str">
+      <x:c r="E8" s="14" t="str">
         <x:v>桃園A線</x:v>
       </x:c>
-      <x:c r="F8" s="18" t="str"/>
-      <x:c r="G8" s="18" t="str">
+      <x:c r="F8" s="16"/>
+      <x:c r="G8" s="16" t="str">
         <x:v>2026-06-23</x:v>
       </x:c>
-      <x:c r="H8" s="18" t="str">
+      <x:c r="H8" s="11" t="str">
         <x:v>台一省道 → 龍安街 → 大興路 → 國道2號 → 國道3號 → 北二高 → 汐止 → 內湖辦公區 (汐止大門口轉乘【中壢線】或【中壢/南崁線】)</x:v>
       </x:c>
-      <x:c r="I8" s="18" t="str"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="18" t="str">
-        <x:v>TRUE</x:v>
-      </x:c>
-      <x:c r="B9" s="18" t="str">
+      <x:c r="I8" s="11"/>
+    </x:row>
+    <x:row r="9" ht="24" customHeight="1">
+      <x:c r="A9" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B9" s="16" t="str">
         <x:v>M008</x:v>
       </x:c>
-      <x:c r="C9" s="18" t="str">
+      <x:c r="C9" s="16" t="str">
         <x:v>上班</x:v>
       </x:c>
-      <x:c r="D9" s="18" t="n">
+      <x:c r="D9" s="16" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="E9" s="18" t="str">
+      <x:c r="E9" s="14" t="str">
         <x:v>桃園B線</x:v>
       </x:c>
-      <x:c r="F9" s="18" t="str"/>
-      <x:c r="G9" s="18" t="str">
+      <x:c r="F9" s="16"/>
+      <x:c r="G9" s="16" t="str">
         <x:v>2026-06-23</x:v>
       </x:c>
-      <x:c r="H9" s="18" t="str">
+      <x:c r="H9" s="11" t="str">
         <x:v>復興路 → 忠義路 → 復興一路 → 文化一路 → 林口交流道 → 中山高 → 汐止 → 內湖辦公區 (汐止大門口轉乘【中壢線】或【中壢/南崁線】)</x:v>
       </x:c>
-      <x:c r="I9" s="18" t="str"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="18" t="str">
-        <x:v>TRUE</x:v>
-      </x:c>
-      <x:c r="B10" s="18" t="str">
+      <x:c r="I9" s="11"/>
+    </x:row>
+    <x:row r="10" ht="24" customHeight="1">
+      <x:c r="A10" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B10" s="16" t="str">
         <x:v>M009</x:v>
       </x:c>
-      <x:c r="C10" s="18" t="str">
+      <x:c r="C10" s="16" t="str">
         <x:v>上班</x:v>
       </x:c>
-      <x:c r="D10" s="18" t="n">
+      <x:c r="D10" s="16" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E10" s="18" t="str">
+      <x:c r="E10" s="14" t="str">
         <x:v>林口A線</x:v>
       </x:c>
-      <x:c r="F10" s="18" t="str"/>
-      <x:c r="G10" s="18" t="str">
+      <x:c r="F10" s="16"/>
+      <x:c r="G10" s="16" t="str">
         <x:v>2026-06-23</x:v>
       </x:c>
-      <x:c r="H10" s="18" t="str">
+      <x:c r="H10" s="11" t="str">
         <x:v>林口交流道 → 中山高 → 汐止 → 內湖辦公區 (汐止大門口轉乘【中壢線】或【中壢/南崁線】)</x:v>
       </x:c>
-      <x:c r="I10" s="18" t="str"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="18" t="str">
-        <x:v>TRUE</x:v>
-      </x:c>
-      <x:c r="B11" s="18" t="str">
+      <x:c r="I10" s="11"/>
+    </x:row>
+    <x:row r="11" ht="24" customHeight="1">
+      <x:c r="A11" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B11" s="16" t="str">
         <x:v>M010</x:v>
       </x:c>
-      <x:c r="C11" s="18" t="str">
+      <x:c r="C11" s="16" t="str">
         <x:v>上班</x:v>
       </x:c>
-      <x:c r="D11" s="18" t="n">
+      <x:c r="D11" s="16" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="E11" s="18" t="str">
+      <x:c r="E11" s="14" t="str">
         <x:v>林口B線</x:v>
       </x:c>
-      <x:c r="F11" s="18" t="str"/>
-      <x:c r="G11" s="18" t="str">
+      <x:c r="F11" s="16"/>
+      <x:c r="G11" s="16" t="str">
         <x:v>2026-06-23</x:v>
       </x:c>
-      <x:c r="H11" s="18" t="str">
+      <x:c r="H11" s="11" t="str">
         <x:v>文化二路 → 龜山一路 → 林口交流道 → 中山高 → 汐止 → 內湖辦公區 (汐止大門口轉乘【中壢線】或【中壢/南崁線】)</x:v>
       </x:c>
-      <x:c r="I11" s="18" t="str"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="18" t="str">
-        <x:v>TRUE</x:v>
-      </x:c>
-      <x:c r="B12" s="18" t="str">
+      <x:c r="I11" s="11"/>
+    </x:row>
+    <x:row r="12" ht="24" customHeight="1">
+      <x:c r="A12" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B12" s="16" t="str">
         <x:v>M011</x:v>
       </x:c>
-      <x:c r="C12" s="18" t="str">
+      <x:c r="C12" s="16" t="str">
         <x:v>上班</x:v>
       </x:c>
-      <x:c r="D12" s="18" t="n">
+      <x:c r="D12" s="16" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="E12" s="18" t="str">
+      <x:c r="E12" s="14" t="str">
         <x:v>基隆A線</x:v>
       </x:c>
-      <x:c r="F12" s="18" t="str"/>
-      <x:c r="G12" s="18" t="str">
+      <x:c r="F12" s="16"/>
+      <x:c r="G12" s="16" t="str">
         <x:v>2026-06-23</x:v>
       </x:c>
-      <x:c r="H12" s="18" t="str">
+      <x:c r="H12" s="11" t="str">
         <x:v>孝二路 → 八堵路 → 明德路 → 新台五路 → 中山高(汐止交流道) → 北二高 → 汐止</x:v>
       </x:c>
-      <x:c r="I12" s="18" t="str"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="18" t="str">
-        <x:v>TRUE</x:v>
-      </x:c>
-      <x:c r="B13" s="18" t="str">
+      <x:c r="I12" s="11"/>
+    </x:row>
+    <x:row r="13" ht="24" customHeight="1">
+      <x:c r="A13" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B13" s="16" t="str">
         <x:v>M012</x:v>
       </x:c>
-      <x:c r="C13" s="18" t="str">
+      <x:c r="C13" s="16" t="str">
         <x:v>上班</x:v>
       </x:c>
-      <x:c r="D13" s="18" t="n">
+      <x:c r="D13" s="16" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="E13" s="18" t="str">
+      <x:c r="E13" s="14" t="str">
         <x:v>基隆B線</x:v>
       </x:c>
-      <x:c r="F13" s="18" t="str"/>
-      <x:c r="G13" s="18" t="str">
+      <x:c r="F13" s="16"/>
+      <x:c r="G13" s="16" t="str">
         <x:v>2026-06-23</x:v>
       </x:c>
-      <x:c r="H13" s="18" t="str">
+      <x:c r="H13" s="11" t="str">
         <x:v>八堵路 → 省道 → 新台五路 → 汐止</x:v>
       </x:c>
-      <x:c r="I13" s="18" t="str"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="18" t="str">
-        <x:v>TRUE</x:v>
-      </x:c>
-      <x:c r="B14" s="18" t="str">
+      <x:c r="I13" s="11"/>
+    </x:row>
+    <x:row r="14" ht="24" customHeight="1">
+      <x:c r="A14" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B14" s="16" t="str">
         <x:v>M013</x:v>
       </x:c>
-      <x:c r="C14" s="18" t="str">
+      <x:c r="C14" s="16" t="str">
         <x:v>上班</x:v>
       </x:c>
-      <x:c r="D14" s="18" t="n">
+      <x:c r="D14" s="16" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="E14" s="18" t="str">
+      <x:c r="E14" s="14" t="str">
         <x:v>基隆C線(中巴)</x:v>
       </x:c>
-      <x:c r="F14" s="18" t="str">
+      <x:c r="F14" s="16" t="str">
         <x:v>中巴</x:v>
       </x:c>
-      <x:c r="G14" s="18" t="str">
+      <x:c r="G14" s="16" t="str">
         <x:v>2026-06-23</x:v>
       </x:c>
-      <x:c r="H14" s="18" t="str">
+      <x:c r="H14" s="11" t="str">
         <x:v>孝二路 → 八堵路 → 明德路 → 新台五路 → 中山高(汐止交流道) → 北二高 → 汐止</x:v>
       </x:c>
-      <x:c r="I14" s="18" t="str"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="18" t="str">
-        <x:v>TRUE</x:v>
-      </x:c>
-      <x:c r="B15" s="18" t="str">
+      <x:c r="I14" s="11"/>
+    </x:row>
+    <x:row r="15" ht="24" customHeight="1">
+      <x:c r="A15" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B15" s="16" t="str">
         <x:v>M014</x:v>
       </x:c>
-      <x:c r="C15" s="18" t="str">
+      <x:c r="C15" s="16" t="str">
         <x:v>上班</x:v>
       </x:c>
-      <x:c r="D15" s="18" t="n">
+      <x:c r="D15" s="16" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="E15" s="18" t="str">
+      <x:c r="E15" s="14" t="str">
         <x:v>新莊A線</x:v>
       </x:c>
-      <x:c r="F15" s="18" t="str"/>
-      <x:c r="G15" s="18" t="str">
+      <x:c r="F15" s="16"/>
+      <x:c r="G15" s="16" t="str">
         <x:v>2026-06-23</x:v>
       </x:c>
-      <x:c r="H15" s="18" t="str">
+      <x:c r="H15" s="11" t="str">
         <x:v>中正路 → 公園路 → 新泰路 → 中山路(二省道) → 中山高(五股交流道) → 汐止</x:v>
       </x:c>
-      <x:c r="I15" s="18" t="str"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="18" t="str">
-        <x:v>TRUE</x:v>
-      </x:c>
-      <x:c r="B16" s="18" t="str">
+      <x:c r="I15" s="11"/>
+    </x:row>
+    <x:row r="16" ht="24" customHeight="1">
+      <x:c r="A16" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B16" s="16" t="str">
         <x:v>M015</x:v>
       </x:c>
-      <x:c r="C16" s="18" t="str">
+      <x:c r="C16" s="16" t="str">
         <x:v>上班</x:v>
       </x:c>
-      <x:c r="D16" s="18" t="n">
+      <x:c r="D16" s="16" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E16" s="18" t="str">
+      <x:c r="E16" s="14" t="str">
         <x:v>新莊B線</x:v>
       </x:c>
-      <x:c r="F16" s="18" t="str"/>
-      <x:c r="G16" s="18" t="str">
+      <x:c r="F16" s="16"/>
+      <x:c r="G16" s="16" t="str">
         <x:v>2026-06-23</x:v>
       </x:c>
-      <x:c r="H16" s="18" t="str">
+      <x:c r="H16" s="11" t="str">
         <x:v>新泰路 → 中山高(五股交流道) → 汐止</x:v>
       </x:c>
-      <x:c r="I16" s="18" t="str"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="18" t="str">
-        <x:v>TRUE</x:v>
-      </x:c>
-      <x:c r="B17" s="18" t="str">
+      <x:c r="I16" s="11"/>
+    </x:row>
+    <x:row r="17" ht="24" customHeight="1">
+      <x:c r="A17" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B17" s="16" t="str">
         <x:v>M016</x:v>
       </x:c>
-      <x:c r="C17" s="18" t="str">
+      <x:c r="C17" s="16" t="str">
         <x:v>上班</x:v>
       </x:c>
-      <x:c r="D17" s="18" t="n">
+      <x:c r="D17" s="16" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E17" s="18" t="str">
+      <x:c r="E17" s="14" t="str">
         <x:v>新莊C線</x:v>
       </x:c>
-      <x:c r="F17" s="18" t="str"/>
-      <x:c r="G17" s="18" t="str">
+      <x:c r="F17" s="16"/>
+      <x:c r="G17" s="16" t="str">
         <x:v>2026-06-23</x:v>
       </x:c>
-      <x:c r="H17" s="18" t="str">
+      <x:c r="H17" s="11" t="str">
         <x:v>公園路 → 新泰路 → 中山高(五股交流道) → 汐止</x:v>
       </x:c>
-      <x:c r="I17" s="18" t="str"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="18" t="str">
-        <x:v>TRUE</x:v>
-      </x:c>
-      <x:c r="B18" s="18" t="str">
+      <x:c r="I17" s="11"/>
+    </x:row>
+    <x:row r="18" ht="24" customHeight="1">
+      <x:c r="A18" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B18" s="16" t="str">
         <x:v>M017</x:v>
       </x:c>
-      <x:c r="C18" s="18" t="str">
+      <x:c r="C18" s="16" t="str">
         <x:v>上班</x:v>
       </x:c>
-      <x:c r="D18" s="18" t="n">
+      <x:c r="D18" s="16" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E18" s="18" t="str">
+      <x:c r="E18" s="14" t="str">
         <x:v>新莊D線</x:v>
       </x:c>
-      <x:c r="F18" s="18" t="str"/>
-      <x:c r="G18" s="18" t="str">
+      <x:c r="F18" s="16"/>
+      <x:c r="G18" s="16" t="str">
         <x:v>2026-06-23</x:v>
       </x:c>
-      <x:c r="H18" s="18" t="str">
+      <x:c r="H18" s="11" t="str">
         <x:v>中正路 → 新泰路 → 中山高 → 五股交流道 → 汐止</x:v>
       </x:c>
-      <x:c r="I18" s="18" t="str"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="18" t="str">
-        <x:v>TRUE</x:v>
-      </x:c>
-      <x:c r="B19" s="18" t="str">
+      <x:c r="I18" s="11"/>
+    </x:row>
+    <x:row r="19" ht="24" customHeight="1">
+      <x:c r="A19" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B19" s="16" t="str">
         <x:v>M018</x:v>
       </x:c>
-      <x:c r="C19" s="18" t="str">
+      <x:c r="C19" s="16" t="str">
         <x:v>上班</x:v>
       </x:c>
-      <x:c r="D19" s="18" t="n">
+      <x:c r="D19" s="16" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="E19" s="18" t="str">
+      <x:c r="E19" s="14" t="str">
         <x:v>北投線</x:v>
       </x:c>
-      <x:c r="F19" s="18" t="str"/>
-      <x:c r="G19" s="18" t="str">
+      <x:c r="F19" s="16"/>
+      <x:c r="G19" s="16" t="str">
         <x:v>2026-06-23</x:v>
       </x:c>
-      <x:c r="H19" s="18" t="str">
+      <x:c r="H19" s="11" t="str">
         <x:v>中央南路 → 西安街 → 富國路 → 文昌路 → 中正路 → 重慶北路 → 中山高(重慶交流道)</x:v>
       </x:c>
-      <x:c r="I19" s="18" t="str"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="18" t="str">
-        <x:v>TRUE</x:v>
-      </x:c>
-      <x:c r="B20" s="18" t="str">
+      <x:c r="I19" s="11"/>
+    </x:row>
+    <x:row r="20" ht="24" customHeight="1">
+      <x:c r="A20" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B20" s="16" t="str">
         <x:v>M019</x:v>
       </x:c>
-      <x:c r="C20" s="18" t="str">
+      <x:c r="C20" s="16" t="str">
         <x:v>上班</x:v>
       </x:c>
-      <x:c r="D20" s="18" t="n">
+      <x:c r="D20" s="16" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="E20" s="18" t="str">
+      <x:c r="E20" s="14" t="str">
         <x:v>劍潭/士林線</x:v>
       </x:c>
-      <x:c r="F20" s="18" t="str"/>
-      <x:c r="G20" s="18" t="str">
+      <x:c r="F20" s="16"/>
+      <x:c r="G20" s="16" t="str">
         <x:v>2026-06-23</x:v>
       </x:c>
-      <x:c r="H20" s="18" t="str">
+      <x:c r="H20" s="11" t="str">
         <x:v>北安路 → 中山北路 → 劍潭路 → (劍潭捷運站高架橋下)右轉基河路往文林路 → 文林路 → 中正路 → 重慶北路 → 中山高(重慶交流道)</x:v>
       </x:c>
-      <x:c r="I20" s="18" t="str"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="18" t="str">
-        <x:v>TRUE</x:v>
-      </x:c>
-      <x:c r="B21" s="18" t="str">
+      <x:c r="I20" s="11"/>
+    </x:row>
+    <x:row r="21" ht="24" customHeight="1">
+      <x:c r="A21" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B21" s="16" t="str">
         <x:v>M020</x:v>
       </x:c>
-      <x:c r="C21" s="18" t="str">
+      <x:c r="C21" s="16" t="str">
         <x:v>上班</x:v>
       </x:c>
-      <x:c r="D21" s="18" t="n">
+      <x:c r="D21" s="16" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="E21" s="18" t="str">
+      <x:c r="E21" s="14" t="str">
         <x:v>天母線</x:v>
       </x:c>
-      <x:c r="F21" s="18" t="str"/>
-      <x:c r="G21" s="18" t="str">
+      <x:c r="F21" s="16"/>
+      <x:c r="G21" s="16" t="str">
         <x:v>2026-06-23</x:v>
       </x:c>
-      <x:c r="H21" s="18" t="str">
+      <x:c r="H21" s="11" t="str">
         <x:v>石牌路 → 天母西路 → 天母東路 → 忠誠路 → 文昌路 → 中正路 → 重慶北路 → 中山高(重慶交流道)</x:v>
       </x:c>
-      <x:c r="I21" s="18" t="str"/>
+      <x:c r="I21" s="11"/>
+    </x:row>
+    <x:row r="22" ht="24" customHeight="1">
+      <x:c r="A22" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B22" s="16" t="str">
+        <x:v>M021</x:v>
+      </x:c>
+      <x:c r="C22" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D22" s="16" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E22" s="14" t="str">
+        <x:v>北投/重慶北線</x:v>
+      </x:c>
+      <x:c r="F22" s="16"/>
+      <x:c r="G22" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H22" s="11" t="str">
+        <x:v>重慶北路 → 中山高(重慶交流道) → 汐止</x:v>
+      </x:c>
+      <x:c r="I22" s="11"/>
+    </x:row>
+    <x:row r="23" ht="24" customHeight="1">
+      <x:c r="A23" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B23" s="16" t="str">
+        <x:v>M022</x:v>
+      </x:c>
+      <x:c r="C23" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D23" s="16" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E23" s="14" t="str">
+        <x:v>劍潭/內湖線</x:v>
+      </x:c>
+      <x:c r="F23" s="16"/>
+      <x:c r="G23" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H23" s="11" t="str">
+        <x:v>北安路 → 內湖路 → 內湖路 → 文德路 → 成功路 → 民權東路六段 → 成功交流道 → 汐止</x:v>
+      </x:c>
+      <x:c r="I23" s="11"/>
+    </x:row>
+    <x:row r="24" ht="24" customHeight="1">
+      <x:c r="A24" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B24" s="16" t="str">
+        <x:v>M023</x:v>
+      </x:c>
+      <x:c r="C24" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D24" s="16" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E24" s="14" t="str">
+        <x:v>內湖A線</x:v>
+      </x:c>
+      <x:c r="F24" s="16"/>
+      <x:c r="G24" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H24" s="11" t="str">
+        <x:v>民權東路六段 → 成功交流道 → 汐止</x:v>
+      </x:c>
+      <x:c r="I24" s="11"/>
+    </x:row>
+    <x:row r="25" ht="24" customHeight="1">
+      <x:c r="A25" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B25" s="16" t="str">
+        <x:v>M024</x:v>
+      </x:c>
+      <x:c r="C25" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D25" s="16" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E25" s="14" t="str">
+        <x:v>內湖B線(中)</x:v>
+      </x:c>
+      <x:c r="F25" s="16" t="str">
+        <x:v>中巴</x:v>
+      </x:c>
+      <x:c r="G25" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H25" s="11" t="str">
+        <x:v>民權東路六段 → 成功交流道 → 汐止</x:v>
+      </x:c>
+      <x:c r="I25" s="11"/>
+    </x:row>
+    <x:row r="26" ht="24" customHeight="1">
+      <x:c r="A26" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B26" s="16" t="str">
+        <x:v>M025</x:v>
+      </x:c>
+      <x:c r="C26" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D26" s="16" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E26" s="14" t="str">
+        <x:v>民權/民生A線</x:v>
+      </x:c>
+      <x:c r="F26" s="16"/>
+      <x:c r="G26" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H26" s="11" t="str">
+        <x:v>民權西路 → 民權東路 → 建國北路 → 民生東路 → 三民路 → 民權東路 → 成功路 → 中山高(成功交流道) → 汐止</x:v>
+      </x:c>
+      <x:c r="I26" s="11"/>
+    </x:row>
+    <x:row r="27" ht="24" customHeight="1">
+      <x:c r="A27" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B27" s="16" t="str">
+        <x:v>M026</x:v>
+      </x:c>
+      <x:c r="C27" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D27" s="16" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E27" s="14" t="str">
+        <x:v>民權/民生B線(中)</x:v>
+      </x:c>
+      <x:c r="F27" s="16" t="str">
+        <x:v>中巴</x:v>
+      </x:c>
+      <x:c r="G27" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H27" s="11" t="str">
+        <x:v>民權西路 → 民權東路 → 建國北路 → 民生東路 → 三民路 → 民權東路 → 成功路 → 中山高(成功交流道) → 汐止</x:v>
+      </x:c>
+      <x:c r="I27" s="11"/>
+    </x:row>
+    <x:row r="28" ht="24" customHeight="1">
+      <x:c r="A28" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B28" s="16" t="str">
+        <x:v>M027</x:v>
+      </x:c>
+      <x:c r="C28" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D28" s="16" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E28" s="14" t="str">
+        <x:v>民生線</x:v>
+      </x:c>
+      <x:c r="F28" s="16"/>
+      <x:c r="G28" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H28" s="11" t="str">
+        <x:v>民生東路 → 三民路 → 民權東路 → 成功路 → 中山高(成功交流道) → 汐止</x:v>
+      </x:c>
+      <x:c r="I28" s="11"/>
+    </x:row>
+    <x:row r="29" ht="24" customHeight="1">
+      <x:c r="A29" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B29" s="16" t="str">
+        <x:v>M028</x:v>
+      </x:c>
+      <x:c r="C29" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D29" s="16" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E29" s="14" t="str">
+        <x:v>南京A線</x:v>
+      </x:c>
+      <x:c r="F29" s="16"/>
+      <x:c r="G29" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H29" s="11" t="str">
+        <x:v>南京東路 → 南港路 → 大同路 → 汐止</x:v>
+      </x:c>
+      <x:c r="I29" s="11"/>
+    </x:row>
+    <x:row r="30" ht="24" customHeight="1">
+      <x:c r="A30" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B30" s="16" t="str">
+        <x:v>M029</x:v>
+      </x:c>
+      <x:c r="C30" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D30" s="16" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E30" s="14" t="str">
+        <x:v>南京B線(中)</x:v>
+      </x:c>
+      <x:c r="F30" s="16" t="str">
+        <x:v>中巴</x:v>
+      </x:c>
+      <x:c r="G30" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H30" s="11" t="str">
+        <x:v>南京東路 → 八德路 → 南港路 → 大同路 → 汐止</x:v>
+      </x:c>
+      <x:c r="I30" s="11"/>
+    </x:row>
+    <x:row r="31" ht="24" customHeight="1">
+      <x:c r="A31" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B31" s="16" t="str">
+        <x:v>M030</x:v>
+      </x:c>
+      <x:c r="C31" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D31" s="16" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E31" s="14" t="str">
+        <x:v>華中/信義A線</x:v>
+      </x:c>
+      <x:c r="F31" s="16"/>
+      <x:c r="G31" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H31" s="11" t="str">
+        <x:v>南寧路 → 愛國西路 → 信義路 → 建國南路 → 忠孝東路 → 光復南路 → 松德路 → 松山路 → 忠孝東路 → 向陽路 → 南港路 → 汐止</x:v>
+      </x:c>
+      <x:c r="I31" s="11"/>
+    </x:row>
+    <x:row r="32" ht="24" customHeight="1">
+      <x:c r="A32" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B32" s="16" t="str">
+        <x:v>M031</x:v>
+      </x:c>
+      <x:c r="C32" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D32" s="16" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E32" s="14" t="str">
+        <x:v>華中/信義B線</x:v>
+      </x:c>
+      <x:c r="F32" s="16"/>
+      <x:c r="G32" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H32" s="11" t="str">
+        <x:v>忠孝東路 → 向陽路 → 南港路 → 汐止</x:v>
+      </x:c>
+      <x:c r="I32" s="11"/>
+    </x:row>
+    <x:row r="33" ht="24" customHeight="1">
+      <x:c r="A33" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B33" s="16" t="str">
+        <x:v>M032</x:v>
+      </x:c>
+      <x:c r="C33" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D33" s="16" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E33" s="14" t="str">
+        <x:v>雙園線</x:v>
+      </x:c>
+      <x:c r="F33" s="16"/>
+      <x:c r="G33" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H33" s="11" t="str">
+        <x:v>萬大路 → 西藏路 → 和平西路 → 和平東路 → 敦化南路 → 辛亥路 → 北二高(辛亥聯絡道) → 汐止</x:v>
+      </x:c>
+      <x:c r="I33" s="11"/>
+    </x:row>
+    <x:row r="34" ht="24" customHeight="1">
+      <x:c r="A34" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B34" s="16" t="str">
+        <x:v>M033</x:v>
+      </x:c>
+      <x:c r="C34" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D34" s="16" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E34" s="14" t="str">
+        <x:v>永和和平A線</x:v>
+      </x:c>
+      <x:c r="F34" s="16"/>
+      <x:c r="G34" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H34" s="11" t="str">
+        <x:v>永和仁愛路 → 和平西路 → 和平東路 → 辛亥路 → 北二高(辛亥聯絡道) → 汐止</x:v>
+      </x:c>
+      <x:c r="I34" s="11"/>
+    </x:row>
+    <x:row r="35" ht="24" customHeight="1">
+      <x:c r="A35" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B35" s="16" t="str">
+        <x:v>M034</x:v>
+      </x:c>
+      <x:c r="C35" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D35" s="16" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E35" s="14" t="str">
+        <x:v>永和和平B線(中)</x:v>
+      </x:c>
+      <x:c r="F35" s="16" t="str">
+        <x:v>中巴</x:v>
+      </x:c>
+      <x:c r="G35" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H35" s="11" t="str">
+        <x:v>中山路 → 永和路 → 中正橋 → 和平西路 → 和平東路 → 建國南路 → 辛亥路 → 北二高(辛亥聯絡道) → 汐止</x:v>
+      </x:c>
+      <x:c r="I35" s="11"/>
+    </x:row>
+    <x:row r="36" ht="24" customHeight="1">
+      <x:c r="A36" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B36" s="16" t="str">
+        <x:v>M035</x:v>
+      </x:c>
+      <x:c r="C36" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D36" s="16" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E36" s="14" t="str">
+        <x:v>和平線</x:v>
+      </x:c>
+      <x:c r="F36" s="16"/>
+      <x:c r="G36" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H36" s="11" t="str">
+        <x:v>和平西路 → 和平東路 → 辛亥路 → 北二高(辛亥聯絡道) → 汐止</x:v>
+      </x:c>
+      <x:c r="I36" s="11"/>
+    </x:row>
+    <x:row r="37" ht="24" customHeight="1">
+      <x:c r="A37" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B37" s="16" t="str">
+        <x:v>M036</x:v>
+      </x:c>
+      <x:c r="C37" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D37" s="16" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E37" s="14" t="str">
+        <x:v>永和線</x:v>
+      </x:c>
+      <x:c r="F37" s="16"/>
+      <x:c r="G37" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H37" s="11" t="str">
+        <x:v>福和路 → 中山路 → 永福橋 → 汀洲路 → 辛亥路 → 北二高(辛亥聯絡道) → 汐止</x:v>
+      </x:c>
+      <x:c r="I37" s="11"/>
+    </x:row>
+    <x:row r="38" ht="24" customHeight="1">
+      <x:c r="A38" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B38" s="16" t="str">
+        <x:v>M037</x:v>
+      </x:c>
+      <x:c r="C38" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D38" s="16" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E38" s="14" t="str">
+        <x:v>萬芳/景美線</x:v>
+      </x:c>
+      <x:c r="F38" s="16"/>
+      <x:c r="G38" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H38" s="11" t="str">
+        <x:v>興隆路 → 景隆街 → 羅斯福路 → 新生南路 → 辛亥路 → 北二高(辛亥聯絡道) → 汐止</x:v>
+      </x:c>
+      <x:c r="I38" s="11"/>
+    </x:row>
+    <x:row r="39" ht="24" customHeight="1">
+      <x:c r="A39" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B39" s="16" t="str">
+        <x:v>M038</x:v>
+      </x:c>
+      <x:c r="C39" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D39" s="16" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E39" s="14" t="str">
+        <x:v>板橋A線</x:v>
+      </x:c>
+      <x:c r="F39" s="16"/>
+      <x:c r="G39" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H39" s="11" t="str">
+        <x:v>民生路 → 中和/中正路 → 北二高(中和交流道) → 汐止</x:v>
+      </x:c>
+      <x:c r="I39" s="11"/>
+    </x:row>
+    <x:row r="40" ht="24" customHeight="1">
+      <x:c r="A40" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B40" s="16" t="str">
+        <x:v>M039</x:v>
+      </x:c>
+      <x:c r="C40" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D40" s="16" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E40" s="14" t="str">
+        <x:v>板橋B線</x:v>
+      </x:c>
+      <x:c r="F40" s="16"/>
+      <x:c r="G40" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H40" s="11" t="str">
+        <x:v>文化路 → 大同街 → 三民路 → 民生路 → 中和/中正路 → 北二高(中和交流道) → 汐止</x:v>
+      </x:c>
+      <x:c r="I40" s="11"/>
+    </x:row>
+    <x:row r="41" ht="24" customHeight="1">
+      <x:c r="A41" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B41" s="16" t="str">
+        <x:v>M040</x:v>
+      </x:c>
+      <x:c r="C41" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D41" s="16" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E41" s="14" t="str">
+        <x:v>板橋C線</x:v>
+      </x:c>
+      <x:c r="F41" s="16"/>
+      <x:c r="G41" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H41" s="11" t="str">
+        <x:v>重慶路 → 忠孝路 → 四川路 → 中山路 → 文化路 → 萬板路 → 64快速道路 → 北二高(中和交流道) → 汐止</x:v>
+      </x:c>
+      <x:c r="I41" s="11"/>
+    </x:row>
+    <x:row r="42" ht="24" customHeight="1">
+      <x:c r="A42" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B42" s="16" t="str">
+        <x:v>M041</x:v>
+      </x:c>
+      <x:c r="C42" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D42" s="16" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E42" s="14" t="str">
+        <x:v>板橋D線</x:v>
+      </x:c>
+      <x:c r="F42" s="16"/>
+      <x:c r="G42" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H42" s="11" t="str">
+        <x:v>三民路 → 民生路 → 中和/中正路 → 北二高(中和交流道) → 汐止</x:v>
+      </x:c>
+      <x:c r="I42" s="11"/>
+    </x:row>
+    <x:row r="43" ht="24" customHeight="1">
+      <x:c r="A43" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B43" s="16" t="str">
+        <x:v>M042</x:v>
+      </x:c>
+      <x:c r="C43" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D43" s="16" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E43" s="14" t="str">
+        <x:v>土城A線</x:v>
+      </x:c>
+      <x:c r="F43" s="16"/>
+      <x:c r="G43" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H43" s="11" t="str">
+        <x:v>國慶路 → 信義路 → 青雲路 → 金城路 → 金城高架 → 北二高(土城交流道) → 汐止</x:v>
+      </x:c>
+      <x:c r="I43" s="11"/>
+    </x:row>
+    <x:row r="44" ht="24" customHeight="1">
+      <x:c r="A44" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B44" s="16" t="str">
+        <x:v>M043</x:v>
+      </x:c>
+      <x:c r="C44" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D44" s="16" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E44" s="14" t="str">
+        <x:v>土城B線</x:v>
+      </x:c>
+      <x:c r="F44" s="16"/>
+      <x:c r="G44" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H44" s="11" t="str">
+        <x:v>信義路 → 青雲路 → 金城路 → 金城高架 → 北二高(土城交流道) → 汐止</x:v>
+      </x:c>
+      <x:c r="I44" s="11"/>
+    </x:row>
+    <x:row r="45" ht="24" customHeight="1">
+      <x:c r="A45" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B45" s="16" t="str">
+        <x:v>M044</x:v>
+      </x:c>
+      <x:c r="C45" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D45" s="16" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E45" s="14" t="str">
+        <x:v>三重A線</x:v>
+      </x:c>
+      <x:c r="F45" s="16"/>
+      <x:c r="G45" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H45" s="11" t="str">
+        <x:v>正義北路 → 三重重陽路 → 中山高(三重交流道) → 汐止</x:v>
+      </x:c>
+      <x:c r="I45" s="11"/>
+    </x:row>
+    <x:row r="46" ht="24" customHeight="1">
+      <x:c r="A46" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B46" s="16" t="str">
+        <x:v>M045</x:v>
+      </x:c>
+      <x:c r="C46" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D46" s="16" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E46" s="14" t="str">
+        <x:v>三重B線</x:v>
+      </x:c>
+      <x:c r="F46" s="16"/>
+      <x:c r="G46" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H46" s="11" t="str">
+        <x:v>正義北路 → 三重重陽路 → 中山高(三重交流道) → 汐止</x:v>
+      </x:c>
+      <x:c r="I46" s="11"/>
+    </x:row>
+    <x:row r="47" ht="24" customHeight="1">
+      <x:c r="A47" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B47" s="16" t="str">
+        <x:v>M046</x:v>
+      </x:c>
+      <x:c r="C47" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D47" s="16" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E47" s="14" t="str">
+        <x:v>三重C線</x:v>
+      </x:c>
+      <x:c r="F47" s="16"/>
+      <x:c r="G47" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H47" s="11" t="str">
+        <x:v>正義北路 → 三重重陽路 → 正義北路 → 中山高(三重交流道) → 汐止</x:v>
+      </x:c>
+      <x:c r="I47" s="11"/>
+    </x:row>
+    <x:row r="48" ht="24" customHeight="1">
+      <x:c r="A48" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B48" s="16" t="str">
+        <x:v>M047</x:v>
+      </x:c>
+      <x:c r="C48" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D48" s="16" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E48" s="14" t="str">
+        <x:v>三重D線</x:v>
+      </x:c>
+      <x:c r="F48" s="16"/>
+      <x:c r="G48" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H48" s="11" t="str">
+        <x:v>中正路 → 環堤大道 → 環河北路 → 龍門路 → 正義北路 → 三重重陽路 → 中山高(三重交流道) → 汐止</x:v>
+      </x:c>
+      <x:c r="I48" s="11"/>
+    </x:row>
+    <x:row r="49" ht="24" customHeight="1">
+      <x:c r="A49" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B49" s="16" t="str">
+        <x:v>M048</x:v>
+      </x:c>
+      <x:c r="C49" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D49" s="16" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E49" s="14" t="str">
+        <x:v>蘆洲/三重A線</x:v>
+      </x:c>
+      <x:c r="F49" s="16"/>
+      <x:c r="G49" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H49" s="11" t="str">
+        <x:v>中正路 → 環堤大道 → 環河北路 → 龍門路 → 正義北路 → 三重重陽路 → 中山高(三重交流道) → 汐止</x:v>
+      </x:c>
+      <x:c r="I49" s="11"/>
+    </x:row>
+    <x:row r="50" ht="24" customHeight="1">
+      <x:c r="A50" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B50" s="16" t="str">
+        <x:v>M049</x:v>
+      </x:c>
+      <x:c r="C50" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D50" s="16" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E50" s="14" t="str">
+        <x:v>蘆洲/三重B線</x:v>
+      </x:c>
+      <x:c r="F50" s="16"/>
+      <x:c r="G50" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H50" s="11" t="str">
+        <x:v>三民路 → 中山一路 → 三和路 → 龍門路 → 正義北路 → 重陽路 → 中山高(三重交流道) → 汐止</x:v>
+      </x:c>
+      <x:c r="I50" s="11"/>
+    </x:row>
+    <x:row r="51" ht="24" customHeight="1">
+      <x:c r="A51" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B51" s="16" t="str">
+        <x:v>M050</x:v>
+      </x:c>
+      <x:c r="C51" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D51" s="16" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E51" s="14" t="str">
+        <x:v>蘆洲/三重C線</x:v>
+      </x:c>
+      <x:c r="F51" s="16"/>
+      <x:c r="G51" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H51" s="11" t="str">
+        <x:v>新五路 → 長榮路 → 三民路 → 三和路 → 中山高(三重交流道) → 汐止</x:v>
+      </x:c>
+      <x:c r="I51" s="11"/>
+    </x:row>
+    <x:row r="52" ht="24" customHeight="1">
+      <x:c r="A52" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B52" s="16" t="str">
+        <x:v>M051</x:v>
+      </x:c>
+      <x:c r="C52" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D52" s="16" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E52" s="14" t="str">
+        <x:v>中和A線</x:v>
+      </x:c>
+      <x:c r="F52" s="16"/>
+      <x:c r="G52" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H52" s="11" t="str">
+        <x:v>景平路 → 北二高(安坑交流道) → 汐止</x:v>
+      </x:c>
+      <x:c r="I52" s="11"/>
+    </x:row>
+    <x:row r="53" ht="24" customHeight="1">
+      <x:c r="A53" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B53" s="16" t="str">
+        <x:v>M052</x:v>
+      </x:c>
+      <x:c r="C53" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D53" s="16" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E53" s="14" t="str">
+        <x:v>中和B線</x:v>
+      </x:c>
+      <x:c r="F53" s="16"/>
+      <x:c r="G53" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H53" s="11" t="str">
+        <x:v>永和中正路 → 景新街 → 安和路 → 北二高(安坑交流道) → 汐止</x:v>
+      </x:c>
+      <x:c r="I53" s="11"/>
+    </x:row>
+    <x:row r="54" ht="24" customHeight="1">
+      <x:c r="A54" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B54" s="16" t="str">
+        <x:v>M053</x:v>
+      </x:c>
+      <x:c r="C54" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D54" s="16" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E54" s="14" t="str">
+        <x:v>中和C線</x:v>
+      </x:c>
+      <x:c r="F54" s="16"/>
+      <x:c r="G54" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H54" s="11" t="str">
+        <x:v>永和中正路 → 景平路 → 中正路 → 北二高(中和交流道) → 汐止</x:v>
+      </x:c>
+      <x:c r="I54" s="11"/>
+    </x:row>
+    <x:row r="55" ht="24" customHeight="1">
+      <x:c r="A55" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B55" s="16" t="str">
+        <x:v>M054</x:v>
+      </x:c>
+      <x:c r="C55" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D55" s="16" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E55" s="14" t="str">
+        <x:v>中和D線</x:v>
+      </x:c>
+      <x:c r="F55" s="16"/>
+      <x:c r="G55" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H55" s="11" t="str">
+        <x:v>中正路 → 北二高(安坑交流道) → 汐止</x:v>
+      </x:c>
+      <x:c r="I55" s="11"/>
+    </x:row>
+    <x:row r="56" ht="24" customHeight="1">
+      <x:c r="A56" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B56" s="16" t="str">
+        <x:v>M055</x:v>
+      </x:c>
+      <x:c r="C56" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D56" s="16" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E56" s="14" t="str">
+        <x:v>中和E線(中巴)</x:v>
+      </x:c>
+      <x:c r="F56" s="16" t="str">
+        <x:v>中巴</x:v>
+      </x:c>
+      <x:c r="G56" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H56" s="11" t="str">
+        <x:v>中正路 → 北二高(安坑交流道) → 汐止</x:v>
+      </x:c>
+      <x:c r="I56" s="11"/>
+    </x:row>
+    <x:row r="57" ht="24" customHeight="1">
+      <x:c r="A57" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B57" s="16" t="str">
+        <x:v>M056</x:v>
+      </x:c>
+      <x:c r="C57" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D57" s="16" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E57" s="14" t="str">
+        <x:v>木柵線</x:v>
+      </x:c>
+      <x:c r="F57" s="16"/>
+      <x:c r="G57" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H57" s="11" t="str">
+        <x:v>寶慶街 → 木柵路 → 北二高(萬芳交流道) → 汐止</x:v>
+      </x:c>
+      <x:c r="I57" s="11"/>
+    </x:row>
+    <x:row r="58" ht="24" customHeight="1">
+      <x:c r="A58" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B58" s="16" t="str">
+        <x:v>M057</x:v>
+      </x:c>
+      <x:c r="C58" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D58" s="16" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E58" s="14" t="str">
+        <x:v>新店A線</x:v>
+      </x:c>
+      <x:c r="F58" s="16"/>
+      <x:c r="G58" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H58" s="11" t="str">
+        <x:v>中正路 → 北新路 → 順安街 → 木柵路二段 → 秀明路 → 木柵路四段 → 北二高(萬芳交流道) → 汐止</x:v>
+      </x:c>
+      <x:c r="I58" s="11"/>
+    </x:row>
+    <x:row r="59" ht="24" customHeight="1">
+      <x:c r="A59" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B59" s="16" t="str">
+        <x:v>M058</x:v>
+      </x:c>
+      <x:c r="C59" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D59" s="16" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E59" s="14" t="str">
+        <x:v>新店B線</x:v>
+      </x:c>
+      <x:c r="F59" s="16"/>
+      <x:c r="G59" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H59" s="11" t="str">
+        <x:v>北新路 → 民權路 → 中興路 → 北二高 → 新店交流道 → 汐止</x:v>
+      </x:c>
+      <x:c r="I59" s="11"/>
+    </x:row>
+    <x:row r="60" ht="24" customHeight="1">
+      <x:c r="A60" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B60" s="16" t="str">
+        <x:v>M059</x:v>
+      </x:c>
+      <x:c r="C60" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D60" s="16" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E60" s="14" t="str">
+        <x:v>新店C線(中)</x:v>
+      </x:c>
+      <x:c r="F60" s="16" t="str">
+        <x:v>中巴</x:v>
+      </x:c>
+      <x:c r="G60" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H60" s="11" t="str">
+        <x:v>中正路 → 北新路 → 順安街 → 木柵路二段 → 秀明路 → 木柵路四段 → 北二高(萬芳交流道) → 汐止</x:v>
+      </x:c>
+      <x:c r="I60" s="11"/>
+    </x:row>
+    <x:row r="61" ht="24" customHeight="1">
+      <x:c r="A61" s="16" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B61" s="16" t="str">
+        <x:v>M060</x:v>
+      </x:c>
+      <x:c r="C61" s="16" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D61" s="16" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E61" s="14" t="str">
+        <x:v>中和/新店/木柵線</x:v>
+      </x:c>
+      <x:c r="F61" s="16"/>
+      <x:c r="G61" s="16" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="H61" s="11" t="str">
+        <x:v>得和路 → 成功路 → 秀朗橋 → 中正路 → 中興路 → 寶橋路 → 木新路二段 → 木柵路四段 → 北二高(萬芳交流道) → 汐止</x:v>
+      </x:c>
+      <x:c r="I61" s="11"/>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="2">
-    <x:dataValidation type="list" sqref="A2:A200">
+  <x:conditionalFormatting sqref="A2:I61">
+    <x:cfRule type="expression" dxfId="0" priority="1">
+      <x:formula>$A2="FALSE"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:dataValidations count="3">
+    <x:dataValidation type="list" sqref="A2:A61">
       <x:formula1>"TRUE,FALSE"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="C2:C200">
+    <x:dataValidation type="list" sqref="C2:C61">
       <x:formula1>"上班,下班,加班"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="F2:F61">
+      <x:formula1>",大巴,中巴,小巴"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf480c41593414a7c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4b474d8357245ad"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -957,1072 +1965,3069 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="28" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="46" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="9" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="11" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="25" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="30" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="38" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="38" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="28" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="16" t="str">
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="10" t="str">
         <x:v>啟用</x:v>
       </x:c>
-      <x:c r="B1" s="16" t="str">
+      <x:c r="B1" s="10" t="str">
         <x:v>StopID</x:v>
       </x:c>
-      <x:c r="C1" s="16" t="str">
+      <x:c r="C1" s="10" t="str">
         <x:v>顯示名稱</x:v>
       </x:c>
-      <x:c r="D1" s="16" t="str">
+      <x:c r="D1" s="10" t="str">
         <x:v>候車地標</x:v>
       </x:c>
-      <x:c r="E1" s="16" t="str">
+      <x:c r="E1" s="10" t="str">
         <x:v>PDF原文</x:v>
       </x:c>
-      <x:c r="F1" s="16" t="str">
+      <x:c r="F1" s="10" t="str">
         <x:v>定位搜尋文字</x:v>
       </x:c>
-      <x:c r="G1" s="16" t="str">
+      <x:c r="G1" s="10" t="str">
         <x:v>備註</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B2" s="18" t="str">
         <x:v>S001</x:v>
       </x:c>
-      <x:c r="C2" s="18" t="str">
+      <x:c r="C2" s="11" t="str">
         <x:v>中華路三段9號</x:v>
       </x:c>
-      <x:c r="D2" s="18" t="str">
+      <x:c r="D2" s="11" t="str">
         <x:v>國泰人壽 / 全家對面</x:v>
       </x:c>
-      <x:c r="E2" s="18" t="str">
+      <x:c r="E2" s="11" t="str">
         <x:v>中華路三段9號(國泰人壽/全家對面)</x:v>
       </x:c>
-      <x:c r="F2" s="18" t="str">
+      <x:c r="F2" s="11" t="str">
         <x:v>新竹市中華路三段9號</x:v>
       </x:c>
-      <x:c r="G2" s="18" t="str"/>
-    </x:row>
-    <x:row r="3">
+      <x:c r="G2" s="11"/>
+    </x:row>
+    <x:row r="3" ht="22" customHeight="1">
       <x:c r="A3" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B3" s="18" t="str">
         <x:v>S002</x:v>
       </x:c>
-      <x:c r="C3" s="18" t="str">
+      <x:c r="C3" s="11" t="str">
         <x:v>民族路34號</x:v>
       </x:c>
-      <x:c r="D3" s="18" t="str">
+      <x:c r="D3" s="11" t="str">
         <x:v>玉山銀行</x:v>
       </x:c>
-      <x:c r="E3" s="18" t="str">
+      <x:c r="E3" s="11" t="str">
         <x:v>民族路34號(玉山銀行)</x:v>
       </x:c>
-      <x:c r="F3" s="18" t="str">
+      <x:c r="F3" s="11" t="str">
         <x:v>新竹市民族路34號</x:v>
       </x:c>
-      <x:c r="G3" s="18" t="str"/>
-    </x:row>
-    <x:row r="4">
+      <x:c r="G3" s="11"/>
+    </x:row>
+    <x:row r="4" ht="22" customHeight="1">
       <x:c r="A4" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B4" s="18" t="str">
         <x:v>S003</x:v>
       </x:c>
-      <x:c r="C4" s="18" t="str">
+      <x:c r="C4" s="11" t="str">
         <x:v>南大路81號</x:v>
       </x:c>
-      <x:c r="D4" s="18" t="str">
+      <x:c r="D4" s="11" t="str">
         <x:v>南大路 / 東大路一段口</x:v>
       </x:c>
-      <x:c r="E4" s="18" t="str">
+      <x:c r="E4" s="11" t="str">
         <x:v>南大路81號(南大路/東大路一段口)</x:v>
       </x:c>
-      <x:c r="F4" s="18" t="str">
+      <x:c r="F4" s="11" t="str">
         <x:v>新竹市南大路81號</x:v>
       </x:c>
-      <x:c r="G4" s="18" t="str"/>
-    </x:row>
-    <x:row r="5">
+      <x:c r="G4" s="11"/>
+    </x:row>
+    <x:row r="5" ht="22" customHeight="1">
       <x:c r="A5" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B5" s="18" t="str">
         <x:v>S004</x:v>
       </x:c>
-      <x:c r="C5" s="18" t="str">
+      <x:c r="C5" s="11" t="str">
         <x:v>光復路二段321號</x:v>
       </x:c>
-      <x:c r="D5" s="18" t="str">
+      <x:c r="D5" s="11" t="str">
         <x:v>工研院光復院區公車站</x:v>
       </x:c>
-      <x:c r="E5" s="18" t="str">
+      <x:c r="E5" s="11" t="str">
         <x:v>光復路二段321號(工研院光復院區公車站)</x:v>
       </x:c>
-      <x:c r="F5" s="18" t="str">
+      <x:c r="F5" s="11" t="str">
         <x:v>新竹市光復路二段321號</x:v>
       </x:c>
-      <x:c r="G5" s="18" t="str"/>
-    </x:row>
-    <x:row r="6">
+      <x:c r="G5" s="11"/>
+    </x:row>
+    <x:row r="6" ht="22" customHeight="1">
       <x:c r="A6" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B6" s="18" t="str">
         <x:v>S005</x:v>
       </x:c>
-      <x:c r="C6" s="18" t="str">
+      <x:c r="C6" s="11" t="str">
         <x:v>光復路二段101號</x:v>
       </x:c>
-      <x:c r="D6" s="18" t="str">
+      <x:c r="D6" s="11" t="str">
         <x:v>清大公車站</x:v>
       </x:c>
-      <x:c r="E6" s="18" t="str">
+      <x:c r="E6" s="11" t="str">
         <x:v>光復路二段101號(清大公車站)</x:v>
       </x:c>
-      <x:c r="F6" s="18" t="str">
+      <x:c r="F6" s="11" t="str">
         <x:v>新竹市光復路二段101號</x:v>
       </x:c>
-      <x:c r="G6" s="18" t="str"/>
-    </x:row>
-    <x:row r="7">
+      <x:c r="G6" s="11"/>
+    </x:row>
+    <x:row r="7" ht="22" customHeight="1">
       <x:c r="A7" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B7" s="18" t="str">
         <x:v>S006</x:v>
       </x:c>
-      <x:c r="C7" s="18" t="str">
+      <x:c r="C7" s="11" t="str">
         <x:v>光復路二段3號</x:v>
       </x:c>
-      <x:c r="D7" s="18" t="str">
+      <x:c r="D7" s="11" t="str">
         <x:v>經濟部訓練所門口旁樹蔭下</x:v>
       </x:c>
-      <x:c r="E7" s="18" t="str">
+      <x:c r="E7" s="11" t="str">
         <x:v>光復路二段3號(經濟部訓練所門口旁樹蔭下)</x:v>
       </x:c>
-      <x:c r="F7" s="18" t="str">
+      <x:c r="F7" s="11" t="str">
         <x:v>新竹市光復路二段3號</x:v>
       </x:c>
-      <x:c r="G7" s="18" t="str"/>
-    </x:row>
-    <x:row r="8">
+      <x:c r="G7" s="11"/>
+    </x:row>
+    <x:row r="8" ht="22" customHeight="1">
       <x:c r="A8" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B8" s="18" t="str">
         <x:v>S007</x:v>
       </x:c>
-      <x:c r="C8" s="18" t="str">
+      <x:c r="C8" s="11" t="str">
         <x:v>南興路一段468號</x:v>
       </x:c>
-      <x:c r="D8" s="18" t="str">
+      <x:c r="D8" s="11" t="str">
         <x:v>勇和興輪胎行</x:v>
       </x:c>
-      <x:c r="E8" s="18" t="str">
+      <x:c r="E8" s="11" t="str">
         <x:v>勇和興輪胎行(南興路一段468號)</x:v>
       </x:c>
-      <x:c r="F8" s="18" t="str">
+      <x:c r="F8" s="11" t="str">
         <x:v>桃園市龍潭區南興路一段468號</x:v>
       </x:c>
-      <x:c r="G8" s="18" t="str"/>
-    </x:row>
-    <x:row r="9">
+      <x:c r="G8" s="11"/>
+    </x:row>
+    <x:row r="9" ht="22" customHeight="1">
       <x:c r="A9" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B9" s="18" t="str">
         <x:v>S008</x:v>
       </x:c>
-      <x:c r="C9" s="18" t="str">
+      <x:c r="C9" s="11" t="str">
         <x:v>大昌路二段100號</x:v>
       </x:c>
-      <x:c r="D9" s="18" t="str">
+      <x:c r="D9" s="11" t="str">
         <x:v>台灣家具</x:v>
       </x:c>
-      <x:c r="E9" s="18" t="str">
+      <x:c r="E9" s="11" t="str">
         <x:v>台灣家具(大昌路2段100號)</x:v>
       </x:c>
-      <x:c r="F9" s="18" t="str">
+      <x:c r="F9" s="11" t="str">
         <x:v>桃園市龍潭區大昌路二段100號</x:v>
       </x:c>
-      <x:c r="G9" s="18" t="str"/>
-    </x:row>
-    <x:row r="10">
+      <x:c r="G9" s="11"/>
+    </x:row>
+    <x:row r="10" ht="22" customHeight="1">
       <x:c r="A10" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B10" s="18" t="str">
         <x:v>S009</x:v>
       </x:c>
-      <x:c r="C10" s="18" t="str">
+      <x:c r="C10" s="11" t="str">
         <x:v>新南路一段328號</x:v>
       </x:c>
-      <x:c r="D10" s="18" t="str">
+      <x:c r="D10" s="11" t="str">
         <x:v>天香回味餐廳</x:v>
       </x:c>
-      <x:c r="E10" s="18" t="str">
+      <x:c r="E10" s="11" t="str">
         <x:v>蘆竹新南路一段328號(天香回味餐廳)</x:v>
       </x:c>
-      <x:c r="F10" s="18" t="str">
+      <x:c r="F10" s="11" t="str">
         <x:v>桃園市蘆竹區新南路一段328號</x:v>
       </x:c>
-      <x:c r="G10" s="18" t="str"/>
-    </x:row>
-    <x:row r="11">
+      <x:c r="G10" s="11"/>
+    </x:row>
+    <x:row r="11" ht="22" customHeight="1">
       <x:c r="A11" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B11" s="18" t="str">
         <x:v>S010</x:v>
       </x:c>
-      <x:c r="C11" s="18" t="str">
+      <x:c r="C11" s="11" t="str">
         <x:v>中豐路南勢二段291號</x:v>
       </x:c>
-      <x:c r="D11" s="18" t="str">
+      <x:c r="D11" s="11" t="str">
         <x:v>三義汽車保養</x:v>
       </x:c>
-      <x:c r="E11" s="18" t="str">
+      <x:c r="E11" s="11" t="str">
         <x:v>中豐路南勢二段291號(三義汽車保養)</x:v>
       </x:c>
-      <x:c r="F11" s="18" t="str">
+      <x:c r="F11" s="11" t="str">
         <x:v>桃園市平鎮區中豐路南勢二段291號</x:v>
       </x:c>
-      <x:c r="G11" s="18" t="str"/>
-    </x:row>
-    <x:row r="12">
+      <x:c r="G11" s="11"/>
+    </x:row>
+    <x:row r="12" ht="22" customHeight="1">
       <x:c r="A12" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B12" s="18" t="str">
         <x:v>S011</x:v>
       </x:c>
-      <x:c r="C12" s="18" t="str">
+      <x:c r="C12" s="11" t="str">
         <x:v>環南路三段88號</x:v>
       </x:c>
-      <x:c r="D12" s="18" t="str">
+      <x:c r="D12" s="11" t="str">
         <x:v>圖書館</x:v>
       </x:c>
-      <x:c r="E12" s="18" t="str">
+      <x:c r="E12" s="11" t="str">
         <x:v>平鎮區環南路三段88號(圖書館)</x:v>
       </x:c>
-      <x:c r="F12" s="18" t="str">
+      <x:c r="F12" s="11" t="str">
         <x:v>桃園市平鎮區環南路三段88號</x:v>
       </x:c>
-      <x:c r="G12" s="18" t="str"/>
-    </x:row>
-    <x:row r="13">
+      <x:c r="G12" s="11"/>
+    </x:row>
+    <x:row r="13" ht="22" customHeight="1">
       <x:c r="A13" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B13" s="18" t="str">
         <x:v>S012</x:v>
       </x:c>
-      <x:c r="C13" s="18" t="str">
+      <x:c r="C13" s="11" t="str">
         <x:v>新興路86號</x:v>
       </x:c>
-      <x:c r="D13" s="18" t="str">
+      <x:c r="D13" s="11" t="str">
         <x:v>頂天國際旅行社 / 鄰中壢後火車站</x:v>
       </x:c>
-      <x:c r="E13" s="18" t="str">
+      <x:c r="E13" s="11" t="str">
         <x:v>新興路86號(頂天國際旅行社/鄰中壢後火車站)</x:v>
       </x:c>
-      <x:c r="F13" s="18" t="str">
+      <x:c r="F13" s="11" t="str">
         <x:v>桃園市中壢區新興路86號</x:v>
       </x:c>
-      <x:c r="G13" s="18" t="str"/>
-    </x:row>
-    <x:row r="14">
+      <x:c r="G13" s="11"/>
+    </x:row>
+    <x:row r="14" ht="22" customHeight="1">
       <x:c r="A14" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B14" s="18" t="str">
         <x:v>S013</x:v>
       </x:c>
-      <x:c r="C14" s="18" t="str">
+      <x:c r="C14" s="11" t="str">
         <x:v>延平路二段231號</x:v>
       </x:c>
-      <x:c r="D14" s="18" t="str">
+      <x:c r="D14" s="11" t="str">
         <x:v>大眾自助餐</x:v>
       </x:c>
-      <x:c r="E14" s="18" t="str">
+      <x:c r="E14" s="11" t="str">
         <x:v>延平路二段231號(大眾自助餐)</x:v>
       </x:c>
-      <x:c r="F14" s="18" t="str">
+      <x:c r="F14" s="11" t="str">
         <x:v>桃園市平鎮區延平路二段231號</x:v>
       </x:c>
-      <x:c r="G14" s="18" t="str"/>
-    </x:row>
-    <x:row r="15">
+      <x:c r="G14" s="11"/>
+    </x:row>
+    <x:row r="15" ht="22" customHeight="1">
       <x:c r="A15" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B15" s="18" t="str">
         <x:v>S014</x:v>
       </x:c>
-      <x:c r="C15" s="18" t="str">
+      <x:c r="C15" s="11" t="str">
         <x:v>延平路二段87號</x:v>
       </x:c>
-      <x:c r="D15" s="18" t="str">
+      <x:c r="D15" s="11" t="str">
         <x:v>一品堂中醫診所 / 陽明醫院對面</x:v>
       </x:c>
-      <x:c r="E15" s="18" t="str">
+      <x:c r="E15" s="11" t="str">
         <x:v>延平路二段87號(一品堂中醫診所/陽明醫院對面)</x:v>
       </x:c>
-      <x:c r="F15" s="18" t="str">
+      <x:c r="F15" s="11" t="str">
         <x:v>桃園市平鎮區延平路二段87號</x:v>
       </x:c>
-      <x:c r="G15" s="18" t="str"/>
-    </x:row>
-    <x:row r="16">
+      <x:c r="G15" s="11"/>
+    </x:row>
+    <x:row r="16" ht="22" customHeight="1">
       <x:c r="A16" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B16" s="18" t="str">
         <x:v>S015</x:v>
       </x:c>
-      <x:c r="C16" s="18" t="str">
+      <x:c r="C16" s="11" t="str">
         <x:v>延平路551號</x:v>
       </x:c>
-      <x:c r="D16" s="18" t="str">
+      <x:c r="D16" s="11" t="str">
         <x:v>上海銀行</x:v>
       </x:c>
-      <x:c r="E16" s="18" t="str">
+      <x:c r="E16" s="11" t="str">
         <x:v>延平路551號(上海銀行)</x:v>
       </x:c>
-      <x:c r="F16" s="18" t="str">
+      <x:c r="F16" s="11" t="str">
         <x:v>桃園市中壢區延平路551號</x:v>
       </x:c>
-      <x:c r="G16" s="18" t="str"/>
-    </x:row>
-    <x:row r="17">
+      <x:c r="G16" s="11"/>
+    </x:row>
+    <x:row r="17" ht="22" customHeight="1">
       <x:c r="A17" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B17" s="18" t="str">
         <x:v>S016</x:v>
       </x:c>
-      <x:c r="C17" s="18" t="str">
+      <x:c r="C17" s="11" t="str">
         <x:v>中園路162號</x:v>
       </x:c>
-      <x:c r="D17" s="18" t="str">
+      <x:c r="D17" s="11" t="str">
         <x:v>豐田汽車</x:v>
       </x:c>
-      <x:c r="E17" s="18" t="str">
+      <x:c r="E17" s="11" t="str">
         <x:v>中園路162號(豐田汽車)</x:v>
       </x:c>
-      <x:c r="F17" s="18" t="str">
+      <x:c r="F17" s="11" t="str">
         <x:v>桃園市中壢區中園路162號</x:v>
       </x:c>
-      <x:c r="G17" s="18" t="str"/>
-    </x:row>
-    <x:row r="18">
+      <x:c r="G17" s="11"/>
+    </x:row>
+    <x:row r="18" ht="22" customHeight="1">
       <x:c r="A18" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B18" s="18" t="str">
         <x:v>S017</x:v>
       </x:c>
-      <x:c r="C18" s="18" t="str">
+      <x:c r="C18" s="11" t="str">
         <x:v>東園路38-2號</x:v>
       </x:c>
-      <x:c r="D18" s="18" t="str"/>
-      <x:c r="E18" s="18" t="str">
+      <x:c r="D18" s="11"/>
+      <x:c r="E18" s="11" t="str">
         <x:v>東園路38-2號</x:v>
       </x:c>
-      <x:c r="F18" s="18" t="str">
+      <x:c r="F18" s="11" t="str">
         <x:v>桃園市中壢區東園路38-2號</x:v>
       </x:c>
-      <x:c r="G18" s="18" t="str"/>
-    </x:row>
-    <x:row r="19">
+      <x:c r="G18" s="11"/>
+    </x:row>
+    <x:row r="19" ht="22" customHeight="1">
       <x:c r="A19" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B19" s="18" t="str">
         <x:v>S018</x:v>
       </x:c>
-      <x:c r="C19" s="18" t="str">
+      <x:c r="C19" s="11" t="str">
         <x:v>自強一路 / 福興路口</x:v>
       </x:c>
-      <x:c r="D19" s="18" t="str">
+      <x:c r="D19" s="11" t="str">
         <x:v>新竹縣體育場地2號門</x:v>
       </x:c>
-      <x:c r="E19" s="18" t="str">
+      <x:c r="E19" s="11" t="str">
         <x:v>自強一路/福興路口(新竹縣體育場地2號門)</x:v>
       </x:c>
-      <x:c r="F19" s="18" t="str">
+      <x:c r="F19" s="11" t="str">
         <x:v>新竹縣竹北市自強一路 福興路口</x:v>
       </x:c>
-      <x:c r="G19" s="18" t="str"/>
-    </x:row>
-    <x:row r="20">
+      <x:c r="G19" s="11"/>
+    </x:row>
+    <x:row r="20" ht="22" customHeight="1">
       <x:c r="A20" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B20" s="18" t="str">
         <x:v>S019</x:v>
       </x:c>
-      <x:c r="C20" s="18" t="str">
+      <x:c r="C20" s="11" t="str">
         <x:v>中山路694號</x:v>
       </x:c>
-      <x:c r="D20" s="18" t="str">
+      <x:c r="D20" s="11" t="str">
         <x:v>保順汽車保養廠</x:v>
       </x:c>
-      <x:c r="E20" s="18" t="str">
+      <x:c r="E20" s="11" t="str">
         <x:v>中山路694號(保順汽車保養廠)</x:v>
       </x:c>
-      <x:c r="F20" s="18" t="str">
+      <x:c r="F20" s="11" t="str">
         <x:v>桃園市桃園區中山路694號</x:v>
       </x:c>
-      <x:c r="G20" s="18" t="str"/>
-    </x:row>
-    <x:row r="21">
+      <x:c r="G20" s="11"/>
+    </x:row>
+    <x:row r="21" ht="22" customHeight="1">
       <x:c r="A21" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B21" s="18" t="str">
         <x:v>S020</x:v>
       </x:c>
-      <x:c r="C21" s="18" t="str">
+      <x:c r="C21" s="11" t="str">
         <x:v>中山路1076號</x:v>
       </x:c>
-      <x:c r="D21" s="18" t="str">
+      <x:c r="D21" s="11" t="str">
         <x:v>華盛窗簾傢飾</x:v>
       </x:c>
-      <x:c r="E21" s="18" t="str">
+      <x:c r="E21" s="11" t="str">
         <x:v>中山路1076號(華盛窗簾傢飾)</x:v>
       </x:c>
-      <x:c r="F21" s="18" t="str">
+      <x:c r="F21" s="11" t="str">
         <x:v>桃園市桃園區中山路1076號</x:v>
       </x:c>
-      <x:c r="G21" s="18" t="str"/>
-    </x:row>
-    <x:row r="22">
+      <x:c r="G21" s="11"/>
+    </x:row>
+    <x:row r="22" ht="22" customHeight="1">
       <x:c r="A22" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B22" s="18" t="str">
         <x:v>S021</x:v>
       </x:c>
-      <x:c r="C22" s="18" t="str">
+      <x:c r="C22" s="11" t="str">
         <x:v>龍安街56號</x:v>
       </x:c>
-      <x:c r="D22" s="18" t="str">
+      <x:c r="D22" s="11" t="str">
         <x:v>和風飯糰屋</x:v>
       </x:c>
-      <x:c r="E22" s="18" t="str">
+      <x:c r="E22" s="11" t="str">
         <x:v>龍安街56號(和風飯糰屋)</x:v>
       </x:c>
-      <x:c r="F22" s="18" t="str">
+      <x:c r="F22" s="11" t="str">
         <x:v>桃園市桃園區龍安街56號</x:v>
       </x:c>
-      <x:c r="G22" s="18" t="str"/>
-    </x:row>
-    <x:row r="23">
+      <x:c r="G22" s="11"/>
+    </x:row>
+    <x:row r="23" ht="22" customHeight="1">
       <x:c r="A23" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B23" s="18" t="str">
         <x:v>S022</x:v>
       </x:c>
-      <x:c r="C23" s="18" t="str">
+      <x:c r="C23" s="11" t="str">
         <x:v>復興路345號</x:v>
       </x:c>
-      <x:c r="D23" s="18" t="str">
+      <x:c r="D23" s="11" t="str">
         <x:v>做點心過生活店 / 台電對面</x:v>
       </x:c>
-      <x:c r="E23" s="18" t="str">
+      <x:c r="E23" s="11" t="str">
         <x:v>復興路345號(做點心過生活店/台電對面)</x:v>
       </x:c>
-      <x:c r="F23" s="18" t="str">
+      <x:c r="F23" s="11" t="str">
         <x:v>桃園市桃園區復興路345號</x:v>
       </x:c>
-      <x:c r="G23" s="18" t="str"/>
-    </x:row>
-    <x:row r="24">
+      <x:c r="G23" s="11"/>
+    </x:row>
+    <x:row r="24" ht="22" customHeight="1">
       <x:c r="A24" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B24" s="18" t="str">
         <x:v>S023</x:v>
       </x:c>
-      <x:c r="C24" s="18" t="str">
+      <x:c r="C24" s="11" t="str">
         <x:v>復興路 / 民權路口</x:v>
       </x:c>
-      <x:c r="D24" s="18" t="str">
+      <x:c r="D24" s="11" t="str">
         <x:v>巨匠電腦 / 民權路6號</x:v>
       </x:c>
-      <x:c r="E24" s="18" t="str">
+      <x:c r="E24" s="11" t="str">
         <x:v>巨匠電腦(復興路民權路口/民權路6號)</x:v>
       </x:c>
-      <x:c r="F24" s="18" t="str">
+      <x:c r="F24" s="11" t="str">
         <x:v>桃園市桃園區民權路6號</x:v>
       </x:c>
-      <x:c r="G24" s="18" t="str"/>
-    </x:row>
-    <x:row r="25">
+      <x:c r="G24" s="11"/>
+    </x:row>
+    <x:row r="25" ht="22" customHeight="1">
       <x:c r="A25" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B25" s="18" t="str">
         <x:v>S024</x:v>
       </x:c>
-      <x:c r="C25" s="18" t="str">
+      <x:c r="C25" s="11" t="str">
         <x:v>文化二路一段356號對面</x:v>
       </x:c>
-      <x:c r="D25" s="18" t="str">
+      <x:c r="D25" s="11" t="str">
         <x:v>空間樂園社區公車站</x:v>
       </x:c>
-      <x:c r="E25" s="18" t="str">
+      <x:c r="E25" s="11" t="str">
         <x:v>空間樂園社區公車站(文化二路一段356號對面)</x:v>
       </x:c>
-      <x:c r="F25" s="18" t="str">
+      <x:c r="F25" s="11" t="str">
         <x:v>新北市林口區文化二路一段356號</x:v>
       </x:c>
-      <x:c r="G25" s="18" t="str"/>
-    </x:row>
-    <x:row r="26">
+      <x:c r="G25" s="11"/>
+    </x:row>
+    <x:row r="26" ht="22" customHeight="1">
       <x:c r="A26" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B26" s="18" t="str">
         <x:v>S025</x:v>
       </x:c>
-      <x:c r="C26" s="18" t="str">
+      <x:c r="C26" s="11" t="str">
         <x:v>文化二路一段269號</x:v>
       </x:c>
-      <x:c r="D26" s="18" t="str">
+      <x:c r="D26" s="11" t="str">
         <x:v>燦坤3C 林口文化店</x:v>
       </x:c>
-      <x:c r="E26" s="18" t="str">
+      <x:c r="E26" s="11" t="str">
         <x:v>燦坤3C 林口文化店(新北市林口區文化二路一段269號)</x:v>
       </x:c>
-      <x:c r="F26" s="18" t="str">
+      <x:c r="F26" s="11" t="str">
         <x:v>新北市林口區文化二路一段269號</x:v>
       </x:c>
-      <x:c r="G26" s="18" t="str"/>
-    </x:row>
-    <x:row r="27">
+      <x:c r="G26" s="11"/>
+    </x:row>
+    <x:row r="27" ht="22" customHeight="1">
       <x:c r="A27" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B27" s="18" t="str">
         <x:v>S026</x:v>
       </x:c>
-      <x:c r="C27" s="18" t="str">
+      <x:c r="C27" s="11" t="str">
         <x:v>復興一路230號</x:v>
       </x:c>
-      <x:c r="D27" s="18" t="str">
+      <x:c r="D27" s="11" t="str">
         <x:v>玉山銀行</x:v>
       </x:c>
-      <x:c r="E27" s="18" t="str">
+      <x:c r="E27" s="11" t="str">
         <x:v>復興一路230號(玉山銀行)</x:v>
       </x:c>
-      <x:c r="F27" s="18" t="str">
+      <x:c r="F27" s="11" t="str">
         <x:v>桃園市龜山區復興一路230號</x:v>
       </x:c>
-      <x:c r="G27" s="18" t="str"/>
-    </x:row>
-    <x:row r="28">
+      <x:c r="G27" s="11"/>
+    </x:row>
+    <x:row r="28" ht="22" customHeight="1">
       <x:c r="A28" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B28" s="18" t="str">
         <x:v>S027</x:v>
       </x:c>
-      <x:c r="C28" s="18" t="str">
+      <x:c r="C28" s="11" t="str">
         <x:v>港西街4號</x:v>
       </x:c>
-      <x:c r="D28" s="18" t="str">
+      <x:c r="D28" s="11" t="str">
         <x:v>基隆市陽明海洋文化藝術館</x:v>
       </x:c>
-      <x:c r="E28" s="18" t="str">
+      <x:c r="E28" s="11" t="str">
         <x:v>基隆市陽明海洋文化藝術館(基隆市仁愛區港西街4號)</x:v>
       </x:c>
-      <x:c r="F28" s="18" t="str">
+      <x:c r="F28" s="11" t="str">
         <x:v>基隆市仁愛區港西街4號</x:v>
       </x:c>
-      <x:c r="G28" s="18" t="str"/>
-    </x:row>
-    <x:row r="29">
+      <x:c r="G28" s="11"/>
+    </x:row>
+    <x:row r="29" ht="22" customHeight="1">
       <x:c r="A29" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B29" s="18" t="str">
         <x:v>S028</x:v>
       </x:c>
-      <x:c r="C29" s="18" t="str">
+      <x:c r="C29" s="11" t="str">
         <x:v>安樂路一段2號</x:v>
       </x:c>
-      <x:c r="D29" s="18" t="str">
+      <x:c r="D29" s="11" t="str">
         <x:v>國軍基隆福利站</x:v>
       </x:c>
-      <x:c r="E29" s="18" t="str">
+      <x:c r="E29" s="11" t="str">
         <x:v>安樂路一段2號(國軍基隆福利站)</x:v>
       </x:c>
-      <x:c r="F29" s="18" t="str">
+      <x:c r="F29" s="11" t="str">
         <x:v>基隆市安樂區安樂路一段2號</x:v>
       </x:c>
-      <x:c r="G29" s="18" t="str"/>
-    </x:row>
-    <x:row r="30">
+      <x:c r="G29" s="11"/>
+    </x:row>
+    <x:row r="30" ht="22" customHeight="1">
       <x:c r="A30" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B30" s="18" t="str">
         <x:v>S029</x:v>
       </x:c>
-      <x:c r="C30" s="18" t="str">
+      <x:c r="C30" s="11" t="str">
         <x:v>安樂路二段132號</x:v>
       </x:c>
-      <x:c r="D30" s="18" t="str">
+      <x:c r="D30" s="11" t="str">
         <x:v>中華郵局 / 基隆長庚旁</x:v>
       </x:c>
-      <x:c r="E30" s="18" t="str">
+      <x:c r="E30" s="11" t="str">
         <x:v>安樂路二段132號(中華郵局/基隆長庚旁)</x:v>
       </x:c>
-      <x:c r="F30" s="18" t="str">
+      <x:c r="F30" s="11" t="str">
         <x:v>基隆市安樂區安樂路二段132號</x:v>
       </x:c>
-      <x:c r="G30" s="18" t="str"/>
-    </x:row>
-    <x:row r="31">
+      <x:c r="G30" s="11"/>
+    </x:row>
+    <x:row r="31" ht="22" customHeight="1">
       <x:c r="A31" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B31" s="18" t="str">
         <x:v>S030</x:v>
       </x:c>
-      <x:c r="C31" s="18" t="str">
+      <x:c r="C31" s="11" t="str">
         <x:v>228紀念碑</x:v>
       </x:c>
-      <x:c r="D31" s="18" t="str">
+      <x:c r="D31" s="11" t="str">
         <x:v>八堵火車站旁</x:v>
       </x:c>
-      <x:c r="E31" s="18" t="str">
+      <x:c r="E31" s="11" t="str">
         <x:v>228紀念碑(八堵火車站旁)</x:v>
       </x:c>
-      <x:c r="F31" s="18" t="str">
+      <x:c r="F31" s="11" t="str">
         <x:v>基隆市八堵火車站</x:v>
       </x:c>
-      <x:c r="G31" s="18" t="str"/>
-    </x:row>
-    <x:row r="32">
+      <x:c r="G31" s="11"/>
+    </x:row>
+    <x:row r="32" ht="22" customHeight="1">
       <x:c r="A32" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B32" s="18" t="str">
         <x:v>S031</x:v>
       </x:c>
-      <x:c r="C32" s="18" t="str">
+      <x:c r="C32" s="11" t="str">
         <x:v>崇智街2之10號</x:v>
       </x:c>
-      <x:c r="D32" s="18" t="str">
+      <x:c r="D32" s="11" t="str">
         <x:v>許家粿仔湯</x:v>
       </x:c>
-      <x:c r="E32" s="18" t="str">
+      <x:c r="E32" s="11" t="str">
         <x:v>七堵區崇智街2之10號(許家粿仔湯)</x:v>
       </x:c>
-      <x:c r="F32" s="18" t="str">
+      <x:c r="F32" s="11" t="str">
         <x:v>基隆市七堵區崇智街2之10號</x:v>
       </x:c>
-      <x:c r="G32" s="18" t="str"/>
-    </x:row>
-    <x:row r="33">
+      <x:c r="G32" s="11"/>
+    </x:row>
+    <x:row r="33" ht="22" customHeight="1">
       <x:c r="A33" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B33" s="18" t="str">
         <x:v>S032</x:v>
       </x:c>
-      <x:c r="C33" s="18" t="str">
+      <x:c r="C33" s="11" t="str">
         <x:v>百一街151號前</x:v>
       </x:c>
-      <x:c r="D33" s="18" t="str">
+      <x:c r="D33" s="11" t="str">
         <x:v>百一街口公車站牌 / 新台五路上</x:v>
       </x:c>
-      <x:c r="E33" s="18" t="str">
+      <x:c r="E33" s="11" t="str">
         <x:v>百一街口公車站牌(百一街151號前，新台五路上)</x:v>
       </x:c>
-      <x:c r="F33" s="18" t="str">
+      <x:c r="F33" s="11" t="str">
         <x:v>基隆市七堵區百一街151號</x:v>
       </x:c>
-      <x:c r="G33" s="18" t="str"/>
-    </x:row>
-    <x:row r="34">
+      <x:c r="G33" s="11"/>
+    </x:row>
+    <x:row r="34" ht="22" customHeight="1">
       <x:c r="A34" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B34" s="18" t="str">
         <x:v>S033</x:v>
       </x:c>
-      <x:c r="C34" s="18" t="str">
+      <x:c r="C34" s="11" t="str">
         <x:v>富國路102號</x:v>
       </x:c>
-      <x:c r="D34" s="18" t="str">
+      <x:c r="D34" s="11" t="str">
         <x:v>富康骨科診所</x:v>
       </x:c>
-      <x:c r="E34" s="18" t="str">
+      <x:c r="E34" s="11" t="str">
         <x:v>富國路102號(富康骨科診所)</x:v>
       </x:c>
-      <x:c r="F34" s="18" t="str">
+      <x:c r="F34" s="11" t="str">
         <x:v>新北市新莊區富國路102號</x:v>
       </x:c>
-      <x:c r="G34" s="18" t="str"/>
-    </x:row>
-    <x:row r="35">
+      <x:c r="G34" s="11"/>
+    </x:row>
+    <x:row r="35" ht="22" customHeight="1">
       <x:c r="A35" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B35" s="18" t="str">
         <x:v>S034</x:v>
       </x:c>
-      <x:c r="C35" s="18" t="str">
+      <x:c r="C35" s="11" t="str">
         <x:v>後港一路132號旁</x:v>
       </x:c>
-      <x:c r="D35" s="18" t="str">
+      <x:c r="D35" s="11" t="str">
         <x:v>過站牌變電箱</x:v>
       </x:c>
-      <x:c r="E35" s="18" t="str">
+      <x:c r="E35" s="11" t="str">
         <x:v>後港一路132號旁(過站牌變電箱)</x:v>
       </x:c>
-      <x:c r="F35" s="18" t="str">
+      <x:c r="F35" s="11" t="str">
         <x:v>新北市新莊區後港一路132號</x:v>
       </x:c>
-      <x:c r="G35" s="18" t="str"/>
-    </x:row>
-    <x:row r="36">
+      <x:c r="G35" s="11"/>
+    </x:row>
+    <x:row r="36" ht="22" customHeight="1">
       <x:c r="A36" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B36" s="18" t="str">
         <x:v>S035</x:v>
       </x:c>
-      <x:c r="C36" s="18" t="str">
+      <x:c r="C36" s="11" t="str">
         <x:v>中正路555號旁</x:v>
       </x:c>
-      <x:c r="D36" s="18" t="str">
+      <x:c r="D36" s="11" t="str">
         <x:v>近捷運輔大2號出口</x:v>
       </x:c>
-      <x:c r="E36" s="18" t="str">
+      <x:c r="E36" s="11" t="str">
         <x:v>中正路555號旁(近捷運輔大2號出口)</x:v>
       </x:c>
-      <x:c r="F36" s="18" t="str">
+      <x:c r="F36" s="11" t="str">
         <x:v>新北市新莊區中正路555號</x:v>
       </x:c>
-      <x:c r="G36" s="18" t="str"/>
-    </x:row>
-    <x:row r="37">
+      <x:c r="G36" s="11"/>
+    </x:row>
+    <x:row r="37" ht="22" customHeight="1">
       <x:c r="A37" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B37" s="18" t="str">
         <x:v>S036</x:v>
       </x:c>
-      <x:c r="C37" s="18" t="str">
+      <x:c r="C37" s="11" t="str">
         <x:v>中平路133號</x:v>
       </x:c>
-      <x:c r="D37" s="18" t="str">
+      <x:c r="D37" s="11" t="str">
         <x:v>新莊文藝中心</x:v>
       </x:c>
-      <x:c r="E37" s="18" t="str">
+      <x:c r="E37" s="11" t="str">
         <x:v>中平路133號(新莊文藝中心)</x:v>
       </x:c>
-      <x:c r="F37" s="18" t="str">
+      <x:c r="F37" s="11" t="str">
         <x:v>新北市新莊區中平路133號</x:v>
       </x:c>
-      <x:c r="G37" s="18" t="str"/>
-    </x:row>
-    <x:row r="38">
+      <x:c r="G37" s="11"/>
+    </x:row>
+    <x:row r="38" ht="22" customHeight="1">
       <x:c r="A38" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B38" s="18" t="str">
         <x:v>S037</x:v>
       </x:c>
-      <x:c r="C38" s="18" t="str">
+      <x:c r="C38" s="11" t="str">
         <x:v>思源路339號</x:v>
       </x:c>
-      <x:c r="D38" s="18" t="str">
+      <x:c r="D38" s="11" t="str">
         <x:v>合作金庫銀行</x:v>
       </x:c>
-      <x:c r="E38" s="18" t="str">
+      <x:c r="E38" s="11" t="str">
         <x:v>思源路339號(合作金庫銀行)</x:v>
       </x:c>
-      <x:c r="F38" s="18" t="str">
+      <x:c r="F38" s="11" t="str">
         <x:v>新北市新莊區思源路339號</x:v>
       </x:c>
-      <x:c r="G38" s="18" t="str"/>
-    </x:row>
-    <x:row r="39">
+      <x:c r="G38" s="11"/>
+    </x:row>
+    <x:row r="39" ht="22" customHeight="1">
       <x:c r="A39" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B39" s="18" t="str">
         <x:v>S038</x:v>
       </x:c>
-      <x:c r="C39" s="18" t="str">
+      <x:c r="C39" s="11" t="str">
         <x:v>新泰路370號</x:v>
       </x:c>
-      <x:c r="D39" s="18" t="str">
+      <x:c r="D39" s="11" t="str">
         <x:v>勝博五金</x:v>
       </x:c>
-      <x:c r="E39" s="18" t="str">
+      <x:c r="E39" s="11" t="str">
         <x:v>新泰路370號(勝博五金)</x:v>
       </x:c>
-      <x:c r="F39" s="18" t="str">
+      <x:c r="F39" s="11" t="str">
         <x:v>新北市新莊區新泰路370號</x:v>
       </x:c>
-      <x:c r="G39" s="18" t="str"/>
-    </x:row>
-    <x:row r="40">
+      <x:c r="G39" s="11"/>
+    </x:row>
+    <x:row r="40" ht="22" customHeight="1">
       <x:c r="A40" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B40" s="18" t="str">
         <x:v>S039</x:v>
       </x:c>
-      <x:c r="C40" s="18" t="str">
+      <x:c r="C40" s="11" t="str">
         <x:v>公園一路16號</x:v>
       </x:c>
-      <x:c r="D40" s="18" t="str">
+      <x:c r="D40" s="11" t="str">
         <x:v>中欣旅行社</x:v>
       </x:c>
-      <x:c r="E40" s="18" t="str">
+      <x:c r="E40" s="11" t="str">
         <x:v>公園一路16號(中欣旅行社)</x:v>
       </x:c>
-      <x:c r="F40" s="18" t="str">
+      <x:c r="F40" s="11" t="str">
         <x:v>新北市新莊區公園一路16號</x:v>
       </x:c>
-      <x:c r="G40" s="18" t="str"/>
-    </x:row>
-    <x:row r="41">
+      <x:c r="G40" s="11"/>
+    </x:row>
+    <x:row r="41" ht="22" customHeight="1">
       <x:c r="A41" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B41" s="18" t="str">
         <x:v>S040</x:v>
       </x:c>
-      <x:c r="C41" s="18" t="str">
+      <x:c r="C41" s="11" t="str">
         <x:v>公園一路146號</x:v>
       </x:c>
-      <x:c r="D41" s="18" t="str">
+      <x:c r="D41" s="11" t="str">
         <x:v>長峰珠算補習班</x:v>
       </x:c>
-      <x:c r="E41" s="18" t="str">
+      <x:c r="E41" s="11" t="str">
         <x:v>公園一路146號(長峰珠算補習班)</x:v>
       </x:c>
-      <x:c r="F41" s="18" t="str">
+      <x:c r="F41" s="11" t="str">
         <x:v>新北市新莊區公園一路146號</x:v>
       </x:c>
-      <x:c r="G41" s="18" t="str"/>
-    </x:row>
-    <x:row r="42">
+      <x:c r="G41" s="11"/>
+    </x:row>
+    <x:row r="42" ht="22" customHeight="1">
       <x:c r="A42" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B42" s="18" t="str">
         <x:v>S041</x:v>
       </x:c>
-      <x:c r="C42" s="18" t="str">
+      <x:c r="C42" s="11" t="str">
         <x:v>北投路二段 / 大業路452巷口</x:v>
       </x:c>
-      <x:c r="D42" s="18" t="str">
+      <x:c r="D42" s="11" t="str">
         <x:v>北投3號廣場公園</x:v>
       </x:c>
-      <x:c r="E42" s="18" t="str">
+      <x:c r="E42" s="11" t="str">
         <x:v>北投路二段與大業路452巷口(北投3號廣場公園)</x:v>
       </x:c>
-      <x:c r="F42" s="18" t="str">
+      <x:c r="F42" s="11" t="str">
         <x:v>台北市北投區北投路二段 大業路452巷口</x:v>
       </x:c>
-      <x:c r="G42" s="18" t="str"/>
-    </x:row>
-    <x:row r="43">
+      <x:c r="G42" s="11"/>
+    </x:row>
+    <x:row r="43" ht="22" customHeight="1">
       <x:c r="A43" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B43" s="18" t="str">
         <x:v>S042</x:v>
       </x:c>
-      <x:c r="C43" s="18" t="str">
+      <x:c r="C43" s="11" t="str">
         <x:v>北安路537之2號</x:v>
       </x:c>
-      <x:c r="D43" s="18" t="str">
+      <x:c r="D43" s="11" t="str">
         <x:v>日昌眼鏡</x:v>
       </x:c>
-      <x:c r="E43" s="18" t="str">
+      <x:c r="E43" s="11" t="str">
         <x:v>北安路537之2號(日昌眼鏡)</x:v>
       </x:c>
-      <x:c r="F43" s="18" t="str">
+      <x:c r="F43" s="11" t="str">
         <x:v>台北市中山區北安路537之2號</x:v>
       </x:c>
-      <x:c r="G43" s="18" t="str"/>
-    </x:row>
-    <x:row r="44">
+      <x:c r="G43" s="11"/>
+    </x:row>
+    <x:row r="44" ht="22" customHeight="1">
       <x:c r="A44" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B44" s="18" t="str">
         <x:v>S043</x:v>
       </x:c>
-      <x:c r="C44" s="18" t="str">
+      <x:c r="C44" s="11" t="str">
         <x:v>捷運劍潭站高架橋下</x:v>
       </x:c>
-      <x:c r="D44" s="18" t="str">
+      <x:c r="D44" s="11" t="str">
         <x:v>劍潭路上</x:v>
       </x:c>
-      <x:c r="E44" s="18" t="str">
+      <x:c r="E44" s="11" t="str">
         <x:v>捷運劍潭站高架橋下(劍潭路上)</x:v>
       </x:c>
-      <x:c r="F44" s="18" t="str">
+      <x:c r="F44" s="11" t="str">
         <x:v>台北市捷運劍潭站</x:v>
       </x:c>
-      <x:c r="G44" s="18" t="str"/>
-    </x:row>
-    <x:row r="45">
+      <x:c r="G44" s="11"/>
+    </x:row>
+    <x:row r="45" ht="22" customHeight="1">
       <x:c r="A45" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B45" s="18" t="str">
         <x:v>S044</x:v>
       </x:c>
-      <x:c r="C45" s="18" t="str">
+      <x:c r="C45" s="11" t="str">
         <x:v>芝山捷運站1號出口</x:v>
       </x:c>
-      <x:c r="D45" s="18" t="str">
+      <x:c r="D45" s="11" t="str">
         <x:v>福國路 / 捷運橋下</x:v>
       </x:c>
-      <x:c r="E45" s="18" t="str">
+      <x:c r="E45" s="11" t="str">
         <x:v>福國路芝山捷運站1號出口(捷運橋下)</x:v>
       </x:c>
-      <x:c r="F45" s="18" t="str">
+      <x:c r="F45" s="11" t="str">
         <x:v>台北市捷運芝山站1號出口</x:v>
       </x:c>
-      <x:c r="G45" s="18" t="str"/>
-    </x:row>
-    <x:row r="46">
+      <x:c r="G45" s="11"/>
+    </x:row>
+    <x:row r="46" ht="22" customHeight="1">
       <x:c r="A46" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B46" s="18" t="str">
         <x:v>S045</x:v>
       </x:c>
-      <x:c r="C46" s="18" t="str">
+      <x:c r="C46" s="11" t="str">
         <x:v>中正路362號</x:v>
       </x:c>
-      <x:c r="D46" s="18" t="str">
+      <x:c r="D46" s="11" t="str">
         <x:v>歐霸韓式料理</x:v>
       </x:c>
-      <x:c r="E46" s="18" t="str">
+      <x:c r="E46" s="11" t="str">
         <x:v>中正路362號(歐霸韓式料理)</x:v>
       </x:c>
-      <x:c r="F46" s="18" t="str">
+      <x:c r="F46" s="11" t="str">
         <x:v>台北市士林區中正路362號</x:v>
       </x:c>
-      <x:c r="G46" s="18" t="str"/>
-    </x:row>
-    <x:row r="47">
+      <x:c r="G46" s="11"/>
+    </x:row>
+    <x:row r="47" ht="22" customHeight="1">
       <x:c r="A47" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B47" s="18" t="str">
         <x:v>S046</x:v>
       </x:c>
-      <x:c r="C47" s="18" t="str">
+      <x:c r="C47" s="11" t="str">
         <x:v>石牌路二段126號</x:v>
       </x:c>
-      <x:c r="D47" s="18" t="str">
+      <x:c r="D47" s="11" t="str">
         <x:v>麥當勞</x:v>
       </x:c>
-      <x:c r="E47" s="18" t="str">
+      <x:c r="E47" s="11" t="str">
         <x:v>石牌路二段126號(麥當勞)</x:v>
       </x:c>
-      <x:c r="F47" s="18" t="str">
+      <x:c r="F47" s="11" t="str">
         <x:v>台北市北投區石牌路二段126號</x:v>
       </x:c>
-      <x:c r="G47" s="18" t="str"/>
-    </x:row>
-    <x:row r="48">
+      <x:c r="G47" s="11"/>
+    </x:row>
+    <x:row r="48" ht="22" customHeight="1">
       <x:c r="A48" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B48" s="18" t="str">
         <x:v>S047</x:v>
       </x:c>
-      <x:c r="C48" s="18" t="str">
+      <x:c r="C48" s="11" t="str">
         <x:v>天母東路8號</x:v>
       </x:c>
-      <x:c r="D48" s="18" t="str"/>
-      <x:c r="E48" s="18" t="str">
+      <x:c r="D48" s="11"/>
+      <x:c r="E48" s="11" t="str">
         <x:v>天母東路8號</x:v>
       </x:c>
-      <x:c r="F48" s="18" t="str">
+      <x:c r="F48" s="11" t="str">
         <x:v>台北市士林區天母東路8號</x:v>
       </x:c>
-      <x:c r="G48" s="18" t="str"/>
-    </x:row>
-    <x:row r="49">
+      <x:c r="G48" s="11"/>
+    </x:row>
+    <x:row r="49" ht="22" customHeight="1">
       <x:c r="A49" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B49" s="18" t="str">
         <x:v>S048</x:v>
       </x:c>
-      <x:c r="C49" s="18" t="str">
+      <x:c r="C49" s="11" t="str">
         <x:v>忠誠路二段76巷口</x:v>
       </x:c>
-      <x:c r="D49" s="18" t="str">
+      <x:c r="D49" s="11" t="str">
         <x:v>梁社漢排骨店</x:v>
       </x:c>
-      <x:c r="E49" s="18" t="str">
+      <x:c r="E49" s="11" t="str">
         <x:v>忠誠路二段76巷口(梁社漢排骨店)</x:v>
       </x:c>
-      <x:c r="F49" s="18" t="str">
+      <x:c r="F49" s="11" t="str">
         <x:v>台北市士林區忠誠路二段76巷口</x:v>
       </x:c>
-      <x:c r="G49" s="18" t="str"/>
-    </x:row>
-    <x:row r="50">
+      <x:c r="G49" s="11"/>
+    </x:row>
+    <x:row r="50" ht="22" customHeight="1">
       <x:c r="A50" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
       <x:c r="B50" s="18" t="str">
         <x:v>S049</x:v>
       </x:c>
-      <x:c r="C50" s="18" t="str">
+      <x:c r="C50" s="11" t="str">
         <x:v>忠誠路一段138號</x:v>
       </x:c>
-      <x:c r="D50" s="18" t="str">
+      <x:c r="D50" s="11" t="str">
         <x:v>橡木桶</x:v>
       </x:c>
-      <x:c r="E50" s="18" t="str">
+      <x:c r="E50" s="11" t="str">
         <x:v>忠誠路一段138號(橡木桶)</x:v>
       </x:c>
-      <x:c r="F50" s="18" t="str">
+      <x:c r="F50" s="11" t="str">
         <x:v>台北市士林區忠誠路一段138號</x:v>
       </x:c>
-      <x:c r="G50" s="18" t="str"/>
+      <x:c r="G50" s="11"/>
+    </x:row>
+    <x:row r="51" ht="22" customHeight="1">
+      <x:c r="A51" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B51" s="18" t="str">
+        <x:v>S050</x:v>
+      </x:c>
+      <x:c r="C51" s="11" t="str">
+        <x:v>西安街二段283號</x:v>
+      </x:c>
+      <x:c r="D51" s="11" t="str">
+        <x:v>永慶房屋</x:v>
+      </x:c>
+      <x:c r="E51" s="11" t="str">
+        <x:v>西安街二段283號(永慶房屋)</x:v>
+      </x:c>
+      <x:c r="F51" s="11" t="str">
+        <x:v>台北市北投區西安街二段283號</x:v>
+      </x:c>
+      <x:c r="G51" s="11"/>
+    </x:row>
+    <x:row r="52" ht="22" customHeight="1">
+      <x:c r="A52" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B52" s="18" t="str">
+        <x:v>S051</x:v>
+      </x:c>
+      <x:c r="C52" s="11" t="str">
+        <x:v>西安街二段85號旁</x:v>
+      </x:c>
+      <x:c r="D52" s="11" t="str">
+        <x:v>石牌國中公車站牌</x:v>
+      </x:c>
+      <x:c r="E52" s="11" t="str">
+        <x:v>石牌國中公車站牌(西安街二段85號旁)</x:v>
+      </x:c>
+      <x:c r="F52" s="11" t="str">
+        <x:v>台北市北投區西安街二段85號</x:v>
+      </x:c>
+      <x:c r="G52" s="11"/>
+    </x:row>
+    <x:row r="53" ht="22" customHeight="1">
+      <x:c r="A53" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B53" s="18" t="str">
+        <x:v>S052</x:v>
+      </x:c>
+      <x:c r="C53" s="11" t="str">
+        <x:v>重慶北路四段117號</x:v>
+      </x:c>
+      <x:c r="D53" s="11" t="str">
+        <x:v>全國加油站旁</x:v>
+      </x:c>
+      <x:c r="E53" s="11" t="str">
+        <x:v>重慶北路四段117號(全國加油站旁)</x:v>
+      </x:c>
+      <x:c r="F53" s="11" t="str">
+        <x:v>台北市士林區重慶北路四段117號</x:v>
+      </x:c>
+      <x:c r="G53" s="11"/>
+    </x:row>
+    <x:row r="54" ht="22" customHeight="1">
+      <x:c r="A54" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B54" s="18" t="str">
+        <x:v>S053</x:v>
+      </x:c>
+      <x:c r="C54" s="11" t="str">
+        <x:v>植福路11號</x:v>
+      </x:c>
+      <x:c r="D54" s="11" t="str">
+        <x:v>中山21號廣場</x:v>
+      </x:c>
+      <x:c r="E54" s="11" t="str">
+        <x:v>植福路11號(中山21號廣場)</x:v>
+      </x:c>
+      <x:c r="F54" s="11" t="str">
+        <x:v>台北市中山區植福路11號</x:v>
+      </x:c>
+      <x:c r="G54" s="11"/>
+    </x:row>
+    <x:row r="55" ht="22" customHeight="1">
+      <x:c r="A55" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B55" s="18" t="str">
+        <x:v>S054</x:v>
+      </x:c>
+      <x:c r="C55" s="11" t="str">
+        <x:v>內湖路一段250號</x:v>
+      </x:c>
+      <x:c r="D55" s="11" t="str">
+        <x:v>陽信銀行</x:v>
+      </x:c>
+      <x:c r="E55" s="11" t="str">
+        <x:v>內湖路一段250號(陽信銀行)</x:v>
+      </x:c>
+      <x:c r="F55" s="11" t="str">
+        <x:v>台北市內湖區內湖路一段250號</x:v>
+      </x:c>
+      <x:c r="G55" s="11"/>
+    </x:row>
+    <x:row r="56" ht="22" customHeight="1">
+      <x:c r="A56" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B56" s="18" t="str">
+        <x:v>S055</x:v>
+      </x:c>
+      <x:c r="C56" s="11" t="str">
+        <x:v>內湖路一段370號</x:v>
+      </x:c>
+      <x:c r="D56" s="11" t="str">
+        <x:v>麗山街公車站</x:v>
+      </x:c>
+      <x:c r="E56" s="11" t="str">
+        <x:v>內湖路一段370號(麗山街公車站)</x:v>
+      </x:c>
+      <x:c r="F56" s="11" t="str">
+        <x:v>台北市內湖區內湖路一段370號</x:v>
+      </x:c>
+      <x:c r="G56" s="11"/>
+    </x:row>
+    <x:row r="57" ht="22" customHeight="1">
+      <x:c r="A57" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B57" s="18" t="str">
+        <x:v>S056</x:v>
+      </x:c>
+      <x:c r="C57" s="11" t="str">
+        <x:v>文德路220巷口前</x:v>
+      </x:c>
+      <x:c r="D57" s="11" t="str">
+        <x:v>內湖高中公車站牌</x:v>
+      </x:c>
+      <x:c r="E57" s="11" t="str">
+        <x:v>內湖高中公車站牌(文德路220巷口前)</x:v>
+      </x:c>
+      <x:c r="F57" s="11" t="str">
+        <x:v>台北市內湖區文德路220巷口</x:v>
+      </x:c>
+      <x:c r="G57" s="11"/>
+    </x:row>
+    <x:row r="58" ht="22" customHeight="1">
+      <x:c r="A58" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B58" s="18" t="str">
+        <x:v>S057</x:v>
+      </x:c>
+      <x:c r="C58" s="11" t="str">
+        <x:v>文德路102號</x:v>
+      </x:c>
+      <x:c r="D58" s="11" t="str">
+        <x:v>大樹連鎖藥局</x:v>
+      </x:c>
+      <x:c r="E58" s="11" t="str">
+        <x:v>文德路102號(大樹連鎖藥局)</x:v>
+      </x:c>
+      <x:c r="F58" s="11" t="str">
+        <x:v>台北市內湖區文德路102號</x:v>
+      </x:c>
+      <x:c r="G58" s="11"/>
+    </x:row>
+    <x:row r="59" ht="22" customHeight="1">
+      <x:c r="A59" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B59" s="18" t="str">
+        <x:v>S058</x:v>
+      </x:c>
+      <x:c r="C59" s="11" t="str">
+        <x:v>成功路四段141號</x:v>
+      </x:c>
+      <x:c r="D59" s="11"/>
+      <x:c r="E59" s="11" t="str">
+        <x:v>成功路四段141號</x:v>
+      </x:c>
+      <x:c r="F59" s="11" t="str">
+        <x:v>台北市內湖區成功路四段141號</x:v>
+      </x:c>
+      <x:c r="G59" s="11"/>
+    </x:row>
+    <x:row r="60" ht="22" customHeight="1">
+      <x:c r="A60" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B60" s="18" t="str">
+        <x:v>S059</x:v>
+      </x:c>
+      <x:c r="C60" s="11" t="str">
+        <x:v>民權東路六段493號</x:v>
+      </x:c>
+      <x:c r="D60" s="11"/>
+      <x:c r="E60" s="11" t="str">
+        <x:v>民權東路六段493號</x:v>
+      </x:c>
+      <x:c r="F60" s="11" t="str">
+        <x:v>台北市內湖區民權東路六段493號</x:v>
+      </x:c>
+      <x:c r="G60" s="11"/>
+    </x:row>
+    <x:row r="61" ht="22" customHeight="1">
+      <x:c r="A61" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B61" s="18" t="str">
+        <x:v>S060</x:v>
+      </x:c>
+      <x:c r="C61" s="11" t="str">
+        <x:v>民權東路六段150號</x:v>
+      </x:c>
+      <x:c r="D61" s="11" t="str">
+        <x:v>聯邦銀行</x:v>
+      </x:c>
+      <x:c r="E61" s="11" t="str">
+        <x:v>民權東路六段150號(聯邦銀行)</x:v>
+      </x:c>
+      <x:c r="F61" s="11" t="str">
+        <x:v>台北市內湖區民權東路六段150號</x:v>
+      </x:c>
+      <x:c r="G61" s="11"/>
+    </x:row>
+    <x:row r="62" ht="22" customHeight="1">
+      <x:c r="A62" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B62" s="18" t="str">
+        <x:v>S061</x:v>
+      </x:c>
+      <x:c r="C62" s="11" t="str">
+        <x:v>民權東路一段24號</x:v>
+      </x:c>
+      <x:c r="D62" s="11" t="str">
+        <x:v>英皇牙醫</x:v>
+      </x:c>
+      <x:c r="E62" s="11" t="str">
+        <x:v>民權東路一段24號(英皇牙醫)</x:v>
+      </x:c>
+      <x:c r="F62" s="11" t="str">
+        <x:v>台北市中山區民權東路一段24號</x:v>
+      </x:c>
+      <x:c r="G62" s="11"/>
+    </x:row>
+    <x:row r="63" ht="22" customHeight="1">
+      <x:c r="A63" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B63" s="18" t="str">
+        <x:v>S062</x:v>
+      </x:c>
+      <x:c r="C63" s="11" t="str">
+        <x:v>民權東路二段48號</x:v>
+      </x:c>
+      <x:c r="D63" s="11"/>
+      <x:c r="E63" s="11" t="str">
+        <x:v>民權東路二段48號</x:v>
+      </x:c>
+      <x:c r="F63" s="11" t="str">
+        <x:v>台北市中山區民權東路二段48號</x:v>
+      </x:c>
+      <x:c r="G63" s="11"/>
+    </x:row>
+    <x:row r="64" ht="22" customHeight="1">
+      <x:c r="A64" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B64" s="18" t="str">
+        <x:v>S063</x:v>
+      </x:c>
+      <x:c r="C64" s="11" t="str">
+        <x:v>建國北路二段262號</x:v>
+      </x:c>
+      <x:c r="D64" s="11" t="str">
+        <x:v>金牌鴻記名產館</x:v>
+      </x:c>
+      <x:c r="E64" s="11" t="str">
+        <x:v>建國北路二段262號(金牌鴻記名產館)</x:v>
+      </x:c>
+      <x:c r="F64" s="11" t="str">
+        <x:v>台北市中山區建國北路二段262號</x:v>
+      </x:c>
+      <x:c r="G64" s="11"/>
+    </x:row>
+    <x:row r="65" ht="22" customHeight="1">
+      <x:c r="A65" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B65" s="18" t="str">
+        <x:v>S064</x:v>
+      </x:c>
+      <x:c r="C65" s="11" t="str">
+        <x:v>建國北路三段39號</x:v>
+      </x:c>
+      <x:c r="D65" s="11" t="str">
+        <x:v>榮星花園游泳池</x:v>
+      </x:c>
+      <x:c r="E65" s="11" t="str">
+        <x:v>建國北路三段39號(榮星花園游泳池)</x:v>
+      </x:c>
+      <x:c r="F65" s="11" t="str">
+        <x:v>台北市中山區建國北路三段39號</x:v>
+      </x:c>
+      <x:c r="G65" s="11"/>
+    </x:row>
+    <x:row r="66" ht="22" customHeight="1">
+      <x:c r="A66" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B66" s="18" t="str">
+        <x:v>S065</x:v>
+      </x:c>
+      <x:c r="C66" s="11" t="str">
+        <x:v>民生東路三段8號</x:v>
+      </x:c>
+      <x:c r="D66" s="11" t="str">
+        <x:v>合江街口公車站牌 / 南山民生大樓</x:v>
+      </x:c>
+      <x:c r="E66" s="11" t="str">
+        <x:v>合江街口公車站牌(民生東路三段8號/南山民生大樓)</x:v>
+      </x:c>
+      <x:c r="F66" s="11" t="str">
+        <x:v>台北市中山區民生東路三段8號</x:v>
+      </x:c>
+      <x:c r="G66" s="11"/>
+    </x:row>
+    <x:row r="67" ht="22" customHeight="1">
+      <x:c r="A67" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B67" s="18" t="str">
+        <x:v>S066</x:v>
+      </x:c>
+      <x:c r="C67" s="11" t="str">
+        <x:v>民生東路三段86巷口</x:v>
+      </x:c>
+      <x:c r="D67" s="11" t="str">
+        <x:v>台北大學(台北校區)公車站牌</x:v>
+      </x:c>
+      <x:c r="E67" s="11" t="str">
+        <x:v>台北大學(台北校區)公車站牌(民生東路三段86巷口)</x:v>
+      </x:c>
+      <x:c r="F67" s="11" t="str">
+        <x:v>台北市中山區民生東路三段86巷口</x:v>
+      </x:c>
+      <x:c r="G67" s="11"/>
+    </x:row>
+    <x:row r="68" ht="22" customHeight="1">
+      <x:c r="A68" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B68" s="18" t="str">
+        <x:v>S067</x:v>
+      </x:c>
+      <x:c r="C68" s="11" t="str">
+        <x:v>民生東路三段138號</x:v>
+      </x:c>
+      <x:c r="D68" s="11" t="str">
+        <x:v>富邦銀行</x:v>
+      </x:c>
+      <x:c r="E68" s="11" t="str">
+        <x:v>民生東路三段138號(富邦銀行)</x:v>
+      </x:c>
+      <x:c r="F68" s="11" t="str">
+        <x:v>台北市松山區民生東路三段138號</x:v>
+      </x:c>
+      <x:c r="G68" s="11"/>
+    </x:row>
+    <x:row r="69" ht="22" customHeight="1">
+      <x:c r="A69" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B69" s="18" t="str">
+        <x:v>S068</x:v>
+      </x:c>
+      <x:c r="C69" s="11" t="str">
+        <x:v>民生東路五段8號</x:v>
+      </x:c>
+      <x:c r="D69" s="11" t="str">
+        <x:v>7-11</x:v>
+      </x:c>
+      <x:c r="E69" s="11" t="str">
+        <x:v>民生東路五段8號(7-11)</x:v>
+      </x:c>
+      <x:c r="F69" s="11" t="str">
+        <x:v>台北市松山區民生東路五段8號</x:v>
+      </x:c>
+      <x:c r="G69" s="11"/>
+    </x:row>
+    <x:row r="70" ht="22" customHeight="1">
+      <x:c r="A70" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B70" s="18" t="str">
+        <x:v>S069</x:v>
+      </x:c>
+      <x:c r="C70" s="11" t="str">
+        <x:v>民生東路五段182號</x:v>
+      </x:c>
+      <x:c r="D70" s="11" t="str">
+        <x:v>恩瑞眼鏡</x:v>
+      </x:c>
+      <x:c r="E70" s="11" t="str">
+        <x:v>民生東路五段182號(恩瑞眼鏡)</x:v>
+      </x:c>
+      <x:c r="F70" s="11" t="str">
+        <x:v>台北市松山區民生東路五段182號</x:v>
+      </x:c>
+      <x:c r="G70" s="11"/>
+    </x:row>
+    <x:row r="71" ht="22" customHeight="1">
+      <x:c r="A71" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B71" s="18" t="str">
+        <x:v>S070</x:v>
+      </x:c>
+      <x:c r="C71" s="11" t="str">
+        <x:v>南京東路一段52號</x:v>
+      </x:c>
+      <x:c r="D71" s="11" t="str">
+        <x:v>日藥本舖</x:v>
+      </x:c>
+      <x:c r="E71" s="11" t="str">
+        <x:v>南京東路一段52號(日藥本舖)</x:v>
+      </x:c>
+      <x:c r="F71" s="11" t="str">
+        <x:v>台北市中山區南京東路一段52號</x:v>
+      </x:c>
+      <x:c r="G71" s="11"/>
+    </x:row>
+    <x:row r="72" ht="22" customHeight="1">
+      <x:c r="A72" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B72" s="18" t="str">
+        <x:v>S071</x:v>
+      </x:c>
+      <x:c r="C72" s="11" t="str">
+        <x:v>南京東路二段176號</x:v>
+      </x:c>
+      <x:c r="D72" s="11" t="str">
+        <x:v>詹記麻辣火鍋</x:v>
+      </x:c>
+      <x:c r="E72" s="11" t="str">
+        <x:v>南京東路二段176號(詹記麻辣火鍋)</x:v>
+      </x:c>
+      <x:c r="F72" s="11" t="str">
+        <x:v>台北市中山區南京東路二段176號</x:v>
+      </x:c>
+      <x:c r="G72" s="11"/>
+    </x:row>
+    <x:row r="73" ht="22" customHeight="1">
+      <x:c r="A73" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B73" s="18" t="str">
+        <x:v>S072</x:v>
+      </x:c>
+      <x:c r="C73" s="11" t="str">
+        <x:v>南京東路三段270號</x:v>
+      </x:c>
+      <x:c r="D73" s="11" t="str">
+        <x:v>台實大樓</x:v>
+      </x:c>
+      <x:c r="E73" s="11" t="str">
+        <x:v>南京東路三段270號(台實大樓)</x:v>
+      </x:c>
+      <x:c r="F73" s="11" t="str">
+        <x:v>台北市松山區南京東路三段270號</x:v>
+      </x:c>
+      <x:c r="G73" s="11"/>
+    </x:row>
+    <x:row r="74" ht="22" customHeight="1">
+      <x:c r="A74" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B74" s="18" t="str">
+        <x:v>S073</x:v>
+      </x:c>
+      <x:c r="C74" s="11" t="str">
+        <x:v>南京東路四段126號</x:v>
+      </x:c>
+      <x:c r="D74" s="11" t="str">
+        <x:v>國泰世華</x:v>
+      </x:c>
+      <x:c r="E74" s="11" t="str">
+        <x:v>南京東路四段126號(國泰世華)</x:v>
+      </x:c>
+      <x:c r="F74" s="11" t="str">
+        <x:v>台北市松山區南京東路四段126號</x:v>
+      </x:c>
+      <x:c r="G74" s="11"/>
+    </x:row>
+    <x:row r="75" ht="22" customHeight="1">
+      <x:c r="A75" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B75" s="18" t="str">
+        <x:v>S074</x:v>
+      </x:c>
+      <x:c r="C75" s="11" t="str">
+        <x:v>南京東路五段60號</x:v>
+      </x:c>
+      <x:c r="D75" s="11" t="str">
+        <x:v>日藥本舖</x:v>
+      </x:c>
+      <x:c r="E75" s="11" t="str">
+        <x:v>南京東路五段60號(日藥本舖)</x:v>
+      </x:c>
+      <x:c r="F75" s="11" t="str">
+        <x:v>台北市松山區南京東路五段60號</x:v>
+      </x:c>
+      <x:c r="G75" s="11"/>
+    </x:row>
+    <x:row r="76" ht="22" customHeight="1">
+      <x:c r="A76" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B76" s="18" t="str">
+        <x:v>S075</x:v>
+      </x:c>
+      <x:c r="C76" s="11" t="str">
+        <x:v>南京東路五段256號</x:v>
+      </x:c>
+      <x:c r="D76" s="11" t="str">
+        <x:v>周牙醫</x:v>
+      </x:c>
+      <x:c r="E76" s="11" t="str">
+        <x:v>南京東路五段256號(周牙醫)</x:v>
+      </x:c>
+      <x:c r="F76" s="11" t="str">
+        <x:v>台北市松山區南京東路五段256號</x:v>
+      </x:c>
+      <x:c r="G76" s="11"/>
+    </x:row>
+    <x:row r="77" ht="22" customHeight="1">
+      <x:c r="A77" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B77" s="18" t="str">
+        <x:v>S076</x:v>
+      </x:c>
+      <x:c r="C77" s="11" t="str">
+        <x:v>八德路四段778號</x:v>
+      </x:c>
+      <x:c r="D77" s="11" t="str">
+        <x:v>7-11</x:v>
+      </x:c>
+      <x:c r="E77" s="11" t="str">
+        <x:v>八德路四段778號(7-11)</x:v>
+      </x:c>
+      <x:c r="F77" s="11" t="str">
+        <x:v>台北市南港區八德路四段778號</x:v>
+      </x:c>
+      <x:c r="G77" s="11"/>
+    </x:row>
+    <x:row r="78" ht="22" customHeight="1">
+      <x:c r="A78" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B78" s="18" t="str">
+        <x:v>S077</x:v>
+      </x:c>
+      <x:c r="C78" s="11" t="str">
+        <x:v>中華路一段67號</x:v>
+      </x:c>
+      <x:c r="D78" s="11" t="str">
+        <x:v>飛飛軍警百貨旁公車站牌</x:v>
+      </x:c>
+      <x:c r="E78" s="11" t="str">
+        <x:v>中正區中華路一段67號(飛飛軍警百貨旁公車站牌)</x:v>
+      </x:c>
+      <x:c r="F78" s="11" t="str">
+        <x:v>台北市中正區中華路一段67號</x:v>
+      </x:c>
+      <x:c r="G78" s="11"/>
+    </x:row>
+    <x:row r="79" ht="22" customHeight="1">
+      <x:c r="A79" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B79" s="18" t="str">
+        <x:v>S078</x:v>
+      </x:c>
+      <x:c r="C79" s="11" t="str">
+        <x:v>忠孝東路二段96號前</x:v>
+      </x:c>
+      <x:c r="D79" s="11" t="str">
+        <x:v>忠孝國小公車站牌</x:v>
+      </x:c>
+      <x:c r="E79" s="11" t="str">
+        <x:v>忠孝國小公車站牌(忠孝東路二段96號前)</x:v>
+      </x:c>
+      <x:c r="F79" s="11" t="str">
+        <x:v>台北市中正區忠孝東路二段96號</x:v>
+      </x:c>
+      <x:c r="G79" s="11"/>
+    </x:row>
+    <x:row r="80" ht="22" customHeight="1">
+      <x:c r="A80" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B80" s="18" t="str">
+        <x:v>S079</x:v>
+      </x:c>
+      <x:c r="C80" s="11" t="str">
+        <x:v>忠孝東路三段242號前</x:v>
+      </x:c>
+      <x:c r="D80" s="11" t="str">
+        <x:v>懷生國中公車站牌</x:v>
+      </x:c>
+      <x:c r="E80" s="11" t="str">
+        <x:v>懷生國中公車站牌(忠孝東路三段242號前)</x:v>
+      </x:c>
+      <x:c r="F80" s="11" t="str">
+        <x:v>台北市大安區忠孝東路三段242號</x:v>
+      </x:c>
+      <x:c r="G80" s="11"/>
+    </x:row>
+    <x:row r="81" ht="22" customHeight="1">
+      <x:c r="A81" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B81" s="18" t="str">
+        <x:v>S080</x:v>
+      </x:c>
+      <x:c r="C81" s="11" t="str">
+        <x:v>忠孝東路四段200號</x:v>
+      </x:c>
+      <x:c r="D81" s="11" t="str">
+        <x:v>明曜百貨</x:v>
+      </x:c>
+      <x:c r="E81" s="11" t="str">
+        <x:v>忠孝東路四段200號(明曜百貨)</x:v>
+      </x:c>
+      <x:c r="F81" s="11" t="str">
+        <x:v>台北市大安區忠孝東路四段200號</x:v>
+      </x:c>
+      <x:c r="G81" s="11"/>
+    </x:row>
+    <x:row r="82" ht="22" customHeight="1">
+      <x:c r="A82" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B82" s="18" t="str">
+        <x:v>S081</x:v>
+      </x:c>
+      <x:c r="C82" s="11" t="str">
+        <x:v>光復南路262號</x:v>
+      </x:c>
+      <x:c r="D82" s="11" t="str">
+        <x:v>7-11</x:v>
+      </x:c>
+      <x:c r="E82" s="11" t="str">
+        <x:v>光復南路262號(7-11)</x:v>
+      </x:c>
+      <x:c r="F82" s="11" t="str">
+        <x:v>台北市大安區光復南路262號</x:v>
+      </x:c>
+      <x:c r="G82" s="11"/>
+    </x:row>
+    <x:row r="83" ht="22" customHeight="1">
+      <x:c r="A83" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B83" s="18" t="str">
+        <x:v>S082</x:v>
+      </x:c>
+      <x:c r="C83" s="11" t="str">
+        <x:v>信義路四段458號</x:v>
+      </x:c>
+      <x:c r="D83" s="11" t="str">
+        <x:v>華南銀行</x:v>
+      </x:c>
+      <x:c r="E83" s="11" t="str">
+        <x:v>信義路四段458號(華南銀行)</x:v>
+      </x:c>
+      <x:c r="F83" s="11" t="str">
+        <x:v>台北市信義區信義路四段458號</x:v>
+      </x:c>
+      <x:c r="G83" s="11"/>
+    </x:row>
+    <x:row r="84" ht="22" customHeight="1">
+      <x:c r="A84" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B84" s="18" t="str">
+        <x:v>S083</x:v>
+      </x:c>
+      <x:c r="C84" s="11" t="str">
+        <x:v>信義路五段108號前</x:v>
+      </x:c>
+      <x:c r="D84" s="11" t="str">
+        <x:v>信義松仁路口公車站牌</x:v>
+      </x:c>
+      <x:c r="E84" s="11" t="str">
+        <x:v>信義松仁路口公車站牌(信義路五段108號前)</x:v>
+      </x:c>
+      <x:c r="F84" s="11" t="str">
+        <x:v>台北市信義區信義路五段108號</x:v>
+      </x:c>
+      <x:c r="G84" s="11"/>
+    </x:row>
+    <x:row r="85" ht="22" customHeight="1">
+      <x:c r="A85" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B85" s="18" t="str">
+        <x:v>S084</x:v>
+      </x:c>
+      <x:c r="C85" s="11" t="str">
+        <x:v>忠孝東路五段506號</x:v>
+      </x:c>
+      <x:c r="D85" s="11" t="str">
+        <x:v>POLAR BEAR 北極熊-永春門市</x:v>
+      </x:c>
+      <x:c r="E85" s="11" t="str">
+        <x:v>忠孝東路五段506號(POLAR BEAR 北極熊-永春門市)</x:v>
+      </x:c>
+      <x:c r="F85" s="11" t="str">
+        <x:v>台北市信義區忠孝東路五段506號</x:v>
+      </x:c>
+      <x:c r="G85" s="11"/>
+    </x:row>
+    <x:row r="86" ht="22" customHeight="1">
+      <x:c r="A86" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B86" s="18" t="str">
+        <x:v>S085</x:v>
+      </x:c>
+      <x:c r="C86" s="11" t="str">
+        <x:v>忠孝東路六段156號</x:v>
+      </x:c>
+      <x:c r="D86" s="11" t="str">
+        <x:v>久億汽車</x:v>
+      </x:c>
+      <x:c r="E86" s="11" t="str">
+        <x:v>忠孝東路六段156號(久億汽車)</x:v>
+      </x:c>
+      <x:c r="F86" s="11" t="str">
+        <x:v>台北市南港區忠孝東路六段156號</x:v>
+      </x:c>
+      <x:c r="G86" s="11"/>
+    </x:row>
+    <x:row r="87" ht="22" customHeight="1">
+      <x:c r="A87" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B87" s="18" t="str">
+        <x:v>S086</x:v>
+      </x:c>
+      <x:c r="C87" s="11" t="str">
+        <x:v>萬大路321號前</x:v>
+      </x:c>
+      <x:c r="D87" s="11" t="str">
+        <x:v>萬大國小公車站牌</x:v>
+      </x:c>
+      <x:c r="E87" s="11" t="str">
+        <x:v>萬大國小公車站牌(萬大路321號前)</x:v>
+      </x:c>
+      <x:c r="F87" s="11" t="str">
+        <x:v>台北市萬華區萬大路321號</x:v>
+      </x:c>
+      <x:c r="G87" s="11"/>
+    </x:row>
+    <x:row r="88" ht="22" customHeight="1">
+      <x:c r="A88" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B88" s="18" t="str">
+        <x:v>S087</x:v>
+      </x:c>
+      <x:c r="C88" s="11" t="str">
+        <x:v>西藏路39號</x:v>
+      </x:c>
+      <x:c r="D88" s="11" t="str">
+        <x:v>惠安街口</x:v>
+      </x:c>
+      <x:c r="E88" s="11" t="str">
+        <x:v>西藏路39號(惠安街口)</x:v>
+      </x:c>
+      <x:c r="F88" s="11" t="str">
+        <x:v>台北市中正區西藏路39號</x:v>
+      </x:c>
+      <x:c r="G88" s="11"/>
+    </x:row>
+    <x:row r="89" ht="22" customHeight="1">
+      <x:c r="A89" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B89" s="18" t="str">
+        <x:v>S088</x:v>
+      </x:c>
+      <x:c r="C89" s="11" t="str">
+        <x:v>敦化南路二段178號</x:v>
+      </x:c>
+      <x:c r="D89" s="11" t="str">
+        <x:v>幸園牙醫</x:v>
+      </x:c>
+      <x:c r="E89" s="11" t="str">
+        <x:v>敦化南路二段178號(幸園牙醫)</x:v>
+      </x:c>
+      <x:c r="F89" s="11" t="str">
+        <x:v>台北市大安區敦化南路二段178號</x:v>
+      </x:c>
+      <x:c r="G89" s="11"/>
+    </x:row>
+    <x:row r="90" ht="22" customHeight="1">
+      <x:c r="A90" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B90" s="18" t="str">
+        <x:v>S089</x:v>
+      </x:c>
+      <x:c r="C90" s="11" t="str">
+        <x:v>仁愛路125號</x:v>
+      </x:c>
+      <x:c r="D90" s="11" t="str">
+        <x:v>早享早餐店前公車站牌</x:v>
+      </x:c>
+      <x:c r="E90" s="11" t="str">
+        <x:v>永和仁愛路125號(早享早餐店前公車站牌)</x:v>
+      </x:c>
+      <x:c r="F90" s="11" t="str">
+        <x:v>新北市永和區仁愛路125號</x:v>
+      </x:c>
+      <x:c r="G90" s="11"/>
+    </x:row>
+    <x:row r="91" ht="22" customHeight="1">
+      <x:c r="A91" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B91" s="18" t="str">
+        <x:v>S090</x:v>
+      </x:c>
+      <x:c r="C91" s="11" t="str">
+        <x:v>永和路二段226號</x:v>
+      </x:c>
+      <x:c r="D91" s="11" t="str">
+        <x:v>英美語言中心</x:v>
+      </x:c>
+      <x:c r="E91" s="11" t="str">
+        <x:v>永和路二段226號(英美語言中心)</x:v>
+      </x:c>
+      <x:c r="F91" s="11" t="str">
+        <x:v>新北市永和區永和路二段226號</x:v>
+      </x:c>
+      <x:c r="G91" s="11"/>
+    </x:row>
+    <x:row r="92" ht="22" customHeight="1">
+      <x:c r="A92" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B92" s="18" t="str">
+        <x:v>S091</x:v>
+      </x:c>
+      <x:c r="C92" s="11" t="str">
+        <x:v>和平東路一段178號</x:v>
+      </x:c>
+      <x:c r="D92" s="11" t="str">
+        <x:v>台北富邦銀行</x:v>
+      </x:c>
+      <x:c r="E92" s="11" t="str">
+        <x:v>和平東路一段178號(台北富邦銀行)</x:v>
+      </x:c>
+      <x:c r="F92" s="11" t="str">
+        <x:v>台北市大安區和平東路一段178號</x:v>
+      </x:c>
+      <x:c r="G92" s="11"/>
+    </x:row>
+    <x:row r="93" ht="22" customHeight="1">
+      <x:c r="A93" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B93" s="18" t="str">
+        <x:v>S092</x:v>
+      </x:c>
+      <x:c r="C93" s="11" t="str">
+        <x:v>和平東路二段24號</x:v>
+      </x:c>
+      <x:c r="D93" s="11" t="str">
+        <x:v>台北靈糧堂</x:v>
+      </x:c>
+      <x:c r="E93" s="11" t="str">
+        <x:v>和平東路二段24號(台北靈糧堂)</x:v>
+      </x:c>
+      <x:c r="F93" s="11" t="str">
+        <x:v>台北市大安區和平東路二段24號</x:v>
+      </x:c>
+      <x:c r="G93" s="11"/>
+    </x:row>
+    <x:row r="94" ht="22" customHeight="1">
+      <x:c r="A94" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B94" s="18" t="str">
+        <x:v>S093</x:v>
+      </x:c>
+      <x:c r="C94" s="11" t="str">
+        <x:v>中山路一段207號</x:v>
+      </x:c>
+      <x:c r="D94" s="11" t="str">
+        <x:v>吳神父民俗療館</x:v>
+      </x:c>
+      <x:c r="E94" s="11" t="str">
+        <x:v>中山路一段207號(吳神父民俗療館)</x:v>
+      </x:c>
+      <x:c r="F94" s="11" t="str">
+        <x:v>新北市永和區中山路一段207號</x:v>
+      </x:c>
+      <x:c r="G94" s="11"/>
+    </x:row>
+    <x:row r="95" ht="22" customHeight="1">
+      <x:c r="A95" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B95" s="18" t="str">
+        <x:v>S094</x:v>
+      </x:c>
+      <x:c r="C95" s="11" t="str">
+        <x:v>和平西路一段34號</x:v>
+      </x:c>
+      <x:c r="D95" s="11" t="str">
+        <x:v>欣鍋園火鍋店</x:v>
+      </x:c>
+      <x:c r="E95" s="11" t="str">
+        <x:v>和平西路一段34號(欣鍋園火鍋店)</x:v>
+      </x:c>
+      <x:c r="F95" s="11" t="str">
+        <x:v>台北市中正區和平西路一段34號</x:v>
+      </x:c>
+      <x:c r="G95" s="11"/>
+    </x:row>
+    <x:row r="96" ht="22" customHeight="1">
+      <x:c r="A96" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B96" s="18" t="str">
+        <x:v>S095</x:v>
+      </x:c>
+      <x:c r="C96" s="11" t="str">
+        <x:v>自來水處公車站牌</x:v>
+      </x:c>
+      <x:c r="D96" s="11"/>
+      <x:c r="E96" s="11" t="str">
+        <x:v>自來水處公車站牌</x:v>
+      </x:c>
+      <x:c r="F96" s="11" t="str">
+        <x:v>台北市自來水處公車站牌</x:v>
+      </x:c>
+      <x:c r="G96" s="11"/>
+    </x:row>
+    <x:row r="97" ht="22" customHeight="1">
+      <x:c r="A97" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B97" s="18" t="str">
+        <x:v>S096</x:v>
+      </x:c>
+      <x:c r="C97" s="11" t="str">
+        <x:v>福和路239號</x:v>
+      </x:c>
+      <x:c r="D97" s="11" t="str">
+        <x:v>老薑汕頭麵</x:v>
+      </x:c>
+      <x:c r="E97" s="11" t="str">
+        <x:v>福和路239號(老薑汕頭麵)</x:v>
+      </x:c>
+      <x:c r="F97" s="11" t="str">
+        <x:v>新北市永和區福和路239號</x:v>
+      </x:c>
+      <x:c r="G97" s="11"/>
+    </x:row>
+    <x:row r="98" ht="22" customHeight="1">
+      <x:c r="A98" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B98" s="18" t="str">
+        <x:v>S097</x:v>
+      </x:c>
+      <x:c r="C98" s="11" t="str">
+        <x:v>福和路73號</x:v>
+      </x:c>
+      <x:c r="D98" s="11" t="str">
+        <x:v>長庚生技</x:v>
+      </x:c>
+      <x:c r="E98" s="11" t="str">
+        <x:v>福和路73號(長庚生技)</x:v>
+      </x:c>
+      <x:c r="F98" s="11" t="str">
+        <x:v>新北市永和區福和路73號</x:v>
+      </x:c>
+      <x:c r="G98" s="11"/>
+    </x:row>
+    <x:row r="99" ht="22" customHeight="1">
+      <x:c r="A99" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B99" s="18" t="str">
+        <x:v>S098</x:v>
+      </x:c>
+      <x:c r="C99" s="11" t="str">
+        <x:v>辛亥路一段32號</x:v>
+      </x:c>
+      <x:c r="D99" s="11" t="str">
+        <x:v>佳音英語</x:v>
+      </x:c>
+      <x:c r="E99" s="11" t="str">
+        <x:v>辛亥路一段32號(佳音英語)</x:v>
+      </x:c>
+      <x:c r="F99" s="11" t="str">
+        <x:v>台北市大安區辛亥路一段32號</x:v>
+      </x:c>
+      <x:c r="G99" s="11"/>
+    </x:row>
+    <x:row r="100" ht="22" customHeight="1">
+      <x:c r="A100" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B100" s="18" t="str">
+        <x:v>S099</x:v>
+      </x:c>
+      <x:c r="C100" s="11" t="str">
+        <x:v>興隆路二段277號</x:v>
+      </x:c>
+      <x:c r="D100" s="11" t="str">
+        <x:v>大埔鐵板燒</x:v>
+      </x:c>
+      <x:c r="E100" s="11" t="str">
+        <x:v>興隆路二段277號(大埔鐵板燒)</x:v>
+      </x:c>
+      <x:c r="F100" s="11" t="str">
+        <x:v>台北市文山區興隆路二段277號</x:v>
+      </x:c>
+      <x:c r="G100" s="11"/>
+    </x:row>
+    <x:row r="101" ht="22" customHeight="1">
+      <x:c r="A101" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B101" s="18" t="str">
+        <x:v>S100</x:v>
+      </x:c>
+      <x:c r="C101" s="11" t="str">
+        <x:v>興隆路二段97號</x:v>
+      </x:c>
+      <x:c r="D101" s="11" t="str">
+        <x:v>興隆市場前公車站牌</x:v>
+      </x:c>
+      <x:c r="E101" s="11" t="str">
+        <x:v>興隆路二段97號(興隆市場前公車站牌)</x:v>
+      </x:c>
+      <x:c r="F101" s="11" t="str">
+        <x:v>台北市文山區興隆路二段97號</x:v>
+      </x:c>
+      <x:c r="G101" s="11"/>
+    </x:row>
+    <x:row r="102" ht="22" customHeight="1">
+      <x:c r="A102" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B102" s="18" t="str">
+        <x:v>S101</x:v>
+      </x:c>
+      <x:c r="C102" s="11" t="str">
+        <x:v>羅斯福路六段11號</x:v>
+      </x:c>
+      <x:c r="D102" s="11" t="str">
+        <x:v>御珍鮑</x:v>
+      </x:c>
+      <x:c r="E102" s="11" t="str">
+        <x:v>羅斯福路六段11號(御珍鮑)</x:v>
+      </x:c>
+      <x:c r="F102" s="11" t="str">
+        <x:v>台北市文山區羅斯福路六段11號</x:v>
+      </x:c>
+      <x:c r="G102" s="11"/>
+    </x:row>
+    <x:row r="103" ht="22" customHeight="1">
+      <x:c r="A103" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B103" s="18" t="str">
+        <x:v>S102</x:v>
+      </x:c>
+      <x:c r="C103" s="11" t="str">
+        <x:v>羅斯福路五段121號</x:v>
+      </x:c>
+      <x:c r="D103" s="11" t="str">
+        <x:v>豐品設計中心</x:v>
+      </x:c>
+      <x:c r="E103" s="11" t="str">
+        <x:v>羅斯福路五段121號(豐品設計中心)</x:v>
+      </x:c>
+      <x:c r="F103" s="11" t="str">
+        <x:v>台北市文山區羅斯福路五段121號</x:v>
+      </x:c>
+      <x:c r="G103" s="11"/>
+    </x:row>
+    <x:row r="104" ht="22" customHeight="1">
+      <x:c r="A104" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B104" s="18" t="str">
+        <x:v>S103</x:v>
+      </x:c>
+      <x:c r="C104" s="11" t="str">
+        <x:v>文化路一段196號</x:v>
+      </x:c>
+      <x:c r="D104" s="11" t="str">
+        <x:v>中英醫院</x:v>
+      </x:c>
+      <x:c r="E104" s="11" t="str">
+        <x:v>文化路一段196號(中英醫院)</x:v>
+      </x:c>
+      <x:c r="F104" s="11" t="str">
+        <x:v>新北市板橋區文化路一段196號</x:v>
+      </x:c>
+      <x:c r="G104" s="11"/>
+    </x:row>
+    <x:row r="105" ht="22" customHeight="1">
+      <x:c r="A105" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B105" s="18" t="str">
+        <x:v>S104</x:v>
+      </x:c>
+      <x:c r="C105" s="11" t="str">
+        <x:v>中正路909號</x:v>
+      </x:c>
+      <x:c r="D105" s="11" t="str">
+        <x:v>新銳科技大樓</x:v>
+      </x:c>
+      <x:c r="E105" s="11" t="str">
+        <x:v>中和市中正路909號(新銳科技大樓)</x:v>
+      </x:c>
+      <x:c r="F105" s="11" t="str">
+        <x:v>新北市中和區中正路909號</x:v>
+      </x:c>
+      <x:c r="G105" s="11"/>
+    </x:row>
+    <x:row r="106" ht="22" customHeight="1">
+      <x:c r="A106" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B106" s="18" t="str">
+        <x:v>S105</x:v>
+      </x:c>
+      <x:c r="C106" s="11" t="str">
+        <x:v>縣民大道二段1號</x:v>
+      </x:c>
+      <x:c r="D106" s="11" t="str">
+        <x:v>台電台北南區營業處</x:v>
+      </x:c>
+      <x:c r="E106" s="11" t="str">
+        <x:v>縣民大道二段1號(台電台北南區營業處)</x:v>
+      </x:c>
+      <x:c r="F106" s="11" t="str">
+        <x:v>新北市板橋區縣民大道二段1號</x:v>
+      </x:c>
+      <x:c r="G106" s="11"/>
+    </x:row>
+    <x:row r="107" ht="22" customHeight="1">
+      <x:c r="A107" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B107" s="18" t="str">
+        <x:v>S106</x:v>
+      </x:c>
+      <x:c r="C107" s="11" t="str">
+        <x:v>文化路二段22號</x:v>
+      </x:c>
+      <x:c r="D107" s="11" t="str">
+        <x:v>信義房屋</x:v>
+      </x:c>
+      <x:c r="E107" s="11" t="str">
+        <x:v>文化路二段22號(信義房屋)</x:v>
+      </x:c>
+      <x:c r="F107" s="11" t="str">
+        <x:v>新北市板橋區文化路二段22號</x:v>
+      </x:c>
+      <x:c r="G107" s="11"/>
+    </x:row>
+    <x:row r="108" ht="22" customHeight="1">
+      <x:c r="A108" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B108" s="18" t="str">
+        <x:v>S107</x:v>
+      </x:c>
+      <x:c r="C108" s="11" t="str">
+        <x:v>重慶路262號</x:v>
+      </x:c>
+      <x:c r="D108" s="11" t="str">
+        <x:v>國泰世華</x:v>
+      </x:c>
+      <x:c r="E108" s="11" t="str">
+        <x:v>重慶路262號(國泰世華)</x:v>
+      </x:c>
+      <x:c r="F108" s="11" t="str">
+        <x:v>新北市板橋區重慶路262號</x:v>
+      </x:c>
+      <x:c r="G108" s="11"/>
+    </x:row>
+    <x:row r="109" ht="22" customHeight="1">
+      <x:c r="A109" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B109" s="18" t="str">
+        <x:v>S108</x:v>
+      </x:c>
+      <x:c r="C109" s="11" t="str">
+        <x:v>中山路一段10號</x:v>
+      </x:c>
+      <x:c r="D109" s="11" t="str">
+        <x:v>壽司郎</x:v>
+      </x:c>
+      <x:c r="E109" s="11" t="str">
+        <x:v>中山路一段10號(壽司郎)</x:v>
+      </x:c>
+      <x:c r="F109" s="11" t="str">
+        <x:v>新北市板橋區中山路一段10號</x:v>
+      </x:c>
+      <x:c r="G109" s="11"/>
+    </x:row>
+    <x:row r="110" ht="22" customHeight="1">
+      <x:c r="A110" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B110" s="18" t="str">
+        <x:v>S109</x:v>
+      </x:c>
+      <x:c r="C110" s="11" t="str">
+        <x:v>雙十路二段71號</x:v>
+      </x:c>
+      <x:c r="D110" s="11" t="str">
+        <x:v>遠傳電信</x:v>
+      </x:c>
+      <x:c r="E110" s="11" t="str">
+        <x:v>雙十路二段71號(遠傳電信)</x:v>
+      </x:c>
+      <x:c r="F110" s="11" t="str">
+        <x:v>新北市板橋區雙十路二段71號</x:v>
+      </x:c>
+      <x:c r="G110" s="11"/>
+    </x:row>
+    <x:row r="111" ht="22" customHeight="1">
+      <x:c r="A111" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B111" s="18" t="str">
+        <x:v>S110</x:v>
+      </x:c>
+      <x:c r="C111" s="11" t="str">
+        <x:v>三民路二段72號</x:v>
+      </x:c>
+      <x:c r="D111" s="11" t="str">
+        <x:v>埔墘公車站牌</x:v>
+      </x:c>
+      <x:c r="E111" s="11" t="str">
+        <x:v>三民路二段72號(埔墘公車站牌)</x:v>
+      </x:c>
+      <x:c r="F111" s="11" t="str">
+        <x:v>新北市板橋區三民路二段72號</x:v>
+      </x:c>
+      <x:c r="G111" s="11"/>
+    </x:row>
+    <x:row r="112" ht="22" customHeight="1">
+      <x:c r="A112" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B112" s="18" t="str">
+        <x:v>S111</x:v>
+      </x:c>
+      <x:c r="C112" s="11" t="str">
+        <x:v>國慶路203號</x:v>
+      </x:c>
+      <x:c r="D112" s="11" t="str">
+        <x:v>北美蛋糕麵包</x:v>
+      </x:c>
+      <x:c r="E112" s="11" t="str">
+        <x:v>國慶路203號(北美蛋糕麵包)</x:v>
+      </x:c>
+      <x:c r="F112" s="11" t="str">
+        <x:v>新北市板橋區國慶路203號</x:v>
+      </x:c>
+      <x:c r="G112" s="11"/>
+    </x:row>
+    <x:row r="113" ht="22" customHeight="1">
+      <x:c r="A113" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B113" s="18" t="str">
+        <x:v>S112</x:v>
+      </x:c>
+      <x:c r="C113" s="11" t="str">
+        <x:v>金城路二段209號</x:v>
+      </x:c>
+      <x:c r="D113" s="11" t="str">
+        <x:v>全國電子</x:v>
+      </x:c>
+      <x:c r="E113" s="11" t="str">
+        <x:v>金城路二段209號(全國電子)</x:v>
+      </x:c>
+      <x:c r="F113" s="11" t="str">
+        <x:v>新北市土城區金城路二段209號</x:v>
+      </x:c>
+      <x:c r="G113" s="11"/>
+    </x:row>
+    <x:row r="114" ht="22" customHeight="1">
+      <x:c r="A114" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B114" s="18" t="str">
+        <x:v>S113</x:v>
+      </x:c>
+      <x:c r="C114" s="11" t="str">
+        <x:v>中央路三段84號</x:v>
+      </x:c>
+      <x:c r="D114" s="11" t="str">
+        <x:v>摩斯漢堡</x:v>
+      </x:c>
+      <x:c r="E114" s="11" t="str">
+        <x:v>新北市土城區中央路三段84號(摩斯漢堡)</x:v>
+      </x:c>
+      <x:c r="F114" s="11" t="str">
+        <x:v>新北市土城區中央路三段84號</x:v>
+      </x:c>
+      <x:c r="G114" s="11"/>
+    </x:row>
+    <x:row r="115" ht="22" customHeight="1">
+      <x:c r="A115" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B115" s="18" t="str">
+        <x:v>S114</x:v>
+      </x:c>
+      <x:c r="C115" s="11" t="str">
+        <x:v>信義路82號</x:v>
+      </x:c>
+      <x:c r="D115" s="11" t="str">
+        <x:v>青葉油漆</x:v>
+      </x:c>
+      <x:c r="E115" s="11" t="str">
+        <x:v>板橋區信義路82號(青葉油漆)</x:v>
+      </x:c>
+      <x:c r="F115" s="11" t="str">
+        <x:v>新北市板橋區信義路82號</x:v>
+      </x:c>
+      <x:c r="G115" s="11"/>
+    </x:row>
+    <x:row r="116" ht="22" customHeight="1">
+      <x:c r="A116" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B116" s="18" t="str">
+        <x:v>S115</x:v>
+      </x:c>
+      <x:c r="C116" s="11" t="str">
+        <x:v>金城路一段校門口</x:v>
+      </x:c>
+      <x:c r="D116" s="11" t="str">
+        <x:v>土城國小 / 興城公共托育中心</x:v>
+      </x:c>
+      <x:c r="E116" s="11" t="str">
+        <x:v>土城國小金城路一段校門口(興城公共托育中心)</x:v>
+      </x:c>
+      <x:c r="F116" s="11" t="str">
+        <x:v>新北市土城區金城路一段 土城國小</x:v>
+      </x:c>
+      <x:c r="G116" s="11"/>
+    </x:row>
+    <x:row r="117" ht="22" customHeight="1">
+      <x:c r="A117" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B117" s="18" t="str">
+        <x:v>S116</x:v>
+      </x:c>
+      <x:c r="C117" s="11" t="str">
+        <x:v>正義北路15號</x:v>
+      </x:c>
+      <x:c r="D117" s="11" t="str">
+        <x:v>麥當勞</x:v>
+      </x:c>
+      <x:c r="E117" s="11" t="str">
+        <x:v>正義北路15號(麥當勞)</x:v>
+      </x:c>
+      <x:c r="F117" s="11" t="str">
+        <x:v>新北市三重區正義北路15號</x:v>
+      </x:c>
+      <x:c r="G117" s="11"/>
+    </x:row>
+    <x:row r="118" ht="22" customHeight="1">
+      <x:c r="A118" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B118" s="18" t="str">
+        <x:v>S117</x:v>
+      </x:c>
+      <x:c r="C118" s="11" t="str">
+        <x:v>正義北路325號</x:v>
+      </x:c>
+      <x:c r="D118" s="11" t="str">
+        <x:v>台灣大哥大</x:v>
+      </x:c>
+      <x:c r="E118" s="11" t="str">
+        <x:v>正義北路325號(台灣大哥大)</x:v>
+      </x:c>
+      <x:c r="F118" s="11" t="str">
+        <x:v>新北市三重區正義北路325號</x:v>
+      </x:c>
+      <x:c r="G118" s="11"/>
+    </x:row>
+    <x:row r="119" ht="22" customHeight="1">
+      <x:c r="A119" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B119" s="18" t="str">
+        <x:v>S118</x:v>
+      </x:c>
+      <x:c r="C119" s="11" t="str">
+        <x:v>新北大道一段17號</x:v>
+      </x:c>
+      <x:c r="D119" s="11" t="str">
+        <x:v>中華郵局</x:v>
+      </x:c>
+      <x:c r="E119" s="11" t="str">
+        <x:v>新北大道一段17號(中華郵局)</x:v>
+      </x:c>
+      <x:c r="F119" s="11" t="str">
+        <x:v>新北市三重區新北大道一段17號</x:v>
+      </x:c>
+      <x:c r="G119" s="11"/>
+    </x:row>
+    <x:row r="120" ht="22" customHeight="1">
+      <x:c r="A120" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B120" s="18" t="str">
+        <x:v>S119</x:v>
+      </x:c>
+      <x:c r="C120" s="11" t="str">
+        <x:v>捷運蘆洲站3號出口</x:v>
+      </x:c>
+      <x:c r="D120" s="11" t="str">
+        <x:v>公車站牌</x:v>
+      </x:c>
+      <x:c r="E120" s="11" t="str">
+        <x:v>蘆洲捷運站3號出口公車站牌</x:v>
+      </x:c>
+      <x:c r="F120" s="11" t="str">
+        <x:v>新北市蘆洲區捷運蘆洲站3號出口</x:v>
+      </x:c>
+      <x:c r="G120" s="11"/>
+    </x:row>
+    <x:row r="121" ht="22" customHeight="1">
+      <x:c r="A121" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B121" s="18" t="str">
+        <x:v>S120</x:v>
+      </x:c>
+      <x:c r="C121" s="11" t="str">
+        <x:v>中山一路63號</x:v>
+      </x:c>
+      <x:c r="D121" s="11" t="str">
+        <x:v>光陽機車</x:v>
+      </x:c>
+      <x:c r="E121" s="11" t="str">
+        <x:v>中山一路63號(光陽機車)</x:v>
+      </x:c>
+      <x:c r="F121" s="11" t="str">
+        <x:v>新北市蘆洲區中山一路63號</x:v>
+      </x:c>
+      <x:c r="G121" s="11"/>
+    </x:row>
+    <x:row r="122" ht="22" customHeight="1">
+      <x:c r="A122" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B122" s="18" t="str">
+        <x:v>S121</x:v>
+      </x:c>
+      <x:c r="C122" s="11" t="str">
+        <x:v>三和路四段390號</x:v>
+      </x:c>
+      <x:c r="D122" s="11" t="str">
+        <x:v>德恩堂眼鏡</x:v>
+      </x:c>
+      <x:c r="E122" s="11" t="str">
+        <x:v>三和路四段390號(德恩堂眼鏡)</x:v>
+      </x:c>
+      <x:c r="F122" s="11" t="str">
+        <x:v>新北市三重區三和路四段390號</x:v>
+      </x:c>
+      <x:c r="G122" s="11"/>
+    </x:row>
+    <x:row r="123" ht="22" customHeight="1">
+      <x:c r="A123" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B123" s="18" t="str">
+        <x:v>S122</x:v>
+      </x:c>
+      <x:c r="C123" s="11" t="str">
+        <x:v>新五路二段236號</x:v>
+      </x:c>
+      <x:c r="D123" s="11" t="str">
+        <x:v>金通物流</x:v>
+      </x:c>
+      <x:c r="E123" s="11" t="str">
+        <x:v>新五路二段236號(金通物流)</x:v>
+      </x:c>
+      <x:c r="F123" s="11" t="str">
+        <x:v>新北市五股區新五路二段236號</x:v>
+      </x:c>
+      <x:c r="G123" s="11"/>
+    </x:row>
+    <x:row r="124" ht="22" customHeight="1">
+      <x:c r="A124" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B124" s="18" t="str">
+        <x:v>S123</x:v>
+      </x:c>
+      <x:c r="C124" s="11" t="str">
+        <x:v>長榮路386號</x:v>
+      </x:c>
+      <x:c r="D124" s="11" t="str">
+        <x:v>家樂福</x:v>
+      </x:c>
+      <x:c r="E124" s="11" t="str">
+        <x:v>長榮路386號(家樂福)</x:v>
+      </x:c>
+      <x:c r="F124" s="11" t="str">
+        <x:v>新北市蘆洲區長榮路386號</x:v>
+      </x:c>
+      <x:c r="G124" s="11"/>
+    </x:row>
+    <x:row r="125" ht="22" customHeight="1">
+      <x:c r="A125" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B125" s="18" t="str">
+        <x:v>S124</x:v>
+      </x:c>
+      <x:c r="C125" s="11" t="str">
+        <x:v>捷運三民高中站1號出口</x:v>
+      </x:c>
+      <x:c r="D125" s="11" t="str">
+        <x:v>復興三民路口</x:v>
+      </x:c>
+      <x:c r="E125" s="11" t="str">
+        <x:v>三民高中捷運站1號出口(復興三民路口)</x:v>
+      </x:c>
+      <x:c r="F125" s="11" t="str">
+        <x:v>新北市蘆洲區捷運三民高中站1號出口</x:v>
+      </x:c>
+      <x:c r="G125" s="11"/>
+    </x:row>
+    <x:row r="126" ht="22" customHeight="1">
+      <x:c r="A126" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B126" s="18" t="str">
+        <x:v>S125</x:v>
+      </x:c>
+      <x:c r="C126" s="11" t="str">
+        <x:v>景平路341號</x:v>
+      </x:c>
+      <x:c r="D126" s="11" t="str">
+        <x:v>日式炭火燒烤店 / 景安捷運站對面</x:v>
+      </x:c>
+      <x:c r="E126" s="11" t="str">
+        <x:v>景平路341號(日式炭火燒烤店/景安捷運站對面)</x:v>
+      </x:c>
+      <x:c r="F126" s="11" t="str">
+        <x:v>新北市中和區景平路341號</x:v>
+      </x:c>
+      <x:c r="G126" s="11"/>
+    </x:row>
+    <x:row r="127" ht="22" customHeight="1">
+      <x:c r="A127" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B127" s="18" t="str">
+        <x:v>S126</x:v>
+      </x:c>
+      <x:c r="C127" s="11" t="str">
+        <x:v>景平路121號</x:v>
+      </x:c>
+      <x:c r="D127" s="11" t="str">
+        <x:v>景平捷運站</x:v>
+      </x:c>
+      <x:c r="E127" s="11" t="str">
+        <x:v>景平路121號(景平捷運站)</x:v>
+      </x:c>
+      <x:c r="F127" s="11" t="str">
+        <x:v>新北市中和區景平路121號</x:v>
+      </x:c>
+      <x:c r="G127" s="11"/>
+    </x:row>
+    <x:row r="128" ht="22" customHeight="1">
+      <x:c r="A128" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B128" s="18" t="str">
+        <x:v>S127</x:v>
+      </x:c>
+      <x:c r="C128" s="11" t="str">
+        <x:v>景新街404號</x:v>
+      </x:c>
+      <x:c r="D128" s="11" t="str">
+        <x:v>李家刀削麵</x:v>
+      </x:c>
+      <x:c r="E128" s="11" t="str">
+        <x:v>景新街404號(李家刀削麵)</x:v>
+      </x:c>
+      <x:c r="F128" s="11" t="str">
+        <x:v>新北市中和區景新街404號</x:v>
+      </x:c>
+      <x:c r="G128" s="11"/>
+    </x:row>
+    <x:row r="129" ht="22" customHeight="1">
+      <x:c r="A129" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B129" s="18" t="str">
+        <x:v>S128</x:v>
+      </x:c>
+      <x:c r="C129" s="11" t="str">
+        <x:v>安和路三段151號前</x:v>
+      </x:c>
+      <x:c r="D129" s="11" t="str">
+        <x:v>新和國小公車站牌</x:v>
+      </x:c>
+      <x:c r="E129" s="11" t="str">
+        <x:v>新和國小公車站牌(安和路三段151號前)</x:v>
+      </x:c>
+      <x:c r="F129" s="11" t="str">
+        <x:v>新北市新店區安和路三段151號</x:v>
+      </x:c>
+      <x:c r="G129" s="11"/>
+    </x:row>
+    <x:row r="130" ht="22" customHeight="1">
+      <x:c r="A130" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B130" s="18" t="str">
+        <x:v>S129</x:v>
+      </x:c>
+      <x:c r="C130" s="11" t="str">
+        <x:v>景平路396號</x:v>
+      </x:c>
+      <x:c r="D130" s="11" t="str">
+        <x:v>長鴻寵物店</x:v>
+      </x:c>
+      <x:c r="E130" s="11" t="str">
+        <x:v>景平路396號(長鴻寵物店)</x:v>
+      </x:c>
+      <x:c r="F130" s="11" t="str">
+        <x:v>新北市中和區景平路396號</x:v>
+      </x:c>
+      <x:c r="G130" s="11"/>
+    </x:row>
+    <x:row r="131" ht="22" customHeight="1">
+      <x:c r="A131" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B131" s="18" t="str">
+        <x:v>S130</x:v>
+      </x:c>
+      <x:c r="C131" s="11" t="str">
+        <x:v>中正路80號</x:v>
+      </x:c>
+      <x:c r="D131" s="11" t="str">
+        <x:v>全聯福利中心</x:v>
+      </x:c>
+      <x:c r="E131" s="11" t="str">
+        <x:v>中正路80號(全聯福利中心)</x:v>
+      </x:c>
+      <x:c r="F131" s="11" t="str">
+        <x:v>新北市中和區中正路80號</x:v>
+      </x:c>
+      <x:c r="G131" s="11"/>
+    </x:row>
+    <x:row r="132" ht="22" customHeight="1">
+      <x:c r="A132" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B132" s="18" t="str">
+        <x:v>S131</x:v>
+      </x:c>
+      <x:c r="C132" s="11" t="str">
+        <x:v>中正路462號</x:v>
+      </x:c>
+      <x:c r="D132" s="11" t="str">
+        <x:v>大印科技 / 天橋旁 / 錦和路口</x:v>
+      </x:c>
+      <x:c r="E132" s="11" t="str">
+        <x:v>中正路462號(大印科技/天橋旁/錦和路口)</x:v>
+      </x:c>
+      <x:c r="F132" s="11" t="str">
+        <x:v>新北市中和區中正路462號</x:v>
+      </x:c>
+      <x:c r="G132" s="11"/>
+    </x:row>
+    <x:row r="133" ht="22" customHeight="1">
+      <x:c r="A133" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B133" s="18" t="str">
+        <x:v>S132</x:v>
+      </x:c>
+      <x:c r="C133" s="11" t="str">
+        <x:v>得和路327號</x:v>
+      </x:c>
+      <x:c r="D133" s="11" t="str">
+        <x:v>小林髮廊</x:v>
+      </x:c>
+      <x:c r="E133" s="11" t="str">
+        <x:v>得和路327號(小林髮廊)</x:v>
+      </x:c>
+      <x:c r="F133" s="11" t="str">
+        <x:v>新北市永和區得和路327號</x:v>
+      </x:c>
+      <x:c r="G133" s="11"/>
+    </x:row>
+    <x:row r="134" ht="22" customHeight="1">
+      <x:c r="A134" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B134" s="18" t="str">
+        <x:v>S133</x:v>
+      </x:c>
+      <x:c r="C134" s="11" t="str">
+        <x:v>中正路191號</x:v>
+      </x:c>
+      <x:c r="D134" s="11" t="str">
+        <x:v>永正健康藥局</x:v>
+      </x:c>
+      <x:c r="E134" s="11" t="str">
+        <x:v>中正路191號(永正健康藥局)</x:v>
+      </x:c>
+      <x:c r="F134" s="11" t="str">
+        <x:v>新北市永和區中正路191號</x:v>
+      </x:c>
+      <x:c r="G134" s="11"/>
+    </x:row>
+    <x:row r="135" ht="22" customHeight="1">
+      <x:c r="A135" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B135" s="18" t="str">
+        <x:v>S134</x:v>
+      </x:c>
+      <x:c r="C135" s="11" t="str">
+        <x:v>中正路61號</x:v>
+      </x:c>
+      <x:c r="D135" s="11" t="str">
+        <x:v>中國信託</x:v>
+      </x:c>
+      <x:c r="E135" s="11" t="str">
+        <x:v>中正路61號(中國信託)</x:v>
+      </x:c>
+      <x:c r="F135" s="11" t="str">
+        <x:v>新北市永和區中正路61號</x:v>
+      </x:c>
+      <x:c r="G135" s="11"/>
+    </x:row>
+    <x:row r="136" ht="22" customHeight="1">
+      <x:c r="A136" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B136" s="18" t="str">
+        <x:v>S135</x:v>
+      </x:c>
+      <x:c r="C136" s="11" t="str">
+        <x:v>安和路一段47號</x:v>
+      </x:c>
+      <x:c r="D136" s="11" t="str">
+        <x:v>神吉MOTO</x:v>
+      </x:c>
+      <x:c r="E136" s="11" t="str">
+        <x:v>安和路一段47號(神吉MOTO)</x:v>
+      </x:c>
+      <x:c r="F136" s="11" t="str">
+        <x:v>新北市新店區安和路一段47號</x:v>
+      </x:c>
+      <x:c r="G136" s="11"/>
+    </x:row>
+    <x:row r="137" ht="22" customHeight="1">
+      <x:c r="A137" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B137" s="18" t="str">
+        <x:v>S136</x:v>
+      </x:c>
+      <x:c r="C137" s="11" t="str">
+        <x:v>木柵路一段72號前</x:v>
+      </x:c>
+      <x:c r="D137" s="11" t="str">
+        <x:v>考試院公車站牌</x:v>
+      </x:c>
+      <x:c r="E137" s="11" t="str">
+        <x:v>考試院公車站牌(木柵路一段72號前)</x:v>
+      </x:c>
+      <x:c r="F137" s="11" t="str">
+        <x:v>台北市文山區木柵路一段72號</x:v>
+      </x:c>
+      <x:c r="G137" s="11"/>
+    </x:row>
+    <x:row r="138" ht="22" customHeight="1">
+      <x:c r="A138" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B138" s="18" t="str">
+        <x:v>S137</x:v>
+      </x:c>
+      <x:c r="C138" s="11" t="str">
+        <x:v>木柵路二段66號</x:v>
+      </x:c>
+      <x:c r="D138" s="11" t="str">
+        <x:v>再興中學公車站</x:v>
+      </x:c>
+      <x:c r="E138" s="11" t="str">
+        <x:v>木柵路二段66號(再興中學公車站)</x:v>
+      </x:c>
+      <x:c r="F138" s="11" t="str">
+        <x:v>台北市文山區木柵路二段66號</x:v>
+      </x:c>
+      <x:c r="G138" s="11"/>
+    </x:row>
+    <x:row r="139" ht="22" customHeight="1">
+      <x:c r="A139" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B139" s="18" t="str">
+        <x:v>S138</x:v>
+      </x:c>
+      <x:c r="C139" s="11" t="str">
+        <x:v>秀明路一段</x:v>
+      </x:c>
+      <x:c r="D139" s="11" t="str">
+        <x:v>久康公園公車站</x:v>
+      </x:c>
+      <x:c r="E139" s="11" t="str">
+        <x:v>秀明路一段(久康公園公車站)</x:v>
+      </x:c>
+      <x:c r="F139" s="11" t="str">
+        <x:v>台北市文山區秀明路一段 久康公園</x:v>
+      </x:c>
+      <x:c r="G139" s="11"/>
+    </x:row>
+    <x:row r="140" ht="22" customHeight="1">
+      <x:c r="A140" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B140" s="18" t="str">
+        <x:v>S139</x:v>
+      </x:c>
+      <x:c r="C140" s="11" t="str">
+        <x:v>木柵國小後門斑馬線</x:v>
+      </x:c>
+      <x:c r="D140" s="11" t="str">
+        <x:v>萬壽橋頭前</x:v>
+      </x:c>
+      <x:c r="E140" s="11" t="str">
+        <x:v>木柵國小後門斑馬線(萬壽橋頭前)</x:v>
+      </x:c>
+      <x:c r="F140" s="11" t="str">
+        <x:v>台北市文山區木柵國小後門</x:v>
+      </x:c>
+      <x:c r="G140" s="11"/>
+    </x:row>
+    <x:row r="141" ht="22" customHeight="1">
+      <x:c r="A141" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B141" s="18" t="str">
+        <x:v>S140</x:v>
+      </x:c>
+      <x:c r="C141" s="11" t="str">
+        <x:v>木柵路四段96號</x:v>
+      </x:c>
+      <x:c r="D141" s="11" t="str">
+        <x:v>雙口組檳榔攤 / 鄰捷運木柵站</x:v>
+      </x:c>
+      <x:c r="E141" s="11" t="str">
+        <x:v>木柵路4段96號(雙口組檳榔攤/鄰捷運木柵站)</x:v>
+      </x:c>
+      <x:c r="F141" s="11" t="str">
+        <x:v>台北市文山區木柵路四段96號</x:v>
+      </x:c>
+      <x:c r="G141" s="11"/>
+    </x:row>
+    <x:row r="142" ht="22" customHeight="1">
+      <x:c r="A142" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B142" s="18" t="str">
+        <x:v>S141</x:v>
+      </x:c>
+      <x:c r="C142" s="11" t="str">
+        <x:v>北新路二段108號</x:v>
+      </x:c>
+      <x:c r="D142" s="11" t="str">
+        <x:v>華南銀行 / 鄰捷運七張站</x:v>
+      </x:c>
+      <x:c r="E142" s="11" t="str">
+        <x:v>北新路二段108號(華南銀行/鄰捷運七張站)</x:v>
+      </x:c>
+      <x:c r="F142" s="11" t="str">
+        <x:v>新北市新店區北新路二段108號</x:v>
+      </x:c>
+      <x:c r="G142" s="11"/>
+    </x:row>
+    <x:row r="143" ht="22" customHeight="1">
+      <x:c r="A143" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B143" s="18" t="str">
+        <x:v>S142</x:v>
+      </x:c>
+      <x:c r="C143" s="11" t="str">
+        <x:v>民權路17號</x:v>
+      </x:c>
+      <x:c r="D143" s="11" t="str">
+        <x:v>康是美</x:v>
+      </x:c>
+      <x:c r="E143" s="11" t="str">
+        <x:v>新店區民權路17號(康是美)</x:v>
+      </x:c>
+      <x:c r="F143" s="11" t="str">
+        <x:v>新北市新店區民權路17號</x:v>
+      </x:c>
+      <x:c r="G143" s="11"/>
+    </x:row>
+    <x:row r="144" ht="22" customHeight="1">
+      <x:c r="A144" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B144" s="18" t="str">
+        <x:v>S143</x:v>
+      </x:c>
+      <x:c r="C144" s="11" t="str">
+        <x:v>成功路76號</x:v>
+      </x:c>
+      <x:c r="D144" s="11" t="str">
+        <x:v>藝立方雷射雕刻</x:v>
+      </x:c>
+      <x:c r="E144" s="11" t="str">
+        <x:v>藝立方雷射雕刻(成功路76號)</x:v>
+      </x:c>
+      <x:c r="F144" s="11" t="str">
+        <x:v>新北市永和區成功路76號</x:v>
+      </x:c>
+      <x:c r="G144" s="11"/>
+    </x:row>
+    <x:row r="145" ht="22" customHeight="1">
+      <x:c r="A145" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B145" s="18" t="str">
+        <x:v>S144</x:v>
+      </x:c>
+      <x:c r="C145" s="11" t="str">
+        <x:v>中正路75巷口</x:v>
+      </x:c>
+      <x:c r="D145" s="11" t="str">
+        <x:v>公車站牌</x:v>
+      </x:c>
+      <x:c r="E145" s="11" t="str">
+        <x:v>中正路75巷口(公車站牌)</x:v>
+      </x:c>
+      <x:c r="F145" s="11" t="str">
+        <x:v>新北市新店區中正路75巷口</x:v>
+      </x:c>
+      <x:c r="G145" s="11"/>
     </x:row>
   </x:sheetData>
+  <x:conditionalFormatting sqref="A2:G145">
+    <x:cfRule type="expression" dxfId="1" priority="1">
+      <x:formula>$A2="FALSE"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="F2:F145">
+    <x:cfRule type="expression" dxfId="3" priority="2">
+      <x:formula>F2=""</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="A2:A500">
+    <x:dataValidation type="list" sqref="A2:A145">
       <x:formula1>"TRUE,FALSE"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b991eed37954783"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5906748f3d2242bf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2031,35 +5036,35 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="8" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="9" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="11" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="9" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="11" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="10" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="28" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="16" t="str">
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="10" t="str">
         <x:v>啟用</x:v>
       </x:c>
-      <x:c r="B1" s="16" t="str">
+      <x:c r="B1" s="10" t="str">
         <x:v>RouteID</x:v>
       </x:c>
-      <x:c r="C1" s="16" t="str">
+      <x:c r="C1" s="10" t="str">
         <x:v>順序</x:v>
       </x:c>
-      <x:c r="D1" s="16" t="str">
+      <x:c r="D1" s="10" t="str">
         <x:v>StopID</x:v>
       </x:c>
-      <x:c r="E1" s="16" t="str">
+      <x:c r="E1" s="10" t="str">
         <x:v>時間</x:v>
       </x:c>
-      <x:c r="F1" s="16" t="str">
+      <x:c r="F1" s="10" t="str">
         <x:v>備註</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="20" customHeight="1">
       <x:c r="A2" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2075,9 +5080,9 @@
       <x:c r="E2" s="18" t="str">
         <x:v>06:25</x:v>
       </x:c>
-      <x:c r="F2" s="18" t="str"/>
-    </x:row>
-    <x:row r="3">
+      <x:c r="F2" s="11"/>
+    </x:row>
+    <x:row r="3" ht="20" customHeight="1">
       <x:c r="A3" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2093,9 +5098,9 @@
       <x:c r="E3" s="18" t="str">
         <x:v>06:30</x:v>
       </x:c>
-      <x:c r="F3" s="18" t="str"/>
-    </x:row>
-    <x:row r="4">
+      <x:c r="F3" s="11"/>
+    </x:row>
+    <x:row r="4" ht="20" customHeight="1">
       <x:c r="A4" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2111,9 +5116,9 @@
       <x:c r="E4" s="18" t="str">
         <x:v>06:34</x:v>
       </x:c>
-      <x:c r="F4" s="18" t="str"/>
-    </x:row>
-    <x:row r="5">
+      <x:c r="F4" s="11"/>
+    </x:row>
+    <x:row r="5" ht="20" customHeight="1">
       <x:c r="A5" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2129,9 +5134,9 @@
       <x:c r="E5" s="18" t="str">
         <x:v>06:37</x:v>
       </x:c>
-      <x:c r="F5" s="18" t="str"/>
-    </x:row>
-    <x:row r="6">
+      <x:c r="F5" s="11"/>
+    </x:row>
+    <x:row r="6" ht="20" customHeight="1">
       <x:c r="A6" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2147,9 +5152,9 @@
       <x:c r="E6" s="18" t="str">
         <x:v>06:38</x:v>
       </x:c>
-      <x:c r="F6" s="18" t="str"/>
-    </x:row>
-    <x:row r="7">
+      <x:c r="F6" s="11"/>
+    </x:row>
+    <x:row r="7" ht="20" customHeight="1">
       <x:c r="A7" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2165,9 +5170,9 @@
       <x:c r="E7" s="18" t="str">
         <x:v>06:41</x:v>
       </x:c>
-      <x:c r="F7" s="18" t="str"/>
-    </x:row>
-    <x:row r="8">
+      <x:c r="F7" s="11"/>
+    </x:row>
+    <x:row r="8" ht="20" customHeight="1">
       <x:c r="A8" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2183,9 +5188,9 @@
       <x:c r="E8" s="18" t="str">
         <x:v>06:50</x:v>
       </x:c>
-      <x:c r="F8" s="18" t="str"/>
-    </x:row>
-    <x:row r="9">
+      <x:c r="F8" s="11"/>
+    </x:row>
+    <x:row r="9" ht="20" customHeight="1">
       <x:c r="A9" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2201,9 +5206,9 @@
       <x:c r="E9" s="18" t="str">
         <x:v>06:55</x:v>
       </x:c>
-      <x:c r="F9" s="18" t="str"/>
-    </x:row>
-    <x:row r="10">
+      <x:c r="F9" s="11"/>
+    </x:row>
+    <x:row r="10" ht="20" customHeight="1">
       <x:c r="A10" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2219,9 +5224,9 @@
       <x:c r="E10" s="18" t="str">
         <x:v>06:55</x:v>
       </x:c>
-      <x:c r="F10" s="18" t="str"/>
-    </x:row>
-    <x:row r="11">
+      <x:c r="F10" s="11"/>
+    </x:row>
+    <x:row r="11" ht="20" customHeight="1">
       <x:c r="A11" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2237,9 +5242,9 @@
       <x:c r="E11" s="18" t="str">
         <x:v>06:23</x:v>
       </x:c>
-      <x:c r="F11" s="18" t="str"/>
-    </x:row>
-    <x:row r="12">
+      <x:c r="F11" s="11"/>
+    </x:row>
+    <x:row r="12" ht="20" customHeight="1">
       <x:c r="A12" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2255,9 +5260,9 @@
       <x:c r="E12" s="18" t="str">
         <x:v>06:31</x:v>
       </x:c>
-      <x:c r="F12" s="18" t="str"/>
-    </x:row>
-    <x:row r="13">
+      <x:c r="F12" s="11"/>
+    </x:row>
+    <x:row r="13" ht="20" customHeight="1">
       <x:c r="A13" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2273,9 +5278,9 @@
       <x:c r="E13" s="18" t="str">
         <x:v>06:38</x:v>
       </x:c>
-      <x:c r="F13" s="18" t="str"/>
-    </x:row>
-    <x:row r="14">
+      <x:c r="F13" s="11"/>
+    </x:row>
+    <x:row r="14" ht="20" customHeight="1">
       <x:c r="A14" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2291,9 +5296,9 @@
       <x:c r="E14" s="18" t="str">
         <x:v>06:28</x:v>
       </x:c>
-      <x:c r="F14" s="18" t="str"/>
-    </x:row>
-    <x:row r="15">
+      <x:c r="F14" s="11"/>
+    </x:row>
+    <x:row r="15" ht="20" customHeight="1">
       <x:c r="A15" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2309,9 +5314,9 @@
       <x:c r="E15" s="18" t="str">
         <x:v>06:30</x:v>
       </x:c>
-      <x:c r="F15" s="18" t="str"/>
-    </x:row>
-    <x:row r="16">
+      <x:c r="F15" s="11"/>
+    </x:row>
+    <x:row r="16" ht="20" customHeight="1">
       <x:c r="A16" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2327,9 +5332,9 @@
       <x:c r="E16" s="18" t="str">
         <x:v>06:32</x:v>
       </x:c>
-      <x:c r="F16" s="18" t="str"/>
-    </x:row>
-    <x:row r="17">
+      <x:c r="F16" s="11"/>
+    </x:row>
+    <x:row r="17" ht="20" customHeight="1">
       <x:c r="A17" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2345,9 +5350,9 @@
       <x:c r="E17" s="18" t="str">
         <x:v>06:40</x:v>
       </x:c>
-      <x:c r="F17" s="18" t="str"/>
-    </x:row>
-    <x:row r="18">
+      <x:c r="F17" s="11"/>
+    </x:row>
+    <x:row r="18" ht="20" customHeight="1">
       <x:c r="A18" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2363,9 +5368,9 @@
       <x:c r="E18" s="18" t="str">
         <x:v>06:45</x:v>
       </x:c>
-      <x:c r="F18" s="18" t="str"/>
-    </x:row>
-    <x:row r="19">
+      <x:c r="F18" s="11"/>
+    </x:row>
+    <x:row r="19" ht="20" customHeight="1">
       <x:c r="A19" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2381,9 +5386,9 @@
       <x:c r="E19" s="18" t="str">
         <x:v>06:15</x:v>
       </x:c>
-      <x:c r="F19" s="18" t="str"/>
-    </x:row>
-    <x:row r="20">
+      <x:c r="F19" s="11"/>
+    </x:row>
+    <x:row r="20" ht="20" customHeight="1">
       <x:c r="A20" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2399,9 +5404,9 @@
       <x:c r="E20" s="18" t="str">
         <x:v>06:45</x:v>
       </x:c>
-      <x:c r="F20" s="18" t="str"/>
-    </x:row>
-    <x:row r="21">
+      <x:c r="F20" s="11"/>
+    </x:row>
+    <x:row r="21" ht="20" customHeight="1">
       <x:c r="A21" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2417,9 +5422,9 @@
       <x:c r="E21" s="18" t="str">
         <x:v>06:40</x:v>
       </x:c>
-      <x:c r="F21" s="18" t="str"/>
-    </x:row>
-    <x:row r="22">
+      <x:c r="F21" s="11"/>
+    </x:row>
+    <x:row r="22" ht="20" customHeight="1">
       <x:c r="A22" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2435,9 +5440,9 @@
       <x:c r="E22" s="18" t="str">
         <x:v>06:43</x:v>
       </x:c>
-      <x:c r="F22" s="18" t="str"/>
-    </x:row>
-    <x:row r="23">
+      <x:c r="F22" s="11"/>
+    </x:row>
+    <x:row r="23" ht="20" customHeight="1">
       <x:c r="A23" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2453,9 +5458,9 @@
       <x:c r="E23" s="18" t="str">
         <x:v>06:45</x:v>
       </x:c>
-      <x:c r="F23" s="18" t="str"/>
-    </x:row>
-    <x:row r="24">
+      <x:c r="F23" s="11"/>
+    </x:row>
+    <x:row r="24" ht="20" customHeight="1">
       <x:c r="A24" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2471,9 +5476,9 @@
       <x:c r="E24" s="18" t="str">
         <x:v>06:33</x:v>
       </x:c>
-      <x:c r="F24" s="18" t="str"/>
-    </x:row>
-    <x:row r="25">
+      <x:c r="F24" s="11"/>
+    </x:row>
+    <x:row r="25" ht="20" customHeight="1">
       <x:c r="A25" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2489,9 +5494,9 @@
       <x:c r="E25" s="18" t="str">
         <x:v>06:36</x:v>
       </x:c>
-      <x:c r="F25" s="18" t="str"/>
-    </x:row>
-    <x:row r="26">
+      <x:c r="F25" s="11"/>
+    </x:row>
+    <x:row r="26" ht="20" customHeight="1">
       <x:c r="A26" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2507,9 +5512,9 @@
       <x:c r="E26" s="18" t="str">
         <x:v>06:53</x:v>
       </x:c>
-      <x:c r="F26" s="18" t="str"/>
-    </x:row>
-    <x:row r="27">
+      <x:c r="F26" s="11"/>
+    </x:row>
+    <x:row r="27" ht="20" customHeight="1">
       <x:c r="A27" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2525,9 +5530,9 @@
       <x:c r="E27" s="18" t="str">
         <x:v>06:56</x:v>
       </x:c>
-      <x:c r="F27" s="18" t="str"/>
-    </x:row>
-    <x:row r="28">
+      <x:c r="F27" s="11"/>
+    </x:row>
+    <x:row r="28" ht="20" customHeight="1">
       <x:c r="A28" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2543,9 +5548,9 @@
       <x:c r="E28" s="18" t="str">
         <x:v>07:02</x:v>
       </x:c>
-      <x:c r="F28" s="18" t="str"/>
-    </x:row>
-    <x:row r="29">
+      <x:c r="F28" s="11"/>
+    </x:row>
+    <x:row r="29" ht="20" customHeight="1">
       <x:c r="A29" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2561,9 +5566,9 @@
       <x:c r="E29" s="18" t="str">
         <x:v>07:30</x:v>
       </x:c>
-      <x:c r="F29" s="18" t="str"/>
-    </x:row>
-    <x:row r="30">
+      <x:c r="F29" s="11"/>
+    </x:row>
+    <x:row r="30" ht="20" customHeight="1">
       <x:c r="A30" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2579,9 +5584,9 @@
       <x:c r="E30" s="18" t="str">
         <x:v>07:10</x:v>
       </x:c>
-      <x:c r="F30" s="18" t="str"/>
-    </x:row>
-    <x:row r="31">
+      <x:c r="F30" s="11"/>
+    </x:row>
+    <x:row r="31" ht="20" customHeight="1">
       <x:c r="A31" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2597,9 +5602,9 @@
       <x:c r="E31" s="18" t="str">
         <x:v>07:13</x:v>
       </x:c>
-      <x:c r="F31" s="18" t="str"/>
-    </x:row>
-    <x:row r="32">
+      <x:c r="F31" s="11"/>
+    </x:row>
+    <x:row r="32" ht="20" customHeight="1">
       <x:c r="A32" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2615,9 +5620,9 @@
       <x:c r="E32" s="18" t="str">
         <x:v>07:18</x:v>
       </x:c>
-      <x:c r="F32" s="18" t="str"/>
-    </x:row>
-    <x:row r="33">
+      <x:c r="F32" s="11"/>
+    </x:row>
+    <x:row r="33" ht="20" customHeight="1">
       <x:c r="A33" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2633,9 +5638,9 @@
       <x:c r="E33" s="18" t="str">
         <x:v>07:26</x:v>
       </x:c>
-      <x:c r="F33" s="18" t="str"/>
-    </x:row>
-    <x:row r="34">
+      <x:c r="F33" s="11"/>
+    </x:row>
+    <x:row r="34" ht="20" customHeight="1">
       <x:c r="A34" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2651,9 +5656,9 @@
       <x:c r="E34" s="18" t="str">
         <x:v>07:32</x:v>
       </x:c>
-      <x:c r="F34" s="18" t="str"/>
-    </x:row>
-    <x:row r="35">
+      <x:c r="F34" s="11"/>
+    </x:row>
+    <x:row r="35" ht="20" customHeight="1">
       <x:c r="A35" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2669,9 +5674,9 @@
       <x:c r="E35" s="18" t="str">
         <x:v>07:30</x:v>
       </x:c>
-      <x:c r="F35" s="18" t="str"/>
-    </x:row>
-    <x:row r="36">
+      <x:c r="F35" s="11"/>
+    </x:row>
+    <x:row r="36" ht="20" customHeight="1">
       <x:c r="A36" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2687,9 +5692,9 @@
       <x:c r="E36" s="18" t="str">
         <x:v>06:50</x:v>
       </x:c>
-      <x:c r="F36" s="18" t="str"/>
-    </x:row>
-    <x:row r="37">
+      <x:c r="F36" s="11"/>
+    </x:row>
+    <x:row r="37" ht="20" customHeight="1">
       <x:c r="A37" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2705,9 +5710,9 @@
       <x:c r="E37" s="18" t="str">
         <x:v>06:52</x:v>
       </x:c>
-      <x:c r="F37" s="18" t="str"/>
-    </x:row>
-    <x:row r="38">
+      <x:c r="F37" s="11"/>
+    </x:row>
+    <x:row r="38" ht="20" customHeight="1">
       <x:c r="A38" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2723,9 +5728,9 @@
       <x:c r="E38" s="18" t="str">
         <x:v>06:55</x:v>
       </x:c>
-      <x:c r="F38" s="18" t="str"/>
-    </x:row>
-    <x:row r="39">
+      <x:c r="F38" s="11"/>
+    </x:row>
+    <x:row r="39" ht="20" customHeight="1">
       <x:c r="A39" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2741,9 +5746,9 @@
       <x:c r="E39" s="18" t="str">
         <x:v>07:05</x:v>
       </x:c>
-      <x:c r="F39" s="18" t="str"/>
-    </x:row>
-    <x:row r="40">
+      <x:c r="F39" s="11"/>
+    </x:row>
+    <x:row r="40" ht="20" customHeight="1">
       <x:c r="A40" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2759,9 +5764,9 @@
       <x:c r="E40" s="18" t="str">
         <x:v>06:57</x:v>
       </x:c>
-      <x:c r="F40" s="18" t="str"/>
-    </x:row>
-    <x:row r="41">
+      <x:c r="F40" s="11"/>
+    </x:row>
+    <x:row r="41" ht="20" customHeight="1">
       <x:c r="A41" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2777,9 +5782,9 @@
       <x:c r="E41" s="18" t="str">
         <x:v>07:08</x:v>
       </x:c>
-      <x:c r="F41" s="18" t="str"/>
-    </x:row>
-    <x:row r="42">
+      <x:c r="F41" s="11"/>
+    </x:row>
+    <x:row r="42" ht="20" customHeight="1">
       <x:c r="A42" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2795,9 +5800,9 @@
       <x:c r="E42" s="18" t="str">
         <x:v>06:58</x:v>
       </x:c>
-      <x:c r="F42" s="18" t="str"/>
-    </x:row>
-    <x:row r="43">
+      <x:c r="F42" s="11"/>
+    </x:row>
+    <x:row r="43" ht="20" customHeight="1">
       <x:c r="A43" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2813,9 +5818,9 @@
       <x:c r="E43" s="18" t="str">
         <x:v>07:00</x:v>
       </x:c>
-      <x:c r="F43" s="18" t="str"/>
-    </x:row>
-    <x:row r="44">
+      <x:c r="F43" s="11"/>
+    </x:row>
+    <x:row r="44" ht="20" customHeight="1">
       <x:c r="A44" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2831,9 +5836,9 @@
       <x:c r="E44" s="18" t="str">
         <x:v>06:53</x:v>
       </x:c>
-      <x:c r="F44" s="18" t="str"/>
-    </x:row>
-    <x:row r="45">
+      <x:c r="F44" s="11"/>
+    </x:row>
+    <x:row r="45" ht="20" customHeight="1">
       <x:c r="A45" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2849,9 +5854,9 @@
       <x:c r="E45" s="18" t="str">
         <x:v>07:03</x:v>
       </x:c>
-      <x:c r="F45" s="18" t="str"/>
-    </x:row>
-    <x:row r="46">
+      <x:c r="F45" s="11"/>
+    </x:row>
+    <x:row r="46" ht="20" customHeight="1">
       <x:c r="A46" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2867,9 +5872,9 @@
       <x:c r="E46" s="18" t="str">
         <x:v>07:13</x:v>
       </x:c>
-      <x:c r="F46" s="18" t="str"/>
-    </x:row>
-    <x:row r="47">
+      <x:c r="F46" s="11"/>
+    </x:row>
+    <x:row r="47" ht="20" customHeight="1">
       <x:c r="A47" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2885,9 +5890,9 @@
       <x:c r="E47" s="18" t="str">
         <x:v>07:19</x:v>
       </x:c>
-      <x:c r="F47" s="18" t="str"/>
-    </x:row>
-    <x:row r="48">
+      <x:c r="F47" s="11"/>
+    </x:row>
+    <x:row r="48" ht="20" customHeight="1">
       <x:c r="A48" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2903,9 +5908,9 @@
       <x:c r="E48" s="18" t="str">
         <x:v>07:22</x:v>
       </x:c>
-      <x:c r="F48" s="18" t="str"/>
-    </x:row>
-    <x:row r="49">
+      <x:c r="F48" s="11"/>
+    </x:row>
+    <x:row r="49" ht="20" customHeight="1">
       <x:c r="A49" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2921,9 +5926,9 @@
       <x:c r="E49" s="18" t="str">
         <x:v>07:06</x:v>
       </x:c>
-      <x:c r="F49" s="18" t="str"/>
-    </x:row>
-    <x:row r="50">
+      <x:c r="F49" s="11"/>
+    </x:row>
+    <x:row r="50" ht="20" customHeight="1">
       <x:c r="A50" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2939,9 +5944,9 @@
       <x:c r="E50" s="18" t="str">
         <x:v>07:10</x:v>
       </x:c>
-      <x:c r="F50" s="18" t="str"/>
-    </x:row>
-    <x:row r="51">
+      <x:c r="F50" s="11"/>
+    </x:row>
+    <x:row r="51" ht="20" customHeight="1">
       <x:c r="A51" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2957,9 +5962,9 @@
       <x:c r="E51" s="18" t="str">
         <x:v>07:12</x:v>
       </x:c>
-      <x:c r="F51" s="18" t="str"/>
-    </x:row>
-    <x:row r="52">
+      <x:c r="F51" s="11"/>
+    </x:row>
+    <x:row r="52" ht="20" customHeight="1">
       <x:c r="A52" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2975,9 +5980,9 @@
       <x:c r="E52" s="18" t="str">
         <x:v>07:14</x:v>
       </x:c>
-      <x:c r="F52" s="18" t="str"/>
-    </x:row>
-    <x:row r="53">
+      <x:c r="F52" s="11"/>
+    </x:row>
+    <x:row r="53" ht="20" customHeight="1">
       <x:c r="A53" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -2993,9 +5998,9 @@
       <x:c r="E53" s="18" t="str">
         <x:v>07:19</x:v>
       </x:c>
-      <x:c r="F53" s="18" t="str"/>
-    </x:row>
-    <x:row r="54">
+      <x:c r="F53" s="11"/>
+    </x:row>
+    <x:row r="54" ht="20" customHeight="1">
       <x:c r="A54" s="18" t="str">
         <x:v>TRUE</x:v>
       </x:c>
@@ -3011,17 +6016,2002 @@
       <x:c r="E54" s="18" t="str">
         <x:v>07:22</x:v>
       </x:c>
-      <x:c r="F54" s="18" t="str"/>
+      <x:c r="F54" s="11"/>
+    </x:row>
+    <x:row r="55" ht="20" customHeight="1">
+      <x:c r="A55" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B55" s="18" t="str">
+        <x:v>M021</x:v>
+      </x:c>
+      <x:c r="C55" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D55" s="18" t="str">
+        <x:v>S041</x:v>
+      </x:c>
+      <x:c r="E55" s="18" t="str">
+        <x:v>07:00</x:v>
+      </x:c>
+      <x:c r="F55" s="11"/>
+    </x:row>
+    <x:row r="56" ht="20" customHeight="1">
+      <x:c r="A56" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B56" s="18" t="str">
+        <x:v>M021</x:v>
+      </x:c>
+      <x:c r="C56" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D56" s="18" t="str">
+        <x:v>S050</x:v>
+      </x:c>
+      <x:c r="E56" s="18" t="str">
+        <x:v>07:05</x:v>
+      </x:c>
+      <x:c r="F56" s="11"/>
+    </x:row>
+    <x:row r="57" ht="20" customHeight="1">
+      <x:c r="A57" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B57" s="18" t="str">
+        <x:v>M021</x:v>
+      </x:c>
+      <x:c r="C57" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D57" s="18" t="str">
+        <x:v>S051</x:v>
+      </x:c>
+      <x:c r="E57" s="18" t="str">
+        <x:v>07:06</x:v>
+      </x:c>
+      <x:c r="F57" s="11"/>
+    </x:row>
+    <x:row r="58" ht="20" customHeight="1">
+      <x:c r="A58" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B58" s="18" t="str">
+        <x:v>M021</x:v>
+      </x:c>
+      <x:c r="C58" s="18" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D58" s="18" t="str">
+        <x:v>S052</x:v>
+      </x:c>
+      <x:c r="E58" s="18" t="str">
+        <x:v>07:25</x:v>
+      </x:c>
+      <x:c r="F58" s="11"/>
+    </x:row>
+    <x:row r="59" ht="20" customHeight="1">
+      <x:c r="A59" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B59" s="18" t="str">
+        <x:v>M022</x:v>
+      </x:c>
+      <x:c r="C59" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D59" s="18" t="str">
+        <x:v>S053</x:v>
+      </x:c>
+      <x:c r="E59" s="18" t="str">
+        <x:v>07:23</x:v>
+      </x:c>
+      <x:c r="F59" s="11"/>
+    </x:row>
+    <x:row r="60" ht="20" customHeight="1">
+      <x:c r="A60" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B60" s="18" t="str">
+        <x:v>M022</x:v>
+      </x:c>
+      <x:c r="C60" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D60" s="18" t="str">
+        <x:v>S054</x:v>
+      </x:c>
+      <x:c r="E60" s="18" t="str">
+        <x:v>07:27</x:v>
+      </x:c>
+      <x:c r="F60" s="11"/>
+    </x:row>
+    <x:row r="61" ht="20" customHeight="1">
+      <x:c r="A61" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B61" s="18" t="str">
+        <x:v>M022</x:v>
+      </x:c>
+      <x:c r="C61" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D61" s="18" t="str">
+        <x:v>S055</x:v>
+      </x:c>
+      <x:c r="E61" s="18" t="str">
+        <x:v>07:30</x:v>
+      </x:c>
+      <x:c r="F61" s="11"/>
+    </x:row>
+    <x:row r="62" ht="20" customHeight="1">
+      <x:c r="A62" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B62" s="18" t="str">
+        <x:v>M022</x:v>
+      </x:c>
+      <x:c r="C62" s="18" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D62" s="18" t="str">
+        <x:v>S056</x:v>
+      </x:c>
+      <x:c r="E62" s="18" t="str">
+        <x:v>07:35</x:v>
+      </x:c>
+      <x:c r="F62" s="11"/>
+    </x:row>
+    <x:row r="63" ht="20" customHeight="1">
+      <x:c r="A63" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B63" s="18" t="str">
+        <x:v>M023</x:v>
+      </x:c>
+      <x:c r="C63" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D63" s="18" t="str">
+        <x:v>S057</x:v>
+      </x:c>
+      <x:c r="E63" s="18" t="str">
+        <x:v>07:25</x:v>
+      </x:c>
+      <x:c r="F63" s="11"/>
+    </x:row>
+    <x:row r="64" ht="20" customHeight="1">
+      <x:c r="A64" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B64" s="18" t="str">
+        <x:v>M023</x:v>
+      </x:c>
+      <x:c r="C64" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D64" s="18" t="str">
+        <x:v>S058</x:v>
+      </x:c>
+      <x:c r="E64" s="18" t="str">
+        <x:v>07:28</x:v>
+      </x:c>
+      <x:c r="F64" s="11"/>
+    </x:row>
+    <x:row r="65" ht="20" customHeight="1">
+      <x:c r="A65" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B65" s="18" t="str">
+        <x:v>M023</x:v>
+      </x:c>
+      <x:c r="C65" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D65" s="18" t="str">
+        <x:v>S059</x:v>
+      </x:c>
+      <x:c r="E65" s="18" t="str">
+        <x:v>07:32</x:v>
+      </x:c>
+      <x:c r="F65" s="11"/>
+    </x:row>
+    <x:row r="66" ht="20" customHeight="1">
+      <x:c r="A66" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B66" s="18" t="str">
+        <x:v>M024</x:v>
+      </x:c>
+      <x:c r="C66" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D66" s="18" t="str">
+        <x:v>S060</x:v>
+      </x:c>
+      <x:c r="E66" s="18" t="str">
+        <x:v>07:47</x:v>
+      </x:c>
+      <x:c r="F66" s="11"/>
+    </x:row>
+    <x:row r="67" ht="20" customHeight="1">
+      <x:c r="A67" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B67" s="18" t="str">
+        <x:v>M025</x:v>
+      </x:c>
+      <x:c r="C67" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D67" s="18" t="str">
+        <x:v>S061</x:v>
+      </x:c>
+      <x:c r="E67" s="18" t="str">
+        <x:v>07:22</x:v>
+      </x:c>
+      <x:c r="F67" s="11"/>
+    </x:row>
+    <x:row r="68" ht="20" customHeight="1">
+      <x:c r="A68" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B68" s="18" t="str">
+        <x:v>M026</x:v>
+      </x:c>
+      <x:c r="C68" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D68" s="18" t="str">
+        <x:v>S062</x:v>
+      </x:c>
+      <x:c r="E68" s="18" t="str">
+        <x:v>07:24</x:v>
+      </x:c>
+      <x:c r="F68" s="11"/>
+    </x:row>
+    <x:row r="69" ht="20" customHeight="1">
+      <x:c r="A69" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B69" s="18" t="str">
+        <x:v>M026</x:v>
+      </x:c>
+      <x:c r="C69" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D69" s="18" t="str">
+        <x:v>S063</x:v>
+      </x:c>
+      <x:c r="E69" s="18" t="str">
+        <x:v>07:26</x:v>
+      </x:c>
+      <x:c r="F69" s="11"/>
+    </x:row>
+    <x:row r="70" ht="20" customHeight="1">
+      <x:c r="A70" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B70" s="18" t="str">
+        <x:v>M026</x:v>
+      </x:c>
+      <x:c r="C70" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D70" s="18" t="str">
+        <x:v>S064</x:v>
+      </x:c>
+      <x:c r="E70" s="18" t="str">
+        <x:v>07:29</x:v>
+      </x:c>
+      <x:c r="F70" s="11"/>
+    </x:row>
+    <x:row r="71" ht="20" customHeight="1">
+      <x:c r="A71" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B71" s="18" t="str">
+        <x:v>M027</x:v>
+      </x:c>
+      <x:c r="C71" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D71" s="18" t="str">
+        <x:v>S065</x:v>
+      </x:c>
+      <x:c r="E71" s="18" t="str">
+        <x:v>07:20</x:v>
+      </x:c>
+      <x:c r="F71" s="11"/>
+    </x:row>
+    <x:row r="72" ht="20" customHeight="1">
+      <x:c r="A72" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B72" s="18" t="str">
+        <x:v>M027</x:v>
+      </x:c>
+      <x:c r="C72" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D72" s="18" t="str">
+        <x:v>S066</x:v>
+      </x:c>
+      <x:c r="E72" s="18" t="str">
+        <x:v>07:22</x:v>
+      </x:c>
+      <x:c r="F72" s="11"/>
+    </x:row>
+    <x:row r="73" ht="20" customHeight="1">
+      <x:c r="A73" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B73" s="18" t="str">
+        <x:v>M027</x:v>
+      </x:c>
+      <x:c r="C73" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D73" s="18" t="str">
+        <x:v>S067</x:v>
+      </x:c>
+      <x:c r="E73" s="18" t="str">
+        <x:v>07:24</x:v>
+      </x:c>
+      <x:c r="F73" s="11"/>
+    </x:row>
+    <x:row r="74" ht="20" customHeight="1">
+      <x:c r="A74" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B74" s="18" t="str">
+        <x:v>M027</x:v>
+      </x:c>
+      <x:c r="C74" s="18" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D74" s="18" t="str">
+        <x:v>S068</x:v>
+      </x:c>
+      <x:c r="E74" s="18" t="str">
+        <x:v>07:26</x:v>
+      </x:c>
+      <x:c r="F74" s="11"/>
+    </x:row>
+    <x:row r="75" ht="20" customHeight="1">
+      <x:c r="A75" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B75" s="18" t="str">
+        <x:v>M027</x:v>
+      </x:c>
+      <x:c r="C75" s="18" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D75" s="18" t="str">
+        <x:v>S069</x:v>
+      </x:c>
+      <x:c r="E75" s="18" t="str">
+        <x:v>07:28</x:v>
+      </x:c>
+      <x:c r="F75" s="11"/>
+    </x:row>
+    <x:row r="76" ht="20" customHeight="1">
+      <x:c r="A76" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B76" s="18" t="str">
+        <x:v>M028</x:v>
+      </x:c>
+      <x:c r="C76" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D76" s="18" t="str">
+        <x:v>S070</x:v>
+      </x:c>
+      <x:c r="E76" s="18" t="str">
+        <x:v>07:22</x:v>
+      </x:c>
+      <x:c r="F76" s="11"/>
+    </x:row>
+    <x:row r="77" ht="20" customHeight="1">
+      <x:c r="A77" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B77" s="18" t="str">
+        <x:v>M028</x:v>
+      </x:c>
+      <x:c r="C77" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D77" s="18" t="str">
+        <x:v>S071</x:v>
+      </x:c>
+      <x:c r="E77" s="18" t="str">
+        <x:v>07:24</x:v>
+      </x:c>
+      <x:c r="F77" s="11"/>
+    </x:row>
+    <x:row r="78" ht="20" customHeight="1">
+      <x:c r="A78" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B78" s="18" t="str">
+        <x:v>M028</x:v>
+      </x:c>
+      <x:c r="C78" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D78" s="18" t="str">
+        <x:v>S072</x:v>
+      </x:c>
+      <x:c r="E78" s="18" t="str">
+        <x:v>07:26</x:v>
+      </x:c>
+      <x:c r="F78" s="11"/>
+    </x:row>
+    <x:row r="79" ht="20" customHeight="1">
+      <x:c r="A79" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B79" s="18" t="str">
+        <x:v>M028</x:v>
+      </x:c>
+      <x:c r="C79" s="18" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D79" s="18" t="str">
+        <x:v>S073</x:v>
+      </x:c>
+      <x:c r="E79" s="18" t="str">
+        <x:v>07:35</x:v>
+      </x:c>
+      <x:c r="F79" s="11"/>
+    </x:row>
+    <x:row r="80" ht="20" customHeight="1">
+      <x:c r="A80" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B80" s="18" t="str">
+        <x:v>M028</x:v>
+      </x:c>
+      <x:c r="C80" s="18" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D80" s="18" t="str">
+        <x:v>S074</x:v>
+      </x:c>
+      <x:c r="E80" s="18" t="str">
+        <x:v>07:37</x:v>
+      </x:c>
+      <x:c r="F80" s="11"/>
+    </x:row>
+    <x:row r="81" ht="20" customHeight="1">
+      <x:c r="A81" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B81" s="18" t="str">
+        <x:v>M029</x:v>
+      </x:c>
+      <x:c r="C81" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D81" s="18" t="str">
+        <x:v>S075</x:v>
+      </x:c>
+      <x:c r="E81" s="18" t="str">
+        <x:v>07:30</x:v>
+      </x:c>
+      <x:c r="F81" s="11"/>
+    </x:row>
+    <x:row r="82" ht="20" customHeight="1">
+      <x:c r="A82" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B82" s="18" t="str">
+        <x:v>M029</x:v>
+      </x:c>
+      <x:c r="C82" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D82" s="18" t="str">
+        <x:v>S076</x:v>
+      </x:c>
+      <x:c r="E82" s="18" t="str">
+        <x:v>07:34</x:v>
+      </x:c>
+      <x:c r="F82" s="11"/>
+    </x:row>
+    <x:row r="83" ht="20" customHeight="1">
+      <x:c r="A83" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B83" s="18" t="str">
+        <x:v>M030</x:v>
+      </x:c>
+      <x:c r="C83" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D83" s="18" t="str">
+        <x:v>S077</x:v>
+      </x:c>
+      <x:c r="E83" s="18" t="str">
+        <x:v>07:01</x:v>
+      </x:c>
+      <x:c r="F83" s="11"/>
+    </x:row>
+    <x:row r="84" ht="20" customHeight="1">
+      <x:c r="A84" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B84" s="18" t="str">
+        <x:v>M030</x:v>
+      </x:c>
+      <x:c r="C84" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D84" s="18" t="str">
+        <x:v>S078</x:v>
+      </x:c>
+      <x:c r="E84" s="18" t="str">
+        <x:v>07:09</x:v>
+      </x:c>
+      <x:c r="F84" s="11"/>
+    </x:row>
+    <x:row r="85" ht="20" customHeight="1">
+      <x:c r="A85" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B85" s="18" t="str">
+        <x:v>M030</x:v>
+      </x:c>
+      <x:c r="C85" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D85" s="18" t="str">
+        <x:v>S079</x:v>
+      </x:c>
+      <x:c r="E85" s="18" t="str">
+        <x:v>07:12</x:v>
+      </x:c>
+      <x:c r="F85" s="11"/>
+    </x:row>
+    <x:row r="86" ht="20" customHeight="1">
+      <x:c r="A86" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B86" s="18" t="str">
+        <x:v>M030</x:v>
+      </x:c>
+      <x:c r="C86" s="18" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D86" s="18" t="str">
+        <x:v>S080</x:v>
+      </x:c>
+      <x:c r="E86" s="18" t="str">
+        <x:v>07:17</x:v>
+      </x:c>
+      <x:c r="F86" s="11"/>
+    </x:row>
+    <x:row r="87" ht="20" customHeight="1">
+      <x:c r="A87" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B87" s="18" t="str">
+        <x:v>M030</x:v>
+      </x:c>
+      <x:c r="C87" s="18" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D87" s="18" t="str">
+        <x:v>S081</x:v>
+      </x:c>
+      <x:c r="E87" s="18" t="str">
+        <x:v>07:19</x:v>
+      </x:c>
+      <x:c r="F87" s="11"/>
+    </x:row>
+    <x:row r="88" ht="20" customHeight="1">
+      <x:c r="A88" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B88" s="18" t="str">
+        <x:v>M030</x:v>
+      </x:c>
+      <x:c r="C88" s="18" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D88" s="18" t="str">
+        <x:v>S082</x:v>
+      </x:c>
+      <x:c r="E88" s="18" t="str">
+        <x:v>07:21</x:v>
+      </x:c>
+      <x:c r="F88" s="11"/>
+    </x:row>
+    <x:row r="89" ht="20" customHeight="1">
+      <x:c r="A89" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B89" s="18" t="str">
+        <x:v>M031</x:v>
+      </x:c>
+      <x:c r="C89" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D89" s="18" t="str">
+        <x:v>S083</x:v>
+      </x:c>
+      <x:c r="E89" s="18" t="str">
+        <x:v>07:25</x:v>
+      </x:c>
+      <x:c r="F89" s="11"/>
+    </x:row>
+    <x:row r="90" ht="20" customHeight="1">
+      <x:c r="A90" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B90" s="18" t="str">
+        <x:v>M031</x:v>
+      </x:c>
+      <x:c r="C90" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D90" s="18" t="str">
+        <x:v>S084</x:v>
+      </x:c>
+      <x:c r="E90" s="18" t="str">
+        <x:v>07:33</x:v>
+      </x:c>
+      <x:c r="F90" s="11"/>
+    </x:row>
+    <x:row r="91" ht="20" customHeight="1">
+      <x:c r="A91" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B91" s="18" t="str">
+        <x:v>M031</x:v>
+      </x:c>
+      <x:c r="C91" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D91" s="18" t="str">
+        <x:v>S085</x:v>
+      </x:c>
+      <x:c r="E91" s="18" t="str">
+        <x:v>07:37</x:v>
+      </x:c>
+      <x:c r="F91" s="11"/>
+    </x:row>
+    <x:row r="92" ht="20" customHeight="1">
+      <x:c r="A92" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B92" s="18" t="str">
+        <x:v>M032</x:v>
+      </x:c>
+      <x:c r="C92" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D92" s="18" t="str">
+        <x:v>S086</x:v>
+      </x:c>
+      <x:c r="E92" s="18" t="str">
+        <x:v>07:12</x:v>
+      </x:c>
+      <x:c r="F92" s="11"/>
+    </x:row>
+    <x:row r="93" ht="20" customHeight="1">
+      <x:c r="A93" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B93" s="18" t="str">
+        <x:v>M032</x:v>
+      </x:c>
+      <x:c r="C93" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D93" s="18" t="str">
+        <x:v>S087</x:v>
+      </x:c>
+      <x:c r="E93" s="18" t="str">
+        <x:v>07:15</x:v>
+      </x:c>
+      <x:c r="F93" s="11"/>
+    </x:row>
+    <x:row r="94" ht="20" customHeight="1">
+      <x:c r="A94" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B94" s="18" t="str">
+        <x:v>M032</x:v>
+      </x:c>
+      <x:c r="C94" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D94" s="18" t="str">
+        <x:v>S088</x:v>
+      </x:c>
+      <x:c r="E94" s="18" t="str">
+        <x:v>07:32</x:v>
+      </x:c>
+      <x:c r="F94" s="11"/>
+    </x:row>
+    <x:row r="95" ht="20" customHeight="1">
+      <x:c r="A95" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B95" s="18" t="str">
+        <x:v>M033</x:v>
+      </x:c>
+      <x:c r="C95" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D95" s="18" t="str">
+        <x:v>S089</x:v>
+      </x:c>
+      <x:c r="E95" s="18" t="str">
+        <x:v>07:20</x:v>
+      </x:c>
+      <x:c r="F95" s="11"/>
+    </x:row>
+    <x:row r="96" ht="20" customHeight="1">
+      <x:c r="A96" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B96" s="18" t="str">
+        <x:v>M033</x:v>
+      </x:c>
+      <x:c r="C96" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D96" s="18" t="str">
+        <x:v>S090</x:v>
+      </x:c>
+      <x:c r="E96" s="18" t="str">
+        <x:v>07:22</x:v>
+      </x:c>
+      <x:c r="F96" s="11"/>
+    </x:row>
+    <x:row r="97" ht="20" customHeight="1">
+      <x:c r="A97" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B97" s="18" t="str">
+        <x:v>M034</x:v>
+      </x:c>
+      <x:c r="C97" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D97" s="18" t="str">
+        <x:v>S091</x:v>
+      </x:c>
+      <x:c r="E97" s="18" t="str">
+        <x:v>07:28</x:v>
+      </x:c>
+      <x:c r="F97" s="11"/>
+    </x:row>
+    <x:row r="98" ht="20" customHeight="1">
+      <x:c r="A98" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B98" s="18" t="str">
+        <x:v>M034</x:v>
+      </x:c>
+      <x:c r="C98" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D98" s="18" t="str">
+        <x:v>S092</x:v>
+      </x:c>
+      <x:c r="E98" s="18" t="str">
+        <x:v>07:33</x:v>
+      </x:c>
+      <x:c r="F98" s="11"/>
+    </x:row>
+    <x:row r="99" ht="20" customHeight="1">
+      <x:c r="A99" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B99" s="18" t="str">
+        <x:v>M035</x:v>
+      </x:c>
+      <x:c r="C99" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D99" s="18" t="str">
+        <x:v>S093</x:v>
+      </x:c>
+      <x:c r="E99" s="18" t="str">
+        <x:v>07:15</x:v>
+      </x:c>
+      <x:c r="F99" s="11"/>
+    </x:row>
+    <x:row r="100" ht="20" customHeight="1">
+      <x:c r="A100" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B100" s="18" t="str">
+        <x:v>M035</x:v>
+      </x:c>
+      <x:c r="C100" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D100" s="18" t="str">
+        <x:v>S094</x:v>
+      </x:c>
+      <x:c r="E100" s="18" t="str">
+        <x:v>07:26</x:v>
+      </x:c>
+      <x:c r="F100" s="11"/>
+    </x:row>
+    <x:row r="101" ht="20" customHeight="1">
+      <x:c r="A101" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B101" s="18" t="str">
+        <x:v>M035</x:v>
+      </x:c>
+      <x:c r="C101" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D101" s="18" t="str">
+        <x:v>S095</x:v>
+      </x:c>
+      <x:c r="E101" s="18" t="str">
+        <x:v>07:35</x:v>
+      </x:c>
+      <x:c r="F101" s="11"/>
+    </x:row>
+    <x:row r="102" ht="20" customHeight="1">
+      <x:c r="A102" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B102" s="18" t="str">
+        <x:v>M036</x:v>
+      </x:c>
+      <x:c r="C102" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D102" s="18" t="str">
+        <x:v>S096</x:v>
+      </x:c>
+      <x:c r="E102" s="18" t="str">
+        <x:v>07:22</x:v>
+      </x:c>
+      <x:c r="F102" s="11"/>
+    </x:row>
+    <x:row r="103" ht="20" customHeight="1">
+      <x:c r="A103" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B103" s="18" t="str">
+        <x:v>M036</x:v>
+      </x:c>
+      <x:c r="C103" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D103" s="18" t="str">
+        <x:v>S097</x:v>
+      </x:c>
+      <x:c r="E103" s="18" t="str">
+        <x:v>07:25</x:v>
+      </x:c>
+      <x:c r="F103" s="11"/>
+    </x:row>
+    <x:row r="104" ht="20" customHeight="1">
+      <x:c r="A104" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B104" s="18" t="str">
+        <x:v>M036</x:v>
+      </x:c>
+      <x:c r="C104" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D104" s="18" t="str">
+        <x:v>S098</x:v>
+      </x:c>
+      <x:c r="E104" s="18" t="str">
+        <x:v>07:30</x:v>
+      </x:c>
+      <x:c r="F104" s="11"/>
+    </x:row>
+    <x:row r="105" ht="20" customHeight="1">
+      <x:c r="A105" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B105" s="18" t="str">
+        <x:v>M036</x:v>
+      </x:c>
+      <x:c r="C105" s="18" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D105" s="18" t="str">
+        <x:v>S095</x:v>
+      </x:c>
+      <x:c r="E105" s="18" t="str">
+        <x:v>07:35</x:v>
+      </x:c>
+      <x:c r="F105" s="11"/>
+    </x:row>
+    <x:row r="106" ht="20" customHeight="1">
+      <x:c r="A106" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B106" s="18" t="str">
+        <x:v>M037</x:v>
+      </x:c>
+      <x:c r="C106" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D106" s="18" t="str">
+        <x:v>S099</x:v>
+      </x:c>
+      <x:c r="E106" s="18" t="str">
+        <x:v>07:17</x:v>
+      </x:c>
+      <x:c r="F106" s="11"/>
+    </x:row>
+    <x:row r="107" ht="20" customHeight="1">
+      <x:c r="A107" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B107" s="18" t="str">
+        <x:v>M037</x:v>
+      </x:c>
+      <x:c r="C107" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D107" s="18" t="str">
+        <x:v>S100</x:v>
+      </x:c>
+      <x:c r="E107" s="18" t="str">
+        <x:v>07:22</x:v>
+      </x:c>
+      <x:c r="F107" s="11"/>
+    </x:row>
+    <x:row r="108" ht="20" customHeight="1">
+      <x:c r="A108" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B108" s="18" t="str">
+        <x:v>M037</x:v>
+      </x:c>
+      <x:c r="C108" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D108" s="18" t="str">
+        <x:v>S101</x:v>
+      </x:c>
+      <x:c r="E108" s="18" t="str">
+        <x:v>07:25</x:v>
+      </x:c>
+      <x:c r="F108" s="11"/>
+    </x:row>
+    <x:row r="109" ht="20" customHeight="1">
+      <x:c r="A109" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B109" s="18" t="str">
+        <x:v>M037</x:v>
+      </x:c>
+      <x:c r="C109" s="18" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D109" s="18" t="str">
+        <x:v>S102</x:v>
+      </x:c>
+      <x:c r="E109" s="18" t="str">
+        <x:v>07:27</x:v>
+      </x:c>
+      <x:c r="F109" s="11"/>
+    </x:row>
+    <x:row r="110" ht="20" customHeight="1">
+      <x:c r="A110" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B110" s="18" t="str">
+        <x:v>M037</x:v>
+      </x:c>
+      <x:c r="C110" s="18" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D110" s="18" t="str">
+        <x:v>S095</x:v>
+      </x:c>
+      <x:c r="E110" s="18" t="str">
+        <x:v>07:38</x:v>
+      </x:c>
+      <x:c r="F110" s="11"/>
+    </x:row>
+    <x:row r="111" ht="20" customHeight="1">
+      <x:c r="A111" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B111" s="18" t="str">
+        <x:v>M038</x:v>
+      </x:c>
+      <x:c r="C111" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D111" s="18" t="str">
+        <x:v>S103</x:v>
+      </x:c>
+      <x:c r="E111" s="18" t="str">
+        <x:v>07:15</x:v>
+      </x:c>
+      <x:c r="F111" s="11"/>
+    </x:row>
+    <x:row r="112" ht="20" customHeight="1">
+      <x:c r="A112" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B112" s="18" t="str">
+        <x:v>M038</x:v>
+      </x:c>
+      <x:c r="C112" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D112" s="18" t="str">
+        <x:v>S104</x:v>
+      </x:c>
+      <x:c r="E112" s="18" t="str">
+        <x:v>07:19</x:v>
+      </x:c>
+      <x:c r="F112" s="11"/>
+    </x:row>
+    <x:row r="113" ht="20" customHeight="1">
+      <x:c r="A113" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B113" s="18" t="str">
+        <x:v>M039</x:v>
+      </x:c>
+      <x:c r="C113" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D113" s="18" t="str">
+        <x:v>S105</x:v>
+      </x:c>
+      <x:c r="E113" s="18" t="str">
+        <x:v>07:05</x:v>
+      </x:c>
+      <x:c r="F113" s="11"/>
+    </x:row>
+    <x:row r="114" ht="20" customHeight="1">
+      <x:c r="A114" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B114" s="18" t="str">
+        <x:v>M039</x:v>
+      </x:c>
+      <x:c r="C114" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D114" s="18" t="str">
+        <x:v>S106</x:v>
+      </x:c>
+      <x:c r="E114" s="18" t="str">
+        <x:v>07:12</x:v>
+      </x:c>
+      <x:c r="F114" s="11"/>
+    </x:row>
+    <x:row r="115" ht="20" customHeight="1">
+      <x:c r="A115" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B115" s="18" t="str">
+        <x:v>M039</x:v>
+      </x:c>
+      <x:c r="C115" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D115" s="18" t="str">
+        <x:v>S104</x:v>
+      </x:c>
+      <x:c r="E115" s="18" t="str">
+        <x:v>07:19</x:v>
+      </x:c>
+      <x:c r="F115" s="11"/>
+    </x:row>
+    <x:row r="116" ht="20" customHeight="1">
+      <x:c r="A116" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B116" s="18" t="str">
+        <x:v>M040</x:v>
+      </x:c>
+      <x:c r="C116" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D116" s="18" t="str">
+        <x:v>S107</x:v>
+      </x:c>
+      <x:c r="E116" s="18" t="str">
+        <x:v>06:58</x:v>
+      </x:c>
+      <x:c r="F116" s="11"/>
+    </x:row>
+    <x:row r="117" ht="20" customHeight="1">
+      <x:c r="A117" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B117" s="18" t="str">
+        <x:v>M040</x:v>
+      </x:c>
+      <x:c r="C117" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D117" s="18" t="str">
+        <x:v>S108</x:v>
+      </x:c>
+      <x:c r="E117" s="18" t="str">
+        <x:v>07:05</x:v>
+      </x:c>
+      <x:c r="F117" s="11"/>
+    </x:row>
+    <x:row r="118" ht="20" customHeight="1">
+      <x:c r="A118" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B118" s="18" t="str">
+        <x:v>M040</x:v>
+      </x:c>
+      <x:c r="C118" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D118" s="18" t="str">
+        <x:v>S104</x:v>
+      </x:c>
+      <x:c r="E118" s="18" t="str">
+        <x:v>07:19</x:v>
+      </x:c>
+      <x:c r="F118" s="11"/>
+    </x:row>
+    <x:row r="119" ht="20" customHeight="1">
+      <x:c r="A119" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B119" s="18" t="str">
+        <x:v>M041</x:v>
+      </x:c>
+      <x:c r="C119" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D119" s="18" t="str">
+        <x:v>S109</x:v>
+      </x:c>
+      <x:c r="E119" s="18" t="str">
+        <x:v>07:05</x:v>
+      </x:c>
+      <x:c r="F119" s="11"/>
+    </x:row>
+    <x:row r="120" ht="20" customHeight="1">
+      <x:c r="A120" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B120" s="18" t="str">
+        <x:v>M041</x:v>
+      </x:c>
+      <x:c r="C120" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D120" s="18" t="str">
+        <x:v>S110</x:v>
+      </x:c>
+      <x:c r="E120" s="18" t="str">
+        <x:v>07:10</x:v>
+      </x:c>
+      <x:c r="F120" s="11"/>
+    </x:row>
+    <x:row r="121" ht="20" customHeight="1">
+      <x:c r="A121" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B121" s="18" t="str">
+        <x:v>M041</x:v>
+      </x:c>
+      <x:c r="C121" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D121" s="18" t="str">
+        <x:v>S104</x:v>
+      </x:c>
+      <x:c r="E121" s="18" t="str">
+        <x:v>07:19</x:v>
+      </x:c>
+      <x:c r="F121" s="11"/>
+    </x:row>
+    <x:row r="122" ht="20" customHeight="1">
+      <x:c r="A122" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B122" s="18" t="str">
+        <x:v>M042</x:v>
+      </x:c>
+      <x:c r="C122" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D122" s="18" t="str">
+        <x:v>S111</x:v>
+      </x:c>
+      <x:c r="E122" s="18" t="str">
+        <x:v>07:00</x:v>
+      </x:c>
+      <x:c r="F122" s="11"/>
+    </x:row>
+    <x:row r="123" ht="20" customHeight="1">
+      <x:c r="A123" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B123" s="18" t="str">
+        <x:v>M042</x:v>
+      </x:c>
+      <x:c r="C123" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D123" s="18" t="str">
+        <x:v>S112</x:v>
+      </x:c>
+      <x:c r="E123" s="18" t="str">
+        <x:v>07:08</x:v>
+      </x:c>
+      <x:c r="F123" s="11"/>
+    </x:row>
+    <x:row r="124" ht="20" customHeight="1">
+      <x:c r="A124" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B124" s="18" t="str">
+        <x:v>M042</x:v>
+      </x:c>
+      <x:c r="C124" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D124" s="18" t="str">
+        <x:v>S113</x:v>
+      </x:c>
+      <x:c r="E124" s="18" t="str">
+        <x:v>07:16</x:v>
+      </x:c>
+      <x:c r="F124" s="11"/>
+    </x:row>
+    <x:row r="125" ht="20" customHeight="1">
+      <x:c r="A125" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B125" s="18" t="str">
+        <x:v>M043</x:v>
+      </x:c>
+      <x:c r="C125" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D125" s="18" t="str">
+        <x:v>S114</x:v>
+      </x:c>
+      <x:c r="E125" s="18" t="str">
+        <x:v>07:03</x:v>
+      </x:c>
+      <x:c r="F125" s="11"/>
+    </x:row>
+    <x:row r="126" ht="20" customHeight="1">
+      <x:c r="A126" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B126" s="18" t="str">
+        <x:v>M043</x:v>
+      </x:c>
+      <x:c r="C126" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D126" s="18" t="str">
+        <x:v>S115</x:v>
+      </x:c>
+      <x:c r="E126" s="18" t="str">
+        <x:v>07:12</x:v>
+      </x:c>
+      <x:c r="F126" s="11"/>
+    </x:row>
+    <x:row r="127" ht="20" customHeight="1">
+      <x:c r="A127" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B127" s="18" t="str">
+        <x:v>M043</x:v>
+      </x:c>
+      <x:c r="C127" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D127" s="18" t="str">
+        <x:v>S113</x:v>
+      </x:c>
+      <x:c r="E127" s="18" t="str">
+        <x:v>07:16</x:v>
+      </x:c>
+      <x:c r="F127" s="11"/>
+    </x:row>
+    <x:row r="128" ht="20" customHeight="1">
+      <x:c r="A128" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B128" s="18" t="str">
+        <x:v>M044</x:v>
+      </x:c>
+      <x:c r="C128" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D128" s="18" t="str">
+        <x:v>S116</x:v>
+      </x:c>
+      <x:c r="E128" s="18" t="str">
+        <x:v>07:26</x:v>
+      </x:c>
+      <x:c r="F128" s="11"/>
+    </x:row>
+    <x:row r="129" ht="20" customHeight="1">
+      <x:c r="A129" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B129" s="18" t="str">
+        <x:v>M044</x:v>
+      </x:c>
+      <x:c r="C129" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D129" s="18" t="str">
+        <x:v>S117</x:v>
+      </x:c>
+      <x:c r="E129" s="18" t="str">
+        <x:v>07:30</x:v>
+      </x:c>
+      <x:c r="F129" s="11"/>
+    </x:row>
+    <x:row r="130" ht="20" customHeight="1">
+      <x:c r="A130" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B130" s="18" t="str">
+        <x:v>M045</x:v>
+      </x:c>
+      <x:c r="C130" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D130" s="18" t="str">
+        <x:v>S117</x:v>
+      </x:c>
+      <x:c r="E130" s="18" t="str">
+        <x:v>07:30</x:v>
+      </x:c>
+      <x:c r="F130" s="11"/>
+    </x:row>
+    <x:row r="131" ht="20" customHeight="1">
+      <x:c r="A131" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B131" s="18" t="str">
+        <x:v>M046</x:v>
+      </x:c>
+      <x:c r="C131" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D131" s="18" t="str">
+        <x:v>S118</x:v>
+      </x:c>
+      <x:c r="E131" s="18" t="str">
+        <x:v>07:20</x:v>
+      </x:c>
+      <x:c r="F131" s="11"/>
+    </x:row>
+    <x:row r="132" ht="20" customHeight="1">
+      <x:c r="A132" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B132" s="18" t="str">
+        <x:v>M046</x:v>
+      </x:c>
+      <x:c r="C132" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D132" s="18" t="str">
+        <x:v>S117</x:v>
+      </x:c>
+      <x:c r="E132" s="18" t="str">
+        <x:v>07:30</x:v>
+      </x:c>
+      <x:c r="F132" s="11"/>
+    </x:row>
+    <x:row r="133" ht="20" customHeight="1">
+      <x:c r="A133" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B133" s="18" t="str">
+        <x:v>M047</x:v>
+      </x:c>
+      <x:c r="C133" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D133" s="18" t="str">
+        <x:v>S117</x:v>
+      </x:c>
+      <x:c r="E133" s="18" t="str">
+        <x:v>07:25</x:v>
+      </x:c>
+      <x:c r="F133" s="11"/>
+    </x:row>
+    <x:row r="134" ht="20" customHeight="1">
+      <x:c r="A134" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B134" s="18" t="str">
+        <x:v>M048</x:v>
+      </x:c>
+      <x:c r="C134" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D134" s="18" t="str">
+        <x:v>S119</x:v>
+      </x:c>
+      <x:c r="E134" s="18" t="str">
+        <x:v>07:15</x:v>
+      </x:c>
+      <x:c r="F134" s="11"/>
+    </x:row>
+    <x:row r="135" ht="20" customHeight="1">
+      <x:c r="A135" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B135" s="18" t="str">
+        <x:v>M049</x:v>
+      </x:c>
+      <x:c r="C135" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D135" s="18" t="str">
+        <x:v>S120</x:v>
+      </x:c>
+      <x:c r="E135" s="18" t="str">
+        <x:v>07:15</x:v>
+      </x:c>
+      <x:c r="F135" s="11"/>
+    </x:row>
+    <x:row r="136" ht="20" customHeight="1">
+      <x:c r="A136" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B136" s="18" t="str">
+        <x:v>M049</x:v>
+      </x:c>
+      <x:c r="C136" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D136" s="18" t="str">
+        <x:v>S121</x:v>
+      </x:c>
+      <x:c r="E136" s="18" t="str">
+        <x:v>07:21</x:v>
+      </x:c>
+      <x:c r="F136" s="11"/>
+    </x:row>
+    <x:row r="137" ht="20" customHeight="1">
+      <x:c r="A137" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B137" s="18" t="str">
+        <x:v>M050</x:v>
+      </x:c>
+      <x:c r="C137" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D137" s="18" t="str">
+        <x:v>S122</x:v>
+      </x:c>
+      <x:c r="E137" s="18" t="str">
+        <x:v>06:58</x:v>
+      </x:c>
+      <x:c r="F137" s="11"/>
+    </x:row>
+    <x:row r="138" ht="20" customHeight="1">
+      <x:c r="A138" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B138" s="18" t="str">
+        <x:v>M050</x:v>
+      </x:c>
+      <x:c r="C138" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D138" s="18" t="str">
+        <x:v>S123</x:v>
+      </x:c>
+      <x:c r="E138" s="18" t="str">
+        <x:v>07:04</x:v>
+      </x:c>
+      <x:c r="F138" s="11"/>
+    </x:row>
+    <x:row r="139" ht="20" customHeight="1">
+      <x:c r="A139" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B139" s="18" t="str">
+        <x:v>M050</x:v>
+      </x:c>
+      <x:c r="C139" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D139" s="18" t="str">
+        <x:v>S124</x:v>
+      </x:c>
+      <x:c r="E139" s="18" t="str">
+        <x:v>07:15</x:v>
+      </x:c>
+      <x:c r="F139" s="11"/>
+    </x:row>
+    <x:row r="140" ht="20" customHeight="1">
+      <x:c r="A140" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B140" s="18" t="str">
+        <x:v>M050</x:v>
+      </x:c>
+      <x:c r="C140" s="18" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D140" s="18" t="str">
+        <x:v>S121</x:v>
+      </x:c>
+      <x:c r="E140" s="18" t="str">
+        <x:v>07:21</x:v>
+      </x:c>
+      <x:c r="F140" s="11"/>
+    </x:row>
+    <x:row r="141" ht="20" customHeight="1">
+      <x:c r="A141" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B141" s="18" t="str">
+        <x:v>M051</x:v>
+      </x:c>
+      <x:c r="C141" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D141" s="18" t="str">
+        <x:v>S125</x:v>
+      </x:c>
+      <x:c r="E141" s="18" t="str">
+        <x:v>07:25</x:v>
+      </x:c>
+      <x:c r="F141" s="11"/>
+    </x:row>
+    <x:row r="142" ht="20" customHeight="1">
+      <x:c r="A142" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B142" s="18" t="str">
+        <x:v>M051</x:v>
+      </x:c>
+      <x:c r="C142" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D142" s="18" t="str">
+        <x:v>S126</x:v>
+      </x:c>
+      <x:c r="E142" s="18" t="str">
+        <x:v>07:28</x:v>
+      </x:c>
+      <x:c r="F142" s="11"/>
+    </x:row>
+    <x:row r="143" ht="20" customHeight="1">
+      <x:c r="A143" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B143" s="18" t="str">
+        <x:v>M052</x:v>
+      </x:c>
+      <x:c r="C143" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D143" s="18" t="str">
+        <x:v>S127</x:v>
+      </x:c>
+      <x:c r="E143" s="18" t="str">
+        <x:v>07:23</x:v>
+      </x:c>
+      <x:c r="F143" s="11"/>
+    </x:row>
+    <x:row r="144" ht="20" customHeight="1">
+      <x:c r="A144" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B144" s="18" t="str">
+        <x:v>M052</x:v>
+      </x:c>
+      <x:c r="C144" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D144" s="18" t="str">
+        <x:v>S128</x:v>
+      </x:c>
+      <x:c r="E144" s="18" t="str">
+        <x:v>07:25</x:v>
+      </x:c>
+      <x:c r="F144" s="11"/>
+    </x:row>
+    <x:row r="145" ht="20" customHeight="1">
+      <x:c r="A145" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B145" s="18" t="str">
+        <x:v>M053</x:v>
+      </x:c>
+      <x:c r="C145" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D145" s="18" t="str">
+        <x:v>S129</x:v>
+      </x:c>
+      <x:c r="E145" s="18" t="str">
+        <x:v>07:19</x:v>
+      </x:c>
+      <x:c r="F145" s="11"/>
+    </x:row>
+    <x:row r="146" ht="20" customHeight="1">
+      <x:c r="A146" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B146" s="18" t="str">
+        <x:v>M053</x:v>
+      </x:c>
+      <x:c r="C146" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D146" s="18" t="str">
+        <x:v>S130</x:v>
+      </x:c>
+      <x:c r="E146" s="18" t="str">
+        <x:v>07:24</x:v>
+      </x:c>
+      <x:c r="F146" s="11"/>
+    </x:row>
+    <x:row r="147" ht="20" customHeight="1">
+      <x:c r="A147" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B147" s="18" t="str">
+        <x:v>M053</x:v>
+      </x:c>
+      <x:c r="C147" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D147" s="18" t="str">
+        <x:v>S131</x:v>
+      </x:c>
+      <x:c r="E147" s="18" t="str">
+        <x:v>07:27</x:v>
+      </x:c>
+      <x:c r="F147" s="11"/>
+    </x:row>
+    <x:row r="148" ht="20" customHeight="1">
+      <x:c r="A148" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B148" s="18" t="str">
+        <x:v>M054</x:v>
+      </x:c>
+      <x:c r="C148" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D148" s="18" t="str">
+        <x:v>S132</x:v>
+      </x:c>
+      <x:c r="E148" s="18" t="str">
+        <x:v>07:12</x:v>
+      </x:c>
+      <x:c r="F148" s="11"/>
+    </x:row>
+    <x:row r="149" ht="20" customHeight="1">
+      <x:c r="A149" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B149" s="18" t="str">
+        <x:v>M054</x:v>
+      </x:c>
+      <x:c r="C149" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D149" s="18" t="str">
+        <x:v>S133</x:v>
+      </x:c>
+      <x:c r="E149" s="18" t="str">
+        <x:v>07:18</x:v>
+      </x:c>
+      <x:c r="F149" s="11"/>
+    </x:row>
+    <x:row r="150" ht="20" customHeight="1">
+      <x:c r="A150" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B150" s="18" t="str">
+        <x:v>M054</x:v>
+      </x:c>
+      <x:c r="C150" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D150" s="18" t="str">
+        <x:v>S134</x:v>
+      </x:c>
+      <x:c r="E150" s="18" t="str">
+        <x:v>07:20</x:v>
+      </x:c>
+      <x:c r="F150" s="11"/>
+    </x:row>
+    <x:row r="151" ht="20" customHeight="1">
+      <x:c r="A151" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B151" s="18" t="str">
+        <x:v>M054</x:v>
+      </x:c>
+      <x:c r="C151" s="18" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D151" s="18" t="str">
+        <x:v>S135</x:v>
+      </x:c>
+      <x:c r="E151" s="18" t="str">
+        <x:v>07:28</x:v>
+      </x:c>
+      <x:c r="F151" s="11"/>
+    </x:row>
+    <x:row r="152" ht="20" customHeight="1">
+      <x:c r="A152" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B152" s="18" t="str">
+        <x:v>M055</x:v>
+      </x:c>
+      <x:c r="C152" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D152" s="18" t="str">
+        <x:v>S135</x:v>
+      </x:c>
+      <x:c r="E152" s="18" t="str">
+        <x:v>07:28</x:v>
+      </x:c>
+      <x:c r="F152" s="11"/>
+    </x:row>
+    <x:row r="153" ht="20" customHeight="1">
+      <x:c r="A153" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B153" s="18" t="str">
+        <x:v>M056</x:v>
+      </x:c>
+      <x:c r="C153" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D153" s="18" t="str">
+        <x:v>S136</x:v>
+      </x:c>
+      <x:c r="E153" s="18" t="str">
+        <x:v>07:12</x:v>
+      </x:c>
+      <x:c r="F153" s="11"/>
+    </x:row>
+    <x:row r="154" ht="20" customHeight="1">
+      <x:c r="A154" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B154" s="18" t="str">
+        <x:v>M056</x:v>
+      </x:c>
+      <x:c r="C154" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D154" s="18" t="str">
+        <x:v>S137</x:v>
+      </x:c>
+      <x:c r="E154" s="18" t="str">
+        <x:v>07:17</x:v>
+      </x:c>
+      <x:c r="F154" s="11"/>
+    </x:row>
+    <x:row r="155" ht="20" customHeight="1">
+      <x:c r="A155" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B155" s="18" t="str">
+        <x:v>M056</x:v>
+      </x:c>
+      <x:c r="C155" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D155" s="18" t="str">
+        <x:v>S138</x:v>
+      </x:c>
+      <x:c r="E155" s="18" t="str">
+        <x:v>07:21</x:v>
+      </x:c>
+      <x:c r="F155" s="11"/>
+    </x:row>
+    <x:row r="156" ht="20" customHeight="1">
+      <x:c r="A156" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B156" s="18" t="str">
+        <x:v>M056</x:v>
+      </x:c>
+      <x:c r="C156" s="18" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D156" s="18" t="str">
+        <x:v>S139</x:v>
+      </x:c>
+      <x:c r="E156" s="18" t="str">
+        <x:v>07:23</x:v>
+      </x:c>
+      <x:c r="F156" s="11"/>
+    </x:row>
+    <x:row r="157" ht="20" customHeight="1">
+      <x:c r="A157" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B157" s="18" t="str">
+        <x:v>M056</x:v>
+      </x:c>
+      <x:c r="C157" s="18" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D157" s="18" t="str">
+        <x:v>S140</x:v>
+      </x:c>
+      <x:c r="E157" s="18" t="str">
+        <x:v>07:30</x:v>
+      </x:c>
+      <x:c r="F157" s="11"/>
+    </x:row>
+    <x:row r="158" ht="20" customHeight="1">
+      <x:c r="A158" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B158" s="18" t="str">
+        <x:v>M057</x:v>
+      </x:c>
+      <x:c r="C158" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D158" s="18" t="str">
+        <x:v>S141</x:v>
+      </x:c>
+      <x:c r="E158" s="18" t="str">
+        <x:v>07:33</x:v>
+      </x:c>
+      <x:c r="F158" s="11"/>
+    </x:row>
+    <x:row r="159" ht="20" customHeight="1">
+      <x:c r="A159" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B159" s="18" t="str">
+        <x:v>M058</x:v>
+      </x:c>
+      <x:c r="C159" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D159" s="18" t="str">
+        <x:v>S142</x:v>
+      </x:c>
+      <x:c r="E159" s="18" t="str">
+        <x:v>07:35</x:v>
+      </x:c>
+      <x:c r="F159" s="11"/>
+    </x:row>
+    <x:row r="160" ht="20" customHeight="1">
+      <x:c r="A160" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B160" s="18" t="str">
+        <x:v>M059</x:v>
+      </x:c>
+      <x:c r="C160" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D160" s="18" t="str">
+        <x:v>S141</x:v>
+      </x:c>
+      <x:c r="E160" s="18" t="str">
+        <x:v>07:30</x:v>
+      </x:c>
+      <x:c r="F160" s="11"/>
+    </x:row>
+    <x:row r="161" ht="20" customHeight="1">
+      <x:c r="A161" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B161" s="18" t="str">
+        <x:v>M059</x:v>
+      </x:c>
+      <x:c r="C161" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D161" s="18" t="str">
+        <x:v>S142</x:v>
+      </x:c>
+      <x:c r="E161" s="18" t="str">
+        <x:v>07:33</x:v>
+      </x:c>
+      <x:c r="F161" s="11"/>
+    </x:row>
+    <x:row r="162" ht="20" customHeight="1">
+      <x:c r="A162" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B162" s="18" t="str">
+        <x:v>M060</x:v>
+      </x:c>
+      <x:c r="C162" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D162" s="18" t="str">
+        <x:v>S143</x:v>
+      </x:c>
+      <x:c r="E162" s="18" t="str">
+        <x:v>07:00</x:v>
+      </x:c>
+      <x:c r="F162" s="11"/>
+    </x:row>
+    <x:row r="163" ht="20" customHeight="1">
+      <x:c r="A163" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B163" s="18" t="str">
+        <x:v>M060</x:v>
+      </x:c>
+      <x:c r="C163" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D163" s="18" t="str">
+        <x:v>S144</x:v>
+      </x:c>
+      <x:c r="E163" s="18" t="str">
+        <x:v>07:17</x:v>
+      </x:c>
+      <x:c r="F163" s="11"/>
+    </x:row>
+    <x:row r="164" ht="20" customHeight="1">
+      <x:c r="A164" s="18" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="B164" s="18" t="str">
+        <x:v>M060</x:v>
+      </x:c>
+      <x:c r="C164" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D164" s="18" t="str">
+        <x:v>S140</x:v>
+      </x:c>
+      <x:c r="E164" s="18" t="str">
+        <x:v>07:32</x:v>
+      </x:c>
+      <x:c r="F164" s="11"/>
     </x:row>
   </x:sheetData>
+  <x:conditionalFormatting sqref="A2:F164">
+    <x:cfRule type="expression" dxfId="2" priority="1">
+      <x:formula>$A2="FALSE"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="A2:A1000">
+    <x:dataValidation type="list" sqref="A2:A164">
       <x:formula1>"TRUE,FALSE"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3ccc868ae304f2a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ed67b280e844f99"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/data/shuttle-data.xlsx
+++ b/data/shuttle-data.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Routes" sheetId="1" r:id="Ra217bca658ae4c2c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stops" sheetId="2" r:id="R9996096d05b2486f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RouteStops" sheetId="3" r:id="R3898ab7644d242ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Routes" sheetId="1" r:id="R1818083175c44593"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stops" sheetId="2" r:id="R7d5d31acbf69484d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RouteStops" sheetId="3" r:id="R273e55eeb4dc4c37"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15,6 +15,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="0.000000"/>
+  </x:numFmts>
   <x:fonts count="2">
     <x:font>
       <x:sz val="11"/>
@@ -27,12 +30,17 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -47,7 +55,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="14">
+  <x:cellXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -78,29 +86,112 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="9">
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF3B0"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C5700"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFCE8D5"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF375623"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF7F6000"/>
+      </x:font>
+      <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FFC65911"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -2627,7 +2718,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2bcfe6fbe09477e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d9a676363c4438d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2643,6 +2734,13 @@
     <x:col min="5" max="5" width="40" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="42" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="52" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="13" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="13" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="38" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="46" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="12" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" hidden="0" customHeight="1">
@@ -2667,6 +2765,27 @@
       <x:c r="G1" s="5" t="str">
         <x:v>備註</x:v>
       </x:c>
+      <x:c r="H1" s="20" t="str">
+        <x:v>緯度</x:v>
+      </x:c>
+      <x:c r="I1" s="20" t="str">
+        <x:v>經度</x:v>
+      </x:c>
+      <x:c r="J1" s="20" t="str">
+        <x:v>定位方式</x:v>
+      </x:c>
+      <x:c r="K1" s="20" t="str">
+        <x:v>需人工確認</x:v>
+      </x:c>
+      <x:c r="L1" s="20" t="str">
+        <x:v>定位備註</x:v>
+      </x:c>
+      <x:c r="M1" s="10" t="str">
+        <x:v>座標來源</x:v>
+      </x:c>
+      <x:c r="N1" s="10" t="str">
+        <x:v>座標信心</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="12" t="str">
@@ -2688,6 +2807,17 @@
         <x:v>新竹市中華路三段9號</x:v>
       </x:c>
       <x:c r="G2" s="12"/>
+      <x:c r="H2" s="21"/>
+      <x:c r="I2" s="21"/>
+      <x:c r="J2" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K2" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L2" s="10" t="str"/>
+      <x:c r="M2" s="10"/>
+      <x:c r="N2" s="10"/>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="12" t="str">
@@ -2709,6 +2839,17 @@
         <x:v>新竹市民族路34號</x:v>
       </x:c>
       <x:c r="G3" s="12"/>
+      <x:c r="H3" s="21"/>
+      <x:c r="I3" s="21"/>
+      <x:c r="J3" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K3" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L3" s="10" t="str"/>
+      <x:c r="M3" s="10"/>
+      <x:c r="N3" s="10"/>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="12" t="str">
@@ -2730,6 +2871,17 @@
         <x:v>新竹市南大路81號</x:v>
       </x:c>
       <x:c r="G4" s="12"/>
+      <x:c r="H4" s="21"/>
+      <x:c r="I4" s="21"/>
+      <x:c r="J4" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K4" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L4" s="10" t="str"/>
+      <x:c r="M4" s="10"/>
+      <x:c r="N4" s="10"/>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="12" t="str">
@@ -2751,6 +2903,17 @@
         <x:v>新竹市光復路二段321號</x:v>
       </x:c>
       <x:c r="G5" s="12"/>
+      <x:c r="H5" s="21"/>
+      <x:c r="I5" s="21"/>
+      <x:c r="J5" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K5" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L5" s="10" t="str"/>
+      <x:c r="M5" s="10"/>
+      <x:c r="N5" s="10"/>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="12" t="str">
@@ -2772,6 +2935,17 @@
         <x:v>新竹市光復路二段101號</x:v>
       </x:c>
       <x:c r="G6" s="12"/>
+      <x:c r="H6" s="21"/>
+      <x:c r="I6" s="21"/>
+      <x:c r="J6" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K6" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L6" s="10" t="str"/>
+      <x:c r="M6" s="10"/>
+      <x:c r="N6" s="10"/>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="12" t="str">
@@ -2793,6 +2967,17 @@
         <x:v>新竹市光復路二段3號</x:v>
       </x:c>
       <x:c r="G7" s="12"/>
+      <x:c r="H7" s="21"/>
+      <x:c r="I7" s="21"/>
+      <x:c r="J7" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K7" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="str"/>
+      <x:c r="M7" s="10"/>
+      <x:c r="N7" s="10"/>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="12" t="str">
@@ -2814,6 +2999,17 @@
         <x:v>桃園市龍潭區南興路一段468號</x:v>
       </x:c>
       <x:c r="G8" s="12"/>
+      <x:c r="H8" s="21"/>
+      <x:c r="I8" s="21"/>
+      <x:c r="J8" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K8" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L8" s="10" t="str"/>
+      <x:c r="M8" s="10"/>
+      <x:c r="N8" s="10"/>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="12" t="str">
@@ -2835,6 +3031,17 @@
         <x:v>桃園市龍潭區大昌路二段100號</x:v>
       </x:c>
       <x:c r="G9" s="12"/>
+      <x:c r="H9" s="21"/>
+      <x:c r="I9" s="21"/>
+      <x:c r="J9" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K9" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L9" s="10" t="str"/>
+      <x:c r="M9" s="10"/>
+      <x:c r="N9" s="10"/>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="12" t="str">
@@ -2856,6 +3063,17 @@
         <x:v>桃園市蘆竹區新南路一段328號</x:v>
       </x:c>
       <x:c r="G10" s="12"/>
+      <x:c r="H10" s="21"/>
+      <x:c r="I10" s="21"/>
+      <x:c r="J10" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K10" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L10" s="10" t="str"/>
+      <x:c r="M10" s="10"/>
+      <x:c r="N10" s="10"/>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="12" t="str">
@@ -2877,6 +3095,17 @@
         <x:v>桃園市平鎮區中豐路南勢二段291號</x:v>
       </x:c>
       <x:c r="G11" s="12"/>
+      <x:c r="H11" s="21"/>
+      <x:c r="I11" s="21"/>
+      <x:c r="J11" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K11" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L11" s="10" t="str"/>
+      <x:c r="M11" s="10"/>
+      <x:c r="N11" s="10"/>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="12" t="str">
@@ -2898,6 +3127,17 @@
         <x:v>桃園市平鎮區環南路三段88號</x:v>
       </x:c>
       <x:c r="G12" s="12"/>
+      <x:c r="H12" s="21"/>
+      <x:c r="I12" s="21"/>
+      <x:c r="J12" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K12" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L12" s="10" t="str"/>
+      <x:c r="M12" s="10"/>
+      <x:c r="N12" s="10"/>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="12" t="str">
@@ -2919,6 +3159,17 @@
         <x:v>桃園市中壢區新興路86號</x:v>
       </x:c>
       <x:c r="G13" s="12"/>
+      <x:c r="H13" s="21"/>
+      <x:c r="I13" s="21"/>
+      <x:c r="J13" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K13" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L13" s="10" t="str"/>
+      <x:c r="M13" s="10"/>
+      <x:c r="N13" s="10"/>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="12" t="str">
@@ -2940,6 +3191,17 @@
         <x:v>桃園市平鎮區延平路二段231號</x:v>
       </x:c>
       <x:c r="G14" s="12"/>
+      <x:c r="H14" s="21"/>
+      <x:c r="I14" s="21"/>
+      <x:c r="J14" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K14" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L14" s="10" t="str"/>
+      <x:c r="M14" s="10"/>
+      <x:c r="N14" s="10"/>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="12" t="str">
@@ -2961,6 +3223,17 @@
         <x:v>桃園市平鎮區延平路二段87號</x:v>
       </x:c>
       <x:c r="G15" s="12"/>
+      <x:c r="H15" s="21"/>
+      <x:c r="I15" s="21"/>
+      <x:c r="J15" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K15" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L15" s="10" t="str"/>
+      <x:c r="M15" s="10"/>
+      <x:c r="N15" s="10"/>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
       <x:c r="A16" s="12" t="str">
@@ -2982,6 +3255,17 @@
         <x:v>桃園市中壢區延平路551號</x:v>
       </x:c>
       <x:c r="G16" s="12"/>
+      <x:c r="H16" s="21"/>
+      <x:c r="I16" s="21"/>
+      <x:c r="J16" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K16" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L16" s="10" t="str"/>
+      <x:c r="M16" s="10"/>
+      <x:c r="N16" s="10"/>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="12" t="str">
@@ -3003,6 +3287,17 @@
         <x:v>桃園市中壢區中園路162號</x:v>
       </x:c>
       <x:c r="G17" s="12"/>
+      <x:c r="H17" s="21"/>
+      <x:c r="I17" s="21"/>
+      <x:c r="J17" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K17" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L17" s="10" t="str"/>
+      <x:c r="M17" s="10"/>
+      <x:c r="N17" s="10"/>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
       <x:c r="A18" s="12" t="str">
@@ -3022,6 +3317,17 @@
         <x:v>桃園市中壢區東園路38-2號</x:v>
       </x:c>
       <x:c r="G18" s="12"/>
+      <x:c r="H18" s="21"/>
+      <x:c r="I18" s="21"/>
+      <x:c r="J18" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K18" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L18" s="10" t="str"/>
+      <x:c r="M18" s="10"/>
+      <x:c r="N18" s="10"/>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
       <x:c r="A19" s="12" t="str">
@@ -3043,6 +3349,19 @@
         <x:v>新竹縣竹北市自強一路 福興路口</x:v>
       </x:c>
       <x:c r="G19" s="12"/>
+      <x:c r="H19" s="21"/>
+      <x:c r="I19" s="21"/>
+      <x:c r="J19" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K19" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L19" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M19" s="10"/>
+      <x:c r="N19" s="10"/>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
       <x:c r="A20" s="12" t="str">
@@ -3064,6 +3383,17 @@
         <x:v>桃園市桃園區中山路694號</x:v>
       </x:c>
       <x:c r="G20" s="12"/>
+      <x:c r="H20" s="21"/>
+      <x:c r="I20" s="21"/>
+      <x:c r="J20" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K20" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L20" s="10" t="str"/>
+      <x:c r="M20" s="10"/>
+      <x:c r="N20" s="10"/>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
       <x:c r="A21" s="12" t="str">
@@ -3085,6 +3415,17 @@
         <x:v>桃園市桃園區中山路1076號</x:v>
       </x:c>
       <x:c r="G21" s="12"/>
+      <x:c r="H21" s="21"/>
+      <x:c r="I21" s="21"/>
+      <x:c r="J21" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K21" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L21" s="10" t="str"/>
+      <x:c r="M21" s="10"/>
+      <x:c r="N21" s="10"/>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="12" t="str">
@@ -3106,6 +3447,17 @@
         <x:v>桃園市桃園區龍安街56號</x:v>
       </x:c>
       <x:c r="G22" s="12"/>
+      <x:c r="H22" s="21"/>
+      <x:c r="I22" s="21"/>
+      <x:c r="J22" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K22" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L22" s="10" t="str"/>
+      <x:c r="M22" s="10"/>
+      <x:c r="N22" s="10"/>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
       <x:c r="A23" s="12" t="str">
@@ -3127,6 +3479,17 @@
         <x:v>桃園市桃園區復興路345號</x:v>
       </x:c>
       <x:c r="G23" s="12"/>
+      <x:c r="H23" s="21"/>
+      <x:c r="I23" s="21"/>
+      <x:c r="J23" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K23" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L23" s="10" t="str"/>
+      <x:c r="M23" s="10"/>
+      <x:c r="N23" s="10"/>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
       <x:c r="A24" s="12" t="str">
@@ -3148,6 +3511,19 @@
         <x:v>桃園市桃園區民權路6號</x:v>
       </x:c>
       <x:c r="G24" s="12"/>
+      <x:c r="H24" s="21"/>
+      <x:c r="I24" s="21"/>
+      <x:c r="J24" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K24" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L24" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M24" s="10"/>
+      <x:c r="N24" s="10"/>
     </x:row>
     <x:row r="25" ht="15" hidden="0" customHeight="1">
       <x:c r="A25" s="12" t="str">
@@ -3169,6 +3545,17 @@
         <x:v>新北市林口區文化二路一段356號</x:v>
       </x:c>
       <x:c r="G25" s="12"/>
+      <x:c r="H25" s="21"/>
+      <x:c r="I25" s="21"/>
+      <x:c r="J25" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K25" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L25" s="10" t="str"/>
+      <x:c r="M25" s="10"/>
+      <x:c r="N25" s="10"/>
     </x:row>
     <x:row r="26" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A26" s="12" t="str">
@@ -3190,6 +3577,17 @@
         <x:v>新北市林口區文化二路一段269號</x:v>
       </x:c>
       <x:c r="G26" s="12"/>
+      <x:c r="H26" s="21"/>
+      <x:c r="I26" s="21"/>
+      <x:c r="J26" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K26" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L26" s="10" t="str"/>
+      <x:c r="M26" s="10"/>
+      <x:c r="N26" s="10"/>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
       <x:c r="A27" s="12" t="str">
@@ -3211,6 +3609,17 @@
         <x:v>桃園市龜山區復興一路230號</x:v>
       </x:c>
       <x:c r="G27" s="12"/>
+      <x:c r="H27" s="21"/>
+      <x:c r="I27" s="21"/>
+      <x:c r="J27" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K27" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L27" s="10" t="str"/>
+      <x:c r="M27" s="10"/>
+      <x:c r="N27" s="10"/>
     </x:row>
     <x:row r="28" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A28" s="12" t="str">
@@ -3232,6 +3641,17 @@
         <x:v>基隆市仁愛區港西街4號</x:v>
       </x:c>
       <x:c r="G28" s="12"/>
+      <x:c r="H28" s="21"/>
+      <x:c r="I28" s="21"/>
+      <x:c r="J28" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K28" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L28" s="10" t="str"/>
+      <x:c r="M28" s="10"/>
+      <x:c r="N28" s="10"/>
     </x:row>
     <x:row r="29" ht="15" hidden="0" customHeight="1">
       <x:c r="A29" s="12" t="str">
@@ -3253,6 +3673,17 @@
         <x:v>基隆市安樂區安樂路一段2號</x:v>
       </x:c>
       <x:c r="G29" s="12"/>
+      <x:c r="H29" s="21"/>
+      <x:c r="I29" s="21"/>
+      <x:c r="J29" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K29" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L29" s="10" t="str"/>
+      <x:c r="M29" s="10"/>
+      <x:c r="N29" s="10"/>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
       <x:c r="A30" s="12" t="str">
@@ -3274,6 +3705,17 @@
         <x:v>基隆市安樂區安樂路二段132號</x:v>
       </x:c>
       <x:c r="G30" s="12"/>
+      <x:c r="H30" s="21"/>
+      <x:c r="I30" s="21"/>
+      <x:c r="J30" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K30" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L30" s="10" t="str"/>
+      <x:c r="M30" s="10"/>
+      <x:c r="N30" s="10"/>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
       <x:c r="A31" s="12" t="str">
@@ -3295,6 +3737,17 @@
         <x:v>基隆市八堵火車站</x:v>
       </x:c>
       <x:c r="G31" s="12"/>
+      <x:c r="H31" s="21"/>
+      <x:c r="I31" s="21"/>
+      <x:c r="J31" t="str">
+        <x:v>Google地標</x:v>
+      </x:c>
+      <x:c r="K31" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L31" s="10" t="str"/>
+      <x:c r="M31" s="10"/>
+      <x:c r="N31" s="10"/>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
       <x:c r="A32" s="12" t="str">
@@ -3316,6 +3769,17 @@
         <x:v>基隆市七堵區崇智街2之10號</x:v>
       </x:c>
       <x:c r="G32" s="12"/>
+      <x:c r="H32" s="21"/>
+      <x:c r="I32" s="21"/>
+      <x:c r="J32" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K32" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L32" s="10" t="str"/>
+      <x:c r="M32" s="10"/>
+      <x:c r="N32" s="10"/>
     </x:row>
     <x:row r="33" ht="15" hidden="0" customHeight="1">
       <x:c r="A33" s="12" t="str">
@@ -3337,6 +3801,17 @@
         <x:v>基隆市七堵區百一街151號</x:v>
       </x:c>
       <x:c r="G33" s="12"/>
+      <x:c r="H33" s="21"/>
+      <x:c r="I33" s="21"/>
+      <x:c r="J33" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K33" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L33" s="10" t="str"/>
+      <x:c r="M33" s="10"/>
+      <x:c r="N33" s="10"/>
     </x:row>
     <x:row r="34" ht="15" hidden="0" customHeight="1">
       <x:c r="A34" s="12" t="str">
@@ -3358,6 +3833,17 @@
         <x:v>新北市新莊區富國路102號</x:v>
       </x:c>
       <x:c r="G34" s="12"/>
+      <x:c r="H34" s="21"/>
+      <x:c r="I34" s="21"/>
+      <x:c r="J34" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K34" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L34" s="10" t="str"/>
+      <x:c r="M34" s="10"/>
+      <x:c r="N34" s="10"/>
     </x:row>
     <x:row r="35" ht="15" hidden="0" customHeight="1">
       <x:c r="A35" s="12" t="str">
@@ -3379,6 +3865,17 @@
         <x:v>新北市新莊區後港一路132號</x:v>
       </x:c>
       <x:c r="G35" s="12"/>
+      <x:c r="H35" s="21"/>
+      <x:c r="I35" s="21"/>
+      <x:c r="J35" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K35" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L35" s="10" t="str"/>
+      <x:c r="M35" s="10"/>
+      <x:c r="N35" s="10"/>
     </x:row>
     <x:row r="36" ht="15" hidden="0" customHeight="1">
       <x:c r="A36" s="12" t="str">
@@ -3400,6 +3897,17 @@
         <x:v>新北市新莊區中正路555號</x:v>
       </x:c>
       <x:c r="G36" s="12"/>
+      <x:c r="H36" s="21"/>
+      <x:c r="I36" s="21"/>
+      <x:c r="J36" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K36" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L36" s="10" t="str"/>
+      <x:c r="M36" s="10"/>
+      <x:c r="N36" s="10"/>
     </x:row>
     <x:row r="37" ht="15" hidden="0" customHeight="1">
       <x:c r="A37" s="12" t="str">
@@ -3421,6 +3929,17 @@
         <x:v>新北市新莊區中平路133號</x:v>
       </x:c>
       <x:c r="G37" s="12"/>
+      <x:c r="H37" s="21"/>
+      <x:c r="I37" s="21"/>
+      <x:c r="J37" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K37" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L37" s="10" t="str"/>
+      <x:c r="M37" s="10"/>
+      <x:c r="N37" s="10"/>
     </x:row>
     <x:row r="38" ht="15" hidden="0" customHeight="1">
       <x:c r="A38" s="12" t="str">
@@ -3442,6 +3961,17 @@
         <x:v>新北市新莊區思源路339號</x:v>
       </x:c>
       <x:c r="G38" s="12"/>
+      <x:c r="H38" s="21"/>
+      <x:c r="I38" s="21"/>
+      <x:c r="J38" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K38" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L38" s="10" t="str"/>
+      <x:c r="M38" s="10"/>
+      <x:c r="N38" s="10"/>
     </x:row>
     <x:row r="39" ht="15" hidden="0" customHeight="1">
       <x:c r="A39" s="12" t="str">
@@ -3463,6 +3993,17 @@
         <x:v>新北市新莊區新泰路370號</x:v>
       </x:c>
       <x:c r="G39" s="12"/>
+      <x:c r="H39" s="21"/>
+      <x:c r="I39" s="21"/>
+      <x:c r="J39" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K39" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L39" s="10" t="str"/>
+      <x:c r="M39" s="10"/>
+      <x:c r="N39" s="10"/>
     </x:row>
     <x:row r="40" ht="15" hidden="0" customHeight="1">
       <x:c r="A40" s="12" t="str">
@@ -3484,6 +4025,17 @@
         <x:v>新北市新莊區公園一路16號</x:v>
       </x:c>
       <x:c r="G40" s="12"/>
+      <x:c r="H40" s="21"/>
+      <x:c r="I40" s="21"/>
+      <x:c r="J40" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K40" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L40" s="10" t="str"/>
+      <x:c r="M40" s="10"/>
+      <x:c r="N40" s="10"/>
     </x:row>
     <x:row r="41" ht="15" hidden="0" customHeight="1">
       <x:c r="A41" s="12" t="str">
@@ -3505,6 +4057,17 @@
         <x:v>新北市新莊區公園一路146號</x:v>
       </x:c>
       <x:c r="G41" s="12"/>
+      <x:c r="H41" s="21"/>
+      <x:c r="I41" s="21"/>
+      <x:c r="J41" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K41" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L41" s="10" t="str"/>
+      <x:c r="M41" s="10"/>
+      <x:c r="N41" s="10"/>
     </x:row>
     <x:row r="42" ht="15" hidden="0" customHeight="1">
       <x:c r="A42" s="12" t="str">
@@ -3526,6 +4089,19 @@
         <x:v>台北市北投區北投路二段 大業路452巷口</x:v>
       </x:c>
       <x:c r="G42" s="12"/>
+      <x:c r="H42" s="21"/>
+      <x:c r="I42" s="21"/>
+      <x:c r="J42" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K42" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L42" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M42" s="10"/>
+      <x:c r="N42" s="10"/>
     </x:row>
     <x:row r="43" ht="15" hidden="0" customHeight="1">
       <x:c r="A43" s="12" t="str">
@@ -3547,6 +4123,17 @@
         <x:v>台北市中山區北安路537之2號</x:v>
       </x:c>
       <x:c r="G43" s="12"/>
+      <x:c r="H43" s="21"/>
+      <x:c r="I43" s="21"/>
+      <x:c r="J43" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K43" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L43" s="10" t="str"/>
+      <x:c r="M43" s="10"/>
+      <x:c r="N43" s="10"/>
     </x:row>
     <x:row r="44" ht="15" hidden="0" customHeight="1">
       <x:c r="A44" s="12" t="str">
@@ -3568,6 +4155,17 @@
         <x:v>台北市捷運劍潭站</x:v>
       </x:c>
       <x:c r="G44" s="12"/>
+      <x:c r="H44" s="21"/>
+      <x:c r="I44" s="21"/>
+      <x:c r="J44" t="str">
+        <x:v>Google地標</x:v>
+      </x:c>
+      <x:c r="K44" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L44" s="10" t="str"/>
+      <x:c r="M44" s="10"/>
+      <x:c r="N44" s="10"/>
     </x:row>
     <x:row r="45" ht="15" hidden="0" customHeight="1">
       <x:c r="A45" s="12" t="str">
@@ -3589,6 +4187,17 @@
         <x:v>台北市捷運芝山站1號出口</x:v>
       </x:c>
       <x:c r="G45" s="12"/>
+      <x:c r="H45" s="21"/>
+      <x:c r="I45" s="21"/>
+      <x:c r="J45" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K45" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L45" s="10" t="str"/>
+      <x:c r="M45" s="10"/>
+      <x:c r="N45" s="10"/>
     </x:row>
     <x:row r="46" ht="15" hidden="0" customHeight="1">
       <x:c r="A46" s="12" t="str">
@@ -3610,6 +4219,17 @@
         <x:v>台北市士林區中正路362號</x:v>
       </x:c>
       <x:c r="G46" s="12"/>
+      <x:c r="H46" s="21"/>
+      <x:c r="I46" s="21"/>
+      <x:c r="J46" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K46" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L46" s="10" t="str"/>
+      <x:c r="M46" s="10"/>
+      <x:c r="N46" s="10"/>
     </x:row>
     <x:row r="47" ht="15" hidden="0" customHeight="1">
       <x:c r="A47" s="12" t="str">
@@ -3631,6 +4251,17 @@
         <x:v>台北市北投區石牌路二段126號</x:v>
       </x:c>
       <x:c r="G47" s="12"/>
+      <x:c r="H47" s="21"/>
+      <x:c r="I47" s="21"/>
+      <x:c r="J47" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K47" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L47" s="10" t="str"/>
+      <x:c r="M47" s="10"/>
+      <x:c r="N47" s="10"/>
     </x:row>
     <x:row r="48" ht="15" hidden="0" customHeight="1">
       <x:c r="A48" s="12" t="str">
@@ -3650,6 +4281,17 @@
         <x:v>台北市士林區天母東路8號</x:v>
       </x:c>
       <x:c r="G48" s="12"/>
+      <x:c r="H48" s="21"/>
+      <x:c r="I48" s="21"/>
+      <x:c r="J48" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K48" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L48" s="10" t="str"/>
+      <x:c r="M48" s="10"/>
+      <x:c r="N48" s="10"/>
     </x:row>
     <x:row r="49" ht="15" hidden="0" customHeight="1">
       <x:c r="A49" s="12" t="str">
@@ -3671,6 +4313,19 @@
         <x:v>台北市士林區忠誠路二段76巷口</x:v>
       </x:c>
       <x:c r="G49" s="12"/>
+      <x:c r="H49" s="21"/>
+      <x:c r="I49" s="21"/>
+      <x:c r="J49" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K49" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L49" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M49" s="10"/>
+      <x:c r="N49" s="10"/>
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
       <x:c r="A50" s="12" t="str">
@@ -3692,6 +4347,17 @@
         <x:v>台北市士林區忠誠路一段138號</x:v>
       </x:c>
       <x:c r="G50" s="12"/>
+      <x:c r="H50" s="21"/>
+      <x:c r="I50" s="21"/>
+      <x:c r="J50" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K50" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L50" s="10" t="str"/>
+      <x:c r="M50" s="10"/>
+      <x:c r="N50" s="10"/>
     </x:row>
     <x:row r="51" ht="15" hidden="0" customHeight="1">
       <x:c r="A51" s="12" t="str">
@@ -3713,6 +4379,17 @@
         <x:v>台北市北投區西安街二段283號</x:v>
       </x:c>
       <x:c r="G51" s="12"/>
+      <x:c r="H51" s="21"/>
+      <x:c r="I51" s="21"/>
+      <x:c r="J51" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L51" s="10" t="str"/>
+      <x:c r="M51" s="10"/>
+      <x:c r="N51" s="10"/>
     </x:row>
     <x:row r="52" ht="15" hidden="0" customHeight="1">
       <x:c r="A52" s="12" t="str">
@@ -3734,6 +4411,17 @@
         <x:v>台北市北投區西安街二段85號</x:v>
       </x:c>
       <x:c r="G52" s="12"/>
+      <x:c r="H52" s="21"/>
+      <x:c r="I52" s="21"/>
+      <x:c r="J52" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K52" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L52" s="10" t="str"/>
+      <x:c r="M52" s="10"/>
+      <x:c r="N52" s="10"/>
     </x:row>
     <x:row r="53" ht="15" hidden="0" customHeight="1">
       <x:c r="A53" s="12" t="str">
@@ -3755,6 +4443,17 @@
         <x:v>台北市士林區重慶北路四段117號</x:v>
       </x:c>
       <x:c r="G53" s="12"/>
+      <x:c r="H53" s="21"/>
+      <x:c r="I53" s="21"/>
+      <x:c r="J53" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K53" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L53" s="10" t="str"/>
+      <x:c r="M53" s="10"/>
+      <x:c r="N53" s="10"/>
     </x:row>
     <x:row r="54" ht="15" hidden="0" customHeight="1">
       <x:c r="A54" s="12" t="str">
@@ -3776,6 +4475,17 @@
         <x:v>台北市中山區植福路11號</x:v>
       </x:c>
       <x:c r="G54" s="12"/>
+      <x:c r="H54" s="21"/>
+      <x:c r="I54" s="21"/>
+      <x:c r="J54" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K54" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L54" s="10" t="str"/>
+      <x:c r="M54" s="10"/>
+      <x:c r="N54" s="10"/>
     </x:row>
     <x:row r="55" ht="15" hidden="0" customHeight="1">
       <x:c r="A55" s="12" t="str">
@@ -3797,6 +4507,17 @@
         <x:v>台北市內湖區內湖路一段250號</x:v>
       </x:c>
       <x:c r="G55" s="12"/>
+      <x:c r="H55" s="21"/>
+      <x:c r="I55" s="21"/>
+      <x:c r="J55" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K55" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L55" s="10" t="str"/>
+      <x:c r="M55" s="10"/>
+      <x:c r="N55" s="10"/>
     </x:row>
     <x:row r="56" ht="15" hidden="0" customHeight="1">
       <x:c r="A56" s="12" t="str">
@@ -3818,6 +4539,17 @@
         <x:v>台北市內湖區內湖路一段370號</x:v>
       </x:c>
       <x:c r="G56" s="12"/>
+      <x:c r="H56" s="21"/>
+      <x:c r="I56" s="21"/>
+      <x:c r="J56" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K56" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L56" s="10" t="str"/>
+      <x:c r="M56" s="10"/>
+      <x:c r="N56" s="10"/>
     </x:row>
     <x:row r="57" ht="15" hidden="0" customHeight="1">
       <x:c r="A57" s="12" t="str">
@@ -3839,6 +4571,19 @@
         <x:v>台北市內湖區文德路220巷口</x:v>
       </x:c>
       <x:c r="G57" s="12"/>
+      <x:c r="H57" s="21"/>
+      <x:c r="I57" s="21"/>
+      <x:c r="J57" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K57" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L57" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M57" s="10"/>
+      <x:c r="N57" s="10"/>
     </x:row>
     <x:row r="58" ht="15" hidden="0" customHeight="1">
       <x:c r="A58" s="12" t="str">
@@ -3860,6 +4605,17 @@
         <x:v>台北市內湖區文德路102號</x:v>
       </x:c>
       <x:c r="G58" s="12"/>
+      <x:c r="H58" s="21"/>
+      <x:c r="I58" s="21"/>
+      <x:c r="J58" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K58" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L58" s="10" t="str"/>
+      <x:c r="M58" s="10"/>
+      <x:c r="N58" s="10"/>
     </x:row>
     <x:row r="59" ht="15" hidden="0" customHeight="1">
       <x:c r="A59" s="12" t="str">
@@ -3879,6 +4635,17 @@
         <x:v>台北市內湖區成功路四段141號</x:v>
       </x:c>
       <x:c r="G59" s="12"/>
+      <x:c r="H59" s="21"/>
+      <x:c r="I59" s="21"/>
+      <x:c r="J59" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K59" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L59" s="10" t="str"/>
+      <x:c r="M59" s="10"/>
+      <x:c r="N59" s="10"/>
     </x:row>
     <x:row r="60" ht="15" hidden="0" customHeight="1">
       <x:c r="A60" s="12" t="str">
@@ -3898,6 +4665,17 @@
         <x:v>台北市內湖區民權東路六段493號</x:v>
       </x:c>
       <x:c r="G60" s="12"/>
+      <x:c r="H60" s="21"/>
+      <x:c r="I60" s="21"/>
+      <x:c r="J60" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K60" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L60" s="10" t="str"/>
+      <x:c r="M60" s="10"/>
+      <x:c r="N60" s="10"/>
     </x:row>
     <x:row r="61" ht="15" hidden="0" customHeight="1">
       <x:c r="A61" s="12" t="str">
@@ -3919,6 +4697,17 @@
         <x:v>台北市內湖區民權東路六段150號</x:v>
       </x:c>
       <x:c r="G61" s="12"/>
+      <x:c r="H61" s="21"/>
+      <x:c r="I61" s="21"/>
+      <x:c r="J61" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K61" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L61" s="10" t="str"/>
+      <x:c r="M61" s="10"/>
+      <x:c r="N61" s="10"/>
     </x:row>
     <x:row r="62" ht="15" hidden="0" customHeight="1">
       <x:c r="A62" s="12" t="str">
@@ -3940,6 +4729,17 @@
         <x:v>台北市中山區民權東路一段24號</x:v>
       </x:c>
       <x:c r="G62" s="12"/>
+      <x:c r="H62" s="21"/>
+      <x:c r="I62" s="21"/>
+      <x:c r="J62" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K62" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L62" s="10" t="str"/>
+      <x:c r="M62" s="10"/>
+      <x:c r="N62" s="10"/>
     </x:row>
     <x:row r="63" ht="15" hidden="0" customHeight="1">
       <x:c r="A63" s="12" t="str">
@@ -3959,6 +4759,17 @@
         <x:v>台北市中山區民權東路二段48號</x:v>
       </x:c>
       <x:c r="G63" s="12"/>
+      <x:c r="H63" s="21"/>
+      <x:c r="I63" s="21"/>
+      <x:c r="J63" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K63" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L63" s="10" t="str"/>
+      <x:c r="M63" s="10"/>
+      <x:c r="N63" s="10"/>
     </x:row>
     <x:row r="64" ht="15" hidden="0" customHeight="1">
       <x:c r="A64" s="12" t="str">
@@ -3980,6 +4791,17 @@
         <x:v>台北市中山區建國北路二段262號</x:v>
       </x:c>
       <x:c r="G64" s="12"/>
+      <x:c r="H64" s="21"/>
+      <x:c r="I64" s="21"/>
+      <x:c r="J64" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K64" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L64" s="10" t="str"/>
+      <x:c r="M64" s="10"/>
+      <x:c r="N64" s="10"/>
     </x:row>
     <x:row r="65" ht="15" hidden="0" customHeight="1">
       <x:c r="A65" s="12" t="str">
@@ -4001,6 +4823,17 @@
         <x:v>台北市中山區建國北路三段39號</x:v>
       </x:c>
       <x:c r="G65" s="12"/>
+      <x:c r="H65" s="21"/>
+      <x:c r="I65" s="21"/>
+      <x:c r="J65" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K65" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L65" s="10" t="str"/>
+      <x:c r="M65" s="10"/>
+      <x:c r="N65" s="10"/>
     </x:row>
     <x:row r="66" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A66" s="12" t="str">
@@ -4022,6 +4855,17 @@
         <x:v>台北市中山區民生東路三段8號</x:v>
       </x:c>
       <x:c r="G66" s="12"/>
+      <x:c r="H66" s="21"/>
+      <x:c r="I66" s="21"/>
+      <x:c r="J66" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K66" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L66" s="10" t="str"/>
+      <x:c r="M66" s="10"/>
+      <x:c r="N66" s="10"/>
     </x:row>
     <x:row r="67" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A67" s="12" t="str">
@@ -4043,6 +4887,19 @@
         <x:v>台北市中山區民生東路三段86巷口</x:v>
       </x:c>
       <x:c r="G67" s="12"/>
+      <x:c r="H67" s="21"/>
+      <x:c r="I67" s="21"/>
+      <x:c r="J67" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K67" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L67" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M67" s="10"/>
+      <x:c r="N67" s="10"/>
     </x:row>
     <x:row r="68" ht="15" hidden="0" customHeight="1">
       <x:c r="A68" s="12" t="str">
@@ -4064,6 +4921,17 @@
         <x:v>台北市松山區民生東路三段138號</x:v>
       </x:c>
       <x:c r="G68" s="12"/>
+      <x:c r="H68" s="21"/>
+      <x:c r="I68" s="21"/>
+      <x:c r="J68" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K68" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L68" s="10" t="str"/>
+      <x:c r="M68" s="10"/>
+      <x:c r="N68" s="10"/>
     </x:row>
     <x:row r="69" ht="15" hidden="0" customHeight="1">
       <x:c r="A69" s="12" t="str">
@@ -4085,6 +4953,17 @@
         <x:v>台北市松山區民生東路五段8號</x:v>
       </x:c>
       <x:c r="G69" s="12"/>
+      <x:c r="H69" s="21"/>
+      <x:c r="I69" s="21"/>
+      <x:c r="J69" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K69" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L69" s="10" t="str"/>
+      <x:c r="M69" s="10"/>
+      <x:c r="N69" s="10"/>
     </x:row>
     <x:row r="70" ht="15" hidden="0" customHeight="1">
       <x:c r="A70" s="12" t="str">
@@ -4106,6 +4985,17 @@
         <x:v>台北市松山區民生東路五段182號</x:v>
       </x:c>
       <x:c r="G70" s="12"/>
+      <x:c r="H70" s="21"/>
+      <x:c r="I70" s="21"/>
+      <x:c r="J70" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K70" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L70" s="10" t="str"/>
+      <x:c r="M70" s="10"/>
+      <x:c r="N70" s="10"/>
     </x:row>
     <x:row r="71" ht="15" hidden="0" customHeight="1">
       <x:c r="A71" s="12" t="str">
@@ -4127,6 +5017,17 @@
         <x:v>台北市中山區南京東路一段52號</x:v>
       </x:c>
       <x:c r="G71" s="12"/>
+      <x:c r="H71" s="21"/>
+      <x:c r="I71" s="21"/>
+      <x:c r="J71" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K71" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L71" s="10" t="str"/>
+      <x:c r="M71" s="10"/>
+      <x:c r="N71" s="10"/>
     </x:row>
     <x:row r="72" ht="15" hidden="0" customHeight="1">
       <x:c r="A72" s="12" t="str">
@@ -4148,6 +5049,17 @@
         <x:v>台北市中山區南京東路二段176號</x:v>
       </x:c>
       <x:c r="G72" s="12"/>
+      <x:c r="H72" s="21"/>
+      <x:c r="I72" s="21"/>
+      <x:c r="J72" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K72" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L72" s="10" t="str"/>
+      <x:c r="M72" s="10"/>
+      <x:c r="N72" s="10"/>
     </x:row>
     <x:row r="73" ht="15" hidden="0" customHeight="1">
       <x:c r="A73" s="12" t="str">
@@ -4169,6 +5081,17 @@
         <x:v>台北市松山區南京東路三段270號</x:v>
       </x:c>
       <x:c r="G73" s="12"/>
+      <x:c r="H73" s="21"/>
+      <x:c r="I73" s="21"/>
+      <x:c r="J73" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K73" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L73" s="10" t="str"/>
+      <x:c r="M73" s="10"/>
+      <x:c r="N73" s="10"/>
     </x:row>
     <x:row r="74" ht="15" hidden="0" customHeight="1">
       <x:c r="A74" s="12" t="str">
@@ -4190,6 +5113,17 @@
         <x:v>台北市松山區南京東路四段126號</x:v>
       </x:c>
       <x:c r="G74" s="12"/>
+      <x:c r="H74" s="21"/>
+      <x:c r="I74" s="21"/>
+      <x:c r="J74" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K74" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L74" s="10" t="str"/>
+      <x:c r="M74" s="10"/>
+      <x:c r="N74" s="10"/>
     </x:row>
     <x:row r="75" ht="15" hidden="0" customHeight="1">
       <x:c r="A75" s="12" t="str">
@@ -4211,6 +5145,17 @@
         <x:v>台北市松山區南京東路五段60號</x:v>
       </x:c>
       <x:c r="G75" s="12"/>
+      <x:c r="H75" s="21"/>
+      <x:c r="I75" s="21"/>
+      <x:c r="J75" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K75" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L75" s="10" t="str"/>
+      <x:c r="M75" s="10"/>
+      <x:c r="N75" s="10"/>
     </x:row>
     <x:row r="76" ht="15" hidden="0" customHeight="1">
       <x:c r="A76" s="12" t="str">
@@ -4232,6 +5177,17 @@
         <x:v>台北市松山區南京東路五段256號</x:v>
       </x:c>
       <x:c r="G76" s="12"/>
+      <x:c r="H76" s="21"/>
+      <x:c r="I76" s="21"/>
+      <x:c r="J76" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K76" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L76" s="10" t="str"/>
+      <x:c r="M76" s="10"/>
+      <x:c r="N76" s="10"/>
     </x:row>
     <x:row r="77" ht="15" hidden="0" customHeight="1">
       <x:c r="A77" s="12" t="str">
@@ -4253,6 +5209,17 @@
         <x:v>台北市南港區八德路四段778號</x:v>
       </x:c>
       <x:c r="G77" s="12"/>
+      <x:c r="H77" s="21"/>
+      <x:c r="I77" s="21"/>
+      <x:c r="J77" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K77" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L77" s="10" t="str"/>
+      <x:c r="M77" s="10"/>
+      <x:c r="N77" s="10"/>
     </x:row>
     <x:row r="78" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A78" s="12" t="str">
@@ -4274,6 +5241,17 @@
         <x:v>台北市中正區中華路一段67號</x:v>
       </x:c>
       <x:c r="G78" s="12"/>
+      <x:c r="H78" s="21"/>
+      <x:c r="I78" s="21"/>
+      <x:c r="J78" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K78" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L78" s="10" t="str"/>
+      <x:c r="M78" s="10"/>
+      <x:c r="N78" s="10"/>
     </x:row>
     <x:row r="79" ht="15" hidden="0" customHeight="1">
       <x:c r="A79" s="12" t="str">
@@ -4295,6 +5273,17 @@
         <x:v>台北市中正區忠孝東路二段96號</x:v>
       </x:c>
       <x:c r="G79" s="12"/>
+      <x:c r="H79" s="21"/>
+      <x:c r="I79" s="21"/>
+      <x:c r="J79" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K79" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L79" s="10" t="str"/>
+      <x:c r="M79" s="10"/>
+      <x:c r="N79" s="10"/>
     </x:row>
     <x:row r="80" ht="15" hidden="0" customHeight="1">
       <x:c r="A80" s="12" t="str">
@@ -4316,6 +5305,17 @@
         <x:v>台北市大安區忠孝東路三段242號</x:v>
       </x:c>
       <x:c r="G80" s="12"/>
+      <x:c r="H80" s="21"/>
+      <x:c r="I80" s="21"/>
+      <x:c r="J80" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K80" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L80" s="10" t="str"/>
+      <x:c r="M80" s="10"/>
+      <x:c r="N80" s="10"/>
     </x:row>
     <x:row r="81" ht="15" hidden="0" customHeight="1">
       <x:c r="A81" s="12" t="str">
@@ -4337,6 +5337,17 @@
         <x:v>台北市大安區忠孝東路四段200號</x:v>
       </x:c>
       <x:c r="G81" s="12"/>
+      <x:c r="H81" s="21"/>
+      <x:c r="I81" s="21"/>
+      <x:c r="J81" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K81" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L81" s="10" t="str"/>
+      <x:c r="M81" s="10"/>
+      <x:c r="N81" s="10"/>
     </x:row>
     <x:row r="82" ht="15" hidden="0" customHeight="1">
       <x:c r="A82" s="12" t="str">
@@ -4358,6 +5369,17 @@
         <x:v>台北市大安區光復南路262號</x:v>
       </x:c>
       <x:c r="G82" s="12"/>
+      <x:c r="H82" s="21"/>
+      <x:c r="I82" s="21"/>
+      <x:c r="J82" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K82" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L82" s="10" t="str"/>
+      <x:c r="M82" s="10"/>
+      <x:c r="N82" s="10"/>
     </x:row>
     <x:row r="83" ht="15" hidden="0" customHeight="1">
       <x:c r="A83" s="12" t="str">
@@ -4379,6 +5401,17 @@
         <x:v>台北市信義區信義路四段458號</x:v>
       </x:c>
       <x:c r="G83" s="12"/>
+      <x:c r="H83" s="21"/>
+      <x:c r="I83" s="21"/>
+      <x:c r="J83" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K83" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L83" s="10" t="str"/>
+      <x:c r="M83" s="10"/>
+      <x:c r="N83" s="10"/>
     </x:row>
     <x:row r="84" ht="15" hidden="0" customHeight="1">
       <x:c r="A84" s="12" t="str">
@@ -4400,6 +5433,17 @@
         <x:v>台北市信義區信義路五段108號</x:v>
       </x:c>
       <x:c r="G84" s="12"/>
+      <x:c r="H84" s="21"/>
+      <x:c r="I84" s="21"/>
+      <x:c r="J84" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K84" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L84" s="10" t="str"/>
+      <x:c r="M84" s="10"/>
+      <x:c r="N84" s="10"/>
     </x:row>
     <x:row r="85" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A85" s="12" t="str">
@@ -4421,6 +5465,17 @@
         <x:v>台北市信義區忠孝東路五段506號</x:v>
       </x:c>
       <x:c r="G85" s="12"/>
+      <x:c r="H85" s="21"/>
+      <x:c r="I85" s="21"/>
+      <x:c r="J85" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K85" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L85" s="10" t="str"/>
+      <x:c r="M85" s="10"/>
+      <x:c r="N85" s="10"/>
     </x:row>
     <x:row r="86" ht="15" hidden="0" customHeight="1">
       <x:c r="A86" s="12" t="str">
@@ -4442,6 +5497,17 @@
         <x:v>台北市南港區忠孝東路六段156號</x:v>
       </x:c>
       <x:c r="G86" s="12"/>
+      <x:c r="H86" s="21"/>
+      <x:c r="I86" s="21"/>
+      <x:c r="J86" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K86" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L86" s="10" t="str"/>
+      <x:c r="M86" s="10"/>
+      <x:c r="N86" s="10"/>
     </x:row>
     <x:row r="87" ht="15" hidden="0" customHeight="1">
       <x:c r="A87" s="12" t="str">
@@ -4463,6 +5529,17 @@
         <x:v>台北市萬華區萬大路321號</x:v>
       </x:c>
       <x:c r="G87" s="12"/>
+      <x:c r="H87" s="21"/>
+      <x:c r="I87" s="21"/>
+      <x:c r="J87" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K87" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L87" s="10" t="str"/>
+      <x:c r="M87" s="10"/>
+      <x:c r="N87" s="10"/>
     </x:row>
     <x:row r="88" ht="15" hidden="0" customHeight="1">
       <x:c r="A88" s="12" t="str">
@@ -4484,6 +5561,17 @@
         <x:v>台北市中正區西藏路39號</x:v>
       </x:c>
       <x:c r="G88" s="12"/>
+      <x:c r="H88" s="21"/>
+      <x:c r="I88" s="21"/>
+      <x:c r="J88" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K88" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L88" s="10" t="str"/>
+      <x:c r="M88" s="10"/>
+      <x:c r="N88" s="10"/>
     </x:row>
     <x:row r="89" ht="15" hidden="0" customHeight="1">
       <x:c r="A89" s="12" t="str">
@@ -4505,6 +5593,17 @@
         <x:v>台北市大安區敦化南路二段178號</x:v>
       </x:c>
       <x:c r="G89" s="12"/>
+      <x:c r="H89" s="21"/>
+      <x:c r="I89" s="21"/>
+      <x:c r="J89" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K89" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L89" s="10" t="str"/>
+      <x:c r="M89" s="10"/>
+      <x:c r="N89" s="10"/>
     </x:row>
     <x:row r="90" ht="15" hidden="0" customHeight="1">
       <x:c r="A90" s="12" t="str">
@@ -4526,6 +5625,17 @@
         <x:v>新北市永和區仁愛路125號</x:v>
       </x:c>
       <x:c r="G90" s="12"/>
+      <x:c r="H90" s="21"/>
+      <x:c r="I90" s="21"/>
+      <x:c r="J90" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K90" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L90" s="10" t="str"/>
+      <x:c r="M90" s="10"/>
+      <x:c r="N90" s="10"/>
     </x:row>
     <x:row r="91" ht="15" hidden="0" customHeight="1">
       <x:c r="A91" s="12" t="str">
@@ -4547,6 +5657,17 @@
         <x:v>新北市永和區永和路二段226號</x:v>
       </x:c>
       <x:c r="G91" s="12"/>
+      <x:c r="H91" s="21"/>
+      <x:c r="I91" s="21"/>
+      <x:c r="J91" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K91" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L91" s="10" t="str"/>
+      <x:c r="M91" s="10"/>
+      <x:c r="N91" s="10"/>
     </x:row>
     <x:row r="92" ht="15" hidden="0" customHeight="1">
       <x:c r="A92" s="12" t="str">
@@ -4568,6 +5689,17 @@
         <x:v>台北市大安區和平東路一段178號</x:v>
       </x:c>
       <x:c r="G92" s="12"/>
+      <x:c r="H92" s="21"/>
+      <x:c r="I92" s="21"/>
+      <x:c r="J92" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K92" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L92" s="10" t="str"/>
+      <x:c r="M92" s="10"/>
+      <x:c r="N92" s="10"/>
     </x:row>
     <x:row r="93" ht="15" hidden="0" customHeight="1">
       <x:c r="A93" s="12" t="str">
@@ -4589,6 +5721,17 @@
         <x:v>台北市大安區和平東路二段24號</x:v>
       </x:c>
       <x:c r="G93" s="12"/>
+      <x:c r="H93" s="21"/>
+      <x:c r="I93" s="21"/>
+      <x:c r="J93" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K93" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L93" s="10" t="str"/>
+      <x:c r="M93" s="10"/>
+      <x:c r="N93" s="10"/>
     </x:row>
     <x:row r="94" ht="15" hidden="0" customHeight="1">
       <x:c r="A94" s="12" t="str">
@@ -4610,6 +5753,17 @@
         <x:v>新北市永和區中山路一段207號</x:v>
       </x:c>
       <x:c r="G94" s="12"/>
+      <x:c r="H94" s="21"/>
+      <x:c r="I94" s="21"/>
+      <x:c r="J94" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K94" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L94" s="10" t="str"/>
+      <x:c r="M94" s="10"/>
+      <x:c r="N94" s="10"/>
     </x:row>
     <x:row r="95" ht="15" hidden="0" customHeight="1">
       <x:c r="A95" s="12" t="str">
@@ -4631,6 +5785,17 @@
         <x:v>台北市中正區和平西路一段34號</x:v>
       </x:c>
       <x:c r="G95" s="12"/>
+      <x:c r="H95" s="21"/>
+      <x:c r="I95" s="21"/>
+      <x:c r="J95" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K95" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L95" s="10" t="str"/>
+      <x:c r="M95" s="10"/>
+      <x:c r="N95" s="10"/>
     </x:row>
     <x:row r="96" ht="15" hidden="0" customHeight="1">
       <x:c r="A96" s="12" t="str">
@@ -4650,6 +5815,19 @@
         <x:v>台北市自來水處公車站牌</x:v>
       </x:c>
       <x:c r="G96" s="12"/>
+      <x:c r="H96" s="21"/>
+      <x:c r="I96" s="21"/>
+      <x:c r="J96" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K96" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L96" s="10" t="str">
+        <x:v>缺少完整門牌或唯一地標；建議人工確認 Google Maps 位置後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M96" s="10"/>
+      <x:c r="N96" s="10"/>
     </x:row>
     <x:row r="97" ht="15" hidden="0" customHeight="1">
       <x:c r="A97" s="12" t="str">
@@ -4671,6 +5849,17 @@
         <x:v>新北市永和區福和路239號</x:v>
       </x:c>
       <x:c r="G97" s="12"/>
+      <x:c r="H97" s="21"/>
+      <x:c r="I97" s="21"/>
+      <x:c r="J97" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K97" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L97" s="10" t="str"/>
+      <x:c r="M97" s="10"/>
+      <x:c r="N97" s="10"/>
     </x:row>
     <x:row r="98" ht="15" hidden="0" customHeight="1">
       <x:c r="A98" s="12" t="str">
@@ -4692,6 +5881,17 @@
         <x:v>新北市永和區福和路73號</x:v>
       </x:c>
       <x:c r="G98" s="12"/>
+      <x:c r="H98" s="21"/>
+      <x:c r="I98" s="21"/>
+      <x:c r="J98" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K98" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L98" s="10" t="str"/>
+      <x:c r="M98" s="10"/>
+      <x:c r="N98" s="10"/>
     </x:row>
     <x:row r="99" ht="15" hidden="0" customHeight="1">
       <x:c r="A99" s="12" t="str">
@@ -4713,6 +5913,17 @@
         <x:v>台北市大安區辛亥路一段32號</x:v>
       </x:c>
       <x:c r="G99" s="12"/>
+      <x:c r="H99" s="21"/>
+      <x:c r="I99" s="21"/>
+      <x:c r="J99" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K99" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L99" s="10" t="str"/>
+      <x:c r="M99" s="10"/>
+      <x:c r="N99" s="10"/>
     </x:row>
     <x:row r="100" ht="15" hidden="0" customHeight="1">
       <x:c r="A100" s="12" t="str">
@@ -4734,6 +5945,17 @@
         <x:v>台北市文山區興隆路二段277號</x:v>
       </x:c>
       <x:c r="G100" s="12"/>
+      <x:c r="H100" s="21"/>
+      <x:c r="I100" s="21"/>
+      <x:c r="J100" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K100" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L100" s="10" t="str"/>
+      <x:c r="M100" s="10"/>
+      <x:c r="N100" s="10"/>
     </x:row>
     <x:row r="101" ht="15" hidden="0" customHeight="1">
       <x:c r="A101" s="12" t="str">
@@ -4755,6 +5977,17 @@
         <x:v>台北市文山區興隆路二段97號</x:v>
       </x:c>
       <x:c r="G101" s="12"/>
+      <x:c r="H101" s="21"/>
+      <x:c r="I101" s="21"/>
+      <x:c r="J101" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K101" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L101" s="10" t="str"/>
+      <x:c r="M101" s="10"/>
+      <x:c r="N101" s="10"/>
     </x:row>
     <x:row r="102" ht="15" hidden="0" customHeight="1">
       <x:c r="A102" s="12" t="str">
@@ -4776,6 +6009,17 @@
         <x:v>台北市文山區羅斯福路六段11號</x:v>
       </x:c>
       <x:c r="G102" s="12"/>
+      <x:c r="H102" s="21"/>
+      <x:c r="I102" s="21"/>
+      <x:c r="J102" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K102" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L102" s="10" t="str"/>
+      <x:c r="M102" s="10"/>
+      <x:c r="N102" s="10"/>
     </x:row>
     <x:row r="103" ht="15" hidden="0" customHeight="1">
       <x:c r="A103" s="12" t="str">
@@ -4797,6 +6041,17 @@
         <x:v>台北市文山區羅斯福路五段121號</x:v>
       </x:c>
       <x:c r="G103" s="12"/>
+      <x:c r="H103" s="21"/>
+      <x:c r="I103" s="21"/>
+      <x:c r="J103" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K103" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L103" s="10" t="str"/>
+      <x:c r="M103" s="10"/>
+      <x:c r="N103" s="10"/>
     </x:row>
     <x:row r="104" ht="15" hidden="0" customHeight="1">
       <x:c r="A104" s="12" t="str">
@@ -4818,6 +6073,17 @@
         <x:v>新北市板橋區文化路一段196號</x:v>
       </x:c>
       <x:c r="G104" s="12"/>
+      <x:c r="H104" s="21"/>
+      <x:c r="I104" s="21"/>
+      <x:c r="J104" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K104" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L104" s="10" t="str"/>
+      <x:c r="M104" s="10"/>
+      <x:c r="N104" s="10"/>
     </x:row>
     <x:row r="105" ht="15" hidden="0" customHeight="1">
       <x:c r="A105" s="12" t="str">
@@ -4839,6 +6105,17 @@
         <x:v>新北市中和區中正路909號</x:v>
       </x:c>
       <x:c r="G105" s="12"/>
+      <x:c r="H105" s="21"/>
+      <x:c r="I105" s="21"/>
+      <x:c r="J105" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K105" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L105" s="10" t="str"/>
+      <x:c r="M105" s="10"/>
+      <x:c r="N105" s="10"/>
     </x:row>
     <x:row r="106" ht="15" hidden="0" customHeight="1">
       <x:c r="A106" s="12" t="str">
@@ -4860,6 +6137,17 @@
         <x:v>新北市板橋區縣民大道二段1號</x:v>
       </x:c>
       <x:c r="G106" s="12"/>
+      <x:c r="H106" s="21"/>
+      <x:c r="I106" s="21"/>
+      <x:c r="J106" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K106" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L106" s="10" t="str"/>
+      <x:c r="M106" s="10"/>
+      <x:c r="N106" s="10"/>
     </x:row>
     <x:row r="107" ht="15" hidden="0" customHeight="1">
       <x:c r="A107" s="12" t="str">
@@ -4881,6 +6169,17 @@
         <x:v>新北市板橋區文化路二段22號</x:v>
       </x:c>
       <x:c r="G107" s="12"/>
+      <x:c r="H107" s="21"/>
+      <x:c r="I107" s="21"/>
+      <x:c r="J107" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K107" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L107" s="10" t="str"/>
+      <x:c r="M107" s="10"/>
+      <x:c r="N107" s="10"/>
     </x:row>
     <x:row r="108" ht="15" hidden="0" customHeight="1">
       <x:c r="A108" s="12" t="str">
@@ -4902,6 +6201,17 @@
         <x:v>新北市板橋區重慶路262號</x:v>
       </x:c>
       <x:c r="G108" s="12"/>
+      <x:c r="H108" s="21"/>
+      <x:c r="I108" s="21"/>
+      <x:c r="J108" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K108" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L108" s="10" t="str"/>
+      <x:c r="M108" s="10"/>
+      <x:c r="N108" s="10"/>
     </x:row>
     <x:row r="109" ht="15" hidden="0" customHeight="1">
       <x:c r="A109" s="12" t="str">
@@ -4923,6 +6233,17 @@
         <x:v>新北市板橋區中山路一段10號</x:v>
       </x:c>
       <x:c r="G109" s="12"/>
+      <x:c r="H109" s="21"/>
+      <x:c r="I109" s="21"/>
+      <x:c r="J109" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K109" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L109" s="10" t="str"/>
+      <x:c r="M109" s="10"/>
+      <x:c r="N109" s="10"/>
     </x:row>
     <x:row r="110" ht="15" hidden="0" customHeight="1">
       <x:c r="A110" s="12" t="str">
@@ -4944,6 +6265,17 @@
         <x:v>新北市板橋區雙十路二段71號</x:v>
       </x:c>
       <x:c r="G110" s="12"/>
+      <x:c r="H110" s="21"/>
+      <x:c r="I110" s="21"/>
+      <x:c r="J110" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K110" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L110" s="10" t="str"/>
+      <x:c r="M110" s="10"/>
+      <x:c r="N110" s="10"/>
     </x:row>
     <x:row r="111" ht="15" hidden="0" customHeight="1">
       <x:c r="A111" s="12" t="str">
@@ -4965,6 +6297,17 @@
         <x:v>新北市板橋區三民路二段72號</x:v>
       </x:c>
       <x:c r="G111" s="12"/>
+      <x:c r="H111" s="21"/>
+      <x:c r="I111" s="21"/>
+      <x:c r="J111" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K111" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L111" s="10" t="str"/>
+      <x:c r="M111" s="10"/>
+      <x:c r="N111" s="10"/>
     </x:row>
     <x:row r="112" ht="15" hidden="0" customHeight="1">
       <x:c r="A112" s="12" t="str">
@@ -4986,6 +6329,17 @@
         <x:v>新北市板橋區國慶路203號</x:v>
       </x:c>
       <x:c r="G112" s="12"/>
+      <x:c r="H112" s="21"/>
+      <x:c r="I112" s="21"/>
+      <x:c r="J112" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K112" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L112" s="10" t="str"/>
+      <x:c r="M112" s="10"/>
+      <x:c r="N112" s="10"/>
     </x:row>
     <x:row r="113" ht="15" hidden="0" customHeight="1">
       <x:c r="A113" s="12" t="str">
@@ -5007,6 +6361,17 @@
         <x:v>新北市土城區金城路二段209號</x:v>
       </x:c>
       <x:c r="G113" s="12"/>
+      <x:c r="H113" s="21"/>
+      <x:c r="I113" s="21"/>
+      <x:c r="J113" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K113" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L113" s="10" t="str"/>
+      <x:c r="M113" s="10"/>
+      <x:c r="N113" s="10"/>
     </x:row>
     <x:row r="114" ht="15" hidden="0" customHeight="1">
       <x:c r="A114" s="12" t="str">
@@ -5028,6 +6393,17 @@
         <x:v>新北市土城區中央路三段84號</x:v>
       </x:c>
       <x:c r="G114" s="12"/>
+      <x:c r="H114" s="21"/>
+      <x:c r="I114" s="21"/>
+      <x:c r="J114" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K114" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L114" s="10" t="str"/>
+      <x:c r="M114" s="10"/>
+      <x:c r="N114" s="10"/>
     </x:row>
     <x:row r="115" ht="15" hidden="0" customHeight="1">
       <x:c r="A115" s="12" t="str">
@@ -5049,6 +6425,17 @@
         <x:v>新北市板橋區信義路82號</x:v>
       </x:c>
       <x:c r="G115" s="12"/>
+      <x:c r="H115" s="21"/>
+      <x:c r="I115" s="21"/>
+      <x:c r="J115" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K115" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L115" s="10" t="str"/>
+      <x:c r="M115" s="10"/>
+      <x:c r="N115" s="10"/>
     </x:row>
     <x:row r="116" ht="15" hidden="0" customHeight="1">
       <x:c r="A116" s="12" t="str">
@@ -5070,6 +6457,17 @@
         <x:v>新北市土城區金城路一段 土城國小</x:v>
       </x:c>
       <x:c r="G116" s="12"/>
+      <x:c r="H116" s="21"/>
+      <x:c r="I116" s="21"/>
+      <x:c r="J116" t="str">
+        <x:v>Google地標</x:v>
+      </x:c>
+      <x:c r="K116" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L116" s="10" t="str"/>
+      <x:c r="M116" s="10"/>
+      <x:c r="N116" s="10"/>
     </x:row>
     <x:row r="117" ht="15" hidden="0" customHeight="1">
       <x:c r="A117" s="12" t="str">
@@ -5091,6 +6489,17 @@
         <x:v>新北市三重區正義北路15號</x:v>
       </x:c>
       <x:c r="G117" s="12"/>
+      <x:c r="H117" s="21"/>
+      <x:c r="I117" s="21"/>
+      <x:c r="J117" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K117" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L117" s="10" t="str"/>
+      <x:c r="M117" s="10"/>
+      <x:c r="N117" s="10"/>
     </x:row>
     <x:row r="118" ht="15" hidden="0" customHeight="1">
       <x:c r="A118" s="12" t="str">
@@ -5112,6 +6521,17 @@
         <x:v>新北市三重區正義北路325號</x:v>
       </x:c>
       <x:c r="G118" s="12"/>
+      <x:c r="H118" s="21"/>
+      <x:c r="I118" s="21"/>
+      <x:c r="J118" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K118" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L118" s="10" t="str"/>
+      <x:c r="M118" s="10"/>
+      <x:c r="N118" s="10"/>
     </x:row>
     <x:row r="119" ht="15" hidden="0" customHeight="1">
       <x:c r="A119" s="12" t="str">
@@ -5133,6 +6553,17 @@
         <x:v>新北市三重區新北大道一段17號</x:v>
       </x:c>
       <x:c r="G119" s="12"/>
+      <x:c r="H119" s="21"/>
+      <x:c r="I119" s="21"/>
+      <x:c r="J119" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K119" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L119" s="10" t="str"/>
+      <x:c r="M119" s="10"/>
+      <x:c r="N119" s="10"/>
     </x:row>
     <x:row r="120" ht="15" hidden="0" customHeight="1">
       <x:c r="A120" s="12" t="str">
@@ -5154,6 +6585,17 @@
         <x:v>新北市蘆洲區捷運蘆洲站3號出口</x:v>
       </x:c>
       <x:c r="G120" s="12"/>
+      <x:c r="H120" s="21"/>
+      <x:c r="I120" s="21"/>
+      <x:c r="J120" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K120" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L120" s="10" t="str"/>
+      <x:c r="M120" s="10"/>
+      <x:c r="N120" s="10"/>
     </x:row>
     <x:row r="121" ht="15" hidden="0" customHeight="1">
       <x:c r="A121" s="12" t="str">
@@ -5175,6 +6617,17 @@
         <x:v>新北市蘆洲區中山一路63號</x:v>
       </x:c>
       <x:c r="G121" s="12"/>
+      <x:c r="H121" s="21"/>
+      <x:c r="I121" s="21"/>
+      <x:c r="J121" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K121" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L121" s="10" t="str"/>
+      <x:c r="M121" s="10"/>
+      <x:c r="N121" s="10"/>
     </x:row>
     <x:row r="122" ht="15" hidden="0" customHeight="1">
       <x:c r="A122" s="12" t="str">
@@ -5196,6 +6649,17 @@
         <x:v>新北市三重區三和路四段390號</x:v>
       </x:c>
       <x:c r="G122" s="12"/>
+      <x:c r="H122" s="21"/>
+      <x:c r="I122" s="21"/>
+      <x:c r="J122" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K122" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L122" s="10" t="str"/>
+      <x:c r="M122" s="10"/>
+      <x:c r="N122" s="10"/>
     </x:row>
     <x:row r="123" ht="15" hidden="0" customHeight="1">
       <x:c r="A123" s="12" t="str">
@@ -5217,6 +6681,17 @@
         <x:v>新北市五股區新五路二段236號</x:v>
       </x:c>
       <x:c r="G123" s="12"/>
+      <x:c r="H123" s="21"/>
+      <x:c r="I123" s="21"/>
+      <x:c r="J123" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K123" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L123" s="10" t="str"/>
+      <x:c r="M123" s="10"/>
+      <x:c r="N123" s="10"/>
     </x:row>
     <x:row r="124" ht="15" hidden="0" customHeight="1">
       <x:c r="A124" s="12" t="str">
@@ -5238,6 +6713,17 @@
         <x:v>新北市蘆洲區長榮路386號</x:v>
       </x:c>
       <x:c r="G124" s="12"/>
+      <x:c r="H124" s="21"/>
+      <x:c r="I124" s="21"/>
+      <x:c r="J124" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K124" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L124" s="10" t="str"/>
+      <x:c r="M124" s="10"/>
+      <x:c r="N124" s="10"/>
     </x:row>
     <x:row r="125" ht="15" hidden="0" customHeight="1">
       <x:c r="A125" s="12" t="str">
@@ -5259,6 +6745,17 @@
         <x:v>新北市蘆洲區捷運三民高中站1號出口</x:v>
       </x:c>
       <x:c r="G125" s="12"/>
+      <x:c r="H125" s="21"/>
+      <x:c r="I125" s="21"/>
+      <x:c r="J125" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K125" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L125" s="10" t="str"/>
+      <x:c r="M125" s="10"/>
+      <x:c r="N125" s="10"/>
     </x:row>
     <x:row r="126" ht="15" hidden="0" customHeight="1">
       <x:c r="A126" s="12" t="str">
@@ -5280,6 +6777,17 @@
         <x:v>新北市中和區景平路341號</x:v>
       </x:c>
       <x:c r="G126" s="12"/>
+      <x:c r="H126" s="21"/>
+      <x:c r="I126" s="21"/>
+      <x:c r="J126" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K126" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L126" s="10" t="str"/>
+      <x:c r="M126" s="10"/>
+      <x:c r="N126" s="10"/>
     </x:row>
     <x:row r="127" ht="15" hidden="0" customHeight="1">
       <x:c r="A127" s="12" t="str">
@@ -5301,6 +6809,17 @@
         <x:v>新北市中和區景平路121號</x:v>
       </x:c>
       <x:c r="G127" s="12"/>
+      <x:c r="H127" s="21"/>
+      <x:c r="I127" s="21"/>
+      <x:c r="J127" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K127" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L127" s="10" t="str"/>
+      <x:c r="M127" s="10"/>
+      <x:c r="N127" s="10"/>
     </x:row>
     <x:row r="128" ht="15" hidden="0" customHeight="1">
       <x:c r="A128" s="12" t="str">
@@ -5322,6 +6841,17 @@
         <x:v>新北市中和區景新街404號</x:v>
       </x:c>
       <x:c r="G128" s="12"/>
+      <x:c r="H128" s="21"/>
+      <x:c r="I128" s="21"/>
+      <x:c r="J128" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K128" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L128" s="10" t="str"/>
+      <x:c r="M128" s="10"/>
+      <x:c r="N128" s="10"/>
     </x:row>
     <x:row r="129" ht="15" hidden="0" customHeight="1">
       <x:c r="A129" s="12" t="str">
@@ -5343,6 +6873,17 @@
         <x:v>新北市新店區安和路三段151號</x:v>
       </x:c>
       <x:c r="G129" s="12"/>
+      <x:c r="H129" s="21"/>
+      <x:c r="I129" s="21"/>
+      <x:c r="J129" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K129" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L129" s="10" t="str"/>
+      <x:c r="M129" s="10"/>
+      <x:c r="N129" s="10"/>
     </x:row>
     <x:row r="130" ht="15" hidden="0" customHeight="1">
       <x:c r="A130" s="12" t="str">
@@ -5364,6 +6905,17 @@
         <x:v>新北市中和區景平路396號</x:v>
       </x:c>
       <x:c r="G130" s="12"/>
+      <x:c r="H130" s="21"/>
+      <x:c r="I130" s="21"/>
+      <x:c r="J130" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K130" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L130" s="10" t="str"/>
+      <x:c r="M130" s="10"/>
+      <x:c r="N130" s="10"/>
     </x:row>
     <x:row r="131" ht="15" hidden="0" customHeight="1">
       <x:c r="A131" s="12" t="str">
@@ -5385,6 +6937,17 @@
         <x:v>新北市中和區中正路80號</x:v>
       </x:c>
       <x:c r="G131" s="12"/>
+      <x:c r="H131" s="21"/>
+      <x:c r="I131" s="21"/>
+      <x:c r="J131" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K131" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L131" s="10" t="str"/>
+      <x:c r="M131" s="10"/>
+      <x:c r="N131" s="10"/>
     </x:row>
     <x:row r="132" ht="15" hidden="0" customHeight="1">
       <x:c r="A132" s="12" t="str">
@@ -5406,6 +6969,17 @@
         <x:v>新北市中和區中正路462號</x:v>
       </x:c>
       <x:c r="G132" s="12"/>
+      <x:c r="H132" s="21"/>
+      <x:c r="I132" s="21"/>
+      <x:c r="J132" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K132" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L132" s="10" t="str"/>
+      <x:c r="M132" s="10"/>
+      <x:c r="N132" s="10"/>
     </x:row>
     <x:row r="133" ht="15" hidden="0" customHeight="1">
       <x:c r="A133" s="12" t="str">
@@ -5427,6 +7001,17 @@
         <x:v>新北市永和區得和路327號</x:v>
       </x:c>
       <x:c r="G133" s="12"/>
+      <x:c r="H133" s="21"/>
+      <x:c r="I133" s="21"/>
+      <x:c r="J133" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K133" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L133" s="10" t="str"/>
+      <x:c r="M133" s="10"/>
+      <x:c r="N133" s="10"/>
     </x:row>
     <x:row r="134" ht="15" hidden="0" customHeight="1">
       <x:c r="A134" s="12" t="str">
@@ -5448,6 +7033,17 @@
         <x:v>新北市永和區中正路191號</x:v>
       </x:c>
       <x:c r="G134" s="12"/>
+      <x:c r="H134" s="21"/>
+      <x:c r="I134" s="21"/>
+      <x:c r="J134" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K134" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L134" s="10" t="str"/>
+      <x:c r="M134" s="10"/>
+      <x:c r="N134" s="10"/>
     </x:row>
     <x:row r="135" ht="15" hidden="0" customHeight="1">
       <x:c r="A135" s="12" t="str">
@@ -5469,6 +7065,17 @@
         <x:v>新北市永和區中正路61號</x:v>
       </x:c>
       <x:c r="G135" s="12"/>
+      <x:c r="H135" s="21"/>
+      <x:c r="I135" s="21"/>
+      <x:c r="J135" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K135" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L135" s="10" t="str"/>
+      <x:c r="M135" s="10"/>
+      <x:c r="N135" s="10"/>
     </x:row>
     <x:row r="136" ht="15" hidden="0" customHeight="1">
       <x:c r="A136" s="12" t="str">
@@ -5490,6 +7097,17 @@
         <x:v>新北市新店區安和路一段47號</x:v>
       </x:c>
       <x:c r="G136" s="12"/>
+      <x:c r="H136" s="21"/>
+      <x:c r="I136" s="21"/>
+      <x:c r="J136" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K136" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L136" s="10" t="str"/>
+      <x:c r="M136" s="10"/>
+      <x:c r="N136" s="10"/>
     </x:row>
     <x:row r="137" ht="15" hidden="0" customHeight="1">
       <x:c r="A137" s="12" t="str">
@@ -5511,6 +7129,17 @@
         <x:v>台北市文山區木柵路一段72號</x:v>
       </x:c>
       <x:c r="G137" s="12"/>
+      <x:c r="H137" s="21"/>
+      <x:c r="I137" s="21"/>
+      <x:c r="J137" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K137" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L137" s="10" t="str"/>
+      <x:c r="M137" s="10"/>
+      <x:c r="N137" s="10"/>
     </x:row>
     <x:row r="138" ht="15" hidden="0" customHeight="1">
       <x:c r="A138" s="12" t="str">
@@ -5532,6 +7161,17 @@
         <x:v>台北市文山區木柵路二段66號</x:v>
       </x:c>
       <x:c r="G138" s="12"/>
+      <x:c r="H138" s="21"/>
+      <x:c r="I138" s="21"/>
+      <x:c r="J138" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K138" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L138" s="10" t="str"/>
+      <x:c r="M138" s="10"/>
+      <x:c r="N138" s="10"/>
     </x:row>
     <x:row r="139" ht="15" hidden="0" customHeight="1">
       <x:c r="A139" s="12" t="str">
@@ -5553,6 +7193,17 @@
         <x:v>台北市文山區秀明路一段 久康公園</x:v>
       </x:c>
       <x:c r="G139" s="12"/>
+      <x:c r="H139" s="21"/>
+      <x:c r="I139" s="21"/>
+      <x:c r="J139" t="str">
+        <x:v>Google地標</x:v>
+      </x:c>
+      <x:c r="K139" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L139" s="10" t="str"/>
+      <x:c r="M139" s="10"/>
+      <x:c r="N139" s="10"/>
     </x:row>
     <x:row r="140" ht="15" hidden="0" customHeight="1">
       <x:c r="A140" s="12" t="str">
@@ -5574,6 +7225,17 @@
         <x:v>台北市文山區木柵國小後門</x:v>
       </x:c>
       <x:c r="G140" s="12"/>
+      <x:c r="H140" s="21"/>
+      <x:c r="I140" s="21"/>
+      <x:c r="J140" t="str">
+        <x:v>Google地標</x:v>
+      </x:c>
+      <x:c r="K140" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L140" s="10" t="str"/>
+      <x:c r="M140" s="10"/>
+      <x:c r="N140" s="10"/>
     </x:row>
     <x:row r="141" ht="15" hidden="0" customHeight="1">
       <x:c r="A141" s="12" t="str">
@@ -5595,6 +7257,17 @@
         <x:v>台北市文山區木柵路四段96號</x:v>
       </x:c>
       <x:c r="G141" s="12"/>
+      <x:c r="H141" s="21"/>
+      <x:c r="I141" s="21"/>
+      <x:c r="J141" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K141" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L141" s="10" t="str"/>
+      <x:c r="M141" s="10"/>
+      <x:c r="N141" s="10"/>
     </x:row>
     <x:row r="142" ht="15" hidden="0" customHeight="1">
       <x:c r="A142" s="12" t="str">
@@ -5616,6 +7289,17 @@
         <x:v>新北市新店區北新路二段108號</x:v>
       </x:c>
       <x:c r="G142" s="12"/>
+      <x:c r="H142" s="21"/>
+      <x:c r="I142" s="21"/>
+      <x:c r="J142" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K142" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L142" s="10" t="str"/>
+      <x:c r="M142" s="10"/>
+      <x:c r="N142" s="10"/>
     </x:row>
     <x:row r="143" ht="15" hidden="0" customHeight="1">
       <x:c r="A143" s="12" t="str">
@@ -5637,6 +7321,17 @@
         <x:v>新北市新店區民權路17號</x:v>
       </x:c>
       <x:c r="G143" s="12"/>
+      <x:c r="H143" s="21"/>
+      <x:c r="I143" s="21"/>
+      <x:c r="J143" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K143" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L143" s="10" t="str"/>
+      <x:c r="M143" s="10"/>
+      <x:c r="N143" s="10"/>
     </x:row>
     <x:row r="144" ht="15" hidden="0" customHeight="1">
       <x:c r="A144" s="12" t="str">
@@ -5658,6 +7353,17 @@
         <x:v>新北市永和區成功路76號</x:v>
       </x:c>
       <x:c r="G144" s="12"/>
+      <x:c r="H144" s="21"/>
+      <x:c r="I144" s="21"/>
+      <x:c r="J144" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K144" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L144" s="10" t="str"/>
+      <x:c r="M144" s="10"/>
+      <x:c r="N144" s="10"/>
     </x:row>
     <x:row r="145" ht="15" hidden="0" customHeight="1">
       <x:c r="A145" s="12" t="str">
@@ -5679,6 +7385,19 @@
         <x:v>新北市新店區中正路75巷口</x:v>
       </x:c>
       <x:c r="G145" s="12"/>
+      <x:c r="H145" s="21"/>
+      <x:c r="I145" s="21"/>
+      <x:c r="J145" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K145" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L145" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M145" s="10"/>
+      <x:c r="N145" s="10"/>
     </x:row>
     <x:row r="146" ht="15" hidden="0" customHeight="1">
       <x:c r="A146" s="12" t="str">
@@ -5700,6 +7419,17 @@
         <x:v>台北市內湖區行善路158號</x:v>
       </x:c>
       <x:c r="G146" s="12"/>
+      <x:c r="H146" s="21"/>
+      <x:c r="I146" s="21"/>
+      <x:c r="J146" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K146" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L146" s="10" t="str"/>
+      <x:c r="M146" s="10"/>
+      <x:c r="N146" s="10"/>
     </x:row>
     <x:row r="147" ht="15" hidden="0" customHeight="1">
       <x:c r="A147" s="12" t="str">
@@ -5721,6 +7451,17 @@
         <x:v>新北市汐止區新台五路一段88號</x:v>
       </x:c>
       <x:c r="G147" s="12"/>
+      <x:c r="H147" s="21"/>
+      <x:c r="I147" s="21"/>
+      <x:c r="J147" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K147" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L147" s="10" t="str"/>
+      <x:c r="M147" s="10"/>
+      <x:c r="N147" s="10"/>
     </x:row>
     <x:row r="148" ht="15" hidden="0" customHeight="1">
       <x:c r="A148" s="12" t="str">
@@ -5742,6 +7483,19 @@
       <x:c r="G148" s="12" t="str">
         <x:v>依上排行駛路線「汐止→基隆」補全為新台五路／百三街口。</x:v>
       </x:c>
+      <x:c r="H148" s="21"/>
+      <x:c r="I148" s="21"/>
+      <x:c r="J148" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K148" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L148" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M148" s="10"/>
+      <x:c r="N148" s="10"/>
     </x:row>
     <x:row r="149" ht="15" hidden="0" customHeight="1">
       <x:c r="A149" s="12" t="str">
@@ -5763,6 +7517,17 @@
         <x:v>基隆市七堵區明德一路171號</x:v>
       </x:c>
       <x:c r="G149" s="12"/>
+      <x:c r="H149" s="21"/>
+      <x:c r="I149" s="21"/>
+      <x:c r="J149" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K149" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L149" s="10" t="str"/>
+      <x:c r="M149" s="10"/>
+      <x:c r="N149" s="10"/>
     </x:row>
     <x:row r="150" ht="15" hidden="0" customHeight="1">
       <x:c r="A150" s="12" t="str">
@@ -5784,6 +7549,19 @@
         <x:v>基隆市仁愛區仁三路 基隆廟口</x:v>
       </x:c>
       <x:c r="G150" s="12"/>
+      <x:c r="H150" s="21"/>
+      <x:c r="I150" s="21"/>
+      <x:c r="J150" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K150" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L150" s="10" t="str">
+        <x:v>缺少完整門牌或唯一地標；建議人工確認 Google Maps 位置後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M150" s="10"/>
+      <x:c r="N150" s="10"/>
     </x:row>
     <x:row r="151" ht="15" hidden="0" customHeight="1">
       <x:c r="A151" s="12" t="str">
@@ -5805,6 +7583,17 @@
         <x:v>基隆市仁愛區忠二路13號</x:v>
       </x:c>
       <x:c r="G151" s="12"/>
+      <x:c r="H151" s="21"/>
+      <x:c r="I151" s="21"/>
+      <x:c r="J151" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K151" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L151" s="10" t="str"/>
+      <x:c r="M151" s="10"/>
+      <x:c r="N151" s="10"/>
     </x:row>
     <x:row r="152" ht="15" hidden="0" customHeight="1">
       <x:c r="A152" s="12" t="str">
@@ -5826,6 +7615,17 @@
         <x:v>桃園市中壢區延平路155號</x:v>
       </x:c>
       <x:c r="G152" s="12"/>
+      <x:c r="H152" s="21"/>
+      <x:c r="I152" s="21"/>
+      <x:c r="J152" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K152" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L152" s="10" t="str"/>
+      <x:c r="M152" s="10"/>
+      <x:c r="N152" s="10"/>
     </x:row>
     <x:row r="153" ht="15" hidden="0" customHeight="1">
       <x:c r="A153" s="12" t="str">
@@ -5847,6 +7647,17 @@
         <x:v>桃園市中壢區中央東路88號</x:v>
       </x:c>
       <x:c r="G153" s="12"/>
+      <x:c r="H153" s="21"/>
+      <x:c r="I153" s="21"/>
+      <x:c r="J153" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K153" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L153" s="10" t="str"/>
+      <x:c r="M153" s="10"/>
+      <x:c r="N153" s="10"/>
     </x:row>
     <x:row r="154" ht="15" hidden="0" customHeight="1">
       <x:c r="A154" s="12" t="str">
@@ -5868,6 +7679,17 @@
         <x:v>桃園市平鎮區延平路二段56號</x:v>
       </x:c>
       <x:c r="G154" s="12"/>
+      <x:c r="H154" s="21"/>
+      <x:c r="I154" s="21"/>
+      <x:c r="J154" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K154" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L154" s="10" t="str"/>
+      <x:c r="M154" s="10"/>
+      <x:c r="N154" s="10"/>
     </x:row>
     <x:row r="155" ht="15" hidden="0" customHeight="1">
       <x:c r="A155" s="12" t="str">
@@ -5889,6 +7711,17 @@
         <x:v>桃園市平鎮區延平路二段323號</x:v>
       </x:c>
       <x:c r="G155" s="12"/>
+      <x:c r="H155" s="21"/>
+      <x:c r="I155" s="21"/>
+      <x:c r="J155" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K155" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L155" s="10" t="str"/>
+      <x:c r="M155" s="10"/>
+      <x:c r="N155" s="10"/>
     </x:row>
     <x:row r="156" ht="15" hidden="0" customHeight="1">
       <x:c r="A156" s="12" t="str">
@@ -5910,6 +7743,17 @@
         <x:v>桃園市平鎮區中豐路379號</x:v>
       </x:c>
       <x:c r="G156" s="12"/>
+      <x:c r="H156" s="21"/>
+      <x:c r="I156" s="21"/>
+      <x:c r="J156" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K156" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L156" s="10" t="str"/>
+      <x:c r="M156" s="10"/>
+      <x:c r="N156" s="10"/>
     </x:row>
     <x:row r="157" ht="15" hidden="0" customHeight="1">
       <x:c r="A157" s="12" t="str">
@@ -5931,6 +7775,17 @@
         <x:v>桃園市中壢區東園路43號</x:v>
       </x:c>
       <x:c r="G157" s="12"/>
+      <x:c r="H157" s="21"/>
+      <x:c r="I157" s="21"/>
+      <x:c r="J157" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K157" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L157" s="10" t="str"/>
+      <x:c r="M157" s="10"/>
+      <x:c r="N157" s="10"/>
     </x:row>
     <x:row r="158" ht="15" hidden="0" customHeight="1">
       <x:c r="A158" s="12" t="str">
@@ -5952,6 +7807,17 @@
         <x:v>桃園市中壢區中園路147號</x:v>
       </x:c>
       <x:c r="G158" s="12"/>
+      <x:c r="H158" s="21"/>
+      <x:c r="I158" s="21"/>
+      <x:c r="J158" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K158" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L158" s="10" t="str"/>
+      <x:c r="M158" s="10"/>
+      <x:c r="N158" s="10"/>
     </x:row>
     <x:row r="159" ht="15" hidden="0" customHeight="1">
       <x:c r="A159" s="12" t="str">
@@ -5973,6 +7839,17 @@
         <x:v>桃園市中壢區中央公園</x:v>
       </x:c>
       <x:c r="G159" s="12"/>
+      <x:c r="H159" s="21"/>
+      <x:c r="I159" s="21"/>
+      <x:c r="J159" t="str">
+        <x:v>Google地標</x:v>
+      </x:c>
+      <x:c r="K159" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L159" s="10" t="str"/>
+      <x:c r="M159" s="10"/>
+      <x:c r="N159" s="10"/>
     </x:row>
     <x:row r="160" ht="15" hidden="0" customHeight="1">
       <x:c r="A160" s="12" t="str">
@@ -5994,6 +7871,17 @@
         <x:v>桃園市桃園區經國路737號</x:v>
       </x:c>
       <x:c r="G160" s="12"/>
+      <x:c r="H160" s="21"/>
+      <x:c r="I160" s="21"/>
+      <x:c r="J160" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K160" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L160" s="10" t="str"/>
+      <x:c r="M160" s="10"/>
+      <x:c r="N160" s="10"/>
     </x:row>
     <x:row r="161" ht="15" hidden="0" customHeight="1">
       <x:c r="A161" s="12" t="str">
@@ -6015,6 +7903,17 @@
         <x:v>桃園市桃園區經國路495號</x:v>
       </x:c>
       <x:c r="G161" s="12"/>
+      <x:c r="H161" s="21"/>
+      <x:c r="I161" s="21"/>
+      <x:c r="J161" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K161" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L161" s="10" t="str"/>
+      <x:c r="M161" s="10"/>
+      <x:c r="N161" s="10"/>
     </x:row>
     <x:row r="162" ht="15" hidden="0" customHeight="1">
       <x:c r="A162" s="12" t="str">
@@ -6036,6 +7935,17 @@
         <x:v>桃園市桃園區經國路369號</x:v>
       </x:c>
       <x:c r="G162" s="12"/>
+      <x:c r="H162" s="21"/>
+      <x:c r="I162" s="21"/>
+      <x:c r="J162" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K162" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L162" s="10" t="str"/>
+      <x:c r="M162" s="10"/>
+      <x:c r="N162" s="10"/>
     </x:row>
     <x:row r="163" ht="15" hidden="0" customHeight="1">
       <x:c r="A163" s="12" t="str">
@@ -6057,6 +7967,17 @@
         <x:v>桃園市桃園區經國路451號</x:v>
       </x:c>
       <x:c r="G163" s="12"/>
+      <x:c r="H163" s="21"/>
+      <x:c r="I163" s="21"/>
+      <x:c r="J163" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K163" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L163" s="10" t="str"/>
+      <x:c r="M163" s="10"/>
+      <x:c r="N163" s="10"/>
     </x:row>
     <x:row r="164" ht="15" hidden="0" customHeight="1">
       <x:c r="A164" s="12" t="str">
@@ -6078,6 +7999,17 @@
         <x:v>桃園市桃園區民生路535號</x:v>
       </x:c>
       <x:c r="G164" s="12"/>
+      <x:c r="H164" s="21"/>
+      <x:c r="I164" s="21"/>
+      <x:c r="J164" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K164" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L164" s="10" t="str"/>
+      <x:c r="M164" s="10"/>
+      <x:c r="N164" s="10"/>
     </x:row>
     <x:row r="165" ht="15" hidden="0" customHeight="1">
       <x:c r="A165" s="12" t="str">
@@ -6101,6 +8033,19 @@
       <x:c r="G165" s="12" t="str">
         <x:v>依上排行駛路線「民生路→成功路」補全為成功路／民生路口。</x:v>
       </x:c>
+      <x:c r="H165" s="21"/>
+      <x:c r="I165" s="21"/>
+      <x:c r="J165" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K165" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L165" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M165" s="10"/>
+      <x:c r="N165" s="10"/>
     </x:row>
     <x:row r="166" ht="15" hidden="0" customHeight="1">
       <x:c r="A166" s="12" t="str">
@@ -6122,6 +8067,19 @@
         <x:v>桃園市桃園區復興路 民權路口</x:v>
       </x:c>
       <x:c r="G166" s="12"/>
+      <x:c r="H166" s="21"/>
+      <x:c r="I166" s="21"/>
+      <x:c r="J166" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K166" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L166" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M166" s="10"/>
+      <x:c r="N166" s="10"/>
     </x:row>
     <x:row r="167" ht="15" hidden="0" customHeight="1">
       <x:c r="A167" s="12" t="str">
@@ -6145,6 +8103,19 @@
       <x:c r="G167" s="12" t="str">
         <x:v>依上排行駛路線「民權路→復興路→中山路」補上復興路脈絡。</x:v>
       </x:c>
+      <x:c r="H167" s="21"/>
+      <x:c r="I167" s="21"/>
+      <x:c r="J167" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K167" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L167" s="10" t="str">
+        <x:v>缺少完整門牌或唯一地標；建議人工確認 Google Maps 位置後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M167" s="10"/>
+      <x:c r="N167" s="10"/>
     </x:row>
     <x:row r="168" ht="15" hidden="0" customHeight="1">
       <x:c r="A168" s="12" t="str">
@@ -6166,6 +8137,19 @@
         <x:v>桃園市桃園區中山路 正光街口</x:v>
       </x:c>
       <x:c r="G168" s="12"/>
+      <x:c r="H168" s="21"/>
+      <x:c r="I168" s="21"/>
+      <x:c r="J168" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K168" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L168" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M168" s="10"/>
+      <x:c r="N168" s="10"/>
     </x:row>
     <x:row r="169" ht="15" hidden="0" customHeight="1">
       <x:c r="A169" s="12" t="str">
@@ -6187,6 +8171,19 @@
         <x:v>桃園市桃園區中山路 龍安街口</x:v>
       </x:c>
       <x:c r="G169" s="12"/>
+      <x:c r="H169" s="21"/>
+      <x:c r="I169" s="21"/>
+      <x:c r="J169" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K169" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L169" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M169" s="10"/>
+      <x:c r="N169" s="10"/>
     </x:row>
     <x:row r="170" ht="15" hidden="0" customHeight="1">
       <x:c r="A170" s="12" t="str">
@@ -6208,6 +8205,17 @@
         <x:v>桃園市蘆竹區新南路一段165號</x:v>
       </x:c>
       <x:c r="G170" s="12"/>
+      <x:c r="H170" s="21"/>
+      <x:c r="I170" s="21"/>
+      <x:c r="J170" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K170" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L170" s="10" t="str"/>
+      <x:c r="M170" s="10"/>
+      <x:c r="N170" s="10"/>
     </x:row>
     <x:row r="171" ht="15" hidden="0" customHeight="1">
       <x:c r="A171" s="12" t="str">
@@ -6229,6 +8237,19 @@
       <x:c r="G171" s="12" t="str">
         <x:v>依上排行駛路線補全林口第二交流道周邊道路脈絡。</x:v>
       </x:c>
+      <x:c r="H171" s="21"/>
+      <x:c r="I171" s="21"/>
+      <x:c r="J171" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K171" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L171" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M171" s="10"/>
+      <x:c r="N171" s="10"/>
     </x:row>
     <x:row r="172" ht="15" hidden="0" customHeight="1">
       <x:c r="A172" s="12" t="str">
@@ -6250,6 +8271,17 @@
         <x:v>新北市林口區文化二路一段106號</x:v>
       </x:c>
       <x:c r="G172" s="12"/>
+      <x:c r="H172" s="21"/>
+      <x:c r="I172" s="21"/>
+      <x:c r="J172" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K172" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L172" s="10" t="str"/>
+      <x:c r="M172" s="10"/>
+      <x:c r="N172" s="10"/>
     </x:row>
     <x:row r="173" ht="15" hidden="0" customHeight="1">
       <x:c r="A173" s="12" t="str">
@@ -6271,6 +8303,17 @@
         <x:v>新竹市東區光復路二段36號</x:v>
       </x:c>
       <x:c r="G173" s="12"/>
+      <x:c r="H173" s="21"/>
+      <x:c r="I173" s="21"/>
+      <x:c r="J173" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K173" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L173" s="10" t="str"/>
+      <x:c r="M173" s="10"/>
+      <x:c r="N173" s="10"/>
     </x:row>
     <x:row r="174" ht="15" hidden="0" customHeight="1">
       <x:c r="A174" s="12" t="str">
@@ -6292,6 +8335,17 @@
         <x:v>新竹市東區國立清華大學 光復路二段</x:v>
       </x:c>
       <x:c r="G174" s="12"/>
+      <x:c r="H174" s="21"/>
+      <x:c r="I174" s="21"/>
+      <x:c r="J174" t="str">
+        <x:v>Google地標</x:v>
+      </x:c>
+      <x:c r="K174" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L174" s="10" t="str"/>
+      <x:c r="M174" s="10"/>
+      <x:c r="N174" s="10"/>
     </x:row>
     <x:row r="175" ht="15" hidden="0" customHeight="1">
       <x:c r="A175" s="12" t="str">
@@ -6313,6 +8367,17 @@
         <x:v>新竹市東區光復路二段752號</x:v>
       </x:c>
       <x:c r="G175" s="12"/>
+      <x:c r="H175" s="21"/>
+      <x:c r="I175" s="21"/>
+      <x:c r="J175" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K175" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L175" s="10" t="str"/>
+      <x:c r="M175" s="10"/>
+      <x:c r="N175" s="10"/>
     </x:row>
     <x:row r="176" ht="15" hidden="0" customHeight="1">
       <x:c r="A176" s="12" t="str">
@@ -6332,6 +8397,19 @@
         <x:v>新竹市東區東大路 南大路口</x:v>
       </x:c>
       <x:c r="G176" s="12"/>
+      <x:c r="H176" s="21"/>
+      <x:c r="I176" s="21"/>
+      <x:c r="J176" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K176" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L176" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M176" s="10"/>
+      <x:c r="N176" s="10"/>
     </x:row>
     <x:row r="177" ht="15" hidden="0" customHeight="1">
       <x:c r="A177" s="12" t="str">
@@ -6351,6 +8429,17 @@
         <x:v>新竹市東區新竹轉運站</x:v>
       </x:c>
       <x:c r="G177" s="12"/>
+      <x:c r="H177" s="21"/>
+      <x:c r="I177" s="21"/>
+      <x:c r="J177" t="str">
+        <x:v>Google地標</x:v>
+      </x:c>
+      <x:c r="K177" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L177" s="10" t="str"/>
+      <x:c r="M177" s="10"/>
+      <x:c r="N177" s="10"/>
     </x:row>
     <x:row r="178" ht="15" hidden="0" customHeight="1">
       <x:c r="A178" s="12" t="str">
@@ -6370,6 +8459,19 @@
         <x:v>新竹市東區南大路 食品路口</x:v>
       </x:c>
       <x:c r="G178" s="12"/>
+      <x:c r="H178" s="21"/>
+      <x:c r="I178" s="21"/>
+      <x:c r="J178" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K178" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L178" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M178" s="10"/>
+      <x:c r="N178" s="10"/>
     </x:row>
     <x:row r="179" ht="15" hidden="0" customHeight="1">
       <x:c r="A179" s="12" t="str">
@@ -6391,6 +8493,17 @@
         <x:v>桃園市大溪區永昌路355號</x:v>
       </x:c>
       <x:c r="G179" s="12"/>
+      <x:c r="H179" s="21"/>
+      <x:c r="I179" s="21"/>
+      <x:c r="J179" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K179" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L179" s="10" t="str"/>
+      <x:c r="M179" s="10"/>
+      <x:c r="N179" s="10"/>
     </x:row>
     <x:row r="180" ht="15" hidden="0" customHeight="1">
       <x:c r="A180" s="12" t="str">
@@ -6412,6 +8525,17 @@
         <x:v>桃園市龍潭區大昌路二段172號</x:v>
       </x:c>
       <x:c r="G180" s="12"/>
+      <x:c r="H180" s="21"/>
+      <x:c r="I180" s="21"/>
+      <x:c r="J180" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K180" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L180" s="10" t="str"/>
+      <x:c r="M180" s="10"/>
+      <x:c r="N180" s="10"/>
     </x:row>
     <x:row r="181" ht="15" hidden="0" customHeight="1">
       <x:c r="A181" s="12" t="str">
@@ -6435,6 +8559,19 @@
       <x:c r="G181" s="12" t="str">
         <x:v>依上排行駛路線補全為重陽路／忠孝路口。</x:v>
       </x:c>
+      <x:c r="H181" s="21"/>
+      <x:c r="I181" s="21"/>
+      <x:c r="J181" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K181" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L181" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M181" s="10"/>
+      <x:c r="N181" s="10"/>
     </x:row>
     <x:row r="182" ht="15" hidden="0" customHeight="1">
       <x:c r="A182" s="12" t="str">
@@ -6458,6 +8595,17 @@
       <x:c r="G182" s="12" t="str">
         <x:v>PDF未提供門牌，使用店名作為 Google Maps 定位搜尋文字。</x:v>
       </x:c>
+      <x:c r="H182" s="21"/>
+      <x:c r="I182" s="21"/>
+      <x:c r="J182" t="str">
+        <x:v>Google地標</x:v>
+      </x:c>
+      <x:c r="K182" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L182" s="10" t="str"/>
+      <x:c r="M182" s="10"/>
+      <x:c r="N182" s="10"/>
     </x:row>
     <x:row r="183" ht="15" hidden="0" customHeight="1">
       <x:c r="A183" s="12" t="str">
@@ -6479,6 +8627,17 @@
         <x:v>新北市蘆洲區中原路49號</x:v>
       </x:c>
       <x:c r="G183" s="12"/>
+      <x:c r="H183" s="21"/>
+      <x:c r="I183" s="21"/>
+      <x:c r="J183" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K183" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L183" s="10" t="str"/>
+      <x:c r="M183" s="10"/>
+      <x:c r="N183" s="10"/>
     </x:row>
     <x:row r="184" ht="15" hidden="0" customHeight="1">
       <x:c r="A184" s="12" t="str">
@@ -6500,6 +8659,17 @@
         <x:v>新北市蘆洲區捷運蘆洲站</x:v>
       </x:c>
       <x:c r="G184" s="12"/>
+      <x:c r="H184" s="21"/>
+      <x:c r="I184" s="21"/>
+      <x:c r="J184" t="str">
+        <x:v>Google地標</x:v>
+      </x:c>
+      <x:c r="K184" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L184" s="10" t="str"/>
+      <x:c r="M184" s="10"/>
+      <x:c r="N184" s="10"/>
     </x:row>
     <x:row r="185" ht="15" hidden="0" customHeight="1">
       <x:c r="A185" s="12" t="str">
@@ -6521,6 +8691,17 @@
         <x:v>新北市蘆洲區三民路221號</x:v>
       </x:c>
       <x:c r="G185" s="12"/>
+      <x:c r="H185" s="21"/>
+      <x:c r="I185" s="21"/>
+      <x:c r="J185" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K185" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L185" s="10" t="str"/>
+      <x:c r="M185" s="10"/>
+      <x:c r="N185" s="10"/>
     </x:row>
     <x:row r="186" ht="15" hidden="0" customHeight="1">
       <x:c r="A186" s="12" t="str">
@@ -6542,6 +8723,17 @@
         <x:v>新北市蘆洲區三民路25號</x:v>
       </x:c>
       <x:c r="G186" s="12"/>
+      <x:c r="H186" s="21"/>
+      <x:c r="I186" s="21"/>
+      <x:c r="J186" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K186" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L186" s="10" t="str"/>
+      <x:c r="M186" s="10"/>
+      <x:c r="N186" s="10"/>
     </x:row>
     <x:row r="187" ht="15" hidden="0" customHeight="1">
       <x:c r="A187" s="12" t="str">
@@ -6563,6 +8755,17 @@
         <x:v>新北市新莊區中平路363號</x:v>
       </x:c>
       <x:c r="G187" s="12"/>
+      <x:c r="H187" s="21"/>
+      <x:c r="I187" s="21"/>
+      <x:c r="J187" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K187" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L187" s="10" t="str"/>
+      <x:c r="M187" s="10"/>
+      <x:c r="N187" s="10"/>
     </x:row>
     <x:row r="188" ht="15" hidden="0" customHeight="1">
       <x:c r="A188" s="12" t="str">
@@ -6584,6 +8787,17 @@
         <x:v>新北市新莊區中平路269號</x:v>
       </x:c>
       <x:c r="G188" s="12"/>
+      <x:c r="H188" s="21"/>
+      <x:c r="I188" s="21"/>
+      <x:c r="J188" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K188" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L188" s="10" t="str"/>
+      <x:c r="M188" s="10"/>
+      <x:c r="N188" s="10"/>
     </x:row>
     <x:row r="189" ht="15" hidden="0" customHeight="1">
       <x:c r="A189" s="12" t="str">
@@ -6605,6 +8819,17 @@
         <x:v>新北市新莊區幸福路651號</x:v>
       </x:c>
       <x:c r="G189" s="12"/>
+      <x:c r="H189" s="21"/>
+      <x:c r="I189" s="21"/>
+      <x:c r="J189" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K189" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L189" s="10" t="str"/>
+      <x:c r="M189" s="10"/>
+      <x:c r="N189" s="10"/>
     </x:row>
     <x:row r="190" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A190" s="12" t="str">
@@ -6626,6 +8851,19 @@
       <x:c r="G190" s="12" t="str">
         <x:v>PDF下排寫「辛福路」；依上排行駛路線修正定位為「幸福路／福壽街口」。</x:v>
       </x:c>
+      <x:c r="H190" s="21"/>
+      <x:c r="I190" s="21"/>
+      <x:c r="J190" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K190" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L190" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M190" s="10"/>
+      <x:c r="N190" s="10"/>
     </x:row>
     <x:row r="191" ht="15" hidden="0" customHeight="1">
       <x:c r="A191" s="12" t="str">
@@ -6647,6 +8885,17 @@
         <x:v>新北市板橋區捷運新埔站2號出口</x:v>
       </x:c>
       <x:c r="G191" s="12"/>
+      <x:c r="H191" s="21"/>
+      <x:c r="I191" s="21"/>
+      <x:c r="J191" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K191" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L191" s="10" t="str"/>
+      <x:c r="M191" s="10"/>
+      <x:c r="N191" s="10"/>
     </x:row>
     <x:row r="192" ht="15" hidden="0" customHeight="1">
       <x:c r="A192" s="12" t="str">
@@ -6668,6 +8917,19 @@
         <x:v>新北市新莊區新泰路 中環路口</x:v>
       </x:c>
       <x:c r="G192" s="12"/>
+      <x:c r="H192" s="21"/>
+      <x:c r="I192" s="21"/>
+      <x:c r="J192" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K192" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L192" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M192" s="10"/>
+      <x:c r="N192" s="10"/>
     </x:row>
     <x:row r="193" ht="15" hidden="0" customHeight="1">
       <x:c r="A193" s="12" t="str">
@@ -6689,6 +8951,17 @@
         <x:v>新北市新莊區新泰國中</x:v>
       </x:c>
       <x:c r="G193" s="12"/>
+      <x:c r="H193" s="21"/>
+      <x:c r="I193" s="21"/>
+      <x:c r="J193" t="str">
+        <x:v>Google地標</x:v>
+      </x:c>
+      <x:c r="K193" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L193" s="10" t="str"/>
+      <x:c r="M193" s="10"/>
+      <x:c r="N193" s="10"/>
     </x:row>
     <x:row r="194" ht="15" hidden="0" customHeight="1">
       <x:c r="A194" s="12" t="str">
@@ -6708,6 +8981,19 @@
         <x:v>新北市新莊區新泰路 公園路口</x:v>
       </x:c>
       <x:c r="G194" s="12"/>
+      <x:c r="H194" s="21"/>
+      <x:c r="I194" s="21"/>
+      <x:c r="J194" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K194" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L194" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M194" s="10"/>
+      <x:c r="N194" s="10"/>
     </x:row>
     <x:row r="195" ht="15" hidden="0" customHeight="1">
       <x:c r="A195" s="12" t="str">
@@ -6727,6 +9013,19 @@
         <x:v>新北市新莊區公園路 中正路口</x:v>
       </x:c>
       <x:c r="G195" s="12"/>
+      <x:c r="H195" s="21"/>
+      <x:c r="I195" s="21"/>
+      <x:c r="J195" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K195" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L195" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M195" s="10"/>
+      <x:c r="N195" s="10"/>
     </x:row>
     <x:row r="196" ht="15" hidden="0" customHeight="1">
       <x:c r="A196" s="12" t="str">
@@ -6748,6 +9047,17 @@
         <x:v>新北市新莊區輔仁大學</x:v>
       </x:c>
       <x:c r="G196" s="12"/>
+      <x:c r="H196" s="21"/>
+      <x:c r="I196" s="21"/>
+      <x:c r="J196" t="str">
+        <x:v>Google地標</x:v>
+      </x:c>
+      <x:c r="K196" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L196" s="10" t="str"/>
+      <x:c r="M196" s="10"/>
+      <x:c r="N196" s="10"/>
     </x:row>
     <x:row r="197" ht="15" hidden="0" customHeight="1">
       <x:c r="A197" s="12" t="str">
@@ -6769,6 +9079,17 @@
         <x:v>台北市士林區重慶北路四段58號</x:v>
       </x:c>
       <x:c r="G197" s="12"/>
+      <x:c r="H197" s="21"/>
+      <x:c r="I197" s="21"/>
+      <x:c r="J197" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K197" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L197" s="10" t="str"/>
+      <x:c r="M197" s="10"/>
+      <x:c r="N197" s="10"/>
     </x:row>
     <x:row r="198" ht="15" hidden="0" customHeight="1">
       <x:c r="A198" s="12" t="str">
@@ -6790,6 +9111,17 @@
         <x:v>台北市士林區中正路429號</x:v>
       </x:c>
       <x:c r="G198" s="12"/>
+      <x:c r="H198" s="21"/>
+      <x:c r="I198" s="21"/>
+      <x:c r="J198" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K198" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L198" s="10" t="str"/>
+      <x:c r="M198" s="10"/>
+      <x:c r="N198" s="10"/>
     </x:row>
     <x:row r="199" ht="15" hidden="0" customHeight="1">
       <x:c r="A199" s="12" t="str">
@@ -6811,6 +9143,17 @@
         <x:v>台北市士林區捷運士林站 中正路</x:v>
       </x:c>
       <x:c r="G199" s="12"/>
+      <x:c r="H199" s="21"/>
+      <x:c r="I199" s="21"/>
+      <x:c r="J199" t="str">
+        <x:v>Google地標</x:v>
+      </x:c>
+      <x:c r="K199" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L199" s="10" t="str"/>
+      <x:c r="M199" s="10"/>
+      <x:c r="N199" s="10"/>
     </x:row>
     <x:row r="200" ht="15" hidden="0" customHeight="1">
       <x:c r="A200" s="12" t="str">
@@ -6832,6 +9175,17 @@
         <x:v>台北市士林區忠誠公園</x:v>
       </x:c>
       <x:c r="G200" s="12"/>
+      <x:c r="H200" s="21"/>
+      <x:c r="I200" s="21"/>
+      <x:c r="J200" t="str">
+        <x:v>Google地標</x:v>
+      </x:c>
+      <x:c r="K200" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L200" s="10" t="str"/>
+      <x:c r="M200" s="10"/>
+      <x:c r="N200" s="10"/>
     </x:row>
     <x:row r="201" ht="15" hidden="0" customHeight="1">
       <x:c r="A201" s="12" t="str">
@@ -6851,6 +9205,17 @@
         <x:v>台北市士林區大葉高島屋</x:v>
       </x:c>
       <x:c r="G201" s="12"/>
+      <x:c r="H201" s="21"/>
+      <x:c r="I201" s="21"/>
+      <x:c r="J201" t="str">
+        <x:v>Google地標</x:v>
+      </x:c>
+      <x:c r="K201" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L201" s="10" t="str"/>
+      <x:c r="M201" s="10"/>
+      <x:c r="N201" s="10"/>
     </x:row>
     <x:row r="202" ht="15" hidden="0" customHeight="1">
       <x:c r="A202" s="12" t="str">
@@ -6872,6 +9237,17 @@
         <x:v>台北市士林區天母東路1之6號</x:v>
       </x:c>
       <x:c r="G202" s="12"/>
+      <x:c r="H202" s="21"/>
+      <x:c r="I202" s="21"/>
+      <x:c r="J202" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K202" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L202" s="10" t="str"/>
+      <x:c r="M202" s="10"/>
+      <x:c r="N202" s="10"/>
     </x:row>
     <x:row r="203" ht="15" hidden="0" customHeight="1">
       <x:c r="A203" s="12" t="str">
@@ -6893,6 +9269,17 @@
         <x:v>台北市士林區天母西路73號</x:v>
       </x:c>
       <x:c r="G203" s="12"/>
+      <x:c r="H203" s="21"/>
+      <x:c r="I203" s="21"/>
+      <x:c r="J203" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K203" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L203" s="10" t="str"/>
+      <x:c r="M203" s="10"/>
+      <x:c r="N203" s="10"/>
     </x:row>
     <x:row r="204" ht="15" hidden="0" customHeight="1">
       <x:c r="A204" s="12" t="str">
@@ -6914,6 +9301,17 @@
         <x:v>台北市北投區捷運唭哩岸站 東華街</x:v>
       </x:c>
       <x:c r="G204" s="12"/>
+      <x:c r="H204" s="21"/>
+      <x:c r="I204" s="21"/>
+      <x:c r="J204" t="str">
+        <x:v>Google地標</x:v>
+      </x:c>
+      <x:c r="K204" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L204" s="10" t="str"/>
+      <x:c r="M204" s="10"/>
+      <x:c r="N204" s="10"/>
     </x:row>
     <x:row r="205" ht="15" hidden="0" customHeight="1">
       <x:c r="A205" s="12" t="str">
@@ -6936,6 +9334,27 @@
       </x:c>
       <x:c r="G205" s="12" t="str">
         <x:v>依上排行駛路線補全為重慶北路／酒泉街口。</x:v>
+      </x:c>
+      <x:c r="H205" s="21" t="n">
+        <x:v>25.07183</x:v>
+      </x:c>
+      <x:c r="I205" s="21" t="n">
+        <x:v>121.51364</x:v>
+      </x:c>
+      <x:c r="J205" t="str">
+        <x:v>公開資料固定座標</x:v>
+      </x:c>
+      <x:c r="K205" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L205" s="10" t="str">
+        <x:v>公開 YouBike 站點「重慶酒泉街口」座標；網站固定使用此座標，不再以路口文字 Geocode。</x:v>
+      </x:c>
+      <x:c r="M205" s="10" t="str">
+        <x:v>https://rplus.github.io/youbike-map/</x:v>
+      </x:c>
+      <x:c r="N205" s="10" t="str">
+        <x:v>高</x:v>
       </x:c>
     </x:row>
     <x:row r="206" ht="15" hidden="0" customHeight="1">
@@ -6956,6 +9375,19 @@
         <x:v>台北市大同區酒泉街 承德路口</x:v>
       </x:c>
       <x:c r="G206" s="12"/>
+      <x:c r="H206" s="21"/>
+      <x:c r="I206" s="21"/>
+      <x:c r="J206" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K206" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L206" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M206" s="10"/>
+      <x:c r="N206" s="10"/>
     </x:row>
     <x:row r="207" ht="15" hidden="0" customHeight="1">
       <x:c r="A207" s="12" t="str">
@@ -6977,6 +9409,27 @@
         <x:v>台北市大同區承德路 民權西路口</x:v>
       </x:c>
       <x:c r="G207" s="12"/>
+      <x:c r="H207" s="21" t="n">
+        <x:v>25.063326</x:v>
+      </x:c>
+      <x:c r="I207" s="21" t="n">
+        <x:v>121.518316</x:v>
+      </x:c>
+      <x:c r="J207" t="str">
+        <x:v>公開資料固定座標</x:v>
+      </x:c>
+      <x:c r="K207" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L207" s="10" t="str">
+        <x:v>公開照片標示拍攝位置為承德路／民權西路口；可代表路口位置，但未確認實際下車側，保留人工確認。</x:v>
+      </x:c>
+      <x:c r="M207" s="10" t="str">
+        <x:v>https://commons.wikimedia.org/wiki/File:%E6%89%BF%E5%BE%B7%E8%B7%AF%E5%A4%A9%E6%A9%8B_-_panoramio.jpg</x:v>
+      </x:c>
+      <x:c r="N207" s="10" t="str">
+        <x:v>中</x:v>
+      </x:c>
     </x:row>
     <x:row r="208" ht="15" hidden="0" customHeight="1">
       <x:c r="A208" s="12" t="str">
@@ -6996,6 +9449,19 @@
         <x:v>台北市內湖區成功路二段 上灣仔公車站</x:v>
       </x:c>
       <x:c r="G208" s="12"/>
+      <x:c r="H208" s="21"/>
+      <x:c r="I208" s="21"/>
+      <x:c r="J208" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K208" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L208" s="10" t="str">
+        <x:v>缺少完整門牌或唯一地標；建議人工確認 Google Maps 位置後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M208" s="10"/>
+      <x:c r="N208" s="10"/>
     </x:row>
     <x:row r="209" ht="15" hidden="0" customHeight="1">
       <x:c r="A209" s="12" t="str">
@@ -7015,6 +9481,19 @@
         <x:v>台北市內湖區方濟中學 公車站</x:v>
       </x:c>
       <x:c r="G209" s="12"/>
+      <x:c r="H209" s="21"/>
+      <x:c r="I209" s="21"/>
+      <x:c r="J209" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K209" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L209" s="10" t="str">
+        <x:v>缺少完整門牌或唯一地標；建議人工確認 Google Maps 位置後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M209" s="10"/>
+      <x:c r="N209" s="10"/>
     </x:row>
     <x:row r="210" ht="15" hidden="0" customHeight="1">
       <x:c r="A210" s="12" t="str">
@@ -7034,6 +9513,17 @@
         <x:v>台北市內湖區捷運文德站</x:v>
       </x:c>
       <x:c r="G210" s="12"/>
+      <x:c r="H210" s="21"/>
+      <x:c r="I210" s="21"/>
+      <x:c r="J210" t="str">
+        <x:v>Google地標</x:v>
+      </x:c>
+      <x:c r="K210" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L210" s="10" t="str"/>
+      <x:c r="M210" s="10"/>
+      <x:c r="N210" s="10"/>
     </x:row>
     <x:row r="211" ht="15" hidden="0" customHeight="1">
       <x:c r="A211" s="12" t="str">
@@ -7055,6 +9545,19 @@
       <x:c r="G211" s="12" t="str">
         <x:v>PDF未提供門牌，使用道路＋地標定位。</x:v>
       </x:c>
+      <x:c r="H211" s="21"/>
+      <x:c r="I211" s="21"/>
+      <x:c r="J211" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K211" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L211" s="10" t="str">
+        <x:v>缺少完整門牌或唯一地標；建議人工確認 Google Maps 位置後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M211" s="10"/>
+      <x:c r="N211" s="10"/>
     </x:row>
     <x:row r="212" ht="15" hidden="0" customHeight="1">
       <x:c r="A212" s="12" t="str">
@@ -7076,6 +9579,19 @@
       <x:c r="G212" s="12" t="str">
         <x:v>PDF未提供門牌，使用道路＋地標定位。</x:v>
       </x:c>
+      <x:c r="H212" s="21"/>
+      <x:c r="I212" s="21"/>
+      <x:c r="J212" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K212" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L212" s="10" t="str">
+        <x:v>缺少完整門牌或唯一地標；建議人工確認 Google Maps 位置後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M212" s="10"/>
+      <x:c r="N212" s="10"/>
     </x:row>
     <x:row r="213" ht="15" hidden="0" customHeight="1">
       <x:c r="A213" s="12" t="str">
@@ -7095,6 +9611,17 @@
         <x:v>台北市內湖區捷運港墘站</x:v>
       </x:c>
       <x:c r="G213" s="12"/>
+      <x:c r="H213" s="21"/>
+      <x:c r="I213" s="21"/>
+      <x:c r="J213" t="str">
+        <x:v>Google地標</x:v>
+      </x:c>
+      <x:c r="K213" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L213" s="10" t="str"/>
+      <x:c r="M213" s="10"/>
+      <x:c r="N213" s="10"/>
     </x:row>
     <x:row r="214" ht="15" hidden="0" customHeight="1">
       <x:c r="A214" s="12" t="str">
@@ -7114,6 +9641,17 @@
         <x:v>台北市內湖區捷運西湖站</x:v>
       </x:c>
       <x:c r="G214" s="12"/>
+      <x:c r="H214" s="21"/>
+      <x:c r="I214" s="21"/>
+      <x:c r="J214" t="str">
+        <x:v>Google地標</x:v>
+      </x:c>
+      <x:c r="K214" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L214" s="10" t="str"/>
+      <x:c r="M214" s="10"/>
+      <x:c r="N214" s="10"/>
     </x:row>
     <x:row r="215" ht="15" hidden="0" customHeight="1">
       <x:c r="A215" s="12" t="str">
@@ -7135,6 +9673,19 @@
       <x:c r="G215" s="12" t="str">
         <x:v>依上排行駛路線補上內湖路脈絡。</x:v>
       </x:c>
+      <x:c r="H215" s="21"/>
+      <x:c r="I215" s="21"/>
+      <x:c r="J215" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K215" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L215" s="10" t="str">
+        <x:v>缺少完整門牌或唯一地標；建議人工確認 Google Maps 位置後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M215" s="10"/>
+      <x:c r="N215" s="10"/>
     </x:row>
     <x:row r="216" ht="15" hidden="0" customHeight="1">
       <x:c r="A216" s="12" t="str">
@@ -7154,6 +9705,17 @@
         <x:v>台北市中山區捷運劍南路站</x:v>
       </x:c>
       <x:c r="G216" s="12"/>
+      <x:c r="H216" s="21"/>
+      <x:c r="I216" s="21"/>
+      <x:c r="J216" t="str">
+        <x:v>Google地標</x:v>
+      </x:c>
+      <x:c r="K216" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L216" s="10" t="str"/>
+      <x:c r="M216" s="10"/>
+      <x:c r="N216" s="10"/>
     </x:row>
     <x:row r="217" ht="15" hidden="0" customHeight="1">
       <x:c r="A217" s="12" t="str">
@@ -7173,6 +9735,19 @@
         <x:v>台北市中山區自強隧道口 公車站</x:v>
       </x:c>
       <x:c r="G217" s="12"/>
+      <x:c r="H217" s="21"/>
+      <x:c r="I217" s="21"/>
+      <x:c r="J217" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K217" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L217" s="10" t="str">
+        <x:v>缺少完整門牌或唯一地標；建議人工確認 Google Maps 位置後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M217" s="10"/>
+      <x:c r="N217" s="10"/>
     </x:row>
     <x:row r="218" ht="15" hidden="0" customHeight="1">
       <x:c r="A218" s="12" t="str">
@@ -7194,6 +9769,17 @@
         <x:v>台北市中山區中山北路四段67號</x:v>
       </x:c>
       <x:c r="G218" s="12"/>
+      <x:c r="H218" s="21"/>
+      <x:c r="I218" s="21"/>
+      <x:c r="J218" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K218" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L218" s="10" t="str"/>
+      <x:c r="M218" s="10"/>
+      <x:c r="N218" s="10"/>
     </x:row>
     <x:row r="219" ht="15" hidden="0" customHeight="1">
       <x:c r="A219" s="12" t="str">
@@ -7215,6 +9801,27 @@
       <x:c r="G219" s="12" t="str">
         <x:v>依上排行駛路線「沿南京東路直行」補全。</x:v>
       </x:c>
+      <x:c r="H219" s="21" t="n">
+        <x:v>25.05618</x:v>
+      </x:c>
+      <x:c r="I219" s="21" t="n">
+        <x:v>121.57988</x:v>
+      </x:c>
+      <x:c r="J219" t="str">
+        <x:v>公開資料固定座標</x:v>
+      </x:c>
+      <x:c r="K219" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L219" s="10" t="str">
+        <x:v>公開交通資料站位「南京舊宗路口」座標；與 PDF 站名一致。</x:v>
+      </x:c>
+      <x:c r="M219" s="10" t="str">
+        <x:v>https://data.zhupiter.com/oddt/24007552/%E5%8D%97%E4%BA%AC%E8%88%8A%E5%AE%97%E8%B7%AF%E5%8F%A3/</x:v>
+      </x:c>
+      <x:c r="N219" s="10" t="str">
+        <x:v>高</x:v>
+      </x:c>
     </x:row>
     <x:row r="220" ht="15" hidden="0" customHeight="1">
       <x:c r="A220" s="12" t="str">
@@ -7234,6 +9841,27 @@
         <x:v>台北市松山區南京東路五段 東興路口</x:v>
       </x:c>
       <x:c r="G220" s="12"/>
+      <x:c r="H220" s="21" t="n">
+        <x:v>25.051489</x:v>
+      </x:c>
+      <x:c r="I220" s="21" t="n">
+        <x:v>121.565347</x:v>
+      </x:c>
+      <x:c r="J220" t="str">
+        <x:v>公開資料固定座標</x:v>
+      </x:c>
+      <x:c r="K220" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L220" s="10" t="str">
+        <x:v>公開 YouBike 站點「南京東興路口」座標；與 PDF 站名一致。</x:v>
+      </x:c>
+      <x:c r="M220" s="10" t="str">
+        <x:v>https://rplus.github.io/youbike-map/</x:v>
+      </x:c>
+      <x:c r="N220" s="10" t="str">
+        <x:v>高</x:v>
+      </x:c>
     </x:row>
     <x:row r="221" ht="15" hidden="0" customHeight="1">
       <x:c r="A221" s="12" t="str">
@@ -7253,6 +9881,19 @@
         <x:v>台北市松山區南京東路五段129巷口</x:v>
       </x:c>
       <x:c r="G221" s="12"/>
+      <x:c r="H221" s="21"/>
+      <x:c r="I221" s="21"/>
+      <x:c r="J221" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K221" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L221" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M221" s="10"/>
+      <x:c r="N221" s="10"/>
     </x:row>
     <x:row r="222" ht="15" hidden="0" customHeight="1">
       <x:c r="A222" s="12" t="str">
@@ -7274,6 +9915,19 @@
       <x:c r="G222" s="12" t="str">
         <x:v>PDF文字「南京的東路」依道路名稱修正顯示為南京東路。</x:v>
       </x:c>
+      <x:c r="H222" s="21"/>
+      <x:c r="I222" s="21"/>
+      <x:c r="J222" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K222" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L222" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M222" s="10"/>
+      <x:c r="N222" s="10"/>
     </x:row>
     <x:row r="223" ht="15" hidden="0" customHeight="1">
       <x:c r="A223" s="12" t="str">
@@ -7293,6 +9947,27 @@
         <x:v>台北市松山區南京東路 復興北路口</x:v>
       </x:c>
       <x:c r="G223" s="12"/>
+      <x:c r="H223" s="21" t="n">
+        <x:v>25.05274</x:v>
+      </x:c>
+      <x:c r="I223" s="21" t="n">
+        <x:v>121.54423</x:v>
+      </x:c>
+      <x:c r="J223" t="str">
+        <x:v>公開資料固定座標</x:v>
+      </x:c>
+      <x:c r="K223" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L223" s="10" t="str">
+        <x:v>公開交通站位「捷運南京復興站」座標；捷運站位於南京東路／復興北路交叉口。</x:v>
+      </x:c>
+      <x:c r="M223" s="10" t="str">
+        <x:v>https://data.zhupiter.com/oddt/23916281/%E6%8D%B7%E9%81%8B%E5%8D%97%E4%BA%AC%E5%BE%A9%E8%88%88%E7%AB%99/</x:v>
+      </x:c>
+      <x:c r="N223" s="10" t="str">
+        <x:v>高</x:v>
+      </x:c>
     </x:row>
     <x:row r="224" ht="15" hidden="0" customHeight="1">
       <x:c r="A224" s="12" t="str">
@@ -7312,6 +9987,27 @@
         <x:v>台北市中山區南京東路 松江路口</x:v>
       </x:c>
       <x:c r="G224" s="12"/>
+      <x:c r="H224" s="21" t="n">
+        <x:v>25.052043</x:v>
+      </x:c>
+      <x:c r="I224" s="21" t="n">
+        <x:v>121.533594</x:v>
+      </x:c>
+      <x:c r="J224" t="str">
+        <x:v>公開資料固定座標</x:v>
+      </x:c>
+      <x:c r="K224" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L224" s="10" t="str">
+        <x:v>公開交通站位「捷運松江南京站」座標；對應南京東路／松江路口。</x:v>
+      </x:c>
+      <x:c r="M224" s="10" t="str">
+        <x:v>https://data.zhupiter.com/oddt/21248803/%E6%8D%B7%E9%81%8B%E6%9D%BE%E6%B1%9F%E5%8D%97%E4%BA%AC%E7%AB%99/</x:v>
+      </x:c>
+      <x:c r="N224" s="10" t="str">
+        <x:v>高</x:v>
+      </x:c>
     </x:row>
     <x:row r="225" ht="15" hidden="0" customHeight="1">
       <x:c r="A225" s="12" t="str">
@@ -7331,6 +10027,27 @@
         <x:v>台北市中山區南京東路 林森北路口</x:v>
       </x:c>
       <x:c r="G225" s="12"/>
+      <x:c r="H225" s="21" t="n">
+        <x:v>25.05215</x:v>
+      </x:c>
+      <x:c r="I225" s="21" t="n">
+        <x:v>121.52585</x:v>
+      </x:c>
+      <x:c r="J225" t="str">
+        <x:v>公開資料固定座標</x:v>
+      </x:c>
+      <x:c r="K225" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L225" s="10" t="str">
+        <x:v>交通部公路局公開站位「南京林森路口」座標；與 PDF 站名一致。</x:v>
+      </x:c>
+      <x:c r="M225" s="10" t="str">
+        <x:v>https://data.zhupiter.com/oddt/15024336/%E5%8D%97%E4%BA%AC%E6%9E%97%E6%A3%AE%E8%B7%AF%E5%8F%A3/</x:v>
+      </x:c>
+      <x:c r="N225" s="10" t="str">
+        <x:v>高</x:v>
+      </x:c>
     </x:row>
     <x:row r="226" ht="15" hidden="0" customHeight="1">
       <x:c r="A226" s="12" t="str">
@@ -7350,6 +10067,27 @@
         <x:v>台北市大同區承德路 長安西路口</x:v>
       </x:c>
       <x:c r="G226" s="12"/>
+      <x:c r="H226" s="21" t="n">
+        <x:v>25.0508672</x:v>
+      </x:c>
+      <x:c r="I226" s="21" t="n">
+        <x:v>121.5171002</x:v>
+      </x:c>
+      <x:c r="J226" t="str">
+        <x:v>公開資料固定座標</x:v>
+      </x:c>
+      <x:c r="K226" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L226" s="10" t="str">
+        <x:v>公開建物資料標示建物位於承德路一段／長安西路口並提供座標；可代表路口附近，但未確認實際下車側。</x:v>
+      </x:c>
+      <x:c r="M226" s="10" t="str">
+        <x:v>https://tw.bpmatlas.com/property/p-1v2p8u/</x:v>
+      </x:c>
+      <x:c r="N226" s="10" t="str">
+        <x:v>中</x:v>
+      </x:c>
     </x:row>
     <x:row r="227" ht="15" hidden="0" customHeight="1">
       <x:c r="A227" s="12" t="str">
@@ -7371,6 +10109,17 @@
       <x:c r="G227" s="12" t="str">
         <x:v>依上排行駛路線補上辛亥路脈絡。</x:v>
       </x:c>
+      <x:c r="H227" s="21"/>
+      <x:c r="I227" s="21"/>
+      <x:c r="J227" t="str">
+        <x:v>Google地標</x:v>
+      </x:c>
+      <x:c r="K227" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L227" s="10" t="str"/>
+      <x:c r="M227" s="10"/>
+      <x:c r="N227" s="10"/>
     </x:row>
     <x:row r="228" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A228" s="12" t="str">
@@ -7393,6 +10142,27 @@
       </x:c>
       <x:c r="G228" s="12" t="str">
         <x:v>下排僅寫「過復興南路」；依上排當時車輛行駛辛亥路，補全為辛亥路／復興南路口。</x:v>
+      </x:c>
+      <x:c r="H228" s="21" t="n">
+        <x:v>25.02056</x:v>
+      </x:c>
+      <x:c r="I228" s="21" t="n">
+        <x:v>121.54367</x:v>
+      </x:c>
+      <x:c r="J228" t="str">
+        <x:v>公開資料固定座標</x:v>
+      </x:c>
+      <x:c r="K228" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L228" s="10" t="str">
+        <x:v>公開資料指出臺大霖澤館位於辛亥路／復興南路口並提供座標；代表路口附近，未確認實際下車側。</x:v>
+      </x:c>
+      <x:c r="M228" s="10" t="str">
+        <x:v>https://www.wikizero.net/wiki/zh/%E5%9C%8B%E7%AB%8B%E5%8F%B0%E7%81%A3%E5%A4%A7%E5%AD%B8%E6%B3%95%E5%BE%8B%E5%AD%B8%E9%99%A2</x:v>
+      </x:c>
+      <x:c r="N228" s="10" t="str">
+        <x:v>中</x:v>
       </x:c>
     </x:row>
     <x:row r="229" ht="15" hidden="0" customHeight="1">
@@ -7413,6 +10183,27 @@
         <x:v>台北市大安區新生南路 辛亥路口</x:v>
       </x:c>
       <x:c r="G229" s="12"/>
+      <x:c r="H229" s="21" t="n">
+        <x:v>25.022413</x:v>
+      </x:c>
+      <x:c r="I229" s="21" t="n">
+        <x:v>121.53456</x:v>
+      </x:c>
+      <x:c r="J229" t="str">
+        <x:v>公開資料固定座標</x:v>
+      </x:c>
+      <x:c r="K229" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L229" s="10" t="str">
+        <x:v>公開 YouBike 站點「辛亥新生路口」座標；對應 PDF 新生南路／辛亥路口。</x:v>
+      </x:c>
+      <x:c r="M229" s="10" t="str">
+        <x:v>https://rplus.github.io/youbike-map/</x:v>
+      </x:c>
+      <x:c r="N229" s="10" t="str">
+        <x:v>高</x:v>
+      </x:c>
     </x:row>
     <x:row r="230" ht="15" hidden="0" customHeight="1">
       <x:c r="A230" s="12" t="str">
@@ -7432,6 +10223,17 @@
         <x:v>台北市中正區捷運公館站</x:v>
       </x:c>
       <x:c r="G230" s="12"/>
+      <x:c r="H230" s="21"/>
+      <x:c r="I230" s="21"/>
+      <x:c r="J230" t="str">
+        <x:v>Google地標</x:v>
+      </x:c>
+      <x:c r="K230" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L230" s="10" t="str"/>
+      <x:c r="M230" s="10"/>
+      <x:c r="N230" s="10"/>
     </x:row>
     <x:row r="231" ht="15" hidden="0" customHeight="1">
       <x:c r="A231" s="12" t="str">
@@ -7453,6 +10255,19 @@
       <x:c r="G231" s="12" t="str">
         <x:v>依上排「左轉羅斯福路直行」補全。</x:v>
       </x:c>
+      <x:c r="H231" s="21"/>
+      <x:c r="I231" s="21"/>
+      <x:c r="J231" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K231" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L231" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M231" s="10"/>
+      <x:c r="N231" s="10"/>
     </x:row>
     <x:row r="232" ht="15" hidden="0" customHeight="1">
       <x:c r="A232" s="12" t="str">
@@ -7474,6 +10289,19 @@
       <x:c r="G232" s="12" t="str">
         <x:v>依上排「羅斯福路直行」補全。</x:v>
       </x:c>
+      <x:c r="H232" s="21"/>
+      <x:c r="I232" s="21"/>
+      <x:c r="J232" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K232" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L232" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M232" s="10"/>
+      <x:c r="N232" s="10"/>
     </x:row>
     <x:row r="233" ht="15" hidden="0" customHeight="1">
       <x:c r="A233" s="12" t="str">
@@ -7493,6 +10321,17 @@
         <x:v>台北市文山區捷運景美站</x:v>
       </x:c>
       <x:c r="G233" s="12"/>
+      <x:c r="H233" s="21"/>
+      <x:c r="I233" s="21"/>
+      <x:c r="J233" t="str">
+        <x:v>Google地標</x:v>
+      </x:c>
+      <x:c r="K233" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L233" s="10" t="str"/>
+      <x:c r="M233" s="10"/>
+      <x:c r="N233" s="10"/>
     </x:row>
     <x:row r="234" ht="15" hidden="0" customHeight="1">
       <x:c r="A234" s="12" t="str">
@@ -7512,6 +10351,17 @@
         <x:v>新北市新店區捷運大坪林站</x:v>
       </x:c>
       <x:c r="G234" s="12"/>
+      <x:c r="H234" s="21"/>
+      <x:c r="I234" s="21"/>
+      <x:c r="J234" t="str">
+        <x:v>Google地標</x:v>
+      </x:c>
+      <x:c r="K234" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L234" s="10" t="str"/>
+      <x:c r="M234" s="10"/>
+      <x:c r="N234" s="10"/>
     </x:row>
     <x:row r="235" ht="15" hidden="0" customHeight="1">
       <x:c r="A235" s="12" t="str">
@@ -7531,6 +10381,17 @@
         <x:v>台北市文山區捷運木柵站</x:v>
       </x:c>
       <x:c r="G235" s="12"/>
+      <x:c r="H235" s="21"/>
+      <x:c r="I235" s="21"/>
+      <x:c r="J235" t="str">
+        <x:v>Google地標</x:v>
+      </x:c>
+      <x:c r="K235" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L235" s="10" t="str"/>
+      <x:c r="M235" s="10"/>
+      <x:c r="N235" s="10"/>
     </x:row>
     <x:row r="236" ht="15" hidden="0" customHeight="1">
       <x:c r="A236" s="12" t="str">
@@ -7552,6 +10413,19 @@
       <x:c r="G236" s="12" t="str">
         <x:v>依上排「木柵捷運站→萬芳→木柵路」補全為萬芳路／秀明路口。</x:v>
       </x:c>
+      <x:c r="H236" s="21"/>
+      <x:c r="I236" s="21"/>
+      <x:c r="J236" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K236" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L236" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M236" s="10"/>
+      <x:c r="N236" s="10"/>
     </x:row>
     <x:row r="237" ht="15" hidden="0" customHeight="1">
       <x:c r="A237" s="12" t="str">
@@ -7573,6 +10447,19 @@
       <x:c r="G237" s="12" t="str">
         <x:v>依上排由萬芳銜接木柵路，補全定位脈絡。</x:v>
       </x:c>
+      <x:c r="H237" s="21"/>
+      <x:c r="I237" s="21"/>
+      <x:c r="J237" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K237" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L237" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M237" s="10"/>
+      <x:c r="N237" s="10"/>
     </x:row>
     <x:row r="238" ht="15" hidden="0" customHeight="1">
       <x:c r="A238" s="12" t="str">
@@ -7594,6 +10481,19 @@
       <x:c r="G238" s="12" t="str">
         <x:v>依上排車輛已進入木柵路補全。</x:v>
       </x:c>
+      <x:c r="H238" s="21"/>
+      <x:c r="I238" s="21"/>
+      <x:c r="J238" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K238" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L238" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M238" s="10"/>
+      <x:c r="N238" s="10"/>
     </x:row>
     <x:row r="239" ht="15" hidden="0" customHeight="1">
       <x:c r="A239" s="12" t="str">
@@ -7615,6 +10515,19 @@
       <x:c r="G239" s="12" t="str">
         <x:v>依上排車輛行駛木柵路補全。</x:v>
       </x:c>
+      <x:c r="H239" s="21"/>
+      <x:c r="I239" s="21"/>
+      <x:c r="J239" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K239" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L239" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M239" s="10"/>
+      <x:c r="N239" s="10"/>
     </x:row>
     <x:row r="240" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A240" s="12" t="str">
@@ -7638,6 +10551,19 @@
       <x:c r="G240" s="12" t="str">
         <x:v>PDF下排文字為「中興路口7-11」；依上排木柵路往景美街的道路連續性，定位搜尋採木柵路／景興路口。PDF原文仍保留供人工核對。</x:v>
       </x:c>
+      <x:c r="H240" s="21"/>
+      <x:c r="I240" s="21"/>
+      <x:c r="J240" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K240" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L240" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M240" s="10"/>
+      <x:c r="N240" s="10"/>
     </x:row>
     <x:row r="241" ht="15" hidden="0" customHeight="1">
       <x:c r="A241" s="12" t="str">
@@ -7659,6 +10585,17 @@
         <x:v>台北市文山區車前路 永豐銀行</x:v>
       </x:c>
       <x:c r="G241" s="12"/>
+      <x:c r="H241" s="21"/>
+      <x:c r="I241" s="21"/>
+      <x:c r="J241" t="str">
+        <x:v>Google地標</x:v>
+      </x:c>
+      <x:c r="K241" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L241" s="10" t="str"/>
+      <x:c r="M241" s="10"/>
+      <x:c r="N241" s="10"/>
     </x:row>
     <x:row r="242" ht="15" hidden="0" customHeight="1">
       <x:c r="A242" s="12" t="str">
@@ -7678,6 +10615,17 @@
         <x:v>台北市中正區捷運台電大樓站2號出口</x:v>
       </x:c>
       <x:c r="G242" s="12"/>
+      <x:c r="H242" s="21"/>
+      <x:c r="I242" s="21"/>
+      <x:c r="J242" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K242" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L242" s="10" t="str"/>
+      <x:c r="M242" s="10"/>
+      <x:c r="N242" s="10"/>
     </x:row>
     <x:row r="243" ht="15" hidden="0" customHeight="1">
       <x:c r="A243" s="12" t="str">
@@ -7697,6 +10645,17 @@
         <x:v>台北市中正區捷運古亭站3號出口</x:v>
       </x:c>
       <x:c r="G243" s="12"/>
+      <x:c r="H243" s="21"/>
+      <x:c r="I243" s="21"/>
+      <x:c r="J243" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K243" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L243" s="10" t="str"/>
+      <x:c r="M243" s="10"/>
+      <x:c r="N243" s="10"/>
     </x:row>
     <x:row r="244" ht="15" hidden="0" customHeight="1">
       <x:c r="A244" s="12" t="str">
@@ -7718,6 +10677,17 @@
         <x:v>台北市中正區羅斯福路一段43號</x:v>
       </x:c>
       <x:c r="G244" s="12"/>
+      <x:c r="H244" s="21"/>
+      <x:c r="I244" s="21"/>
+      <x:c r="J244" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K244" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L244" s="10" t="str"/>
+      <x:c r="M244" s="10"/>
+      <x:c r="N244" s="10"/>
     </x:row>
     <x:row r="245" ht="15" hidden="0" customHeight="1">
       <x:c r="A245" s="12" t="str">
@@ -7734,9 +10704,26 @@
         <x:v>基隆路.忠孝東路口</x:v>
       </x:c>
       <x:c r="F245" s="12" t="str">
-        <x:v>台北市信義區忠孝東路 基隆路口</x:v>
+        <x:v>台北市信義區忠孝東路四段550號</x:v>
       </x:c>
       <x:c r="G245" s="12"/>
+      <x:c r="H245" s="21"/>
+      <x:c r="I245" s="21"/>
+      <x:c r="J245" t="str">
+        <x:v>Google地址（公開資料補全）</x:v>
+      </x:c>
+      <x:c r="K245" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L245" s="10" t="str">
+        <x:v>公開臺北市自行車站點資料將基隆路／忠孝東路口附近定位到忠孝東路四段550號；改用完整門牌讓 Google 定位。</x:v>
+      </x:c>
+      <x:c r="M245" s="10" t="str">
+        <x:v>https://atis.taipei.gov.tw/aspx/park/bikeL.aspx?lang=zh-Hant-TW&amp;region=%E4%BF%A1%E7%BE%A9%E5%8D%80</x:v>
+      </x:c>
+      <x:c r="N245" s="10" t="str">
+        <x:v>高</x:v>
+      </x:c>
     </x:row>
     <x:row r="246" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A246" s="12" t="str">
@@ -7760,6 +10747,27 @@
       <x:c r="G246" s="12" t="str">
         <x:v>上排明確沿忠孝東路往西，該交叉口道路為光復南路；保留PDF原文於「PDF原文」。</x:v>
       </x:c>
+      <x:c r="H246" s="21" t="n">
+        <x:v>25.041254</x:v>
+      </x:c>
+      <x:c r="I246" s="21" t="n">
+        <x:v>121.55742</x:v>
+      </x:c>
+      <x:c r="J246" t="str">
+        <x:v>公開資料固定座標</x:v>
+      </x:c>
+      <x:c r="K246" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L246" s="10" t="str">
+        <x:v>臺北市官方 YouBike 資料：捷運國父紀念館站(2號出口)，位於忠孝東路四段／光復南路口西南側。</x:v>
+      </x:c>
+      <x:c r="M246" s="10" t="str">
+        <x:v>https://www-ws.gov.taipei/001/Upload/371/relfile/18936/4254292/6f0e1c92-4ce3-4d6e-8418-9b8fbba7589b.pdf</x:v>
+      </x:c>
+      <x:c r="N246" s="10" t="str">
+        <x:v>高</x:v>
+      </x:c>
     </x:row>
     <x:row r="247" ht="15" hidden="0" customHeight="1">
       <x:c r="A247" s="12" t="str">
@@ -7783,6 +10791,27 @@
       <x:c r="G247" s="12" t="str">
         <x:v>依上排行駛忠孝東路脈絡修正定位道路方向。</x:v>
       </x:c>
+      <x:c r="H247" s="21" t="n">
+        <x:v>25.040901</x:v>
+      </x:c>
+      <x:c r="I247" s="21" t="n">
+        <x:v>121.548252</x:v>
+      </x:c>
+      <x:c r="J247" t="str">
+        <x:v>公開資料固定座標</x:v>
+      </x:c>
+      <x:c r="K247" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L247" s="10" t="str">
+        <x:v>公開 YouBike 舊站資料「龍門廣場」座標，可代表忠孝東路／敦化南路附近；未確認實際下車側。</x:v>
+      </x:c>
+      <x:c r="M247" s="10" t="str">
+        <x:v>https://rplus.github.io/youbike-map/</x:v>
+      </x:c>
+      <x:c r="N247" s="10" t="str">
+        <x:v>中</x:v>
+      </x:c>
     </x:row>
     <x:row r="248" ht="15" hidden="0" customHeight="1">
       <x:c r="A248" s="12" t="str">
@@ -7806,6 +10835,19 @@
       <x:c r="G248" s="12" t="str">
         <x:v>依上下排脈絡將大安街站定位於忠孝東路／大安路口附近。</x:v>
       </x:c>
+      <x:c r="H248" s="21"/>
+      <x:c r="I248" s="21"/>
+      <x:c r="J248" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K248" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L248" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M248" s="10"/>
+      <x:c r="N248" s="10"/>
     </x:row>
     <x:row r="249" ht="15" hidden="0" customHeight="1">
       <x:c r="A249" s="12" t="str">
@@ -7829,6 +10871,27 @@
       <x:c r="G249" s="12" t="str">
         <x:v>依上排行駛忠孝東路脈絡修正定位道路方向。</x:v>
       </x:c>
+      <x:c r="H249" s="21" t="n">
+        <x:v>25.04167</x:v>
+      </x:c>
+      <x:c r="I249" s="21" t="n">
+        <x:v>121.54389</x:v>
+      </x:c>
+      <x:c r="J249" t="str">
+        <x:v>公開資料固定座標</x:v>
+      </x:c>
+      <x:c r="K249" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L249" s="10" t="str">
+        <x:v>公開捷運站資料提供忠孝復興站座標，可代表忠孝東路／復興南路口；未確認實際下車側。</x:v>
+      </x:c>
+      <x:c r="M249" s="10" t="str">
+        <x:v>https://wikis.tw/%E5%BF%A0%E5%AD%9D%E5%BE%A9%E8%88%88%E7%AB%99</x:v>
+      </x:c>
+      <x:c r="N249" s="10" t="str">
+        <x:v>中</x:v>
+      </x:c>
     </x:row>
     <x:row r="250" ht="15" hidden="0" customHeight="1">
       <x:c r="A250" s="12" t="str">
@@ -7852,6 +10915,19 @@
       <x:c r="G250" s="12" t="str">
         <x:v>上排明確寫「忠孝東路/建國南路交叉口」，以此作定位。</x:v>
       </x:c>
+      <x:c r="H250" s="21"/>
+      <x:c r="I250" s="21"/>
+      <x:c r="J250" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K250" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L250" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M250" s="10"/>
+      <x:c r="N250" s="10"/>
     </x:row>
     <x:row r="251" ht="15" hidden="0" customHeight="1">
       <x:c r="A251" s="12" t="str">
@@ -7871,6 +10947,19 @@
         <x:v>台北市南港區忠孝東路 研究院路口</x:v>
       </x:c>
       <x:c r="G251" s="12"/>
+      <x:c r="H251" s="21"/>
+      <x:c r="I251" s="21"/>
+      <x:c r="J251" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K251" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L251" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M251" s="10"/>
+      <x:c r="N251" s="10"/>
     </x:row>
     <x:row r="252" ht="15" hidden="0" customHeight="1">
       <x:c r="A252" s="12" t="str">
@@ -7890,6 +10979,17 @@
         <x:v>台北市南港區捷運昆陽站</x:v>
       </x:c>
       <x:c r="G252" s="12"/>
+      <x:c r="H252" s="21"/>
+      <x:c r="I252" s="21"/>
+      <x:c r="J252" t="str">
+        <x:v>Google地標</x:v>
+      </x:c>
+      <x:c r="K252" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L252" s="10" t="str"/>
+      <x:c r="M252" s="10"/>
+      <x:c r="N252" s="10"/>
     </x:row>
     <x:row r="253" ht="15" hidden="0" customHeight="1">
       <x:c r="A253" s="12" t="str">
@@ -7909,6 +11009,17 @@
         <x:v>台北市南港區捷運後山埤站</x:v>
       </x:c>
       <x:c r="G253" s="12"/>
+      <x:c r="H253" s="21"/>
+      <x:c r="I253" s="21"/>
+      <x:c r="J253" t="str">
+        <x:v>Google地標</x:v>
+      </x:c>
+      <x:c r="K253" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L253" s="10" t="str"/>
+      <x:c r="M253" s="10"/>
+      <x:c r="N253" s="10"/>
     </x:row>
     <x:row r="254" ht="15" hidden="0" customHeight="1">
       <x:c r="A254" s="12" t="str">
@@ -7928,6 +11039,17 @@
         <x:v>台北市信義區捷運永春站</x:v>
       </x:c>
       <x:c r="G254" s="12"/>
+      <x:c r="H254" s="21"/>
+      <x:c r="I254" s="21"/>
+      <x:c r="J254" t="str">
+        <x:v>Google地標</x:v>
+      </x:c>
+      <x:c r="K254" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L254" s="10" t="str"/>
+      <x:c r="M254" s="10"/>
+      <x:c r="N254" s="10"/>
     </x:row>
     <x:row r="255" ht="15" hidden="0" customHeight="1">
       <x:c r="A255" s="12" t="str">
@@ -7947,6 +11069,27 @@
         <x:v>台北市信義區忠孝東路 松仁路口</x:v>
       </x:c>
       <x:c r="G255" s="12"/>
+      <x:c r="H255" s="21" t="n">
+        <x:v>25.0408578889</x:v>
+      </x:c>
+      <x:c r="I255" s="21" t="n">
+        <x:v>121.567904444</x:v>
+      </x:c>
+      <x:c r="J255" t="str">
+        <x:v>公開資料固定座標</x:v>
+      </x:c>
+      <x:c r="K255" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L255" s="10" t="str">
+        <x:v>臺北市官方 YouBike 資料：捷運市政府站(3號出口)，地址欄標示忠孝東路／松仁路東南側。</x:v>
+      </x:c>
+      <x:c r="M255" s="10" t="str">
+        <x:v>https://www-ws.gov.taipei/001/Upload/public/mmo/dot/YouBike_JSON%E6%AA%94%E6%A1%88%E8%AA%AA%E6%98%8E%28%E4%BF%AE%E6%AD%A3%E7%89%88%29_%E5%B1%80%E7%B6%B2.pdf</x:v>
+      </x:c>
+      <x:c r="N255" s="10" t="str">
+        <x:v>高</x:v>
+      </x:c>
     </x:row>
     <x:row r="256" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A256" s="12" t="str">
@@ -7968,6 +11111,17 @@
       <x:c r="G256" s="12" t="str">
         <x:v>PDF未提供門牌；依上排進入中和中正路/中山路走廊，加上中和區域定位。</x:v>
       </x:c>
+      <x:c r="H256" s="21"/>
+      <x:c r="I256" s="21"/>
+      <x:c r="J256" t="str">
+        <x:v>Google地標</x:v>
+      </x:c>
+      <x:c r="K256" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L256" s="10" t="str"/>
+      <x:c r="M256" s="10"/>
+      <x:c r="N256" s="10"/>
     </x:row>
     <x:row r="257" ht="15" hidden="0" customHeight="1">
       <x:c r="A257" s="12" t="str">
@@ -7989,6 +11143,19 @@
       <x:c r="G257" s="12" t="str">
         <x:v>PDF未提供門牌；依上排行駛區域加上中和區定位。</x:v>
       </x:c>
+      <x:c r="H257" s="21"/>
+      <x:c r="I257" s="21"/>
+      <x:c r="J257" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K257" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L257" s="10" t="str">
+        <x:v>缺少完整門牌或唯一地標；建議人工確認 Google Maps 位置後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M257" s="10"/>
+      <x:c r="N257" s="10"/>
     </x:row>
     <x:row r="258" ht="15" hidden="0" customHeight="1">
       <x:c r="A258" s="12" t="str">
@@ -8010,6 +11177,17 @@
         <x:v>新北市板橋區民生路一段52號</x:v>
       </x:c>
       <x:c r="G258" s="12"/>
+      <x:c r="H258" s="21"/>
+      <x:c r="I258" s="21"/>
+      <x:c r="J258" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K258" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L258" s="10" t="str"/>
+      <x:c r="M258" s="10"/>
+      <x:c r="N258" s="10"/>
     </x:row>
     <x:row r="259" ht="15" hidden="0" customHeight="1">
       <x:c r="A259" s="12" t="str">
@@ -8031,6 +11209,19 @@
         <x:v>新北市板橋區民生路二段226巷6弄</x:v>
       </x:c>
       <x:c r="G259" s="12"/>
+      <x:c r="H259" s="21"/>
+      <x:c r="I259" s="21"/>
+      <x:c r="J259" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K259" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L259" s="10" t="str">
+        <x:v>缺少完整門牌或唯一地標；建議人工確認 Google Maps 位置後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M259" s="10"/>
+      <x:c r="N259" s="10"/>
     </x:row>
     <x:row r="260" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A260" s="12" t="str">
@@ -8054,6 +11245,19 @@
       <x:c r="G260" s="12" t="str">
         <x:v>依上排「文化路(新埔捷運站)→民權路」補全；板橋此處道路為陽明街。</x:v>
       </x:c>
+      <x:c r="H260" s="21"/>
+      <x:c r="I260" s="21"/>
+      <x:c r="J260" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K260" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L260" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M260" s="10"/>
+      <x:c r="N260" s="10"/>
     </x:row>
     <x:row r="261" ht="15" hidden="0" customHeight="1">
       <x:c r="A261" s="12" t="str">
@@ -8075,6 +11279,17 @@
         <x:v>新北市板橋區文化路一段143號</x:v>
       </x:c>
       <x:c r="G261" s="12"/>
+      <x:c r="H261" s="21"/>
+      <x:c r="I261" s="21"/>
+      <x:c r="J261" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K261" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L261" s="10" t="str"/>
+      <x:c r="M261" s="10"/>
+      <x:c r="N261" s="10"/>
     </x:row>
     <x:row r="262" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A262" s="12" t="str">
@@ -8098,6 +11313,19 @@
       <x:c r="G262" s="12" t="str">
         <x:v>保留PDF交叉路口文字；上排用於確認板橋府中方向。</x:v>
       </x:c>
+      <x:c r="H262" s="21"/>
+      <x:c r="I262" s="21"/>
+      <x:c r="J262" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K262" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L262" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M262" s="10"/>
+      <x:c r="N262" s="10"/>
     </x:row>
     <x:row r="263" ht="15" hidden="0" customHeight="1">
       <x:c r="A263" s="12" t="str">
@@ -8119,6 +11347,19 @@
       <x:c r="G263" s="12" t="str">
         <x:v>上排寫「中興街口」，以此作定位。</x:v>
       </x:c>
+      <x:c r="H263" s="21"/>
+      <x:c r="I263" s="21"/>
+      <x:c r="J263" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K263" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L263" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M263" s="10"/>
+      <x:c r="N263" s="10"/>
     </x:row>
     <x:row r="264" ht="15" hidden="0" customHeight="1">
       <x:c r="A264" s="12" t="str">
@@ -8138,6 +11379,17 @@
         <x:v>新北市中和區捷運景安站</x:v>
       </x:c>
       <x:c r="G264" s="12"/>
+      <x:c r="H264" s="21"/>
+      <x:c r="I264" s="21"/>
+      <x:c r="J264" t="str">
+        <x:v>Google地標</x:v>
+      </x:c>
+      <x:c r="K264" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L264" s="10" t="str"/>
+      <x:c r="M264" s="10"/>
+      <x:c r="N264" s="10"/>
     </x:row>
     <x:row r="265" ht="15" hidden="0" customHeight="1">
       <x:c r="A265" s="12" t="str">
@@ -8157,6 +11409,17 @@
         <x:v>新北市永和區智光商工</x:v>
       </x:c>
       <x:c r="G265" s="12"/>
+      <x:c r="H265" s="21"/>
+      <x:c r="I265" s="21"/>
+      <x:c r="J265" t="str">
+        <x:v>Google地標</x:v>
+      </x:c>
+      <x:c r="K265" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L265" s="10" t="str"/>
+      <x:c r="M265" s="10"/>
+      <x:c r="N265" s="10"/>
     </x:row>
     <x:row r="266" ht="15" hidden="0" customHeight="1">
       <x:c r="A266" s="12" t="str">
@@ -8178,6 +11441,19 @@
       <x:c r="G266" s="12" t="str">
         <x:v>依上排進入永和中正路後補全道路。</x:v>
       </x:c>
+      <x:c r="H266" s="21"/>
+      <x:c r="I266" s="21"/>
+      <x:c r="J266" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K266" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L266" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M266" s="10"/>
+      <x:c r="N266" s="10"/>
     </x:row>
     <x:row r="267" ht="15" hidden="0" customHeight="1">
       <x:c r="A267" s="12" t="str">
@@ -8199,6 +11475,27 @@
       <x:c r="G267" s="12" t="str">
         <x:v>依上排永和中正路→永和路補全。</x:v>
       </x:c>
+      <x:c r="H267" s="21" t="n">
+        <x:v>25.0042</x:v>
+      </x:c>
+      <x:c r="I267" s="21" t="n">
+        <x:v>121.5172</x:v>
+      </x:c>
+      <x:c r="J267" t="str">
+        <x:v>公開資料固定座標</x:v>
+      </x:c>
+      <x:c r="K267" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L267" s="10" t="str">
+        <x:v>新北市政府道路即時影像資料標示「永和區中正路、永貞路」GPS 座標。</x:v>
+      </x:c>
+      <x:c r="M267" s="10" t="str">
+        <x:v>https://livecam.tw/cam/NWT0058/</x:v>
+      </x:c>
+      <x:c r="N267" s="10" t="str">
+        <x:v>高</x:v>
+      </x:c>
     </x:row>
     <x:row r="268" ht="15" hidden="0" customHeight="1">
       <x:c r="A268" s="12" t="str">
@@ -8220,6 +11517,17 @@
         <x:v>新北市永和區捷運頂溪站</x:v>
       </x:c>
       <x:c r="G268" s="12"/>
+      <x:c r="H268" s="21"/>
+      <x:c r="I268" s="21"/>
+      <x:c r="J268" t="str">
+        <x:v>Google地標</x:v>
+      </x:c>
+      <x:c r="K268" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L268" s="10" t="str"/>
+      <x:c r="M268" s="10"/>
+      <x:c r="N268" s="10"/>
     </x:row>
     <x:row r="269" ht="15" hidden="0" customHeight="1">
       <x:c r="A269" s="12" t="str">
@@ -8241,6 +11549,19 @@
         <x:v>新北市新店區安和路一段 吉安路口</x:v>
       </x:c>
       <x:c r="G269" s="12"/>
+      <x:c r="H269" s="21"/>
+      <x:c r="I269" s="21"/>
+      <x:c r="J269" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K269" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L269" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M269" s="10"/>
+      <x:c r="N269" s="10"/>
     </x:row>
     <x:row r="270" ht="15" hidden="0" customHeight="1">
       <x:c r="A270" s="12" t="str">
@@ -8264,6 +11585,19 @@
       <x:c r="G270" s="12" t="str">
         <x:v>上排行駛路線寫「中和景新街」，以景新街作定位。</x:v>
       </x:c>
+      <x:c r="H270" s="21"/>
+      <x:c r="I270" s="21"/>
+      <x:c r="J270" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K270" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L270" s="10" t="str">
+        <x:v>缺少完整門牌或唯一地標；建議人工確認 Google Maps 位置後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M270" s="10"/>
+      <x:c r="N270" s="10"/>
     </x:row>
     <x:row r="271" ht="15" hidden="0" customHeight="1">
       <x:c r="A271" s="12" t="str">
@@ -8285,6 +11619,27 @@
       <x:c r="G271" s="12" t="str">
         <x:v>上排終點脈絡為中正路/連城路。</x:v>
       </x:c>
+      <x:c r="H271" s="21" t="n">
+        <x:v>24.995729</x:v>
+      </x:c>
+      <x:c r="I271" s="21" t="n">
+        <x:v>121.485259</x:v>
+      </x:c>
+      <x:c r="J271" t="str">
+        <x:v>公開資料固定座標</x:v>
+      </x:c>
+      <x:c r="K271" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L271" s="10" t="str">
+        <x:v>亞東動物醫院公開頁面明載位於中和區中正路／連城路交叉口，並提供 WGS84 座標。</x:v>
+      </x:c>
+      <x:c r="M271" s="10" t="str">
+        <x:v>https://www.vet639.url.tw/hospital.htm</x:v>
+      </x:c>
+      <x:c r="N271" s="10" t="str">
+        <x:v>高</x:v>
+      </x:c>
     </x:row>
     <x:row r="272" ht="15" hidden="0" customHeight="1">
       <x:c r="A272" s="12" t="str">
@@ -8304,6 +11659,17 @@
         <x:v>新北市土城區捷運永寧站2號出口</x:v>
       </x:c>
       <x:c r="G272" s="12"/>
+      <x:c r="H272" s="21"/>
+      <x:c r="I272" s="21"/>
+      <x:c r="J272" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K272" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L272" s="10" t="str"/>
+      <x:c r="M272" s="10"/>
+      <x:c r="N272" s="10"/>
     </x:row>
     <x:row r="273" ht="15" hidden="0" customHeight="1">
       <x:c r="A273" s="12" t="str">
@@ -8320,9 +11686,26 @@
         <x:v>金城路與和平路口</x:v>
       </x:c>
       <x:c r="F273" s="12" t="str">
-        <x:v>新北市土城區金城路 和平路口</x:v>
+        <x:v>新北市土城區 捷運土城站2號出口</x:v>
       </x:c>
       <x:c r="G273" s="12"/>
+      <x:c r="H273" s="21"/>
+      <x:c r="I273" s="21"/>
+      <x:c r="J273" t="str">
+        <x:v>Google地標（公開資料補全）</x:v>
+      </x:c>
+      <x:c r="K273" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L273" s="10" t="str">
+        <x:v>臺北捷運官方資料指出土城站2號出口位於金城路一段／和平路交叉口；改用捷運出口作 Google 定位，仍建議確認實際下車側。</x:v>
+      </x:c>
+      <x:c r="M273" s="10" t="str">
+        <x:v>https://web.metro.taipei/pages2026/WebStation/078/1</x:v>
+      </x:c>
+      <x:c r="N273" s="10" t="str">
+        <x:v>中</x:v>
+      </x:c>
     </x:row>
     <x:row r="274" ht="15" hidden="0" customHeight="1">
       <x:c r="A274" s="12" t="str">
@@ -8342,6 +11725,19 @@
         <x:v>新北市土城區金城路 裕民路口</x:v>
       </x:c>
       <x:c r="G274" s="12"/>
+      <x:c r="H274" s="21"/>
+      <x:c r="I274" s="21"/>
+      <x:c r="J274" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K274" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L274" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M274" s="10"/>
+      <x:c r="N274" s="10"/>
     </x:row>
     <x:row r="275" ht="15" hidden="0" customHeight="1">
       <x:c r="A275" s="12" t="str">
@@ -8363,6 +11759,17 @@
         <x:v>新北市土城區青雲路101號</x:v>
       </x:c>
       <x:c r="G275" s="12"/>
+      <x:c r="H275" s="21"/>
+      <x:c r="I275" s="21"/>
+      <x:c r="J275" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K275" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L275" s="10" t="str"/>
+      <x:c r="M275" s="10"/>
+      <x:c r="N275" s="10"/>
     </x:row>
     <x:row r="276" ht="15" hidden="0" customHeight="1">
       <x:c r="A276" s="12" t="str">
@@ -8382,6 +11789,17 @@
         <x:v>新北市板橋區國慶路164號</x:v>
       </x:c>
       <x:c r="G276" s="12"/>
+      <x:c r="H276" s="21"/>
+      <x:c r="I276" s="21"/>
+      <x:c r="J276" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K276" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L276" s="10" t="str"/>
+      <x:c r="M276" s="10"/>
+      <x:c r="N276" s="10"/>
     </x:row>
     <x:row r="277" ht="15" hidden="0" customHeight="1">
       <x:c r="A277" s="12" t="str">
@@ -8401,6 +11819,17 @@
         <x:v>新北市板橋區國慶路256號</x:v>
       </x:c>
       <x:c r="G277" s="12"/>
+      <x:c r="H277" s="21"/>
+      <x:c r="I277" s="21"/>
+      <x:c r="J277" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K277" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L277" s="10" t="str"/>
+      <x:c r="M277" s="10"/>
+      <x:c r="N277" s="10"/>
     </x:row>
     <x:row r="278" ht="15" hidden="0" customHeight="1">
       <x:c r="A278" s="12" t="str">
@@ -8422,6 +11851,17 @@
         <x:v>新北市五股區中興路199號</x:v>
       </x:c>
       <x:c r="G278" s="12"/>
+      <x:c r="H278" s="21"/>
+      <x:c r="I278" s="21"/>
+      <x:c r="J278" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K278" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L278" s="10" t="str"/>
+      <x:c r="M278" s="10"/>
+      <x:c r="N278" s="10"/>
     </x:row>
     <x:row r="279" ht="15" hidden="0" customHeight="1">
       <x:c r="A279" s="12" t="str">
@@ -8441,6 +11881,19 @@
         <x:v>新北市蘆洲區永安南路二段16巷口</x:v>
       </x:c>
       <x:c r="G279" s="12"/>
+      <x:c r="H279" s="21"/>
+      <x:c r="I279" s="21"/>
+      <x:c r="J279" t="str">
+        <x:v>人工座標優先</x:v>
+      </x:c>
+      <x:c r="K279" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="L279" s="10" t="str">
+        <x:v>路口/巷口文字可能只定位到交叉口中心；建議在 Google Maps 找到實際候車側後填入緯度、經度。</x:v>
+      </x:c>
+      <x:c r="M279" s="10"/>
+      <x:c r="N279" s="10"/>
     </x:row>
     <x:row r="280" ht="15" hidden="0" customHeight="1">
       <x:c r="A280" s="12" t="str">
@@ -8462,6 +11915,17 @@
         <x:v>新北市蘆洲區中山一路207號</x:v>
       </x:c>
       <x:c r="G280" s="12"/>
+      <x:c r="H280" s="21"/>
+      <x:c r="I280" s="21"/>
+      <x:c r="J280" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K280" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L280" s="10" t="str"/>
+      <x:c r="M280" s="10"/>
+      <x:c r="N280" s="10"/>
     </x:row>
     <x:row r="281" ht="15" hidden="0" customHeight="1">
       <x:c r="A281" s="12" t="str">
@@ -8483,6 +11947,17 @@
         <x:v>新北市蘆洲區中山一路23號</x:v>
       </x:c>
       <x:c r="G281" s="12"/>
+      <x:c r="H281" s="21"/>
+      <x:c r="I281" s="21"/>
+      <x:c r="J281" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K281" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L281" s="10" t="str"/>
+      <x:c r="M281" s="10"/>
+      <x:c r="N281" s="10"/>
     </x:row>
     <x:row r="282" ht="15" hidden="0" customHeight="1">
       <x:c r="A282" s="12" t="str">
@@ -8504,6 +11979,17 @@
         <x:v>新北市三重區三和路四段398-3號</x:v>
       </x:c>
       <x:c r="G282" s="12"/>
+      <x:c r="H282" s="21"/>
+      <x:c r="I282" s="21"/>
+      <x:c r="J282" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K282" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L282" s="10" t="str"/>
+      <x:c r="M282" s="10"/>
+      <x:c r="N282" s="10"/>
     </x:row>
     <x:row r="283" ht="15" hidden="0" customHeight="1">
       <x:c r="A283" s="12" t="str">
@@ -8525,6 +12011,17 @@
         <x:v>新北市三重區三和路三段168號</x:v>
       </x:c>
       <x:c r="G283" s="12"/>
+      <x:c r="H283" s="21"/>
+      <x:c r="I283" s="21"/>
+      <x:c r="J283" t="str">
+        <x:v>Google地址</x:v>
+      </x:c>
+      <x:c r="K283" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="L283" s="10" t="str"/>
+      <x:c r="M283" s="10"/>
+      <x:c r="N283" s="10"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="G2:G283">
@@ -8532,14 +12029,47 @@
       <x:formula>G2&lt;&gt;""</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:dataValidations count="1">
+  <x:conditionalFormatting sqref="K2:K283">
+    <x:cfRule type="expression" dxfId="3" priority="2">
+      <x:formula>K2="TRUE"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="H2:I283">
+    <x:cfRule type="expression" dxfId="4" priority="3">
+      <x:formula>AND(ISNUMBER($H2),ISNUMBER($I2))</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="5" priority="4">
+      <x:formula>AND($K2="TRUE",OR($H2="",$I2=""))</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="N2:N283">
+    <x:cfRule type="expression" dxfId="6" priority="5">
+      <x:formula>N2="高"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="7" priority="6">
+      <x:formula>N2="中"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="8" priority="7">
+      <x:formula>N2="待確認"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:dataValidations count="4">
     <x:dataValidation type="list" sqref="A2:A283">
       <x:formula1>"TRUE,FALSE"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="J2:J283">
+      <x:formula1>"Google地址,Google地標,人工座標優先"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="K2:K283">
+      <x:formula1>"TRUE,FALSE"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="N2:N283">
+      <x:formula1>"高,中,待確認"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08066d0e52874790"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R692414f59d2b43ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14578,7 +18108,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5691634311b4e7b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09aff79f37e64572"/>
   </x:tableParts>
 </x:worksheet>
 </file>